--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,3522 +482,3234 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.160503334780851e-05</v>
+        <v>4.560426566781149e-06</v>
       </c>
       <c r="B2" t="n">
-        <v>1482606292.809757</v>
+        <v>6964202207.055857</v>
       </c>
       <c r="C2" t="n">
-        <v>7.062092302230862e+32</v>
+        <v>1.851382902238399e+16</v>
       </c>
       <c r="D2" t="n">
-        <v>5.819594009466984</v>
+        <v>2.246000774221471</v>
       </c>
       <c r="E2" t="n">
-        <v>34102.28244116078</v>
+        <v>56243.93485847223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001513562866046527</v>
+        <v>0.0001035838266851309</v>
       </c>
       <c r="G2" t="n">
-        <v>3494.294154738242</v>
+        <v>5793.810858016026</v>
       </c>
       <c r="H2" t="n">
-        <v>4.145667142421004e-07</v>
+        <v>3.466823135950804e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>34008.87587380283</v>
+        <v>56055.69333384022</v>
       </c>
       <c r="J2" t="n">
-        <v>33672.24124816755</v>
+        <v>55414.32099554676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.041299909899336e-05</v>
+        <v>1.352488537581947e-05</v>
       </c>
       <c r="B3" t="n">
-        <v>1191681304.642194</v>
+        <v>1573269896.403693</v>
       </c>
       <c r="C3" t="n">
-        <v>1.190711135711601e+57</v>
+        <v>3.587364184016141e+30</v>
       </c>
       <c r="D3" t="n">
-        <v>10.64331458313252</v>
+        <v>5.410807050454403</v>
       </c>
       <c r="E3" t="n">
-        <v>26253.18459082625</v>
+        <v>41981.94544725444</v>
       </c>
       <c r="F3" t="n">
-        <v>5.236081513804993e-05</v>
+        <v>7.049265139175086e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2719.244708616617</v>
+        <v>4475.135263305197</v>
       </c>
       <c r="H3" t="n">
-        <v>2.08146387872596e-07</v>
+        <v>5.166846875892542e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>26148.82209134403</v>
+        <v>41674.23353772138</v>
       </c>
       <c r="J3" t="n">
-        <v>25810.77881985869</v>
+        <v>40858.53790813831</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.69660005020634e-05</v>
+        <v>2.589438315188088e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>635958036.5622116</v>
+        <v>6469454847.742629</v>
       </c>
       <c r="C4" t="n">
-        <v>1.095457386682558e+84</v>
+        <v>43280423954.9711</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7759944722376</v>
+        <v>1.199403727542084</v>
       </c>
       <c r="E4" t="n">
-        <v>23477.83233505329</v>
+        <v>28295.66549598575</v>
       </c>
       <c r="F4" t="n">
-        <v>5.539979246361132e-05</v>
+        <v>7.254195448066391e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2430.535381400838</v>
+        <v>2924.161945548653</v>
       </c>
       <c r="H4" t="n">
-        <v>2.16963614106954e-07</v>
+        <v>2.694615661997333e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>23385.88550405828</v>
+        <v>28190.55950048567</v>
       </c>
       <c r="J4" t="n">
-        <v>23086.70673871917</v>
+        <v>27843.15688745091</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.027815755777385e-06</v>
+        <v>5.203192417143199e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>4204397382.341263</v>
+        <v>2872397540.100661</v>
       </c>
       <c r="C5" t="n">
-        <v>1.680270728763488e+19</v>
+        <v>2.368987907963854e+32</v>
       </c>
       <c r="D5" t="n">
-        <v>2.817439379913818</v>
+        <v>5.359645552717599</v>
       </c>
       <c r="E5" t="n">
-        <v>30709.48605479106</v>
+        <v>29263.76569332258</v>
       </c>
       <c r="F5" t="n">
-        <v>7.312736924201082e-05</v>
+        <v>0.0002125363170761006</v>
       </c>
       <c r="G5" t="n">
-        <v>3170.455496071062</v>
+        <v>2951.22333490591</v>
       </c>
       <c r="H5" t="n">
-        <v>2.632801082107705e-07</v>
+        <v>2.005073479917156e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>30598.92284302222</v>
+        <v>29236.15817601853</v>
       </c>
       <c r="J5" t="n">
-        <v>30230.10831489622</v>
+        <v>29107.46288958696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.231315034634312e-05</v>
+        <v>2.175386317926847e-06</v>
       </c>
       <c r="B6" t="n">
-        <v>2662625810.272587</v>
+        <v>8568270870.115607</v>
       </c>
       <c r="C6" t="n">
-        <v>4.063231754172296e+23</v>
+        <v>9424517431.870955</v>
       </c>
       <c r="D6" t="n">
-        <v>3.921549999357189</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E6" t="n">
-        <v>62235.75837642534</v>
+        <v>31243.39077144613</v>
       </c>
       <c r="F6" t="n">
-        <v>6.30487981069083e-05</v>
+        <v>8.448969910208129e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>6777.452933409903</v>
+        <v>3203.20139577698</v>
       </c>
       <c r="H6" t="n">
-        <v>6.234587477982679e-07</v>
+        <v>2.369586870915514e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>61620.33938112827</v>
+        <v>31155.76597296573</v>
       </c>
       <c r="J6" t="n">
-        <v>60161.46169682081</v>
+        <v>30842.00867161845</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.412469258106603e-06</v>
+        <v>3.411639216528512e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>12055907246.20468</v>
+        <v>3751740567.747574</v>
       </c>
       <c r="C7" t="n">
-        <v>12908405823.24952</v>
+        <v>6.096338641120691e+25</v>
       </c>
       <c r="D7" t="n">
-        <v>1.05980198019802</v>
+        <v>3.994045071228693</v>
       </c>
       <c r="E7" t="n">
-        <v>68856.96234788657</v>
+        <v>24141.36014202307</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002832203293188202</v>
+        <v>0.0001429952815182308</v>
       </c>
       <c r="G7" t="n">
-        <v>6967.030010834023</v>
+        <v>2439.986003495022</v>
       </c>
       <c r="H7" t="n">
-        <v>3.717106375440635e-07</v>
+        <v>1.701287966842386e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>68766.59148561391</v>
+        <v>24112.63793169783</v>
       </c>
       <c r="J7" t="n">
-        <v>68375.04698434834</v>
+        <v>23985.38857709709</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9.269906747753529e-06</v>
+        <v>1.078508718230297e-05</v>
       </c>
       <c r="B8" t="n">
-        <v>2693458879.103903</v>
+        <v>2124920890.324209</v>
       </c>
       <c r="C8" t="n">
-        <v>1.782724091157093e+29</v>
+        <v>9.61497288575889e+33</v>
       </c>
       <c r="D8" t="n">
-        <v>4.963815064677163</v>
+        <v>5.98485417336918</v>
       </c>
       <c r="E8" t="n">
-        <v>48449.10562794642</v>
+        <v>45529.03559545665</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002193153129578554</v>
+        <v>0.0002369557063500751</v>
       </c>
       <c r="G8" t="n">
-        <v>4921.033996004876</v>
+        <v>4617.814698706182</v>
       </c>
       <c r="H8" t="n">
-        <v>3.828767978168974e-07</v>
+        <v>3.753664405485725e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>48364.52403549061</v>
+        <v>45456.91210750051</v>
       </c>
       <c r="J8" t="n">
-        <v>48022.03983459414</v>
+        <v>45157.91591760625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.595285036580002e-06</v>
+        <v>1.894436182726925e-06</v>
       </c>
       <c r="B9" t="n">
-        <v>6684820763.831833</v>
+        <v>14571876833.80109</v>
       </c>
       <c r="C9" t="n">
-        <v>7275652693.007202</v>
+        <v>16161174470.75793</v>
       </c>
       <c r="D9" t="n">
-        <v>1.059801980198019</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E9" t="n">
-        <v>29252.40361332352</v>
+        <v>46204.32455772989</v>
       </c>
       <c r="F9" t="n">
-        <v>3.263966505793334e-05</v>
+        <v>0.0001550727340122957</v>
       </c>
       <c r="G9" t="n">
-        <v>3153.263898326557</v>
+        <v>4675.768220173491</v>
       </c>
       <c r="H9" t="n">
-        <v>2.826970684831835e-07</v>
+        <v>2.063555824261638e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>28999.0441277744</v>
+        <v>46142.84037506267</v>
       </c>
       <c r="J9" t="n">
-        <v>28367.21238077557</v>
+        <v>45877.29671868407</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.237441937563047e-06</v>
+        <v>8.619769071005988e-06</v>
       </c>
       <c r="B10" t="n">
-        <v>3442959911.150497</v>
+        <v>3056133245.937701</v>
       </c>
       <c r="C10" t="n">
-        <v>3.846015210238707e+27</v>
+        <v>3.331303052513671e+28</v>
       </c>
       <c r="D10" t="n">
-        <v>4.44478427777047</v>
+        <v>4.785377521186479</v>
       </c>
       <c r="E10" t="n">
-        <v>34544.1569009809</v>
+        <v>50925.7842164287</v>
       </c>
       <c r="F10" t="n">
-        <v>7.678937155357565e-05</v>
+        <v>0.0001363444005832036</v>
       </c>
       <c r="G10" t="n">
-        <v>3550.954866099477</v>
+        <v>5216.226668762961</v>
       </c>
       <c r="H10" t="n">
-        <v>2.384446562344368e-07</v>
+        <v>3.678282119788031e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>34436.89114986824</v>
+        <v>50788.39727518415</v>
       </c>
       <c r="J10" t="n">
-        <v>34063.53510944732</v>
+        <v>50291.20746843443</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6.358196955767389e-06</v>
+        <v>3.847295808092264e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>5467973777.983959</v>
+        <v>4141250178.452193</v>
       </c>
       <c r="C11" t="n">
-        <v>1.136632634355198e+19</v>
+        <v>4.299697471180586e+22</v>
       </c>
       <c r="D11" t="n">
-        <v>2.832026947817243</v>
+        <v>3.436641189057665</v>
       </c>
       <c r="E11" t="n">
-        <v>62977.96553007249</v>
+        <v>29509.13653792693</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0002125324679721645</v>
+        <v>0.0001314572251611558</v>
       </c>
       <c r="G11" t="n">
-        <v>6408.227662285073</v>
+        <v>2994.698157816682</v>
       </c>
       <c r="H11" t="n">
-        <v>4.140812672103444e-07</v>
+        <v>2.16723439258792e-07</v>
       </c>
       <c r="I11" t="n">
-        <v>62855.26429754158</v>
+        <v>29460.48708901138</v>
       </c>
       <c r="J11" t="n">
-        <v>62371.77797652392</v>
+        <v>29260.73366148319</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.058927082147424e-06</v>
+        <v>1.192006547311992e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>2219461782.725915</v>
+        <v>1571847403.433163</v>
       </c>
       <c r="C12" t="n">
-        <v>3.820094971262197e+29</v>
+        <v>6.946518563910915e+29</v>
       </c>
       <c r="D12" t="n">
-        <v>4.694304091047112</v>
+        <v>5.217881943904674</v>
       </c>
       <c r="E12" t="n">
-        <v>13085.07395805081</v>
+        <v>36715.95115705371</v>
       </c>
       <c r="F12" t="n">
-        <v>6.162501651052814e-05</v>
+        <v>9.127388326542004e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>1333.879563369287</v>
+        <v>3841.998614648212</v>
       </c>
       <c r="H12" t="n">
-        <v>1.327687689606119e-07</v>
+        <v>4.706821658459907e-07</v>
       </c>
       <c r="I12" t="n">
-        <v>13056.88266075725</v>
+        <v>36526.61393600611</v>
       </c>
       <c r="J12" t="n">
-        <v>12948.60455853285</v>
+        <v>35961.09110659748</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2.137666361680774e-06</v>
+        <v>3.572366718127481e-06</v>
       </c>
       <c r="B13" t="n">
-        <v>5330860963.264245</v>
+        <v>3074063120.243857</v>
       </c>
       <c r="C13" t="n">
-        <v>7.394324063586855e+18</v>
+        <v>2.014701260913252e+30</v>
       </c>
       <c r="D13" t="n">
-        <v>2.649534984378466</v>
+        <v>4.845840627477699</v>
       </c>
       <c r="E13" t="n">
-        <v>20506.88291839214</v>
+        <v>21224.38921497412</v>
       </c>
       <c r="F13" t="n">
-        <v>5.603412194549317e-05</v>
+        <v>0.0001778700342902951</v>
       </c>
       <c r="G13" t="n">
-        <v>2098.731205710792</v>
+        <v>2138.62859159873</v>
       </c>
       <c r="H13" t="n">
-        <v>1.45861189100367e-07</v>
+        <v>1.50751998190123e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>20453.50190297928</v>
+        <v>21206.40069263932</v>
       </c>
       <c r="J13" t="n">
-        <v>20258.44227997409</v>
+        <v>21120.62212874688</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4.626380600327891e-06</v>
+        <v>9.579946479944955e-06</v>
       </c>
       <c r="B14" t="n">
-        <v>8419414074.014755</v>
+        <v>2091067776.725971</v>
       </c>
       <c r="C14" t="n">
-        <v>8852183291.460579</v>
+        <v>2.090863093981906e+39</v>
       </c>
       <c r="D14" t="n">
-        <v>1.05980198019802</v>
+        <v>6.994997546082007</v>
       </c>
       <c r="E14" t="n">
-        <v>65432.25906936578</v>
+        <v>40591.0346721908</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000101582960298116</v>
+        <v>0.0001109500703427731</v>
       </c>
       <c r="G14" t="n">
-        <v>6835.365997645508</v>
+        <v>4153.85168947879</v>
       </c>
       <c r="H14" t="n">
-        <v>5.039385712806461e-07</v>
+        <v>2.8775708203285e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>65107.65896857808</v>
+        <v>40485.75886968001</v>
       </c>
       <c r="J14" t="n">
-        <v>64125.99014572705</v>
+        <v>40100.69045602215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.729805664505545e-06</v>
+        <v>1.125262376223038e-05</v>
       </c>
       <c r="B15" t="n">
-        <v>7592869077.872826</v>
+        <v>1151074464.082067</v>
       </c>
       <c r="C15" t="n">
-        <v>8466900966.461835</v>
+        <v>2.170040278085731e+45</v>
       </c>
       <c r="D15" t="n">
-        <v>1.05980198019802</v>
+        <v>8.344022140939265</v>
       </c>
       <c r="E15" t="n">
-        <v>21995.69652382386</v>
+        <v>26796.95875364222</v>
       </c>
       <c r="F15" t="n">
-        <v>9.920646799044051e-05</v>
+        <v>7.025422344411424e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>2237.168436235454</v>
+        <v>2777.605520375386</v>
       </c>
       <c r="H15" t="n">
-        <v>1.884228450859211e-07</v>
+        <v>2.852133806669919e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>21953.92009732045</v>
+        <v>26688.17025918537</v>
       </c>
       <c r="J15" t="n">
-        <v>21788.25167412291</v>
+        <v>26338.01722100365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7.915119221593421e-06</v>
+        <v>1.299192770400155e-05</v>
       </c>
       <c r="B16" t="n">
-        <v>2837792180.876665</v>
+        <v>1714546269.36053</v>
       </c>
       <c r="C16" t="n">
-        <v>2.301969542827669e+24</v>
+        <v>1.293989948809826e+39</v>
       </c>
       <c r="D16" t="n">
-        <v>3.953655318138515</v>
+        <v>7.131884804368005</v>
       </c>
       <c r="E16" t="n">
-        <v>42319.19542539863</v>
+        <v>45233.5213640965</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002844683593883114</v>
+        <v>0.0001517971431136251</v>
       </c>
       <c r="G16" t="n">
-        <v>4285.216106248004</v>
+        <v>4626.090552775608</v>
       </c>
       <c r="H16" t="n">
-        <v>3.980643321858691e-07</v>
+        <v>3.830835977405852e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>42259.97702127848</v>
+        <v>45119.36756813433</v>
       </c>
       <c r="J16" t="n">
-        <v>42007.18086167795</v>
+        <v>44698.75102193086</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5.502842386244831e-06</v>
+        <v>3.420750071828355e-06</v>
       </c>
       <c r="B17" t="n">
-        <v>11200915344.71087</v>
+        <v>7833537331.992668</v>
       </c>
       <c r="C17" t="n">
-        <v>11655105811.47262</v>
+        <v>29338019186.22629</v>
       </c>
       <c r="D17" t="n">
-        <v>1.05980198019802</v>
+        <v>1.158183511505733</v>
       </c>
       <c r="E17" t="n">
-        <v>103409.158644193</v>
+        <v>45080.32019488366</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0001620332504733737</v>
+        <v>0.0002128042084702863</v>
       </c>
       <c r="G17" t="n">
-        <v>10685.20291311128</v>
+        <v>4576.814942442413</v>
       </c>
       <c r="H17" t="n">
-        <v>5.994090779972276e-07</v>
+        <v>3.607707658052495e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>103026.6174789797</v>
+        <v>45003.89472493472</v>
       </c>
       <c r="J17" t="n">
-        <v>101760.6816330447</v>
+        <v>44692.21210980479</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4.955876126538063e-06</v>
+        <v>8.108216034673211e-06</v>
       </c>
       <c r="B18" t="n">
-        <v>1852237432.494826</v>
+        <v>3862496487.139654</v>
       </c>
       <c r="C18" t="n">
-        <v>6.805644893837938e+34</v>
+        <v>6.283083402273255e+18</v>
       </c>
       <c r="D18" t="n">
-        <v>5.839552234293852</v>
+        <v>2.848960732739439</v>
       </c>
       <c r="E18" t="n">
-        <v>18191.09671138948</v>
+        <v>56848.11996208006</v>
       </c>
       <c r="F18" t="n">
-        <v>8.197071878868255e-05</v>
+        <v>0.0001573436963294648</v>
       </c>
       <c r="G18" t="n">
-        <v>1854.357363218167</v>
+        <v>5855.788799703504</v>
       </c>
       <c r="H18" t="n">
-        <v>1.764769693667834e-07</v>
+        <v>5.258088915306845e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>18151.93260907924</v>
+        <v>56658.14573597395</v>
       </c>
       <c r="J18" t="n">
-        <v>18001.48235357287</v>
+        <v>56010.58561020045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.079329005200108e-06</v>
+        <v>1.339285827201886e-05</v>
       </c>
       <c r="B19" t="n">
-        <v>9779870088.039499</v>
+        <v>1941534846.638352</v>
       </c>
       <c r="C19" t="n">
-        <v>10786285900.56182</v>
+        <v>8.668142316610188e+39</v>
       </c>
       <c r="D19" t="n">
-        <v>1.05980198019802</v>
+        <v>7.306372079696652</v>
       </c>
       <c r="E19" t="n">
-        <v>34050.79569117977</v>
+        <v>52890.90539113988</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0001291827511840616</v>
+        <v>0.0002667100034857817</v>
       </c>
       <c r="G19" t="n">
-        <v>3458.810541330909</v>
+        <v>5357.959245821735</v>
       </c>
       <c r="H19" t="n">
-        <v>2.264954353363585e-07</v>
+        <v>3.858670738328471e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>33991.09461094318</v>
+        <v>52814.38460590905</v>
       </c>
       <c r="J19" t="n">
-        <v>33749.61010752628</v>
+        <v>52490.26320229185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5.089301258816564e-06</v>
+        <v>9.530619108733576e-06</v>
       </c>
       <c r="B20" t="n">
-        <v>3270445545.414374</v>
+        <v>1314369037.990128</v>
       </c>
       <c r="C20" t="n">
-        <v>5.544993921196145e+25</v>
+        <v>9.91738579708885e+38</v>
       </c>
       <c r="D20" t="n">
-        <v>4.095145894398673</v>
+        <v>6.968052731042225</v>
       </c>
       <c r="E20" t="n">
-        <v>31495.91721572883</v>
+        <v>25360.97151136518</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001914552551618893</v>
+        <v>0.0001314149759380556</v>
       </c>
       <c r="G20" t="n">
-        <v>3186.386789414003</v>
+        <v>2586.002503985684</v>
       </c>
       <c r="H20" t="n">
-        <v>2.485193046863528e-07</v>
+        <v>2.873317346833225e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>31455.03380701647</v>
+        <v>25305.52111931054</v>
       </c>
       <c r="J20" t="n">
-        <v>31277.45217540422</v>
+        <v>25093.35381401839</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3.815046576295236e-06</v>
+        <v>5.45125241552055e-06</v>
       </c>
       <c r="B21" t="n">
-        <v>3460244154.852675</v>
+        <v>1824103096.573968</v>
       </c>
       <c r="C21" t="n">
-        <v>4.320084280289163e+24</v>
+        <v>3.551627992043119e+51</v>
       </c>
       <c r="D21" t="n">
-        <v>3.816313134314767</v>
+        <v>9.046005734992635</v>
       </c>
       <c r="E21" t="n">
-        <v>24836.80785520054</v>
+        <v>20755.31061604728</v>
       </c>
       <c r="F21" t="n">
-        <v>4.460530759398453e-05</v>
+        <v>2.605529293164568e-05</v>
       </c>
       <c r="G21" t="n">
-        <v>2582.68209477925</v>
+        <v>2167.107198228156</v>
       </c>
       <c r="H21" t="n">
-        <v>1.975555293873594e-07</v>
+        <v>1.277340055495649e-07</v>
       </c>
       <c r="I21" t="n">
-        <v>24726.80640046809</v>
+        <v>20653.55935313236</v>
       </c>
       <c r="J21" t="n">
-        <v>24382.05725173629</v>
+        <v>20344.67420215446</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6.166462752799862e-06</v>
+        <v>3.408960377644804e-06</v>
       </c>
       <c r="B22" t="n">
-        <v>6942505882.194219</v>
+        <v>2264348730.849747</v>
       </c>
       <c r="C22" t="n">
-        <v>3.408757725559291e+22</v>
+        <v>7.425566601698884e+32</v>
       </c>
       <c r="D22" t="n">
-        <v>3.469794444753711</v>
+        <v>5.323011366601214</v>
       </c>
       <c r="E22" t="n">
-        <v>79363.18412487399</v>
+        <v>15122.7209170203</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0002464568258389581</v>
+        <v>5.53582131249317e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>8036.232304985799</v>
+        <v>1544.772457044843</v>
       </c>
       <c r="H22" t="n">
-        <v>3.447506838886807e-07</v>
+        <v>1.321897737816534e-07</v>
       </c>
       <c r="I22" t="n">
-        <v>79252.16868876466</v>
+        <v>15086.60939997272</v>
       </c>
       <c r="J22" t="n">
-        <v>78778.21733634954</v>
+        <v>14951.5813500676</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.755289346691994e-06</v>
+        <v>2.711718363782546e-06</v>
       </c>
       <c r="B23" t="n">
-        <v>8558429903.000626</v>
+        <v>5261070560.235528</v>
       </c>
       <c r="C23" t="n">
-        <v>9535266598.991247</v>
+        <v>2.836316052110892e+20</v>
       </c>
       <c r="D23" t="n">
-        <v>1.05980198019802</v>
+        <v>2.963192896746786</v>
       </c>
       <c r="E23" t="n">
-        <v>25143.88581387477</v>
+        <v>25962.94674577226</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0001430826061302562</v>
+        <v>0.0001148944705159412</v>
       </c>
       <c r="G23" t="n">
-        <v>2544.627971132578</v>
+        <v>2631.05645998661</v>
       </c>
       <c r="H23" t="n">
-        <v>1.911987106061723e-07</v>
+        <v>1.709246543591647e-07</v>
       </c>
       <c r="I23" t="n">
-        <v>25110.28649193577</v>
+        <v>25924.32253976184</v>
       </c>
       <c r="J23" t="n">
-        <v>24965.3144775874</v>
+        <v>25761.7912896653</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4.02328227012193e-06</v>
+        <v>7.128057478414073e-06</v>
       </c>
       <c r="B24" t="n">
-        <v>1722957807.528512</v>
+        <v>3287231147.379159</v>
       </c>
       <c r="C24" t="n">
-        <v>5.330215418890706e+35</v>
+        <v>1.301078939038449e+25</v>
       </c>
       <c r="D24" t="n">
-        <v>5.929487734747979</v>
+        <v>4.060596652713865</v>
       </c>
       <c r="E24" t="n">
-        <v>13758.88621336003</v>
+        <v>44303.89858623786</v>
       </c>
       <c r="F24" t="n">
-        <v>7.717918145721789e-05</v>
+        <v>0.0002232162051255052</v>
       </c>
       <c r="G24" t="n">
-        <v>1398.55073380644</v>
+        <v>4493.012274380001</v>
       </c>
       <c r="H24" t="n">
-        <v>1.412455487907306e-07</v>
+        <v>3.505670418017015e-07</v>
       </c>
       <c r="I24" t="n">
-        <v>13733.70608839287</v>
+        <v>44234.3181242865</v>
       </c>
       <c r="J24" t="n">
-        <v>13632.92566269463</v>
+        <v>43945.26952123412</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9.991875791789189e-06</v>
+        <v>7.134233710219896e-06</v>
       </c>
       <c r="B25" t="n">
-        <v>2741284454.342722</v>
+        <v>2493874952.951794</v>
       </c>
       <c r="C25" t="n">
-        <v>3.335009128535186e+30</v>
+        <v>5.409674751668405e+24</v>
       </c>
       <c r="D25" t="n">
-        <v>5.241078446159634</v>
+        <v>4.010397054175508</v>
       </c>
       <c r="E25" t="n">
-        <v>53605.36649925767</v>
+        <v>33609.23149123318</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0001186666625048084</v>
+        <v>0.0001600289361475454</v>
       </c>
       <c r="G25" t="n">
-        <v>5520.297597261605</v>
+        <v>3427.939527659104</v>
       </c>
       <c r="H25" t="n">
-        <v>3.929602089624275e-07</v>
+        <v>3.545507285977004e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>53427.85433555118</v>
+        <v>33534.76884841564</v>
       </c>
       <c r="J25" t="n">
-        <v>52821.18847531552</v>
+        <v>33250.82840807548</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.254671885585531e-06</v>
+        <v>1.392976892429447e-05</v>
       </c>
       <c r="B26" t="n">
-        <v>14408612678.55872</v>
+        <v>515988004.9229412</v>
       </c>
       <c r="C26" t="n">
-        <v>16378764833.12601</v>
+        <v>1.278238408189659e+67</v>
       </c>
       <c r="D26" t="n">
-        <v>1.05980198019802</v>
+        <v>13.0319972916943</v>
       </c>
       <c r="E26" t="n">
-        <v>30258.16899786387</v>
+        <v>15460.10730425537</v>
       </c>
       <c r="F26" t="n">
-        <v>0.000102146451034919</v>
+        <v>3.902366891950905e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>3062.252697324335</v>
+        <v>1627.405109496655</v>
       </c>
       <c r="H26" t="n">
-        <v>1.366678645944422e-07</v>
+        <v>2.282798084608994e-07</v>
       </c>
       <c r="I26" t="n">
-        <v>30217.68477837726</v>
+        <v>15369.66910528746</v>
       </c>
       <c r="J26" t="n">
-        <v>30043.05679556639</v>
+        <v>15110.50249954412</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7.450278233778199e-06</v>
+        <v>4.65720527500993e-06</v>
       </c>
       <c r="B27" t="n">
-        <v>1195043614.352483</v>
+        <v>3540741792.982863</v>
       </c>
       <c r="C27" t="n">
-        <v>4.416657719851011e+41</v>
+        <v>1.229602623357255e+26</v>
       </c>
       <c r="D27" t="n">
-        <v>7.366982523413188</v>
+        <v>4.130958030553324</v>
       </c>
       <c r="E27" t="n">
-        <v>18139.96146989845</v>
+        <v>31384.76280512183</v>
       </c>
       <c r="F27" t="n">
-        <v>9.824753412688646e-05</v>
+        <v>3.791932238826347e-05</v>
       </c>
       <c r="G27" t="n">
-        <v>1849.383777690767</v>
+        <v>3306.64087378852</v>
       </c>
       <c r="H27" t="n">
-        <v>2.129581550733718e-07</v>
+        <v>2.257531240852116e-07</v>
       </c>
       <c r="I27" t="n">
-        <v>18100.64188023076</v>
+        <v>31197.91325703701</v>
       </c>
       <c r="J27" t="n">
-        <v>17949.85737632942</v>
+        <v>30665.61547637856</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2.366886597495623e-06</v>
+        <v>7.904811203399205e-07</v>
       </c>
       <c r="B28" t="n">
-        <v>11865710736.81797</v>
+        <v>13191460576.42801</v>
       </c>
       <c r="C28" t="n">
-        <v>12985793237.11368</v>
+        <v>15415245781.7239</v>
       </c>
       <c r="D28" t="n">
         <v>1.05980198019802</v>
       </c>
       <c r="E28" t="n">
-        <v>47045.26883626018</v>
+        <v>17454.10959286932</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0001197674983907399</v>
+        <v>6.190798176079416e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>4795.671952671114</v>
+        <v>1767.259443187758</v>
       </c>
       <c r="H28" t="n">
-        <v>2.578182716399765e-07</v>
+        <v>8.610487567326191e-08</v>
       </c>
       <c r="I28" t="n">
-        <v>46943.99653732119</v>
+        <v>17429.83349964618</v>
       </c>
       <c r="J28" t="n">
-        <v>46554.94389185282</v>
+        <v>17326.05520225468</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.991904448728948e-06</v>
+        <v>2.849459881884504e-06</v>
       </c>
       <c r="B29" t="n">
-        <v>3691764782.570659</v>
+        <v>4067473408.855938</v>
       </c>
       <c r="C29" t="n">
-        <v>2.019586059777957e+30</v>
+        <v>1.448036989741659e+17</v>
       </c>
       <c r="D29" t="n">
-        <v>4.661829317435211</v>
+        <v>2.401926867659881</v>
       </c>
       <c r="E29" t="n">
-        <v>14163.82275095436</v>
+        <v>20620.0995708107</v>
       </c>
       <c r="F29" t="n">
-        <v>3.62563179814201e-05</v>
+        <v>0.0001520021490151803</v>
       </c>
       <c r="G29" t="n">
-        <v>1446.965960661049</v>
+        <v>2087.354338683304</v>
       </c>
       <c r="H29" t="n">
-        <v>8.69862331195503e-08</v>
+        <v>2.075860473348733e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>14129.84087810367</v>
+        <v>20591.93914680821</v>
       </c>
       <c r="J29" t="n">
-        <v>14002.9343023542</v>
+        <v>20471.04407328253</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4.020427476987301e-06</v>
+        <v>1.332904472715312e-06</v>
       </c>
       <c r="B30" t="n">
-        <v>9359862942.755127</v>
+        <v>7990841438.73449</v>
       </c>
       <c r="C30" t="n">
-        <v>4.022472812667842e+17</v>
+        <v>9050666526.541487</v>
       </c>
       <c r="D30" t="n">
-        <v>2.455448350336283</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E30" t="n">
-        <v>67113.2450996128</v>
+        <v>17831.36015771138</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0001826272002641705</v>
+        <v>9.224740965244726e-05</v>
       </c>
       <c r="G30" t="n">
-        <v>6806.813016303865</v>
+        <v>1808.394545611344</v>
       </c>
       <c r="H30" t="n">
-        <v>2.887126502024081e-07</v>
+        <v>1.451895193374559e-07</v>
       </c>
       <c r="I30" t="n">
-        <v>67007.14675923214</v>
+        <v>17803.29512455559</v>
       </c>
       <c r="J30" t="n">
-        <v>66567.08962574801</v>
+        <v>17686.76846822216</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6.376515305154227e-06</v>
+        <v>2.20226918056215e-06</v>
       </c>
       <c r="B31" t="n">
-        <v>2467379929.552399</v>
+        <v>7739764096.160237</v>
       </c>
       <c r="C31" t="n">
-        <v>1.031220133068693e+52</v>
+        <v>8506965551.400846</v>
       </c>
       <c r="D31" t="n">
-        <v>9.214986138217048</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E31" t="n">
-        <v>32807.03662883295</v>
+        <v>28590.01652401209</v>
       </c>
       <c r="F31" t="n">
-        <v>6.834469014471805e-05</v>
+        <v>6.923213084369926e-05</v>
       </c>
       <c r="G31" t="n">
-        <v>3344.09994779813</v>
+        <v>2948.158737351614</v>
       </c>
       <c r="H31" t="n">
-        <v>1.467435679814101e-07</v>
+        <v>2.398869613860201e-07</v>
       </c>
       <c r="I31" t="n">
-        <v>32736.59631226091</v>
+        <v>28490.95309628941</v>
       </c>
       <c r="J31" t="n">
-        <v>32465.80961171716</v>
+        <v>28156.78855996814</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3.435780296181419e-06</v>
+        <v>4.66252142670127e-06</v>
       </c>
       <c r="B32" t="n">
-        <v>3006377560.46514</v>
+        <v>3439725221.304719</v>
       </c>
       <c r="C32" t="n">
-        <v>1.680668151537774e+23</v>
+        <v>5.702274758850166e+22</v>
       </c>
       <c r="D32" t="n">
-        <v>3.54777148732991</v>
+        <v>3.512365427367434</v>
       </c>
       <c r="E32" t="n">
-        <v>19239.44174155622</v>
+        <v>29805.61994718812</v>
       </c>
       <c r="F32" t="n">
-        <v>5.521175347912027e-05</v>
+        <v>0.000106939958527225</v>
       </c>
       <c r="G32" t="n">
-        <v>1983.134165995194</v>
+        <v>3045.321349865056</v>
       </c>
       <c r="H32" t="n">
-        <v>1.887316968604e-07</v>
+        <v>2.581676716546195e-07</v>
       </c>
       <c r="I32" t="n">
-        <v>19173.67508395668</v>
+        <v>29733.66510813673</v>
       </c>
       <c r="J32" t="n">
-        <v>18950.95574785461</v>
+        <v>29465.38844790293</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2.071964168315211e-06</v>
+        <v>4.749362600614948e-06</v>
       </c>
       <c r="B33" t="n">
-        <v>9526721972.092529</v>
+        <v>8375613154.512581</v>
       </c>
       <c r="C33" t="n">
-        <v>1103405447042.515</v>
+        <v>8792325487.968328</v>
       </c>
       <c r="D33" t="n">
-        <v>1.411643195940286</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E33" t="n">
-        <v>33609.05606285583</v>
+        <v>66791.84709095115</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0001218640531666162</v>
+        <v>0.0001147337484614228</v>
       </c>
       <c r="G33" t="n">
-        <v>3410.918178952951</v>
+        <v>6950.232798810216</v>
       </c>
       <c r="H33" t="n">
-        <v>2.014911564026393e-07</v>
+        <v>5.173346532012521e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>33553.48653766987</v>
+        <v>66490.68254682326</v>
       </c>
       <c r="J33" t="n">
-        <v>33325.47935877303</v>
+        <v>65552.05326965055</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6.043344022951703e-06</v>
+        <v>6.488233421909339e-06</v>
       </c>
       <c r="B34" t="n">
-        <v>3888902443.940736</v>
+        <v>2064146715.287051</v>
       </c>
       <c r="C34" t="n">
-        <v>3.420330745894088e+25</v>
+        <v>6.961564805957601e+25</v>
       </c>
       <c r="D34" t="n">
-        <v>4.084844786376609</v>
+        <v>4.214896882694463</v>
       </c>
       <c r="E34" t="n">
-        <v>44475.14672096013</v>
+        <v>25452.72665371642</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0001768372553875316</v>
+        <v>0.000158514678172845</v>
       </c>
       <c r="G34" t="n">
-        <v>4514.454923747096</v>
+        <v>2589.954012373991</v>
       </c>
       <c r="H34" t="n">
-        <v>2.957339660381916e-07</v>
+        <v>3.091853570462354e-07</v>
       </c>
       <c r="I34" t="n">
-        <v>44400.76866357004</v>
+        <v>25403.0807126027</v>
       </c>
       <c r="J34" t="n">
-        <v>44096.42830909204</v>
+        <v>25207.51318954585</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7.24329165412316e-06</v>
+        <v>5.78032707732946e-06</v>
       </c>
       <c r="B35" t="n">
-        <v>677999278.5743735</v>
+        <v>1306816706.786149</v>
       </c>
       <c r="C35" t="n">
-        <v>5.351110009453841e+78</v>
+        <v>6.906913685048214e+34</v>
       </c>
       <c r="D35" t="n">
-        <v>14.60396676543062</v>
+        <v>5.931077865682411</v>
       </c>
       <c r="E35" t="n">
-        <v>10589.82127728424</v>
+        <v>15007.42720685111</v>
       </c>
       <c r="F35" t="n">
-        <v>6.29949944095214e-05</v>
+        <v>7.401390686435853e-05</v>
       </c>
       <c r="G35" t="n">
-        <v>1075.040812955304</v>
+        <v>1537.765894526768</v>
       </c>
       <c r="H35" t="n">
-        <v>1.061414184226085e-07</v>
+        <v>2.028795255672102e-07</v>
       </c>
       <c r="I35" t="n">
-        <v>10571.97829369881</v>
+        <v>14966.29034702704</v>
       </c>
       <c r="J35" t="n">
-        <v>10499.100053243</v>
+        <v>14818.06491351848</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6.729868463728901e-06</v>
+        <v>4.150559859603353e-06</v>
       </c>
       <c r="B36" t="n">
-        <v>2504549826.296229</v>
+        <v>5673805399.830998</v>
       </c>
       <c r="C36" t="n">
-        <v>1.240119674308213e+34</v>
+        <v>1.01662129581785e+29</v>
       </c>
       <c r="D36" t="n">
-        <v>5.795778681014534</v>
+        <v>4.603200522724224</v>
       </c>
       <c r="E36" t="n">
-        <v>33374.68027444869</v>
+        <v>45237.79495843065</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0001066852373318616</v>
+        <v>0.0001343811249864321</v>
       </c>
       <c r="G36" t="n">
-        <v>3405.413756171699</v>
+        <v>4579.308666063096</v>
       </c>
       <c r="H36" t="n">
-        <v>2.413275285102771e-07</v>
+        <v>1.832801869073274e-07</v>
       </c>
       <c r="I36" t="n">
-        <v>33299.18502030778</v>
+        <v>45176.09588040839</v>
       </c>
       <c r="J36" t="n">
-        <v>33012.8574944754</v>
+        <v>44911.13584628489</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.847776724117558e-06</v>
+        <v>3.702036177376312e-06</v>
       </c>
       <c r="B37" t="n">
-        <v>4111090947.457424</v>
+        <v>11333526918.3554</v>
       </c>
       <c r="C37" t="n">
-        <v>1012720152068.874</v>
+        <v>12075982714.98902</v>
       </c>
       <c r="D37" t="n">
-        <v>1.464692467727386</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E37" t="n">
-        <v>12973.74796664001</v>
+        <v>70209.87118611073</v>
       </c>
       <c r="F37" t="n">
-        <v>7.968118240059137e-05</v>
+        <v>0.0003623519590478717</v>
       </c>
       <c r="G37" t="n">
-        <v>1323.272684045084</v>
+        <v>7091.308431877868</v>
       </c>
       <c r="H37" t="n">
-        <v>1.767307586150308e-07</v>
+        <v>4.032523441595056e-07</v>
       </c>
       <c r="I37" t="n">
-        <v>12944.97253621658</v>
+        <v>70131.73639359206</v>
       </c>
       <c r="J37" t="n">
-        <v>12835.27777864066</v>
+        <v>69780.37300702838</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2.064368001472543e-06</v>
+        <v>1.498487609185992e-05</v>
       </c>
       <c r="B38" t="n">
-        <v>3916513988.615311</v>
+        <v>1697987629.90512</v>
       </c>
       <c r="C38" t="n">
-        <v>1.877753473188154e+18</v>
+        <v>1.668377734770309e+33</v>
       </c>
       <c r="D38" t="n">
-        <v>2.564680012410822</v>
+        <v>5.994914263445493</v>
       </c>
       <c r="E38" t="n">
-        <v>14498.10608704708</v>
+        <v>50692.84922134422</v>
       </c>
       <c r="F38" t="n">
-        <v>5.743556105136041e-05</v>
+        <v>0.0001234899177122289</v>
       </c>
       <c r="G38" t="n">
-        <v>1482.527978327727</v>
+        <v>5261.665876526965</v>
       </c>
       <c r="H38" t="n">
-        <v>1.44014249488893e-07</v>
+        <v>5.20720127685129e-07</v>
       </c>
       <c r="I38" t="n">
-        <v>14461.75345413262</v>
+        <v>50479.0926053525</v>
       </c>
       <c r="J38" t="n">
-        <v>14327.5755086693</v>
+        <v>49798.97540063271</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2.433844096832569e-06</v>
+        <v>1.615526073241728e-06</v>
       </c>
       <c r="B39" t="n">
-        <v>6862846528.322561</v>
+        <v>6537416237.421388</v>
       </c>
       <c r="C39" t="n">
-        <v>7498156394.286886</v>
+        <v>78251868917935</v>
       </c>
       <c r="D39" t="n">
-        <v>1.05980198019802</v>
+        <v>1.748422831545854</v>
       </c>
       <c r="E39" t="n">
-        <v>27970.86981662047</v>
+        <v>18286.77606739392</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0001440395247234917</v>
+        <v>5.023313097430813e-05</v>
       </c>
       <c r="G39" t="n">
-        <v>2843.420555446573</v>
+        <v>1875.102996426443</v>
       </c>
       <c r="H39" t="n">
-        <v>2.651117629169358e-07</v>
+        <v>1.416987926192145e-07</v>
       </c>
       <c r="I39" t="n">
-        <v>27919.388067971</v>
+        <v>18235.19230107498</v>
       </c>
       <c r="J39" t="n">
-        <v>27713.62902572513</v>
+        <v>18050.77970832515</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4.644503865315605e-06</v>
+        <v>2.974529968958377e-06</v>
       </c>
       <c r="B40" t="n">
-        <v>2811057930.060166</v>
+        <v>13062874036.9826</v>
       </c>
       <c r="C40" t="n">
-        <v>3.828178358090652e+34</v>
+        <v>14101933539.86748</v>
       </c>
       <c r="D40" t="n">
-        <v>5.733579609230691</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E40" t="n">
-        <v>25795.28249860082</v>
+        <v>65110.39685344094</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0001177344471151351</v>
+        <v>0.0001299244245899159</v>
       </c>
       <c r="G40" t="n">
-        <v>2612.699367003198</v>
+        <v>6657.175491885746</v>
       </c>
       <c r="H40" t="n">
-        <v>1.682212473130388e-07</v>
+        <v>3.240071477651686e-07</v>
       </c>
       <c r="I40" t="n">
-        <v>25758.42570177513</v>
+        <v>64948.02373506132</v>
       </c>
       <c r="J40" t="n">
-        <v>25601.85230902228</v>
+        <v>64347.83285533027</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6.398112527271401e-06</v>
+        <v>7.245120542902627e-06</v>
       </c>
       <c r="B41" t="n">
-        <v>3380345174.891744</v>
+        <v>1869886483.32057</v>
       </c>
       <c r="C41" t="n">
-        <v>3.365228482983499e+29</v>
+        <v>6.743349307581867e+37</v>
       </c>
       <c r="D41" t="n">
-        <v>4.875513475329511</v>
+        <v>6.574152996227569</v>
       </c>
       <c r="E41" t="n">
-        <v>41910.14679122037</v>
+        <v>27248.20652396843</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0001000586272454534</v>
+        <v>9.327023171910216e-05</v>
       </c>
       <c r="G41" t="n">
-        <v>4292.243833670702</v>
+        <v>2785.517834339075</v>
       </c>
       <c r="H41" t="n">
-        <v>2.685334914720486e-07</v>
+        <v>2.308506767416344e-07</v>
       </c>
       <c r="I41" t="n">
-        <v>41797.66995283296</v>
+        <v>27180.76521069928</v>
       </c>
       <c r="J41" t="n">
-        <v>41390.04863996821</v>
+        <v>26930.97551007539</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5.460447808996555e-06</v>
+        <v>6.10473263824813e-06</v>
       </c>
       <c r="B42" t="n">
-        <v>3595525413.610224</v>
+        <v>7558211369.346231</v>
       </c>
       <c r="C42" t="n">
-        <v>9.430300128814895e+23</v>
+        <v>4467664210.938383</v>
       </c>
       <c r="D42" t="n">
-        <v>3.771193529249966</v>
+        <v>1.013773592334332</v>
       </c>
       <c r="E42" t="n">
-        <v>36749.26899934277</v>
+        <v>77271.59505068914</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0003627097374823082</v>
+        <v>0.0001637192876804239</v>
       </c>
       <c r="G42" t="n">
-        <v>3700.963245967699</v>
+        <v>8013.969746358111</v>
       </c>
       <c r="H42" t="n">
-        <v>2.855275611045348e-07</v>
+        <v>6.751995042438009e-07</v>
       </c>
       <c r="I42" t="n">
-        <v>36720.3397259723</v>
+        <v>76952.91700481225</v>
       </c>
       <c r="J42" t="n">
-        <v>36580.25739541119</v>
+        <v>75932.08758984316</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4.733644579259607e-06</v>
+        <v>6.344839775701451e-06</v>
       </c>
       <c r="B43" t="n">
-        <v>3737650036.425769</v>
+        <v>4850223258.398315</v>
       </c>
       <c r="C43" t="n">
-        <v>1014887003260067</v>
+        <v>1.187311207940563e+24</v>
       </c>
       <c r="D43" t="n">
-        <v>2.065449395280845</v>
+        <v>3.799992463308844</v>
       </c>
       <c r="E43" t="n">
-        <v>31115.95707839436</v>
+        <v>57720.37793025657</v>
       </c>
       <c r="F43" t="n">
-        <v>8.93716604911352e-05</v>
+        <v>0.0001751899881266408</v>
       </c>
       <c r="G43" t="n">
-        <v>3230.209539364657</v>
+        <v>5869.806337228453</v>
       </c>
       <c r="H43" t="n">
-        <v>3.785380048613032e-07</v>
+        <v>3.297135202549308e-07</v>
       </c>
       <c r="I43" t="n">
-        <v>30984.16393225522</v>
+        <v>57611.74621447568</v>
       </c>
       <c r="J43" t="n">
-        <v>30565.40411225626</v>
+        <v>57179.97283603074</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5.329352714251218e-06</v>
+        <v>3.72797041139364e-06</v>
       </c>
       <c r="B44" t="n">
-        <v>4342253448.754601</v>
+        <v>5076408682.374186</v>
       </c>
       <c r="C44" t="n">
-        <v>3.705656932075223e+21</v>
+        <v>1.290502846435742e+16</v>
       </c>
       <c r="D44" t="n">
-        <v>3.297281035177612</v>
+        <v>2.222548918589796</v>
       </c>
       <c r="E44" t="n">
-        <v>42677.77741912066</v>
+        <v>33439.94970057624</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0001321733472199618</v>
+        <v>0.0001332986568608472</v>
       </c>
       <c r="G44" t="n">
-        <v>4357.874639007827</v>
+        <v>3408.397331626988</v>
       </c>
       <c r="H44" t="n">
-        <v>3.100340682987616e-07</v>
+        <v>2.852459200158745e-07</v>
       </c>
       <c r="I44" t="n">
-        <v>42577.66975568093</v>
+        <v>33368.39152105473</v>
       </c>
       <c r="J44" t="n">
-        <v>42201.5849240376</v>
+        <v>33093.06919942379</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4.919528444948073e-06</v>
+        <v>4.213105414238847e-06</v>
       </c>
       <c r="B45" t="n">
-        <v>3127050373.547384</v>
+        <v>6933645238.718513</v>
       </c>
       <c r="C45" t="n">
-        <v>2.390822355667606e+22</v>
+        <v>298205332454351.2</v>
       </c>
       <c r="D45" t="n">
-        <v>3.460444669545506</v>
+        <v>1.908095261660647</v>
       </c>
       <c r="E45" t="n">
-        <v>28510.29296528606</v>
+        <v>50972.61552823446</v>
       </c>
       <c r="F45" t="n">
-        <v>0.000191079850967239</v>
+        <v>0.0001055145957531326</v>
       </c>
       <c r="G45" t="n">
-        <v>2888.041540333048</v>
+        <v>5250.532281235014</v>
       </c>
       <c r="H45" t="n">
-        <v>2.756234208983617e-07</v>
+        <v>3.525269572372783e-07</v>
       </c>
       <c r="I45" t="n">
-        <v>28469.16824994778</v>
+        <v>50802.31471888829</v>
       </c>
       <c r="J45" t="n">
-        <v>28294.85311728625</v>
+        <v>50221.77771940541</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3.731048246814628e-06</v>
+        <v>4.808462662730538e-06</v>
       </c>
       <c r="B46" t="n">
-        <v>2172562283.296831</v>
+        <v>984856453.3263053</v>
       </c>
       <c r="C46" t="n">
-        <v>9.76347473167705e+35</v>
+        <v>2.856245929977432e+54</v>
       </c>
       <c r="D46" t="n">
-        <v>5.929620442648989</v>
+        <v>9.559321528056824</v>
       </c>
       <c r="E46" t="n">
-        <v>16108.99621709621</v>
+        <v>9902.664844574016</v>
       </c>
       <c r="F46" t="n">
-        <v>4.278610507683708e-05</v>
+        <v>6.809843154251682e-05</v>
       </c>
       <c r="G46" t="n">
-        <v>1655.283404590585</v>
+        <v>1004.239542830454</v>
       </c>
       <c r="H46" t="n">
-        <v>1.309833456797846e-07</v>
+        <v>1.067662508573554e-07</v>
       </c>
       <c r="I46" t="n">
-        <v>16059.68090278403</v>
+        <v>9887.139224159513</v>
       </c>
       <c r="J46" t="n">
-        <v>15887.34225485699</v>
+        <v>9822.615906279849</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3.904913629344324e-06</v>
+        <v>1.95719730700988e-06</v>
       </c>
       <c r="B47" t="n">
-        <v>3137260321.055439</v>
+        <v>7832470697.271846</v>
       </c>
       <c r="C47" t="n">
-        <v>1.96101329533005e+32</v>
+        <v>8669813013.282312</v>
       </c>
       <c r="D47" t="n">
-        <v>5.237448056811255</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E47" t="n">
-        <v>23931.56712734617</v>
+        <v>25684.3492252103</v>
       </c>
       <c r="F47" t="n">
-        <v>9.807650531472968e-05</v>
+        <v>9.031985461083066e-05</v>
       </c>
       <c r="G47" t="n">
-        <v>2426.90368078162</v>
+        <v>2622.997979912797</v>
       </c>
       <c r="H47" t="n">
-        <v>1.536689396898375e-07</v>
+        <v>2.131919744214263e-07</v>
       </c>
       <c r="I47" t="n">
-        <v>23894.07049618283</v>
+        <v>25623.72360588611</v>
       </c>
       <c r="J47" t="n">
-        <v>23738.21532611614</v>
+        <v>25396.34017239131</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4.262391622030914e-06</v>
+        <v>1.489115700338444e-05</v>
       </c>
       <c r="B48" t="n">
-        <v>2493277015.660057</v>
+        <v>1631298951.025132</v>
       </c>
       <c r="C48" t="n">
-        <v>1.706428147432588e+26</v>
+        <v>2.064200256720277e+37</v>
       </c>
       <c r="D48" t="n">
-        <v>4.163200200725894</v>
+        <v>6.840289087059374</v>
       </c>
       <c r="E48" t="n">
-        <v>20155.45260767893</v>
+        <v>49207.37272692782</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0001409669050846657</v>
+        <v>9.346886212558359e-05</v>
       </c>
       <c r="G48" t="n">
-        <v>2041.958375114719</v>
+        <v>5137.236326575962</v>
       </c>
       <c r="H48" t="n">
-        <v>2.052587652137835e-07</v>
+        <v>4.569306295267704e-07</v>
       </c>
       <c r="I48" t="n">
-        <v>20126.10470284912</v>
+        <v>48966.81822261318</v>
       </c>
       <c r="J48" t="n">
-        <v>20001.98214561542</v>
+        <v>48235.91157039408</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4.580647037544872e-06</v>
+        <v>1.311142921004322e-05</v>
       </c>
       <c r="B49" t="n">
-        <v>4922593447.481127</v>
+        <v>1829550097.03091</v>
       </c>
       <c r="C49" t="n">
-        <v>8.667410363864545e+22</v>
+        <v>9.662711666720449e+32</v>
       </c>
       <c r="D49" t="n">
-        <v>3.513637729521253</v>
+        <v>5.880836780814231</v>
       </c>
       <c r="E49" t="n">
-        <v>41975.96753278222</v>
+        <v>47655.32936992825</v>
       </c>
       <c r="F49" t="n">
-        <v>6.280693624105497e-05</v>
+        <v>0.0001238360585286933</v>
       </c>
       <c r="G49" t="n">
-        <v>4350.113921611821</v>
+        <v>4926.183074194605</v>
       </c>
       <c r="H49" t="n">
-        <v>2.535613863049801e-07</v>
+        <v>4.638464494526086e-07</v>
       </c>
       <c r="I49" t="n">
-        <v>41806.50401241155</v>
+        <v>47476.82921748183</v>
       </c>
       <c r="J49" t="n">
-        <v>41260.14184792199</v>
+        <v>46888.28969034924</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>5.98092978691525e-06</v>
+        <v>4.097292645750295e-06</v>
       </c>
       <c r="B50" t="n">
-        <v>2284329355.579435</v>
+        <v>1605455489.867154</v>
       </c>
       <c r="C50" t="n">
-        <v>2.40732974358042e+39</v>
+        <v>4.310809212136719e+62</v>
       </c>
       <c r="D50" t="n">
-        <v>6.765263881015472</v>
+        <v>10.92565014828944</v>
       </c>
       <c r="E50" t="n">
-        <v>27568.19555394989</v>
+        <v>13915.76809683419</v>
       </c>
       <c r="F50" t="n">
-        <v>8.033753193804362e-05</v>
+        <v>4.429435409371074e-05</v>
       </c>
       <c r="G50" t="n">
-        <v>2814.096409661444</v>
+        <v>1414.147750059552</v>
       </c>
       <c r="H50" t="n">
-        <v>1.854585214947374e-07</v>
+        <v>7.982672911377316e-08</v>
       </c>
       <c r="I50" t="n">
-        <v>27504.55460476494</v>
+        <v>13890.68927419404</v>
       </c>
       <c r="J50" t="n">
-        <v>27264.46414626601</v>
+        <v>13789.9308440019</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9.604775850305662e-06</v>
+        <v>7.023517036257792e-06</v>
       </c>
       <c r="B51" t="n">
-        <v>1252520215.806906</v>
+        <v>2923351325.179805</v>
       </c>
       <c r="C51" t="n">
-        <v>1.437546973323079e+48</v>
+        <v>5.290483127499957e+20</v>
       </c>
       <c r="D51" t="n">
-        <v>8.797324194012212</v>
+        <v>3.220619529627567</v>
       </c>
       <c r="E51" t="n">
-        <v>24971.72054147578</v>
+        <v>37774.80551118204</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0001112596778053243</v>
+        <v>0.0001525058740117838</v>
       </c>
       <c r="G51" t="n">
-        <v>2543.885030245083</v>
+        <v>3870.222182746339</v>
       </c>
       <c r="H51" t="n">
-        <v>2.312513941210707e-07</v>
+        <v>4.160222489664072e-07</v>
       </c>
       <c r="I51" t="n">
-        <v>24919.81723470077</v>
+        <v>37671.75925381744</v>
       </c>
       <c r="J51" t="n">
-        <v>24718.62235275851</v>
+        <v>37299.97142355145</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.090836371424759e-05</v>
+        <v>4.267971024124427e-06</v>
       </c>
       <c r="B52" t="n">
-        <v>2493130462.110478</v>
+        <v>8939635789.657091</v>
       </c>
       <c r="C52" t="n">
-        <v>2.317217942742192e+26</v>
+        <v>9444579211.914169</v>
       </c>
       <c r="D52" t="n">
-        <v>4.448347868417287</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E52" t="n">
-        <v>52175.42816615274</v>
+        <v>64000.01585800864</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0001111201856664587</v>
+        <v>0.0001322001904398243</v>
       </c>
       <c r="G52" t="n">
-        <v>5427.263729331268</v>
+        <v>6602.559032862019</v>
       </c>
       <c r="H52" t="n">
-        <v>4.962793061414954e-07</v>
+        <v>4.648980284959744e-07</v>
       </c>
       <c r="I52" t="n">
-        <v>51942.40492980164</v>
+        <v>63774.95202794068</v>
       </c>
       <c r="J52" t="n">
-        <v>51213.99030666382</v>
+        <v>63019.01570792383</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.906572599410185e-06</v>
+        <v>4.61412521902998e-06</v>
       </c>
       <c r="B53" t="n">
-        <v>5248234051.096502</v>
+        <v>970668129.2471819</v>
       </c>
       <c r="C53" t="n">
-        <v>3.269059228764442e+18</v>
+        <v>2.006814084391082e+91</v>
       </c>
       <c r="D53" t="n">
-        <v>2.575021801105887</v>
+        <v>16.43096077696319</v>
       </c>
       <c r="E53" t="n">
-        <v>17960.67265594398</v>
+        <v>9711.181512922651</v>
       </c>
       <c r="F53" t="n">
-        <v>4.310501281717924e-05</v>
+        <v>4.587186070937378e-05</v>
       </c>
       <c r="G53" t="n">
-        <v>1845.810011751847</v>
+        <v>982.5925115186564</v>
       </c>
       <c r="H53" t="n">
-        <v>1.326454719370137e-07</v>
+        <v>6.022270460245357e-08</v>
       </c>
       <c r="I53" t="n">
-        <v>17905.40293799126</v>
+        <v>9698.432223782214</v>
       </c>
       <c r="J53" t="n">
-        <v>17712.53820734554</v>
+        <v>9643.196256879068</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>7.345061849367184e-06</v>
+        <v>2.118601197278911e-05</v>
       </c>
       <c r="B54" t="n">
-        <v>1896015881.909625</v>
+        <v>2355066981.866176</v>
       </c>
       <c r="C54" t="n">
-        <v>4.030512500827435e+42</v>
+        <v>6.182536877502095e+24</v>
       </c>
       <c r="D54" t="n">
-        <v>7.506925862086634</v>
+        <v>4.330386009146245</v>
       </c>
       <c r="E54" t="n">
-        <v>28465.45251013737</v>
+        <v>95174.99867412631</v>
       </c>
       <c r="F54" t="n">
-        <v>6.269917404461156e-05</v>
+        <v>0.0004515275855927844</v>
       </c>
       <c r="G54" t="n">
-        <v>2930.794038927638</v>
+        <v>9704.643844550199</v>
       </c>
       <c r="H54" t="n">
-        <v>2.061887091058509e-07</v>
+        <v>9.864946949458965e-07</v>
       </c>
       <c r="I54" t="n">
-        <v>28371.84274578859</v>
+        <v>94967.06092175124</v>
       </c>
       <c r="J54" t="n">
-        <v>28051.2852971162</v>
+        <v>94171.28382567933</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2.521809169186105e-06</v>
+        <v>7.846028303035443e-06</v>
       </c>
       <c r="B55" t="n">
-        <v>4450246757.346883</v>
+        <v>2224543100.976759</v>
       </c>
       <c r="C55" t="n">
-        <v>2.258201603700831e+22</v>
+        <v>1.413017596888114e+31</v>
       </c>
       <c r="D55" t="n">
-        <v>3.3021940265378</v>
+        <v>5.294192262981406</v>
       </c>
       <c r="E55" t="n">
-        <v>20706.6881542389</v>
+        <v>34195.58257607574</v>
       </c>
       <c r="F55" t="n">
-        <v>5.565596237648656e-05</v>
+        <v>9.825204682524447e-05</v>
       </c>
       <c r="G55" t="n">
-        <v>2119.735904620599</v>
+        <v>3515.331243550878</v>
       </c>
       <c r="H55" t="n">
-        <v>1.465375207337269e-07</v>
+        <v>3.057539792054377e-07</v>
       </c>
       <c r="I55" t="n">
-        <v>20652.16916624255</v>
+        <v>34089.16814724985</v>
       </c>
       <c r="J55" t="n">
-        <v>20453.56322855231</v>
+        <v>33719.0013084842</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.194681866108806e-05</v>
+        <v>1.99558981611416e-06</v>
       </c>
       <c r="B56" t="n">
-        <v>3138671923.909281</v>
+        <v>5379314537.775192</v>
       </c>
       <c r="C56" t="n">
-        <v>1.153953839920457e+27</v>
+        <v>5947485084.446679</v>
       </c>
       <c r="D56" t="n">
-        <v>4.596445426701322</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E56" t="n">
-        <v>72161.38766212658</v>
+        <v>17986.69616008742</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0001572685012223295</v>
+        <v>9.050594556303678e-05</v>
       </c>
       <c r="G56" t="n">
-        <v>7434.273912465612</v>
+        <v>1837.54944257585</v>
       </c>
       <c r="H56" t="n">
-        <v>5.282262844214597e-07</v>
+        <v>2.173739619960152e-07</v>
       </c>
       <c r="I56" t="n">
-        <v>71919.01527740108</v>
+        <v>17943.49635279063</v>
       </c>
       <c r="J56" t="n">
-        <v>71094.04930642026</v>
+        <v>17782.21109110923</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2.976957991606334e-06</v>
+        <v>3.836864239484918e-06</v>
       </c>
       <c r="B57" t="n">
-        <v>10626226445.44305</v>
+        <v>8923897544.918446</v>
       </c>
       <c r="C57" t="n">
-        <v>11470908083.72246</v>
+        <v>5275645813182.299</v>
       </c>
       <c r="D57" t="n">
-        <v>1.05980198019802</v>
+        <v>1.561083876533692</v>
       </c>
       <c r="E57" t="n">
-        <v>52935.87317761424</v>
+        <v>58764.08703099637</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0002878887417525694</v>
+        <v>0.000136702182557034</v>
       </c>
       <c r="G57" t="n">
-        <v>5347.250553705177</v>
+        <v>6014.212180386407</v>
       </c>
       <c r="H57" t="n">
-        <v>3.242716254141027e-07</v>
+        <v>3.561895077385821e-07</v>
       </c>
       <c r="I57" t="n">
-        <v>52876.24735989897</v>
+        <v>58610.9720562333</v>
       </c>
       <c r="J57" t="n">
-        <v>52608.83323705227</v>
+        <v>58051.62018795902</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>5.865655703980265e-06</v>
+        <v>4.9911570772831e-06</v>
       </c>
       <c r="B58" t="n">
-        <v>5259624076.248075</v>
+        <v>9984354361.444616</v>
       </c>
       <c r="C58" t="n">
-        <v>1.036224243907895e+24</v>
+        <v>2016733712032.083</v>
       </c>
       <c r="D58" t="n">
-        <v>3.763957603033222</v>
+        <v>1.48602287747167</v>
       </c>
       <c r="E58" t="n">
-        <v>57772.40686870294</v>
+        <v>85139.0773496558</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0002095461546008306</v>
+        <v>0.0003033991046688659</v>
       </c>
       <c r="G58" t="n">
-        <v>5853.466290593447</v>
+        <v>8633.674827681147</v>
       </c>
       <c r="H58" t="n">
-        <v>3.07197443824974e-07</v>
+        <v>4.742205319925126e-07</v>
       </c>
       <c r="I58" t="n">
-        <v>57687.71175345498</v>
+        <v>85006.00280219408</v>
       </c>
       <c r="J58" t="n">
-        <v>57330.07854767362</v>
+        <v>84452.55660395786</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>8.755783999779685e-06</v>
+        <v>1.230346296972792e-05</v>
       </c>
       <c r="B59" t="n">
-        <v>2002354500.78709</v>
+        <v>2269330732.122569</v>
       </c>
       <c r="C59" t="n">
-        <v>2.121722932386629e+53</v>
+        <v>3.665450344423184e+29</v>
       </c>
       <c r="D59" t="n">
-        <v>9.715373137627861</v>
+        <v>5.141055148240159</v>
       </c>
       <c r="E59" t="n">
-        <v>36754.31226344102</v>
+        <v>54561.40877799818</v>
       </c>
       <c r="F59" t="n">
-        <v>7.266242739622733e-05</v>
+        <v>0.0001149445574893499</v>
       </c>
       <c r="G59" t="n">
-        <v>3762.546431344107</v>
+        <v>5666.492787812773</v>
       </c>
       <c r="H59" t="n">
-        <v>1.913608338601725e-07</v>
+        <v>4.923872376100195e-07</v>
       </c>
       <c r="I59" t="n">
-        <v>36657.51759121879</v>
+        <v>54327.68443353933</v>
       </c>
       <c r="J59" t="n">
-        <v>36304.92628339164</v>
+        <v>53587.61395361676</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>3.461043248735363e-06</v>
+        <v>1.575344018286131e-06</v>
       </c>
       <c r="B60" t="n">
-        <v>6577985714.811481</v>
+        <v>12594438599.18532</v>
       </c>
       <c r="C60" t="n">
-        <v>335688847127898.8</v>
+        <v>14122990028.26291</v>
       </c>
       <c r="D60" t="n">
-        <v>1.907504668029352</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E60" t="n">
-        <v>39694.51986932087</v>
+        <v>33226.24434915128</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0001122087631399491</v>
+        <v>9.117086532522473e-05</v>
       </c>
       <c r="G60" t="n">
-        <v>4061.670492702796</v>
+        <v>3378.907706999938</v>
       </c>
       <c r="H60" t="n">
-        <v>2.896488400025294e-07</v>
+        <v>1.715977742502118e-07</v>
       </c>
       <c r="I60" t="n">
-        <v>39592.05486290898</v>
+        <v>33163.70738016816</v>
       </c>
       <c r="J60" t="n">
-        <v>39216.7908174265</v>
+        <v>32915.14912921555</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7.254871543803031e-06</v>
+        <v>2.428431383085002e-06</v>
       </c>
       <c r="B61" t="n">
-        <v>1822929549.275784</v>
+        <v>7126728948.893823</v>
       </c>
       <c r="C61" t="n">
-        <v>4.402781154958844e+30</v>
+        <v>30253708177.27902</v>
       </c>
       <c r="D61" t="n">
-        <v>5.184579457300848</v>
+        <v>1.163623351316804</v>
       </c>
       <c r="E61" t="n">
-        <v>25777.32456660987</v>
+        <v>29142.70654101423</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0004576974790258815</v>
+        <v>0.0001079920101589257</v>
       </c>
       <c r="G61" t="n">
-        <v>2592.337401468802</v>
+        <v>2976.364239076627</v>
       </c>
       <c r="H61" t="n">
-        <v>2.88136377060805e-07</v>
+        <v>2.556618735618976e-07</v>
       </c>
       <c r="I61" t="n">
-        <v>25761.09685015674</v>
+        <v>29073.71366881956</v>
       </c>
       <c r="J61" t="n">
-        <v>25678.89533669435</v>
+        <v>28815.14957100108</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.054206375328997e-05</v>
+        <v>3.406496304373198e-06</v>
       </c>
       <c r="B62" t="n">
-        <v>1019944203.70742</v>
+        <v>3300788932.341217</v>
       </c>
       <c r="C62" t="n">
-        <v>1.948109376214942e+70</v>
+        <v>8.874048406003807e+22</v>
       </c>
       <c r="D62" t="n">
-        <v>13.31926237889343</v>
+        <v>3.488300583870213</v>
       </c>
       <c r="E62" t="n">
-        <v>23068.0170125935</v>
+        <v>20873.59104497406</v>
       </c>
       <c r="F62" t="n">
-        <v>8.811631892950001e-05</v>
+        <v>8.850047713578944e-05</v>
       </c>
       <c r="G62" t="n">
-        <v>2346.644235618151</v>
+        <v>2127.616617352091</v>
       </c>
       <c r="H62" t="n">
-        <v>1.691026951877407e-07</v>
+        <v>1.89650011094742e-07</v>
       </c>
       <c r="I62" t="n">
-        <v>23023.74752997261</v>
+        <v>20828.86047513552</v>
       </c>
       <c r="J62" t="n">
-        <v>22848.6441522317</v>
+        <v>20656.82094596701</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3.69505691303149e-06</v>
+        <v>1.110167730644319e-05</v>
       </c>
       <c r="B63" t="n">
-        <v>8220931584.205828</v>
+        <v>2151552162.334291</v>
       </c>
       <c r="C63" t="n">
-        <v>8760470782.656313</v>
+        <v>1.453680587325648e+30</v>
       </c>
       <c r="D63" t="n">
-        <v>1.05980198019802</v>
+        <v>5.228740802071007</v>
       </c>
       <c r="E63" t="n">
-        <v>50896.86864893774</v>
+        <v>46672.80981556957</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0001682710577916133</v>
+        <v>0.0002142881736528437</v>
       </c>
       <c r="G63" t="n">
-        <v>5199.254306917597</v>
+        <v>4753.049349721923</v>
       </c>
       <c r="H63" t="n">
-        <v>4.024921126078104e-07</v>
+        <v>4.375411399742524e-07</v>
       </c>
       <c r="I63" t="n">
-        <v>50775.12704668904</v>
+        <v>46577.51162871961</v>
       </c>
       <c r="J63" t="n">
-        <v>50320.11507615202</v>
+        <v>46206.42639518439</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.335024891499276e-06</v>
+        <v>2.608066499420685e-06</v>
       </c>
       <c r="B64" t="n">
-        <v>7726326856.382698</v>
+        <v>5725197051.28875</v>
       </c>
       <c r="C64" t="n">
-        <v>8750237554.313671</v>
+        <v>2.421767692719088e+17</v>
       </c>
       <c r="D64" t="n">
-        <v>1.05980198019802</v>
+        <v>2.405653934485956</v>
       </c>
       <c r="E64" t="n">
-        <v>17309.15041548751</v>
+        <v>26776.56742590687</v>
       </c>
       <c r="F64" t="n">
-        <v>3.712575050959326e-05</v>
+        <v>2.086916645169204e-05</v>
       </c>
       <c r="G64" t="n">
-        <v>1791.934538774824</v>
+        <v>2896.841415923794</v>
       </c>
       <c r="H64" t="n">
-        <v>1.454204905663323e-07</v>
+        <v>1.898094686335797e-07</v>
       </c>
       <c r="I64" t="n">
-        <v>17241.35097412521</v>
+        <v>26533.0288999812</v>
       </c>
       <c r="J64" t="n">
-        <v>17020.76511933612</v>
+        <v>25936.80342389093</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3.365538668472491e-06</v>
+        <v>6.798719738023104e-06</v>
       </c>
       <c r="B65" t="n">
-        <v>2977364759.17032</v>
+        <v>3565685367.807933</v>
       </c>
       <c r="C65" t="n">
-        <v>700596168989033.9</v>
+        <v>5.937242820830379e+29</v>
       </c>
       <c r="D65" t="n">
-        <v>2.02562853876106</v>
+        <v>4.938198558128478</v>
       </c>
       <c r="E65" t="n">
-        <v>17577.70258707089</v>
+        <v>47076.04217725175</v>
       </c>
       <c r="F65" t="n">
-        <v>7.947030623381323e-05</v>
+        <v>8.909549281746078e-05</v>
       </c>
       <c r="G65" t="n">
-        <v>1811.958118353626</v>
+        <v>4841.759595737913</v>
       </c>
       <c r="H65" t="n">
-        <v>2.722088635325157e-07</v>
+        <v>2.821118760520655e-07</v>
       </c>
       <c r="I65" t="n">
-        <v>17517.49385413029</v>
+        <v>46926.98064612649</v>
       </c>
       <c r="J65" t="n">
-        <v>17313.71682140851</v>
+        <v>46411.00310969088</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2.513070804720795e-06</v>
+        <v>6.304332699115388e-06</v>
       </c>
       <c r="B66" t="n">
-        <v>6693162536.621108</v>
+        <v>3552960466.178642</v>
       </c>
       <c r="C66" t="n">
-        <v>27556901795.75782</v>
+        <v>2.40805628257263e+20</v>
       </c>
       <c r="D66" t="n">
-        <v>1.16170603491932</v>
+        <v>3.119360395351765</v>
       </c>
       <c r="E66" t="n">
-        <v>28297.77254247163</v>
+        <v>41134.31360723434</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0001712871572123859</v>
+        <v>8.24015379412926e-05</v>
       </c>
       <c r="G66" t="n">
-        <v>2869.140063984469</v>
+        <v>4285.301084368695</v>
       </c>
       <c r="H66" t="n">
-        <v>2.647379074595811e-07</v>
+        <v>3.825497582583737e-07</v>
       </c>
       <c r="I66" t="n">
-        <v>28254.03608720796</v>
+        <v>40943.3472476285</v>
       </c>
       <c r="J66" t="n">
-        <v>28071.65206375336</v>
+        <v>40353.56825834756</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>7.570669124544609e-06</v>
+        <v>4.009496853391559e-06</v>
       </c>
       <c r="B67" t="n">
-        <v>3129594917.374793</v>
+        <v>2550847795.600993</v>
       </c>
       <c r="C67" t="n">
-        <v>2.864278809734355e+24</v>
+        <v>1.279121342274326e+30</v>
       </c>
       <c r="D67" t="n">
-        <v>3.952750152172878</v>
+        <v>4.859951229990035</v>
       </c>
       <c r="E67" t="n">
-        <v>44714.56937047594</v>
+        <v>19788.51194774975</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0001228800591469725</v>
+        <v>0.000108162911246111</v>
       </c>
       <c r="G67" t="n">
-        <v>4596.173169774188</v>
+        <v>2006.638754134372</v>
       </c>
       <c r="H67" t="n">
-        <v>3.808139362824578e-07</v>
+        <v>1.687614019393641e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>44575.9957785575</v>
+        <v>19757.63688179486</v>
       </c>
       <c r="J67" t="n">
-        <v>44093.40005709772</v>
+        <v>19629.17553084892</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2.973231372652353e-06</v>
+        <v>3.549441119749793e-06</v>
       </c>
       <c r="B68" t="n">
-        <v>3790712782.693125</v>
+        <v>1915321495.486168</v>
       </c>
       <c r="C68" t="n">
-        <v>1.743513948931903e+26</v>
+        <v>2.258976981133836e+36</v>
       </c>
       <c r="D68" t="n">
-        <v>4.043148712981276</v>
+        <v>5.986692607138855</v>
       </c>
       <c r="E68" t="n">
-        <v>21346.61026757682</v>
+        <v>13541.65758685235</v>
       </c>
       <c r="F68" t="n">
-        <v>3.850096126931066e-05</v>
+        <v>2.95295772979468e-05</v>
       </c>
       <c r="G68" t="n">
-        <v>2207.892761675069</v>
+        <v>1405.1369076962</v>
       </c>
       <c r="H68" t="n">
-        <v>1.467572162718539e-07</v>
+        <v>1.235001020641366e-07</v>
       </c>
       <c r="I68" t="n">
-        <v>21265.24167322416</v>
+        <v>13485.02297684016</v>
       </c>
       <c r="J68" t="n">
-        <v>20998.34880149098</v>
+        <v>13304.37393445276</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3.424296239245128e-06</v>
+        <v>1.399720136497225e-06</v>
       </c>
       <c r="B69" t="n">
-        <v>4714256837.669841</v>
+        <v>8908697759.093161</v>
       </c>
       <c r="C69" t="n">
-        <v>992661457715044.6</v>
+        <v>10060786913.63093</v>
       </c>
       <c r="D69" t="n">
-        <v>2.018281940762387</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E69" t="n">
-        <v>28300.09311598074</v>
+        <v>20862.39491804246</v>
       </c>
       <c r="F69" t="n">
-        <v>8.88588187539755e-05</v>
+        <v>0.0001656680172062921</v>
       </c>
       <c r="G69" t="n">
-        <v>2909.563390714803</v>
+        <v>2103.519559910288</v>
       </c>
       <c r="H69" t="n">
-        <v>2.775444930478164e-07</v>
+        <v>1.524675608680292e-07</v>
       </c>
       <c r="I69" t="n">
-        <v>28211.69969473993</v>
+        <v>20843.19484236908</v>
       </c>
       <c r="J69" t="n">
-        <v>27904.54086234659</v>
+        <v>20753.09620949982</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5.690501643381666e-06</v>
+        <v>9.886996149550922e-06</v>
       </c>
       <c r="B70" t="n">
-        <v>2820191076.412663</v>
+        <v>1858022155.107461</v>
       </c>
       <c r="C70" t="n">
-        <v>5.194473532994498e+22</v>
+        <v>2.043794925646221e+42</v>
       </c>
       <c r="D70" t="n">
-        <v>3.562179566717059</v>
+        <v>7.617251385741232</v>
       </c>
       <c r="E70" t="n">
-        <v>29884.70630239716</v>
+        <v>37554.95025312097</v>
       </c>
       <c r="F70" t="n">
-        <v>0.000116036710950322</v>
+        <v>0.0001483270427515913</v>
       </c>
       <c r="G70" t="n">
-        <v>3060.69155474103</v>
+        <v>3817.85780685703</v>
       </c>
       <c r="H70" t="n">
-        <v>3.1157811981842e-07</v>
+        <v>2.736756229346753e-07</v>
       </c>
       <c r="I70" t="n">
-        <v>29804.46083072904</v>
+        <v>37485.65827362661</v>
       </c>
       <c r="J70" t="n">
-        <v>29513.69013776615</v>
+        <v>37208.88410436144</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2.859168422177762e-06</v>
+        <v>2.045807680394766e-06</v>
       </c>
       <c r="B71" t="n">
-        <v>7840759648.515244</v>
+        <v>10610391991.07631</v>
       </c>
       <c r="C71" t="n">
-        <v>8484482936.999005</v>
+        <v>11713653610.60887</v>
       </c>
       <c r="D71" t="n">
         <v>1.05980198019802</v>
       </c>
       <c r="E71" t="n">
-        <v>37571.86002731576</v>
+        <v>36339.07249594975</v>
       </c>
       <c r="F71" t="n">
-        <v>0.000117163994699924</v>
+        <v>0.0001448286782584842</v>
       </c>
       <c r="G71" t="n">
-        <v>3847.070959835989</v>
+        <v>3684.229821312211</v>
       </c>
       <c r="H71" t="n">
-        <v>3.114411403205524e-07</v>
+        <v>2.22844052108476e-07</v>
       </c>
       <c r="I71" t="n">
-        <v>37471.9878527553</v>
+        <v>36283.15852737505</v>
       </c>
       <c r="J71" t="n">
-        <v>37109.10524840251</v>
+        <v>36049.74468136064</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1.51426775676688e-06</v>
+        <v>8.541204139752655e-06</v>
       </c>
       <c r="B72" t="n">
-        <v>6974416495.09037</v>
+        <v>3789410022.1747</v>
       </c>
       <c r="C72" t="n">
-        <v>7839397413.170462</v>
+        <v>1.080191297461213e+21</v>
       </c>
       <c r="D72" t="n">
-        <v>1.05980198019802</v>
+        <v>3.296177838851641</v>
       </c>
       <c r="E72" t="n">
-        <v>17704.97750909996</v>
+        <v>59854.19589954857</v>
       </c>
       <c r="F72" t="n">
-        <v>5.622373036865022e-05</v>
+        <v>9.708693077834375e-05</v>
       </c>
       <c r="G72" t="n">
-        <v>1817.245117296985</v>
+        <v>6261.186624219298</v>
       </c>
       <c r="H72" t="n">
-        <v>1.64944909596795e-07</v>
+        <v>4.970110108443792e-07</v>
       </c>
       <c r="I72" t="n">
-        <v>17653.03599089219</v>
+        <v>59547.78808369918</v>
       </c>
       <c r="J72" t="n">
-        <v>17469.34836858116</v>
+        <v>58630.43145904878</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1.600500280431833e-05</v>
+        <v>1.282255617887248e-05</v>
       </c>
       <c r="B73" t="n">
-        <v>854169355.7347326</v>
+        <v>2265814731.563877</v>
       </c>
       <c r="C73" t="n">
-        <v>3.561932557288665e+61</v>
+        <v>7.429921397309086e+29</v>
       </c>
       <c r="D73" t="n">
-        <v>11.98043261721869</v>
+        <v>5.218714373657768</v>
       </c>
       <c r="E73" t="n">
-        <v>29141.06842615036</v>
+        <v>56872.62475427108</v>
       </c>
       <c r="F73" t="n">
-        <v>0.000114864317517476</v>
+        <v>0.0001241166200751542</v>
       </c>
       <c r="G73" t="n">
-        <v>2979.151584585367</v>
+        <v>5896.036632545985</v>
       </c>
       <c r="H73" t="n">
-        <v>2.848717290687902e-07</v>
+        <v>5.062451761007495e-07</v>
       </c>
       <c r="I73" t="n">
-        <v>29068.79649062777</v>
+        <v>56640.65346858343</v>
       </c>
       <c r="J73" t="n">
-        <v>28801.25669490906</v>
+        <v>55895.07882233625</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3.16619358367039e-06</v>
+        <v>4.435135066932549e-06</v>
       </c>
       <c r="B74" t="n">
-        <v>8757260543.5077</v>
+        <v>2345702607.913626</v>
       </c>
       <c r="C74" t="n">
-        <v>88949745852825.05</v>
+        <v>1.214397989519475e+38</v>
       </c>
       <c r="D74" t="n">
-        <v>1.774957467905896</v>
+        <v>6.382195761854057</v>
       </c>
       <c r="E74" t="n">
-        <v>48017.27036128903</v>
+        <v>20815.5006110513</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0001540383179258332</v>
+        <v>0.0001786002301399802</v>
       </c>
       <c r="G74" t="n">
-        <v>4879.024550909575</v>
+        <v>2096.794109931537</v>
       </c>
       <c r="H74" t="n">
-        <v>2.75520755739975e-07</v>
+        <v>1.453292310878487e-07</v>
       </c>
       <c r="I74" t="n">
-        <v>47931.38423375494</v>
+        <v>20798.56277902196</v>
       </c>
       <c r="J74" t="n">
-        <v>47585.68445142033</v>
+        <v>20717.10551669217</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>9.796923155011164e-07</v>
+        <v>5.107399630190671e-06</v>
       </c>
       <c r="B75" t="n">
-        <v>11467947022.03674</v>
+        <v>2566156959.055822</v>
       </c>
       <c r="C75" t="n">
-        <v>13230303616.81282</v>
+        <v>1.154159412785191e+42</v>
       </c>
       <c r="D75" t="n">
-        <v>1.05980198019802</v>
+        <v>7.18631755709253</v>
       </c>
       <c r="E75" t="n">
-        <v>18800.3522830329</v>
+        <v>26617.12952161649</v>
       </c>
       <c r="F75" t="n">
-        <v>9.625537718478863e-05</v>
+        <v>8.54328876024044e-05</v>
       </c>
       <c r="G75" t="n">
-        <v>1898.794217798666</v>
+        <v>2703.634586397697</v>
       </c>
       <c r="H75" t="n">
-        <v>1.067151167228372e-07</v>
+        <v>1.495063237749771e-07</v>
       </c>
       <c r="I75" t="n">
-        <v>18779.50896137137</v>
+        <v>26570.54992802088</v>
       </c>
       <c r="J75" t="n">
-        <v>18685.70021202434</v>
+        <v>26382.05293958833</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1.831916510505366e-05</v>
+        <v>2.355150008314258e-06</v>
       </c>
       <c r="B76" t="n">
-        <v>1703000447.185737</v>
+        <v>8932892121.907604</v>
       </c>
       <c r="C76" t="n">
-        <v>2.434935860043485e+38</v>
+        <v>9779033212.488623</v>
       </c>
       <c r="D76" t="n">
-        <v>7.172403776309888</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E76" t="n">
-        <v>63349.50354266095</v>
+        <v>35224.13582374471</v>
       </c>
       <c r="F76" t="n">
-        <v>0.000291447954890677</v>
+        <v>0.0001546913860540007</v>
       </c>
       <c r="G76" t="n">
-        <v>6440.048700270961</v>
+        <v>3574.98764547998</v>
       </c>
       <c r="H76" t="n">
-        <v>5.372434982397726e-07</v>
+        <v>2.565398381312104e-07</v>
       </c>
       <c r="I76" t="n">
-        <v>63232.72760265555</v>
+        <v>35165.72019807191</v>
       </c>
       <c r="J76" t="n">
-        <v>62766.17952832238</v>
+        <v>34926.20984206545</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>5.634533492435621e-06</v>
+        <v>1.79720219814648e-06</v>
       </c>
       <c r="B77" t="n">
-        <v>3707772854.610089</v>
+        <v>10434008715.14014</v>
       </c>
       <c r="C77" t="n">
-        <v>1.141317249246196e+18</v>
+        <v>11608525859.77732</v>
       </c>
       <c r="D77" t="n">
-        <v>2.657185694780225</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E77" t="n">
-        <v>37599.71887079034</v>
+        <v>31378.79667876631</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0001590219322262973</v>
+        <v>0.0001774815507563969</v>
       </c>
       <c r="G77" t="n">
-        <v>3841.623928584992</v>
+        <v>3169.029718955867</v>
       </c>
       <c r="H77" t="n">
-        <v>3.837045654256645e-07</v>
+        <v>1.95764159129533e-07</v>
       </c>
       <c r="I77" t="n">
-        <v>37508.99438022816</v>
+        <v>31344.18551090049</v>
       </c>
       <c r="J77" t="n">
-        <v>37170.69094406863</v>
+        <v>31188.23595542648</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3.462696029236128e-06</v>
+        <v>1.870259611548814e-06</v>
       </c>
       <c r="B78" t="n">
-        <v>6130846292.788325</v>
+        <v>13000216740.86377</v>
       </c>
       <c r="C78" t="n">
-        <v>42622166253982.91</v>
+        <v>14429178316.35742</v>
       </c>
       <c r="D78" t="n">
-        <v>1.750567409467439</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E78" t="n">
-        <v>36722.76951212377</v>
+        <v>40755.95258566954</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0001717927353971771</v>
+        <v>7.205023952347994e-05</v>
       </c>
       <c r="G78" t="n">
-        <v>3730.67004977405</v>
+        <v>4179.308991596299</v>
       </c>
       <c r="H78" t="n">
-        <v>3.035207451670794e-07</v>
+        <v>2.037220968160308e-07</v>
       </c>
       <c r="I78" t="n">
-        <v>36657.88829149969</v>
+        <v>40640.71510452581</v>
       </c>
       <c r="J78" t="n">
-        <v>36395.94371218011</v>
+        <v>40229.00741655332</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2.911774800229722e-06</v>
+        <v>6.482355621209123e-06</v>
       </c>
       <c r="B79" t="n">
-        <v>6382997185.019775</v>
+        <v>1977566520.14719</v>
       </c>
       <c r="C79" t="n">
-        <v>5.80527605865175e+17</v>
+        <v>6.017867976438455e+37</v>
       </c>
       <c r="D79" t="n">
-        <v>2.477234084605293</v>
+        <v>6.508258754230982</v>
       </c>
       <c r="E79" t="n">
-        <v>33184.46606906089</v>
+        <v>25705.19867382592</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0001157673745211715</v>
+        <v>0.0003236234075084104</v>
       </c>
       <c r="G79" t="n">
-        <v>3372.077734280526</v>
+        <v>2585.42657565991</v>
       </c>
       <c r="H79" t="n">
-        <v>2.078862506808633e-07</v>
+        <v>2.085250358477307e-07</v>
       </c>
       <c r="I79" t="n">
-        <v>33124.87592753374</v>
+        <v>25688.6356646289</v>
       </c>
       <c r="J79" t="n">
-        <v>32885.25295201225</v>
+        <v>25605.12021722161</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3.713232155980497e-06</v>
+        <v>4.970915240843809e-06</v>
       </c>
       <c r="B80" t="n">
-        <v>7301782639.441262</v>
+        <v>3424494951.347258</v>
       </c>
       <c r="C80" t="n">
-        <v>10811137216.06892</v>
+        <v>4.699375658853646e+28</v>
       </c>
       <c r="D80" t="n">
-        <v>1.085829217747275</v>
+        <v>4.634405932467148</v>
       </c>
       <c r="E80" t="n">
-        <v>45554.77307106254</v>
+        <v>32864.81070028093</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0001028182760947699</v>
+        <v>3.970765239276479e-05</v>
       </c>
       <c r="G80" t="n">
-        <v>4715.383300565923</v>
+        <v>3449.024791672007</v>
       </c>
       <c r="H80" t="n">
-        <v>4.010131949436764e-07</v>
+        <v>2.18208048877157e-07</v>
       </c>
       <c r="I80" t="n">
-        <v>45377.09974499624</v>
+        <v>32684.20656512103</v>
       </c>
       <c r="J80" t="n">
-        <v>44798.29619402991</v>
+        <v>32155.82346971353</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2.546121066885075e-06</v>
+        <v>3.609928967089435e-06</v>
       </c>
       <c r="B81" t="n">
-        <v>6639419195.683711</v>
+        <v>7151377793.093711</v>
       </c>
       <c r="C81" t="n">
-        <v>7234507947.546941</v>
+        <v>9.509756949872517e+21</v>
       </c>
       <c r="D81" t="n">
-        <v>1.05980198019802</v>
+        <v>3.261526985251812</v>
       </c>
       <c r="E81" t="n">
-        <v>28312.49760992711</v>
+        <v>47531.56612416225</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0001401636225906879</v>
+        <v>0.0001064710158427139</v>
       </c>
       <c r="G81" t="n">
-        <v>2881.669509040312</v>
+        <v>4838.244019739586</v>
       </c>
       <c r="H81" t="n">
-        <v>2.773417761311469e-07</v>
+        <v>2.11773714743965e-07</v>
       </c>
       <c r="I81" t="n">
-        <v>28256.475667652</v>
+        <v>47437.02456046962</v>
       </c>
       <c r="J81" t="n">
-        <v>28036.58785612242</v>
+        <v>47066.43293337614</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3.874100970396674e-06</v>
+        <v>2.849008969840443e-06</v>
       </c>
       <c r="B82" t="n">
-        <v>4071100378.712838</v>
+        <v>3749376433.010259</v>
       </c>
       <c r="C82" t="n">
-        <v>624497115329822.9</v>
+        <v>4.664043630126341e+19</v>
       </c>
       <c r="D82" t="n">
-        <v>2.003094875217167</v>
+        <v>2.856769064968423</v>
       </c>
       <c r="E82" t="n">
-        <v>27593.04644434669</v>
+        <v>19395.31742353888</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0001795686343292163</v>
+        <v>5.560026018811023e-05</v>
       </c>
       <c r="G82" t="n">
-        <v>2802.919642683216</v>
+        <v>1997.422350422929</v>
       </c>
       <c r="H82" t="n">
-        <v>3.153727591623157e-07</v>
+        <v>1.84393468725731e-07</v>
       </c>
       <c r="I82" t="n">
-        <v>27544.58533518163</v>
+        <v>19330.99452568438</v>
       </c>
       <c r="J82" t="n">
-        <v>27348.64708389356</v>
+        <v>19111.25849453102</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2.501046050180331e-06</v>
+        <v>8.242500096203821e-06</v>
       </c>
       <c r="B83" t="n">
-        <v>4730348126.287757</v>
+        <v>3922146547.077455</v>
       </c>
       <c r="C83" t="n">
-        <v>9.517074191837958e+17</v>
+        <v>8.944489091833796e+18</v>
       </c>
       <c r="D83" t="n">
-        <v>2.521001745278251</v>
+        <v>2.88014723758024</v>
       </c>
       <c r="E83" t="n">
-        <v>21155.01869259681</v>
+        <v>58699.20355880319</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0001194359875603416</v>
+        <v>0.0002190570531930158</v>
       </c>
       <c r="G83" t="n">
-        <v>2143.637904368012</v>
+        <v>5997.825183196284</v>
       </c>
       <c r="H83" t="n">
-        <v>1.764989716060948e-07</v>
+        <v>5.303584084867285e-07</v>
       </c>
       <c r="I83" t="n">
-        <v>21123.75643136533</v>
+        <v>58557.08708400768</v>
       </c>
       <c r="J83" t="n">
-        <v>20991.99695541976</v>
+        <v>58027.62342697538</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3.074923675332455e-06</v>
+        <v>1.323863036535314e-06</v>
       </c>
       <c r="B84" t="n">
-        <v>3841723886.193989</v>
+        <v>15176375033.50193</v>
       </c>
       <c r="C84" t="n">
-        <v>3.645835277061885e+17</v>
+        <v>17196215277.8832</v>
       </c>
       <c r="D84" t="n">
-        <v>2.486847343652018</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E84" t="n">
-        <v>21138.5079884886</v>
+        <v>33600.54888625658</v>
       </c>
       <c r="F84" t="n">
-        <v>6.071058263177232e-05</v>
+        <v>0.0002766790893580762</v>
       </c>
       <c r="G84" t="n">
-        <v>2182.469594964926</v>
+        <v>3375.816181618739</v>
       </c>
       <c r="H84" t="n">
-        <v>2.189730437805621e-07</v>
+        <v>1.442046612324936e-07</v>
       </c>
       <c r="I84" t="n">
-        <v>21062.26488169296</v>
+        <v>33583.03633848648</v>
       </c>
       <c r="J84" t="n">
-        <v>20808.06996285437</v>
+        <v>33485.99192373411</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>6.418406203147793e-06</v>
+        <v>2.568086311849477e-06</v>
       </c>
       <c r="B85" t="n">
-        <v>1852611649.778141</v>
+        <v>5010222515.153585</v>
       </c>
       <c r="C85" t="n">
-        <v>1.563426432931161e+31</v>
+        <v>1.55541929899787e+18</v>
       </c>
       <c r="D85" t="n">
-        <v>5.246048731931989</v>
+        <v>2.557516707052066</v>
       </c>
       <c r="E85" t="n">
-        <v>23233.98223388767</v>
+        <v>23049.19613202176</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0001582109994017015</v>
+        <v>9.974700551044669e-05</v>
       </c>
       <c r="G85" t="n">
-        <v>2356.732002846718</v>
+        <v>2342.248441451554</v>
       </c>
       <c r="H85" t="n">
-        <v>2.522057996673171e-07</v>
+        <v>1.794923449709753e-07</v>
       </c>
       <c r="I85" t="n">
-        <v>23196.94470115661</v>
+        <v>23007.71965618912</v>
       </c>
       <c r="J85" t="n">
-        <v>23043.63299209351</v>
+        <v>22841.02114380627</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.941253613188303e-06</v>
+        <v>7.664413358424158e-06</v>
       </c>
       <c r="B86" t="n">
-        <v>4830216837.317586</v>
+        <v>4086681065.964694</v>
       </c>
       <c r="C86" t="n">
-        <v>1.057385798173992e+17</v>
+        <v>1.091935876155669e+21</v>
       </c>
       <c r="D86" t="n">
-        <v>2.324705491966597</v>
+        <v>3.26977482503503</v>
       </c>
       <c r="E86" t="n">
-        <v>16659.93669286032</v>
+        <v>57748.44620478991</v>
       </c>
       <c r="F86" t="n">
-        <v>4.404057615481319e-05</v>
+        <v>0.0001466133114622527</v>
       </c>
       <c r="G86" t="n">
-        <v>1715.161490090487</v>
+        <v>5933.926440640052</v>
       </c>
       <c r="H86" t="n">
-        <v>1.444169257613078e-07</v>
+        <v>4.487569022789501e-07</v>
       </c>
       <c r="I86" t="n">
-        <v>16605.30578085537</v>
+        <v>57571.68862683317</v>
       </c>
       <c r="J86" t="n">
-        <v>16418.07471101205</v>
+        <v>56953.95962453196</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>7.754707633761841e-06</v>
+        <v>4.587891556554006e-06</v>
       </c>
       <c r="B87" t="n">
-        <v>1311136842.202267</v>
+        <v>3232218558.593748</v>
       </c>
       <c r="C87" t="n">
-        <v>5.383212962578583e+41</v>
+        <v>3.376198888610927e+23</v>
       </c>
       <c r="D87" t="n">
-        <v>7.397504403900562</v>
+        <v>3.657805078692776</v>
       </c>
       <c r="E87" t="n">
-        <v>20739.88056274877</v>
+        <v>27670.27921382385</v>
       </c>
       <c r="F87" t="n">
-        <v>7.659287028413497e-05</v>
+        <v>0.0001695046345685114</v>
       </c>
       <c r="G87" t="n">
-        <v>2127.793177801327</v>
+        <v>2803.158344541355</v>
       </c>
       <c r="H87" t="n">
-        <v>2.207817650438196e-07</v>
+        <v>2.459226750133515e-07</v>
       </c>
       <c r="I87" t="n">
-        <v>20680.09709438605</v>
+        <v>27630.13429920276</v>
       </c>
       <c r="J87" t="n">
-        <v>20467.64272350738</v>
+        <v>27460.20341045213</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3.87750638584191e-06</v>
+        <v>9.92382902342357e-06</v>
       </c>
       <c r="B88" t="n">
-        <v>5569395387.226421</v>
+        <v>2489523187.31364</v>
       </c>
       <c r="C88" t="n">
-        <v>9.927228256090504e+16</v>
+        <v>2.837697533033391e+36</v>
       </c>
       <c r="D88" t="n">
-        <v>2.38125484409768</v>
+        <v>6.427061658145814</v>
       </c>
       <c r="E88" t="n">
-        <v>38404.16851026173</v>
+        <v>49956.56792054175</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0001574423329273009</v>
+        <v>3.082018306449411e-05</v>
       </c>
       <c r="G88" t="n">
-        <v>3902.777793522904</v>
+        <v>5466.911113855975</v>
       </c>
       <c r="H88" t="n">
-        <v>2.840621112843597e-07</v>
+        <v>3.230393713854884e-07</v>
       </c>
       <c r="I88" t="n">
-        <v>38334.87857415425</v>
+        <v>49432.95200742864</v>
       </c>
       <c r="J88" t="n">
-        <v>38056.57583458409</v>
+        <v>48219.82747843143</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4.59425982324057e-06</v>
+        <v>6.968091249740581e-06</v>
       </c>
       <c r="B89" t="n">
-        <v>3488492916.28722</v>
+        <v>3100472548.505892</v>
       </c>
       <c r="C89" t="n">
-        <v>1.279553339155292e+16</v>
+        <v>1.412059337080039e+34</v>
       </c>
       <c r="D89" t="n">
-        <v>2.272689755987642</v>
+        <v>5.802758235334235</v>
       </c>
       <c r="E89" t="n">
-        <v>28433.27580887619</v>
+        <v>42724.95621086025</v>
       </c>
       <c r="F89" t="n">
-        <v>8.693542712821391e-05</v>
+        <v>0.0002875193388463503</v>
       </c>
       <c r="G89" t="n">
-        <v>2945.378508798684</v>
+        <v>4305.875626250329</v>
       </c>
       <c r="H89" t="n">
-        <v>3.466924171841665e-07</v>
+        <v>2.495912320908921e-07</v>
       </c>
       <c r="I89" t="n">
-        <v>28319.885888975</v>
+        <v>42687.86731623325</v>
       </c>
       <c r="J89" t="n">
-        <v>27952.95411207919</v>
+        <v>42511.89486629768</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2.372363745697104e-06</v>
+        <v>4.594405317875789e-06</v>
       </c>
       <c r="B90" t="n">
-        <v>9073395594.278711</v>
+        <v>2550683653.728129</v>
       </c>
       <c r="C90" t="n">
-        <v>9928520620.536858</v>
+        <v>5.614400073153928e+37</v>
       </c>
       <c r="D90" t="n">
-        <v>1.05980198019802</v>
+        <v>6.328246969846115</v>
       </c>
       <c r="E90" t="n">
-        <v>36041.56033453505</v>
+        <v>23472.4677747282</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0001510532898421412</v>
+        <v>5.212789167933043e-05</v>
       </c>
       <c r="G90" t="n">
-        <v>3659.648423001012</v>
+        <v>2408.747501543719</v>
       </c>
       <c r="H90" t="n">
-        <v>2.584148819230023e-07</v>
+        <v>1.517571382086255e-07</v>
       </c>
       <c r="I90" t="n">
-        <v>35979.9021239267</v>
+        <v>23404.13363687164</v>
       </c>
       <c r="J90" t="n">
-        <v>35728.99873047241</v>
+        <v>23161.95686613785</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>8.283163950902474e-06</v>
+        <v>4.370407984837527e-06</v>
       </c>
       <c r="B91" t="n">
-        <v>3046078180.466307</v>
+        <v>2640755852.553349</v>
       </c>
       <c r="C91" t="n">
-        <v>3.100592941055815e+32</v>
+        <v>8.057278009646429e+30</v>
       </c>
       <c r="D91" t="n">
-        <v>5.549986042931597</v>
+        <v>5.032384569148459</v>
       </c>
       <c r="E91" t="n">
-        <v>49617.54923479009</v>
+        <v>22444.38393780284</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0003644182241037601</v>
+        <v>8.150585913897968e-05</v>
       </c>
       <c r="G91" t="n">
-        <v>4999.638699267584</v>
+        <v>2288.628258897407</v>
       </c>
       <c r="H91" t="n">
-        <v>3.09154467144266e-07</v>
+        <v>1.783040906599146e-07</v>
       </c>
       <c r="I91" t="n">
-        <v>49575.45615058057</v>
+        <v>22395.2840876727</v>
       </c>
       <c r="J91" t="n">
-        <v>49374.77473712924</v>
+        <v>22207.44106305349</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.449677344004392e-06</v>
+        <v>5.211273622048677e-06</v>
       </c>
       <c r="B92" t="n">
-        <v>11898273333.25235</v>
+        <v>1662968311.435907</v>
       </c>
       <c r="C92" t="n">
-        <v>13408829687.99843</v>
+        <v>3.546951379905081e+60</v>
       </c>
       <c r="D92" t="n">
-        <v>1.059801980198021</v>
+        <v>10.72464433072561</v>
       </c>
       <c r="E92" t="n">
-        <v>28891.0144436495</v>
+        <v>18315.27625101465</v>
       </c>
       <c r="F92" t="n">
-        <v>7.639286559827887e-05</v>
+        <v>4.489271617271129e-05</v>
       </c>
       <c r="G92" t="n">
-        <v>2942.849170227523</v>
+        <v>1869.492163640048</v>
       </c>
       <c r="H92" t="n">
-        <v>1.579092583744013e-07</v>
+        <v>1.033946398916365e-07</v>
       </c>
       <c r="I92" t="n">
-        <v>28831.29474824664</v>
+        <v>18273.09343041623</v>
       </c>
       <c r="J92" t="n">
-        <v>28599.47591286322</v>
+        <v>18113.85839868793</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>5.665427378810072e-06</v>
+        <v>4.174676950520057e-06</v>
       </c>
       <c r="B93" t="n">
-        <v>5251747650.763853</v>
+        <v>4146405682.561856</v>
       </c>
       <c r="C93" t="n">
-        <v>40510610814001.7</v>
+        <v>2.053053385586421e+17</v>
       </c>
       <c r="D93" t="n">
-        <v>1.789351694462781</v>
+        <v>2.471165684454101</v>
       </c>
       <c r="E93" t="n">
-        <v>51635.86876864041</v>
+        <v>30876.25072137923</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0001506873484544192</v>
+        <v>0.000277626857068088</v>
       </c>
       <c r="G93" t="n">
-        <v>5314.981000107731</v>
+        <v>3117.50634349377</v>
       </c>
       <c r="H93" t="n">
-        <v>4.908986190155276e-07</v>
+        <v>2.985337798434441e-07</v>
       </c>
       <c r="I93" t="n">
-        <v>51467.65307614741</v>
+        <v>30843.04930876162</v>
       </c>
       <c r="J93" t="n">
-        <v>50890.06302556466</v>
+        <v>30692.60986443211</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.672810799545358e-06</v>
+        <v>3.488085860816901e-06</v>
       </c>
       <c r="B94" t="n">
-        <v>13080461630.93063</v>
+        <v>2885176410.875945</v>
       </c>
       <c r="C94" t="n">
-        <v>14615436418.64001</v>
+        <v>3.440244296992651e+24</v>
       </c>
       <c r="D94" t="n">
-        <v>1.05980198019802</v>
+        <v>3.792724898609005</v>
       </c>
       <c r="E94" t="n">
-        <v>36593.35050210881</v>
+        <v>18911.77389564573</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0003542759944693154</v>
+        <v>4.519668394516483e-05</v>
       </c>
       <c r="G94" t="n">
-        <v>3676.273982223849</v>
+        <v>1959.545345420223</v>
       </c>
       <c r="H94" t="n">
-        <v>1.82214555431513e-07</v>
+        <v>1.815450411318309e-07</v>
       </c>
       <c r="I94" t="n">
-        <v>36574.52946653885</v>
+        <v>18835.80950025056</v>
       </c>
       <c r="J94" t="n">
-        <v>36469.74328225415</v>
+        <v>18590.52060061644</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.650853435075035e-05</v>
+        <v>4.438984142041004e-06</v>
       </c>
       <c r="B95" t="n">
-        <v>1587590407.871537</v>
+        <v>4429462804.104851</v>
       </c>
       <c r="C95" t="n">
-        <v>6.343537923823074e+40</v>
+        <v>5.042411596114895e+23</v>
       </c>
       <c r="D95" t="n">
-        <v>7.62423610457834</v>
+        <v>3.657670506634589</v>
       </c>
       <c r="E95" t="n">
-        <v>53634.59559851291</v>
+        <v>36700.49122378264</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0001648585961312079</v>
+        <v>0.000134314224502145</v>
       </c>
       <c r="G95" t="n">
-        <v>5497.141534347269</v>
+        <v>3728.565076902693</v>
       </c>
       <c r="H95" t="n">
-        <v>4.56559021643975e-07</v>
+        <v>2.379479217632793e-07</v>
       </c>
       <c r="I95" t="n">
-        <v>53486.06007129517</v>
+        <v>36635.47349653327</v>
       </c>
       <c r="J95" t="n">
-        <v>52952.35313394345</v>
+        <v>36373.15260302457</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4.396270003623415e-06</v>
+        <v>1.586835863660611e-06</v>
       </c>
       <c r="B96" t="n">
-        <v>4607774361.194345</v>
+        <v>4596635459.601551</v>
       </c>
       <c r="C96" t="n">
-        <v>4.016700826277014e+33</v>
+        <v>1537208197109.66</v>
       </c>
       <c r="D96" t="n">
-        <v>5.490675828648457</v>
+        <v>1.482111049816301</v>
       </c>
       <c r="E96" t="n">
-        <v>39790.25543809297</v>
+        <v>12452.80251508037</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0001556691235089003</v>
+        <v>0.0001470155337119163</v>
       </c>
       <c r="G96" t="n">
-        <v>4017.14663063836</v>
+        <v>1256.787874911181</v>
       </c>
       <c r="H96" t="n">
-        <v>1.657099237140119e-07</v>
+        <v>1.509521334495018e-07</v>
       </c>
       <c r="I96" t="n">
-        <v>39747.89867494957</v>
+        <v>12440.01626685465</v>
       </c>
       <c r="J96" t="n">
-        <v>39555.54839757518</v>
+        <v>12381.49176760674</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4.296466600406641e-06</v>
+        <v>8.562198591445636e-06</v>
       </c>
       <c r="B97" t="n">
-        <v>2895462284.521056</v>
+        <v>1809680269.154519</v>
       </c>
       <c r="C97" t="n">
-        <v>3.886741380762722e+16</v>
+        <v>2.775534913732903e+38</v>
       </c>
       <c r="D97" t="n">
-        <v>2.369879590570332</v>
+        <v>6.777319058990563</v>
       </c>
       <c r="E97" t="n">
-        <v>22115.52631680088</v>
+        <v>31242.69365018229</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0001629978688949413</v>
+        <v>0.0001942196187606583</v>
       </c>
       <c r="G97" t="n">
-        <v>2250.106503860449</v>
+        <v>3162.642404394491</v>
       </c>
       <c r="H97" t="n">
-        <v>3.157258496450151e-07</v>
+        <v>2.650503101725254e-07</v>
       </c>
       <c r="I97" t="n">
-        <v>22072.68868104492</v>
+        <v>31200.05693976422</v>
       </c>
       <c r="J97" t="n">
-        <v>21903.645802928</v>
+        <v>31016.98340547877</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1.174533067215058e-06</v>
+        <v>5.633980028832379e-06</v>
       </c>
       <c r="B98" t="n">
-        <v>11691098010.73275</v>
+        <v>1832699184.111412</v>
       </c>
       <c r="C98" t="n">
-        <v>13342232380.61613</v>
+        <v>4.118316882710075e+35</v>
       </c>
       <c r="D98" t="n">
-        <v>1.05980198019802</v>
+        <v>6.039935927334142</v>
       </c>
       <c r="E98" t="n">
-        <v>22976.20799492548</v>
+        <v>20618.42819347581</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0001238256510444066</v>
+        <v>3.493998086849626e-05</v>
       </c>
       <c r="G98" t="n">
-        <v>2318.986234215168</v>
+        <v>2165.096998607803</v>
       </c>
       <c r="H98" t="n">
-        <v>1.279385694666542e-07</v>
+        <v>1.944161048602342e-07</v>
       </c>
       <c r="I98" t="n">
-        <v>22952.46862301146</v>
+        <v>20503.70132763112</v>
       </c>
       <c r="J98" t="n">
-        <v>22843.95804560229</v>
+        <v>20169.42675859095</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>7.369974554339542e-06</v>
+        <v>1.839246122242665e-06</v>
       </c>
       <c r="B99" t="n">
-        <v>4248255385.139149</v>
+        <v>6978118840.349827</v>
       </c>
       <c r="C99" t="n">
-        <v>7.157605119158429e+20</v>
+        <v>7752890562.662872</v>
       </c>
       <c r="D99" t="n">
-        <v>3.223592524325189</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E99" t="n">
-        <v>57533.37114219125</v>
+        <v>21503.85278670231</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0003079485037515945</v>
+        <v>8.463866592227069e-05</v>
       </c>
       <c r="G99" t="n">
-        <v>5826.68824397404</v>
+        <v>2196.195888124253</v>
       </c>
       <c r="H99" t="n">
-        <v>4.362370763277748e-07</v>
+        <v>2.003438850255308e-07</v>
       </c>
       <c r="I99" t="n">
-        <v>57451.86988690801</v>
+        <v>21452.95210953117</v>
       </c>
       <c r="J99" t="n">
-        <v>57104.94491781537</v>
+        <v>21262.18437416603</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>3.459570503319064e-06</v>
+        <v>2.701727851504217e-06</v>
       </c>
       <c r="B100" t="n">
-        <v>4783855326.322792</v>
+        <v>9053369834.412766</v>
       </c>
       <c r="C100" t="n">
-        <v>2.751140500639392e+16</v>
+        <v>9829886848.8634</v>
       </c>
       <c r="D100" t="n">
-        <v>2.27968093584804</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E100" t="n">
-        <v>29408.57794428983</v>
+        <v>41070.43775199963</v>
       </c>
       <c r="F100" t="n">
-        <v>4.919716580326226e-05</v>
+        <v>6.507059649218134e-05</v>
       </c>
       <c r="G100" t="n">
-        <v>3081.039741572001</v>
+        <v>4274.216297617553</v>
       </c>
       <c r="H100" t="n">
-        <v>2.605647353519972e-07</v>
+        <v>2.942915836582206e-07</v>
       </c>
       <c r="I100" t="n">
-        <v>29252.82022524203</v>
+        <v>40884.69050486897</v>
       </c>
       <c r="J100" t="n">
-        <v>28791.60154963595</v>
+        <v>40306.32258426701</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>5.383542154259929e-06</v>
+        <v>4.416349625033305e-06</v>
       </c>
       <c r="B101" t="n">
-        <v>2619270891.590416</v>
+        <v>3288413395.827895</v>
       </c>
       <c r="C101" t="n">
-        <v>5.233551124573665e+35</v>
+        <v>6.466147251216041e+24</v>
       </c>
       <c r="D101" t="n">
-        <v>6.011474549664106</v>
+        <v>3.886130076185295</v>
       </c>
       <c r="E101" t="n">
-        <v>28029.58317913961</v>
+        <v>27394.12879523556</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0001165361771052047</v>
+        <v>4.764157270051151e-05</v>
       </c>
       <c r="G101" t="n">
-        <v>2843.350697269994</v>
+        <v>2856.007827147475</v>
       </c>
       <c r="H101" t="n">
-        <v>1.865954522346889e-07</v>
+        <v>2.253024002680702e-07</v>
       </c>
       <c r="I101" t="n">
-        <v>27984.70275763291</v>
+        <v>27264.5788534312</v>
       </c>
       <c r="J101" t="n">
-        <v>27799.12298048521</v>
+        <v>26866.79641461041</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2.374979332712718e-06</v>
+        <v>1.028193293135666e-05</v>
       </c>
       <c r="B102" t="n">
-        <v>7437742614.468287</v>
+        <v>1960219300.336402</v>
       </c>
       <c r="C102" t="n">
-        <v>8138178712.949842</v>
+        <v>1.886027671688805e+36</v>
       </c>
       <c r="D102" t="n">
-        <v>1.05980198019802</v>
+        <v>6.429048326641047</v>
       </c>
       <c r="E102" t="n">
-        <v>29644.87417213831</v>
+        <v>40384.62553674074</v>
       </c>
       <c r="F102" t="n">
-        <v>6.470771184136293e-05</v>
+        <v>0.0002426231781610949</v>
       </c>
       <c r="G102" t="n">
-        <v>3071.154926628745</v>
+        <v>4088.587110415034</v>
       </c>
       <c r="H102" t="n">
-        <v>2.586997904287173e-07</v>
+        <v>3.345987103528314e-07</v>
       </c>
       <c r="I102" t="n">
-        <v>29526.35471723285</v>
+        <v>40328.93158480633</v>
       </c>
       <c r="J102" t="n">
-        <v>29143.11455486115</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>5.195234586147919e-06</v>
-      </c>
-      <c r="B103" t="n">
-        <v>2366408027.384725</v>
-      </c>
-      <c r="C103" t="n">
-        <v>1.058289245531574e+29</v>
-      </c>
-      <c r="D103" t="n">
-        <v>4.744095250281443</v>
-      </c>
-      <c r="E103" t="n">
-        <v>23754.15544375683</v>
-      </c>
-      <c r="F103" t="n">
-        <v>6.784479061647594e-05</v>
-      </c>
-      <c r="G103" t="n">
-        <v>2445.812147454671</v>
-      </c>
-      <c r="H103" t="n">
-        <v>2.234015109629215e-07</v>
-      </c>
-      <c r="I103" t="n">
-        <v>23675.93699589129</v>
-      </c>
-      <c r="J103" t="n">
-        <v>23408.18471763727</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>9.56199537096044e-06</v>
-      </c>
-      <c r="B104" t="n">
-        <v>1901041819.776649</v>
-      </c>
-      <c r="C104" t="n">
-        <v>1.225526591843707e+43</v>
-      </c>
-      <c r="D104" t="n">
-        <v>7.750748395390957</v>
-      </c>
-      <c r="E104" t="n">
-        <v>37216.72650229133</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0.0001813850833400643</v>
-      </c>
-      <c r="G104" t="n">
-        <v>3769.737496674158</v>
-      </c>
-      <c r="H104" t="n">
-        <v>2.602845846035657e-07</v>
-      </c>
-      <c r="I104" t="n">
-        <v>37163.32111735242</v>
-      </c>
-      <c r="J104" t="n">
-        <v>36936.67443594321</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>8.051318958552742e-06</v>
-      </c>
-      <c r="B105" t="n">
-        <v>2851420022.644676</v>
-      </c>
-      <c r="C105" t="n">
-        <v>3.145174647434313e+31</v>
-      </c>
-      <c r="D105" t="n">
-        <v>5.350431412307272</v>
-      </c>
-      <c r="E105" t="n">
-        <v>44996.03116196772</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.000144451315733652</v>
-      </c>
-      <c r="G105" t="n">
-        <v>4586.720394445182</v>
-      </c>
-      <c r="H105" t="n">
-        <v>3.107485295220174e-07</v>
-      </c>
-      <c r="I105" t="n">
-        <v>44899.23418613616</v>
-      </c>
-      <c r="J105" t="n">
-        <v>44527.30913040797</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>3.386788105182919e-06</v>
-      </c>
-      <c r="B106" t="n">
-        <v>1674687274.306981</v>
-      </c>
-      <c r="C106" t="n">
-        <v>3.247229468325986e+40</v>
-      </c>
-      <c r="D106" t="n">
-        <v>6.736267699971765</v>
-      </c>
-      <c r="E106" t="n">
-        <v>11431.43014174797</v>
-      </c>
-      <c r="F106" t="n">
-        <v>6.351463917543211e-05</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1160.223809434483</v>
-      </c>
-      <c r="H106" t="n">
-        <v>1.054481211785803e-07</v>
-      </c>
-      <c r="I106" t="n">
-        <v>11412.45148034832</v>
-      </c>
-      <c r="J106" t="n">
-        <v>11334.65758039253</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>1.294517420413393e-05</v>
-      </c>
-      <c r="B107" t="n">
-        <v>2104653956.37481</v>
-      </c>
-      <c r="C107" t="n">
-        <v>3.184676665077729e+52</v>
-      </c>
-      <c r="D107" t="n">
-        <v>9.845004894027927</v>
-      </c>
-      <c r="E107" t="n">
-        <v>57071.5284855529</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0.0004166720461318112</v>
-      </c>
-      <c r="G107" t="n">
-        <v>5741.580499984439</v>
-      </c>
-      <c r="H107" t="n">
-        <v>2.792799442531116e-07</v>
-      </c>
-      <c r="I107" t="n">
-        <v>57033.2755395205</v>
-      </c>
-      <c r="J107" t="n">
-        <v>56841.90095330483</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>1.439498997154753e-05</v>
-      </c>
-      <c r="B108" t="n">
-        <v>2100008428.771138</v>
-      </c>
-      <c r="C108" t="n">
-        <v>2.169887095065105e+42</v>
-      </c>
-      <c r="D108" t="n">
-        <v>7.834011623533038</v>
-      </c>
-      <c r="E108" t="n">
-        <v>61949.37640721706</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.0003191488641259197</v>
-      </c>
-      <c r="G108" t="n">
-        <v>6262.68925893747</v>
-      </c>
-      <c r="H108" t="n">
-        <v>3.878229693390446e-07</v>
-      </c>
-      <c r="I108" t="n">
-        <v>61874.09683142178</v>
-      </c>
-      <c r="J108" t="n">
-        <v>61542.16746510283</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>1.959135172404058e-06</v>
-      </c>
-      <c r="B109" t="n">
-        <v>4610131963.849661</v>
-      </c>
-      <c r="C109" t="n">
-        <v>1.899400233726261e+17</v>
-      </c>
-      <c r="D109" t="n">
-        <v>2.373326305303982</v>
-      </c>
-      <c r="E109" t="n">
-        <v>16046.97289548041</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.0001187095167437088</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1622.196060619272</v>
-      </c>
-      <c r="H109" t="n">
-        <v>1.438326420402401e-07</v>
-      </c>
-      <c r="I109" t="n">
-        <v>16027.52981651238</v>
-      </c>
-      <c r="J109" t="n">
-        <v>15941.74310294031</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>3.521244887806283e-06</v>
-      </c>
-      <c r="B110" t="n">
-        <v>3913966522.04185</v>
-      </c>
-      <c r="C110" t="n">
-        <v>7.081732359869771e+22</v>
-      </c>
-      <c r="D110" t="n">
-        <v>3.463501501474009</v>
-      </c>
-      <c r="E110" t="n">
-        <v>25600.02961443891</v>
-      </c>
-      <c r="F110" t="n">
-        <v>5.483762434726297e-05</v>
-      </c>
-      <c r="G110" t="n">
-        <v>2642.833616480225</v>
-      </c>
-      <c r="H110" t="n">
-        <v>1.971454466494631e-07</v>
-      </c>
-      <c r="I110" t="n">
-        <v>25507.99555328743</v>
-      </c>
-      <c r="J110" t="n">
-        <v>25200.85948024528</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>1.699410958702172e-06</v>
-      </c>
-      <c r="B111" t="n">
-        <v>6918016278.19268</v>
-      </c>
-      <c r="C111" t="n">
-        <v>692550556138.2568</v>
-      </c>
-      <c r="D111" t="n">
-        <v>1.39470032858333</v>
-      </c>
-      <c r="E111" t="n">
-        <v>20066.2489940154</v>
-      </c>
-      <c r="F111" t="n">
-        <v>3.410043678457838e-05</v>
-      </c>
-      <c r="G111" t="n">
-        <v>2094.615431126644</v>
-      </c>
-      <c r="H111" t="n">
-        <v>1.661449623211267e-07</v>
-      </c>
-      <c r="I111" t="n">
-        <v>19968.48173654306</v>
-      </c>
-      <c r="J111" t="n">
-        <v>19671.10698996836</v>
+        <v>40090.37409814701</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,3234 +482,3074 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.560426566781149e-06</v>
+        <v>9.439992912664949e-06</v>
       </c>
       <c r="B2" t="n">
-        <v>6964202207.055857</v>
+        <v>3048758098.289415</v>
       </c>
       <c r="C2" t="n">
-        <v>1.851382902238399e+16</v>
+        <v>3.119819472481836e+26</v>
       </c>
       <c r="D2" t="n">
-        <v>2.246000774221471</v>
+        <v>4.41378296282147</v>
       </c>
       <c r="E2" t="n">
-        <v>56243.93485847223</v>
+        <v>55017.43463385406</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001035838266851309</v>
+        <v>0.0002283555517872283</v>
       </c>
       <c r="G2" t="n">
-        <v>5793.810858016026</v>
+        <v>5595.500510072858</v>
       </c>
       <c r="H2" t="n">
-        <v>3.466823135950804e-07</v>
+        <v>4.323870196327335e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>56055.69333384022</v>
+        <v>54913.26013753466</v>
       </c>
       <c r="J2" t="n">
-        <v>55414.32099554676</v>
+        <v>54499.82863648152</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.352488537581947e-05</v>
+        <v>1.183779413098444e-05</v>
       </c>
       <c r="B3" t="n">
-        <v>1573269896.403693</v>
+        <v>1426983397.775857</v>
       </c>
       <c r="C3" t="n">
-        <v>3.587364184016141e+30</v>
+        <v>7.689774145887341e+51</v>
       </c>
       <c r="D3" t="n">
-        <v>5.410807050454403</v>
+        <v>9.684544163682361</v>
       </c>
       <c r="E3" t="n">
-        <v>41981.94544725444</v>
+        <v>35597.5972875804</v>
       </c>
       <c r="F3" t="n">
-        <v>7.049265139175086e-05</v>
+        <v>3.207821276779866e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>4475.135263305197</v>
+        <v>3818.957052406633</v>
       </c>
       <c r="H3" t="n">
-        <v>5.166846875892542e-07</v>
+        <v>2.595239732262746e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>41674.23353772138</v>
+        <v>35309.60026130419</v>
       </c>
       <c r="J3" t="n">
-        <v>40858.53790813831</v>
+        <v>34572.9778215911</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.589438315188088e-06</v>
+        <v>2.494972373944577e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>6469454847.742629</v>
+        <v>4169184618.44648</v>
       </c>
       <c r="C4" t="n">
-        <v>43280423954.9711</v>
+        <v>2.064354590635987e+17</v>
       </c>
       <c r="D4" t="n">
-        <v>1.199403727542084</v>
+        <v>2.412966849597873</v>
       </c>
       <c r="E4" t="n">
-        <v>28295.66549598575</v>
+        <v>18512.13787392905</v>
       </c>
       <c r="F4" t="n">
-        <v>7.254195448066391e-05</v>
+        <v>0.0001488278303931308</v>
       </c>
       <c r="G4" t="n">
-        <v>2924.161945548653</v>
+        <v>1871.501093194444</v>
       </c>
       <c r="H4" t="n">
-        <v>2.694615661997333e-07</v>
+        <v>1.812213831167308e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>28190.55950048567</v>
+        <v>18489.59642303845</v>
       </c>
       <c r="J4" t="n">
-        <v>27843.15688745091</v>
+        <v>18390.25041329118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5.203192417143199e-06</v>
+        <v>3.245194087591309e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>2872397540.100661</v>
+        <v>2249591865.546821</v>
       </c>
       <c r="C5" t="n">
-        <v>2.368987907963854e+32</v>
+        <v>3.870253089792063e+36</v>
       </c>
       <c r="D5" t="n">
-        <v>5.359645552717599</v>
+        <v>5.981226653131942</v>
       </c>
       <c r="E5" t="n">
-        <v>29263.76569332258</v>
+        <v>14545.9196411555</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002125363170761006</v>
+        <v>2.464682172837094e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2951.22333490591</v>
+        <v>1514.618165803905</v>
       </c>
       <c r="H5" t="n">
-        <v>2.005073479917156e-07</v>
+        <v>1.130103171001396e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>29236.15817601853</v>
+        <v>14479.22386150178</v>
       </c>
       <c r="J5" t="n">
-        <v>29107.46288958696</v>
+        <v>14272.43854476488</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.175386317926847e-06</v>
+        <v>4.003758908677272e-06</v>
       </c>
       <c r="B6" t="n">
-        <v>8568270870.115607</v>
+        <v>4496482501.823675</v>
       </c>
       <c r="C6" t="n">
-        <v>9424517431.870955</v>
+        <v>1.070750985857365e+17</v>
       </c>
       <c r="D6" t="n">
-        <v>1.05980198019802</v>
+        <v>2.407882160973281</v>
       </c>
       <c r="E6" t="n">
-        <v>31243.39077144613</v>
+        <v>32088.19102511141</v>
       </c>
       <c r="F6" t="n">
-        <v>8.448969910208129e-05</v>
+        <v>9.847561773147152e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3203.20139577698</v>
+        <v>3294.220579681041</v>
       </c>
       <c r="H6" t="n">
-        <v>2.369586870915514e-07</v>
+        <v>2.912100457733533e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>31155.76597296573</v>
+        <v>31993.30049492263</v>
       </c>
       <c r="J6" t="n">
-        <v>30842.00867161845</v>
+        <v>31658.46867783114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.411639216528512e-06</v>
+        <v>6.302452752710277e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>3751740567.747574</v>
+        <v>1366598483.411706</v>
       </c>
       <c r="C7" t="n">
-        <v>6.096338641120691e+25</v>
+        <v>1.471748540414189e+38</v>
       </c>
       <c r="D7" t="n">
-        <v>3.994045071228693</v>
+        <v>6.6005409160586</v>
       </c>
       <c r="E7" t="n">
-        <v>24141.36014202307</v>
+        <v>17319.32481344121</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001429952815182308</v>
+        <v>0.0001126409879957645</v>
       </c>
       <c r="G7" t="n">
-        <v>2439.986003495022</v>
+        <v>1759.616192871323</v>
       </c>
       <c r="H7" t="n">
-        <v>1.701287966842386e-07</v>
+        <v>2.000540277280799e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>24112.63793169783</v>
+        <v>17288.56513396654</v>
       </c>
       <c r="J7" t="n">
-        <v>23985.38857709709</v>
+        <v>17164.53812702717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.078508718230297e-05</v>
+        <v>1.664859349641697e-05</v>
       </c>
       <c r="B8" t="n">
-        <v>2124920890.324209</v>
+        <v>855351733.1281062</v>
       </c>
       <c r="C8" t="n">
-        <v>9.61497288575889e+33</v>
+        <v>9.971755078072989e+70</v>
       </c>
       <c r="D8" t="n">
-        <v>5.98485417336918</v>
+        <v>13.99471039824628</v>
       </c>
       <c r="E8" t="n">
-        <v>45529.03559545665</v>
+        <v>30775.7063394353</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002369557063500751</v>
+        <v>4.059653647080123e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4617.814698706182</v>
+        <v>3251.136720577002</v>
       </c>
       <c r="H8" t="n">
-        <v>3.753664405485725e-07</v>
+        <v>2.543919215730085e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>45456.91210750051</v>
+        <v>30582.85513206476</v>
       </c>
       <c r="J8" t="n">
-        <v>45157.91591760625</v>
+        <v>30042.90284163069</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.894436182726925e-06</v>
+        <v>4.808372188634755e-06</v>
       </c>
       <c r="B9" t="n">
-        <v>14571876833.80109</v>
+        <v>2557284835.699354</v>
       </c>
       <c r="C9" t="n">
-        <v>16161174470.75793</v>
+        <v>1.724852951766933e+31</v>
       </c>
       <c r="D9" t="n">
-        <v>1.05980198019802</v>
+        <v>5.128155102449199</v>
       </c>
       <c r="E9" t="n">
-        <v>46204.32455772989</v>
+        <v>23963.26616388398</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001550727340122957</v>
+        <v>0.000103179750116592</v>
       </c>
       <c r="G9" t="n">
-        <v>4675.768220173491</v>
+        <v>2436.640715871029</v>
       </c>
       <c r="H9" t="n">
-        <v>2.063555824261638e-07</v>
+        <v>1.928692154782934e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>46142.84037506267</v>
+        <v>23918.47272001439</v>
       </c>
       <c r="J9" t="n">
-        <v>45877.29671868407</v>
+        <v>23740.13212440407</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8.619769071005988e-06</v>
+        <v>1.628432640769274e-06</v>
       </c>
       <c r="B10" t="n">
-        <v>3056133245.937701</v>
+        <v>9950675847.335356</v>
       </c>
       <c r="C10" t="n">
-        <v>3.331303052513671e+28</v>
+        <v>11136266229.4472</v>
       </c>
       <c r="D10" t="n">
-        <v>4.785377521186479</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E10" t="n">
-        <v>50925.7842164287</v>
+        <v>27124.98508320027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0001363444005832036</v>
+        <v>0.0001207813797067774</v>
       </c>
       <c r="G10" t="n">
-        <v>5216.226668762961</v>
+        <v>2748.350895038207</v>
       </c>
       <c r="H10" t="n">
-        <v>3.678282119788031e-07</v>
+        <v>1.773805679450316e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>50788.39727518415</v>
+        <v>27085.14909795784</v>
       </c>
       <c r="J10" t="n">
-        <v>50291.20746843443</v>
+        <v>26917.00814861999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.847295808092264e-06</v>
+        <v>6.469080484160136e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>4141250178.452193</v>
+        <v>6462820141.110523</v>
       </c>
       <c r="C11" t="n">
-        <v>4.299697471180586e+22</v>
+        <v>1.517044951506999e+22</v>
       </c>
       <c r="D11" t="n">
-        <v>3.436641189057665</v>
+        <v>3.418313088655944</v>
       </c>
       <c r="E11" t="n">
-        <v>29509.13653792693</v>
+        <v>77389.26438116365</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001314572251611558</v>
+        <v>0.0002137277379976955</v>
       </c>
       <c r="G11" t="n">
-        <v>2994.698157816682</v>
+        <v>7858.181454718791</v>
       </c>
       <c r="H11" t="n">
-        <v>2.16723439258792e-07</v>
+        <v>3.65943736901254e-07</v>
       </c>
       <c r="I11" t="n">
-        <v>29460.48708901138</v>
+        <v>77256.75880716096</v>
       </c>
       <c r="J11" t="n">
-        <v>29260.73366148319</v>
+        <v>76717.66934483001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.192006547311992e-05</v>
+        <v>1.795456062710636e-06</v>
       </c>
       <c r="B12" t="n">
-        <v>1571847403.433163</v>
+        <v>2428573741.665152</v>
       </c>
       <c r="C12" t="n">
-        <v>6.946518563910915e+29</v>
+        <v>7.666565624872392e+23</v>
       </c>
       <c r="D12" t="n">
-        <v>5.217881943904674</v>
+        <v>3.553602253066118</v>
       </c>
       <c r="E12" t="n">
-        <v>36715.95115705371</v>
+        <v>8104.603594945501</v>
       </c>
       <c r="F12" t="n">
-        <v>9.127388326542004e-05</v>
+        <v>8.882183312661844e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>3841.998614648212</v>
+        <v>818.5490945133788</v>
       </c>
       <c r="H12" t="n">
-        <v>4.706821658459907e-07</v>
+        <v>9.84976917585078e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>36526.61393600611</v>
+        <v>8095.616111591245</v>
       </c>
       <c r="J12" t="n">
-        <v>35961.09110659748</v>
+        <v>8055.16858924754</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3.572366718127481e-06</v>
+        <v>2.661993907200325e-06</v>
       </c>
       <c r="B13" t="n">
-        <v>3074063120.243857</v>
+        <v>3639870202.047464</v>
       </c>
       <c r="C13" t="n">
-        <v>2.014701260913252e+30</v>
+        <v>2.762564940499918e+20</v>
       </c>
       <c r="D13" t="n">
-        <v>4.845840627477699</v>
+        <v>2.98682733442818</v>
       </c>
       <c r="E13" t="n">
-        <v>21224.38921497412</v>
+        <v>17642.08224879312</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0001778700342902951</v>
+        <v>0.0001524265563757594</v>
       </c>
       <c r="G13" t="n">
-        <v>2138.62859159873</v>
+        <v>1781.585169005541</v>
       </c>
       <c r="H13" t="n">
-        <v>1.50751998190123e-07</v>
+        <v>1.668175317114788e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>21206.40069263932</v>
+        <v>17622.77453309731</v>
       </c>
       <c r="J13" t="n">
-        <v>21120.62212874688</v>
+        <v>17535.6280091382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9.579946479944955e-06</v>
+        <v>1.406038420674774e-05</v>
       </c>
       <c r="B14" t="n">
-        <v>2091067776.725971</v>
+        <v>1720130045.971</v>
       </c>
       <c r="C14" t="n">
-        <v>2.090863093981906e+39</v>
+        <v>1.404754887238453e+36</v>
       </c>
       <c r="D14" t="n">
-        <v>6.994997546082007</v>
+        <v>6.565952287123869</v>
       </c>
       <c r="E14" t="n">
-        <v>40591.0346721908</v>
+        <v>48906.07137225179</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001109500703427731</v>
+        <v>5.639010516143903e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>4153.85168947879</v>
+        <v>5240.712184588895</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8775708203285e-07</v>
+        <v>4.485346407565526e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>40485.75886968001</v>
+        <v>48517.06576406988</v>
       </c>
       <c r="J14" t="n">
-        <v>40100.69045602215</v>
+        <v>47515.87970180038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.125262376223038e-05</v>
+        <v>1.930085628595315e-06</v>
       </c>
       <c r="B15" t="n">
-        <v>1151074464.082067</v>
+        <v>9825390570.862261</v>
       </c>
       <c r="C15" t="n">
-        <v>2.170040278085731e+45</v>
+        <v>10884865263.65736</v>
       </c>
       <c r="D15" t="n">
-        <v>8.344022140939265</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E15" t="n">
-        <v>26796.95875364222</v>
+        <v>31782.50119576448</v>
       </c>
       <c r="F15" t="n">
-        <v>7.025422344411424e-05</v>
+        <v>7.930713202852761e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>2777.605520375386</v>
+        <v>3254.078390970563</v>
       </c>
       <c r="H15" t="n">
-        <v>2.852133806669919e-07</v>
+        <v>2.102387758704277e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>26688.17025918537</v>
+        <v>31698.24756088213</v>
       </c>
       <c r="J15" t="n">
-        <v>26338.01722100365</v>
+        <v>31391.88892783369</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.299192770400155e-05</v>
+        <v>3.063061019379628e-06</v>
       </c>
       <c r="B16" t="n">
-        <v>1714546269.36053</v>
+        <v>10313283561.49126</v>
       </c>
       <c r="C16" t="n">
-        <v>1.293989948809826e+39</v>
+        <v>11114122199.94113</v>
       </c>
       <c r="D16" t="n">
-        <v>7.131884804368005</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E16" t="n">
-        <v>45233.5213640965</v>
+        <v>52903.71159938141</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001517971431136251</v>
+        <v>0.0001758740991601987</v>
       </c>
       <c r="G16" t="n">
-        <v>4626.090552775608</v>
+        <v>5380.69838247126</v>
       </c>
       <c r="H16" t="n">
-        <v>3.830835977405852e-07</v>
+        <v>3.336505850258425e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>45119.36756813433</v>
+        <v>52803.34801878907</v>
       </c>
       <c r="J16" t="n">
-        <v>44698.75102193086</v>
+        <v>52405.2313168429</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3.420750071828355e-06</v>
+        <v>7.176632558066223e-06</v>
       </c>
       <c r="B17" t="n">
-        <v>7833537331.992668</v>
+        <v>7156749405.396035</v>
       </c>
       <c r="C17" t="n">
-        <v>29338019186.22629</v>
+        <v>4.656826699554423e+22</v>
       </c>
       <c r="D17" t="n">
-        <v>1.158183511505733</v>
+        <v>3.52479681398787</v>
       </c>
       <c r="E17" t="n">
-        <v>45080.32019488366</v>
+        <v>95394.26455851001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0002128042084702863</v>
+        <v>0.0002896847916510379</v>
       </c>
       <c r="G17" t="n">
-        <v>4576.814942442413</v>
+        <v>9656.868390562046</v>
       </c>
       <c r="H17" t="n">
-        <v>3.607707658052495e-07</v>
+        <v>3.962635436710531e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>45003.89472493472</v>
+        <v>95263.77351994217</v>
       </c>
       <c r="J17" t="n">
-        <v>44692.21210980479</v>
+        <v>94703.77656179332</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8.108216034673211e-06</v>
+        <v>3.960823501406056e-06</v>
       </c>
       <c r="B18" t="n">
-        <v>3862496487.139654</v>
+        <v>3456698658.712824</v>
       </c>
       <c r="C18" t="n">
-        <v>6.283083402273255e+18</v>
+        <v>9.367498295552474e+33</v>
       </c>
       <c r="D18" t="n">
-        <v>2.848960732739439</v>
+        <v>5.54397570619297</v>
       </c>
       <c r="E18" t="n">
-        <v>56848.11996208006</v>
+        <v>26921.74517836158</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001573436963294648</v>
+        <v>0.0001664356589114101</v>
       </c>
       <c r="G18" t="n">
-        <v>5855.788799703504</v>
+        <v>2713.717046071354</v>
       </c>
       <c r="H18" t="n">
-        <v>5.258088915306845e-07</v>
+        <v>1.479780608446247e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>56658.14573597395</v>
+        <v>26897.80903587803</v>
       </c>
       <c r="J18" t="n">
-        <v>56010.58561020045</v>
+        <v>26784.81266789971</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.339285827201886e-05</v>
+        <v>9.665473372933216e-06</v>
       </c>
       <c r="B19" t="n">
-        <v>1941534846.638352</v>
+        <v>946127344.8712419</v>
       </c>
       <c r="C19" t="n">
-        <v>8.668142316610188e+39</v>
+        <v>2.362326112067609e+47</v>
       </c>
       <c r="D19" t="n">
-        <v>7.306372079696652</v>
+        <v>8.669749494124776</v>
       </c>
       <c r="E19" t="n">
-        <v>52890.90539113988</v>
+        <v>18971.20225240725</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0002667100034857817</v>
+        <v>8.037766921790816e-05</v>
       </c>
       <c r="G19" t="n">
-        <v>5357.959245821735</v>
+        <v>1947.261109646188</v>
       </c>
       <c r="H19" t="n">
-        <v>3.858670738328471e-07</v>
+        <v>2.360424071187715e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>52814.38460590905</v>
+        <v>18915.4901586234</v>
       </c>
       <c r="J19" t="n">
-        <v>52490.26320229185</v>
+        <v>18718.52296602117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9.530619108733576e-06</v>
+        <v>3.253026534758316e-06</v>
       </c>
       <c r="B20" t="n">
-        <v>1314369037.990128</v>
+        <v>7790107992.300687</v>
       </c>
       <c r="C20" t="n">
-        <v>9.91738579708885e+38</v>
+        <v>8364865152.804113</v>
       </c>
       <c r="D20" t="n">
-        <v>6.968052731042225</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E20" t="n">
-        <v>25360.97151136518</v>
+        <v>42586.40812525606</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001314149759380556</v>
+        <v>6.619374170257542e-05</v>
       </c>
       <c r="G20" t="n">
-        <v>2586.002503985684</v>
+        <v>4463.813921020703</v>
       </c>
       <c r="H20" t="n">
-        <v>2.873317346833225e-07</v>
+        <v>3.543429920460826e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>25305.52111931054</v>
+        <v>42358.43800470595</v>
       </c>
       <c r="J20" t="n">
-        <v>25093.35381401839</v>
+        <v>41685.7292062762</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5.45125241552055e-06</v>
+        <v>4.528671518778344e-06</v>
       </c>
       <c r="B21" t="n">
-        <v>1824103096.573968</v>
+        <v>2397849066.436916</v>
       </c>
       <c r="C21" t="n">
-        <v>3.551627992043119e+51</v>
+        <v>9.466865811871655e+27</v>
       </c>
       <c r="D21" t="n">
-        <v>9.046005734992635</v>
+        <v>4.506337138223834</v>
       </c>
       <c r="E21" t="n">
-        <v>20755.31061604728</v>
+        <v>20956.66938751683</v>
       </c>
       <c r="F21" t="n">
-        <v>2.605529293164568e-05</v>
+        <v>2.344946301202333e-05</v>
       </c>
       <c r="G21" t="n">
-        <v>2167.107198228156</v>
+        <v>2259.529954227302</v>
       </c>
       <c r="H21" t="n">
-        <v>1.277340055495649e-07</v>
+        <v>2.037272266345379e-07</v>
       </c>
       <c r="I21" t="n">
-        <v>20653.55935313236</v>
+        <v>20774.5993703217</v>
       </c>
       <c r="J21" t="n">
-        <v>20344.67420215446</v>
+        <v>20321.0739649536</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.408960377644804e-06</v>
+        <v>2.205711139356928e-06</v>
       </c>
       <c r="B22" t="n">
-        <v>2264348730.849747</v>
+        <v>3958622299.627164</v>
       </c>
       <c r="C22" t="n">
-        <v>7.425566601698884e+32</v>
+        <v>5.063176498207946e+20</v>
       </c>
       <c r="D22" t="n">
-        <v>5.323011366601214</v>
+        <v>2.998129519514705</v>
       </c>
       <c r="E22" t="n">
-        <v>15122.7209170203</v>
+        <v>15918.22636605442</v>
       </c>
       <c r="F22" t="n">
-        <v>5.53582131249317e-05</v>
+        <v>7.189596252364757e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>1544.772457044843</v>
+        <v>1619.289661742752</v>
       </c>
       <c r="H22" t="n">
-        <v>1.321897737816534e-07</v>
+        <v>1.378411670647554e-07</v>
       </c>
       <c r="I22" t="n">
-        <v>15086.60939997272</v>
+        <v>15887.70744923519</v>
       </c>
       <c r="J22" t="n">
-        <v>14951.5813500676</v>
+        <v>15766.96570086355</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2.711718363782546e-06</v>
+        <v>9.59849218315935e-06</v>
       </c>
       <c r="B23" t="n">
-        <v>5261070560.235528</v>
+        <v>6169020036.925264</v>
       </c>
       <c r="C23" t="n">
-        <v>2.836316052110892e+20</v>
+        <v>9.36460630917528e+16</v>
       </c>
       <c r="D23" t="n">
-        <v>2.963192896746786</v>
+        <v>2.474815636868869</v>
       </c>
       <c r="E23" t="n">
-        <v>25962.94674577226</v>
+        <v>105853.5842730285</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0001148944705159412</v>
+        <v>0.000219633725663728</v>
       </c>
       <c r="G23" t="n">
-        <v>2631.05645998661</v>
+        <v>10882.79884579468</v>
       </c>
       <c r="H23" t="n">
-        <v>1.709246543591647e-07</v>
+        <v>6.857265021617045e-07</v>
       </c>
       <c r="I23" t="n">
-        <v>25924.32253976184</v>
+        <v>105523.0949191486</v>
       </c>
       <c r="J23" t="n">
-        <v>25761.7912896653</v>
+        <v>104374.5409139513</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7.128057478414073e-06</v>
+        <v>4.909913300901887e-06</v>
       </c>
       <c r="B24" t="n">
-        <v>3287231147.379159</v>
+        <v>3649244548.45049</v>
       </c>
       <c r="C24" t="n">
-        <v>1.301078939038449e+25</v>
+        <v>1.095008271282334e+24</v>
       </c>
       <c r="D24" t="n">
-        <v>4.060596652713865</v>
+        <v>3.758198255855427</v>
       </c>
       <c r="E24" t="n">
-        <v>44303.89858623786</v>
+        <v>33558.58465625175</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0002232162051255052</v>
+        <v>0.0001402997310983152</v>
       </c>
       <c r="G24" t="n">
-        <v>4493.012274380001</v>
+        <v>3411.283625463873</v>
       </c>
       <c r="H24" t="n">
-        <v>3.505670418017015e-07</v>
+        <v>2.574646729692795e-07</v>
       </c>
       <c r="I24" t="n">
-        <v>44234.3181242865</v>
+        <v>33497.00114531986</v>
       </c>
       <c r="J24" t="n">
-        <v>43945.26952123412</v>
+        <v>33250.68729096821</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7.134233710219896e-06</v>
+        <v>2.082726859263919e-06</v>
       </c>
       <c r="B25" t="n">
-        <v>2493874952.951794</v>
+        <v>20850752464.51262</v>
       </c>
       <c r="C25" t="n">
-        <v>5.409674751668405e+24</v>
+        <v>22994192783.72028</v>
       </c>
       <c r="D25" t="n">
-        <v>4.010397054175508</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E25" t="n">
-        <v>33609.23149123318</v>
+        <v>72669.62293365037</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0001600289361475454</v>
+        <v>0.0002011863533390634</v>
       </c>
       <c r="G25" t="n">
-        <v>3427.939527659104</v>
+        <v>7340.7128763037</v>
       </c>
       <c r="H25" t="n">
-        <v>3.545507285977004e-07</v>
+        <v>2.268655539820695e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>33534.76884841564</v>
+        <v>72587.6778414963</v>
       </c>
       <c r="J25" t="n">
-        <v>33250.82840807548</v>
+        <v>72220.25594314303</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.392976892429447e-05</v>
+        <v>4.098169153462153e-06</v>
       </c>
       <c r="B26" t="n">
-        <v>515988004.9229412</v>
+        <v>3403044976.841362</v>
       </c>
       <c r="C26" t="n">
-        <v>1.278238408189659e+67</v>
+        <v>3.949342244064879e+18</v>
       </c>
       <c r="D26" t="n">
-        <v>13.0319972916943</v>
+        <v>2.721096710293128</v>
       </c>
       <c r="E26" t="n">
-        <v>15460.10730425537</v>
+        <v>25256.34496466115</v>
       </c>
       <c r="F26" t="n">
-        <v>3.902366891950905e-05</v>
+        <v>4.536643879093073e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>1627.405109496655</v>
+        <v>2663.183447610799</v>
       </c>
       <c r="H26" t="n">
-        <v>2.282798084608994e-07</v>
+        <v>2.745231426704942e-07</v>
       </c>
       <c r="I26" t="n">
-        <v>15369.66910528746</v>
+        <v>25103.51279672261</v>
       </c>
       <c r="J26" t="n">
-        <v>15110.50249954412</v>
+        <v>24670.50581671296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4.65720527500993e-06</v>
+        <v>1.343259505958799e-06</v>
       </c>
       <c r="B27" t="n">
-        <v>3540741792.982863</v>
+        <v>6490738679.268723</v>
       </c>
       <c r="C27" t="n">
-        <v>1.229602623357255e+26</v>
+        <v>1005220612463952</v>
       </c>
       <c r="D27" t="n">
-        <v>4.130958030553324</v>
+        <v>1.925915901058746</v>
       </c>
       <c r="E27" t="n">
-        <v>31384.76280512183</v>
+        <v>15207.40454545077</v>
       </c>
       <c r="F27" t="n">
-        <v>3.791932238826347e-05</v>
+        <v>5.194474541888909e-05</v>
       </c>
       <c r="G27" t="n">
-        <v>3306.64087378852</v>
+        <v>1550.201849168413</v>
       </c>
       <c r="H27" t="n">
-        <v>2.257531240852116e-07</v>
+        <v>1.118142911399023e-07</v>
       </c>
       <c r="I27" t="n">
-        <v>31197.91325703701</v>
+        <v>15174.66966253596</v>
       </c>
       <c r="J27" t="n">
-        <v>30665.61547637856</v>
+        <v>15048.91224182552</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7.904811203399205e-07</v>
+        <v>9.824516201868969e-06</v>
       </c>
       <c r="B28" t="n">
-        <v>13191460576.42801</v>
+        <v>1248012543.640667</v>
       </c>
       <c r="C28" t="n">
-        <v>15415245781.7239</v>
+        <v>2.806672985492267e+43</v>
       </c>
       <c r="D28" t="n">
-        <v>1.05980198019802</v>
+        <v>7.87464199992707</v>
       </c>
       <c r="E28" t="n">
-        <v>17454.10959286932</v>
+        <v>25189.64928424512</v>
       </c>
       <c r="F28" t="n">
-        <v>6.190798176079416e-05</v>
+        <v>8.339042213530124e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>1767.259443187758</v>
+        <v>2590.564855575013</v>
       </c>
       <c r="H28" t="n">
-        <v>8.610487567326191e-08</v>
+        <v>2.63368677196731e-07</v>
       </c>
       <c r="I28" t="n">
-        <v>17429.83349964618</v>
+        <v>25110.09380963345</v>
       </c>
       <c r="J28" t="n">
-        <v>17326.05520225468</v>
+        <v>24834.50986041805</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2.849459881884504e-06</v>
+        <v>9.430398490125876e-06</v>
       </c>
       <c r="B29" t="n">
-        <v>4067473408.855938</v>
+        <v>1927621544.181029</v>
       </c>
       <c r="C29" t="n">
-        <v>1.448036989741659e+17</v>
+        <v>4.989591500786709e+55</v>
       </c>
       <c r="D29" t="n">
-        <v>2.401926867659881</v>
+        <v>10.24558209291215</v>
       </c>
       <c r="E29" t="n">
-        <v>20620.0995708107</v>
+        <v>38223.08526489556</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0001520021490151803</v>
+        <v>0.0001963370147580364</v>
       </c>
       <c r="G29" t="n">
-        <v>2087.354338683304</v>
+        <v>3856.592035726986</v>
       </c>
       <c r="H29" t="n">
-        <v>2.075860473348733e-07</v>
+        <v>1.956677289670525e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>20591.93914680821</v>
+        <v>38184.99247685397</v>
       </c>
       <c r="J29" t="n">
-        <v>20471.04407328253</v>
+        <v>38009.50256487952</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1.332904472715312e-06</v>
+        <v>1.026112920703547e-05</v>
       </c>
       <c r="B30" t="n">
-        <v>7990841438.73449</v>
+        <v>1885265320.893143</v>
       </c>
       <c r="C30" t="n">
-        <v>9050666526.541487</v>
+        <v>1.024414715085853e+48</v>
       </c>
       <c r="D30" t="n">
-        <v>1.05980198019802</v>
+        <v>8.777143583283532</v>
       </c>
       <c r="E30" t="n">
-        <v>17831.36015771138</v>
+        <v>40169.94396243522</v>
       </c>
       <c r="F30" t="n">
-        <v>9.224740965244726e-05</v>
+        <v>9.291175743132632e-05</v>
       </c>
       <c r="G30" t="n">
-        <v>1808.394545611344</v>
+        <v>4113.340834779389</v>
       </c>
       <c r="H30" t="n">
-        <v>1.451895193374559e-07</v>
+        <v>2.476068214082269e-07</v>
       </c>
       <c r="I30" t="n">
-        <v>17803.29512455559</v>
+        <v>40062.89236406203</v>
       </c>
       <c r="J30" t="n">
-        <v>17686.76846822216</v>
+        <v>39674.18887648093</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2.20226918056215e-06</v>
+        <v>1.400120822612118e-05</v>
       </c>
       <c r="B31" t="n">
-        <v>7739764096.160237</v>
+        <v>2828584289.956901</v>
       </c>
       <c r="C31" t="n">
-        <v>8506965551.400846</v>
+        <v>8.777175868187194e+24</v>
       </c>
       <c r="D31" t="n">
-        <v>1.05980198019802</v>
+        <v>4.222617694798981</v>
       </c>
       <c r="E31" t="n">
-        <v>28590.01652401209</v>
+        <v>75368.49986494302</v>
       </c>
       <c r="F31" t="n">
-        <v>6.923213084369926e-05</v>
+        <v>0.0002171421490171001</v>
       </c>
       <c r="G31" t="n">
-        <v>2948.158737351614</v>
+        <v>7744.948477243128</v>
       </c>
       <c r="H31" t="n">
-        <v>2.398869613860201e-07</v>
+        <v>6.661632669909711e-07</v>
       </c>
       <c r="I31" t="n">
-        <v>28490.95309628941</v>
+        <v>75137.27931966654</v>
       </c>
       <c r="J31" t="n">
-        <v>28156.78855996814</v>
+        <v>74329.73368836509</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4.66252142670127e-06</v>
+        <v>1.321949696397632e-05</v>
       </c>
       <c r="B32" t="n">
-        <v>3439725221.304719</v>
+        <v>1704840833.2163</v>
       </c>
       <c r="C32" t="n">
-        <v>5.702274758850166e+22</v>
+        <v>1.479483370414989e+43</v>
       </c>
       <c r="D32" t="n">
-        <v>3.512365427367434</v>
+        <v>7.971261028911139</v>
       </c>
       <c r="E32" t="n">
-        <v>29805.61994718812</v>
+        <v>46315.78497898042</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000106939958527225</v>
+        <v>0.0001610094339804892</v>
       </c>
       <c r="G32" t="n">
-        <v>3045.321349865056</v>
+        <v>4722.249991181069</v>
       </c>
       <c r="H32" t="n">
-        <v>2.581676716546195e-07</v>
+        <v>3.502277491666139e-07</v>
       </c>
       <c r="I32" t="n">
-        <v>29733.66510813673</v>
+        <v>46215.03887533261</v>
       </c>
       <c r="J32" t="n">
-        <v>29465.38844790293</v>
+        <v>45829.0438632401</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4.749362600614948e-06</v>
+        <v>9.890336390736244e-07</v>
       </c>
       <c r="B33" t="n">
-        <v>8375613154.512581</v>
+        <v>9309902969.348192</v>
       </c>
       <c r="C33" t="n">
-        <v>8792325487.968328</v>
+        <v>10734524754.20921</v>
       </c>
       <c r="D33" t="n">
-        <v>1.05980198019802</v>
+        <v>1.059801980198019</v>
       </c>
       <c r="E33" t="n">
-        <v>66791.84709095115</v>
+        <v>15414.83202191156</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0001147337484614228</v>
+        <v>6.950005618314826e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>6950.232798810216</v>
+        <v>1562.988400690018</v>
       </c>
       <c r="H33" t="n">
-        <v>5.173346532012521e-07</v>
+        <v>1.077326407144142e-07</v>
       </c>
       <c r="I33" t="n">
-        <v>66490.68254682326</v>
+        <v>15390.93735691282</v>
       </c>
       <c r="J33" t="n">
-        <v>65552.05326965055</v>
+        <v>15291.36442201943</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6.488233421909339e-06</v>
+        <v>4.612606576472222e-06</v>
       </c>
       <c r="B34" t="n">
-        <v>2064146715.287051</v>
+        <v>3153596655.693273</v>
       </c>
       <c r="C34" t="n">
-        <v>6.961564805957601e+25</v>
+        <v>2.305133504418848e+25</v>
       </c>
       <c r="D34" t="n">
-        <v>4.214896882694463</v>
+        <v>4.002467318573071</v>
       </c>
       <c r="E34" t="n">
-        <v>25452.72665371642</v>
+        <v>27444.40148978162</v>
       </c>
       <c r="F34" t="n">
-        <v>0.000158514678172845</v>
+        <v>0.0001859293845188363</v>
       </c>
       <c r="G34" t="n">
-        <v>2589.954012373991</v>
+        <v>2774.943301639826</v>
       </c>
       <c r="H34" t="n">
-        <v>3.091853570462354e-07</v>
+        <v>2.296130071628138e-07</v>
       </c>
       <c r="I34" t="n">
-        <v>25403.0807126027</v>
+        <v>27410.50909793533</v>
       </c>
       <c r="J34" t="n">
-        <v>25207.51318954585</v>
+        <v>27261.61211225505</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5.78032707732946e-06</v>
+        <v>1.152116274405077e-05</v>
       </c>
       <c r="B35" t="n">
-        <v>1306816706.786149</v>
+        <v>1035742275.548166</v>
       </c>
       <c r="C35" t="n">
-        <v>6.906913685048214e+34</v>
+        <v>1.267188017471785e+65</v>
       </c>
       <c r="D35" t="n">
-        <v>5.931077865682411</v>
+        <v>12.36473839113017</v>
       </c>
       <c r="E35" t="n">
-        <v>15007.42720685111</v>
+        <v>25456.72010263647</v>
       </c>
       <c r="F35" t="n">
-        <v>7.401390686435853e-05</v>
+        <v>0.0001818530749539712</v>
       </c>
       <c r="G35" t="n">
-        <v>1537.765894526768</v>
+        <v>2570.7189774096</v>
       </c>
       <c r="H35" t="n">
-        <v>2.028795255672102e-07</v>
+        <v>1.988066183353234e-07</v>
       </c>
       <c r="I35" t="n">
-        <v>14966.29034702704</v>
+        <v>25428.89013914097</v>
       </c>
       <c r="J35" t="n">
-        <v>14818.06491351848</v>
+        <v>25303.24639529588</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4.150559859603353e-06</v>
+        <v>4.163241377258146e-06</v>
       </c>
       <c r="B36" t="n">
-        <v>5673805399.830998</v>
+        <v>2523341863.494816</v>
       </c>
       <c r="C36" t="n">
-        <v>1.01662129581785e+29</v>
+        <v>8.242470697963659e+19</v>
       </c>
       <c r="D36" t="n">
-        <v>4.603200522724224</v>
+        <v>2.990468261881889</v>
       </c>
       <c r="E36" t="n">
-        <v>45237.79495843065</v>
+        <v>19206.70109628222</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0001343811249864321</v>
+        <v>5.150704638693757e-05</v>
       </c>
       <c r="G36" t="n">
-        <v>4579.308666063096</v>
+        <v>2008.149683765743</v>
       </c>
       <c r="H36" t="n">
-        <v>1.832801869073274e-07</v>
+        <v>2.606621778295805e-07</v>
       </c>
       <c r="I36" t="n">
-        <v>45176.09588040839</v>
+        <v>19109.50156946276</v>
       </c>
       <c r="J36" t="n">
-        <v>44911.13584628489</v>
+        <v>18817.4168439047</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3.702036177376312e-06</v>
+        <v>6.819695601901273e-06</v>
       </c>
       <c r="B37" t="n">
-        <v>11333526918.3554</v>
+        <v>4880070479.805596</v>
       </c>
       <c r="C37" t="n">
-        <v>12075982714.98902</v>
+        <v>1181697787001936</v>
       </c>
       <c r="D37" t="n">
-        <v>1.05980198019802</v>
+        <v>2.088294202501676</v>
       </c>
       <c r="E37" t="n">
-        <v>70209.87118611073</v>
+        <v>58480.8659105843</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0003623519590478717</v>
+        <v>0.0002259127835282656</v>
       </c>
       <c r="G37" t="n">
-        <v>7091.308431877868</v>
+        <v>5974.320981403002</v>
       </c>
       <c r="H37" t="n">
-        <v>4.032523441595056e-07</v>
+        <v>5.418289299641101e-07</v>
       </c>
       <c r="I37" t="n">
-        <v>70131.73639359206</v>
+        <v>58340.60547686811</v>
       </c>
       <c r="J37" t="n">
-        <v>69780.37300702838</v>
+        <v>57816.75252675213</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.498487609185992e-05</v>
+        <v>2.934691913667719e-06</v>
       </c>
       <c r="B38" t="n">
-        <v>1697987629.90512</v>
+        <v>2878806710.733086</v>
       </c>
       <c r="C38" t="n">
-        <v>1.668377734770309e+33</v>
+        <v>2.622027211976051e+38</v>
       </c>
       <c r="D38" t="n">
-        <v>5.994914263445493</v>
+        <v>6.252508397207359</v>
       </c>
       <c r="E38" t="n">
-        <v>50692.84922134422</v>
+        <v>16879.04143459168</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0001234899177122289</v>
+        <v>5.310354895905691e-05</v>
       </c>
       <c r="G38" t="n">
-        <v>5261.665876526965</v>
+        <v>1715.949969837847</v>
       </c>
       <c r="H38" t="n">
-        <v>5.20720127685129e-07</v>
+        <v>9.803959280038753e-08</v>
       </c>
       <c r="I38" t="n">
-        <v>50479.0926053525</v>
+        <v>16847.87940528203</v>
       </c>
       <c r="J38" t="n">
-        <v>49798.97540063271</v>
+        <v>16723.42729930856</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.615526073241728e-06</v>
+        <v>2.839699674333028e-06</v>
       </c>
       <c r="B39" t="n">
-        <v>6537416237.421388</v>
+        <v>4121149575.295157</v>
       </c>
       <c r="C39" t="n">
-        <v>78251868917935</v>
+        <v>4.523147800974733e+20</v>
       </c>
       <c r="D39" t="n">
-        <v>1.748422831545854</v>
+        <v>3.02546592353721</v>
       </c>
       <c r="E39" t="n">
-        <v>18286.77606739392</v>
+        <v>21352.87301768179</v>
       </c>
       <c r="F39" t="n">
-        <v>5.023313097430813e-05</v>
+        <v>0.000102751416348254</v>
       </c>
       <c r="G39" t="n">
-        <v>1875.102996426443</v>
+        <v>2168.256611736783</v>
       </c>
       <c r="H39" t="n">
-        <v>1.416987926192145e-07</v>
+        <v>1.762782976684442e-07</v>
       </c>
       <c r="I39" t="n">
-        <v>18235.19230107498</v>
+        <v>21316.24045105</v>
       </c>
       <c r="J39" t="n">
-        <v>18050.77970832515</v>
+        <v>21167.27509145089</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2.974529968958377e-06</v>
+        <v>8.260959599802577e-06</v>
       </c>
       <c r="B40" t="n">
-        <v>13062874036.9826</v>
+        <v>1620397655.442308</v>
       </c>
       <c r="C40" t="n">
-        <v>14101933539.86748</v>
+        <v>1.710669776175048e+43</v>
       </c>
       <c r="D40" t="n">
-        <v>1.05980198019802</v>
+        <v>7.708643746169185</v>
       </c>
       <c r="E40" t="n">
-        <v>65110.39685344094</v>
+        <v>27448.51998007723</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0001299244245899159</v>
+        <v>6.345362936195641e-05</v>
       </c>
       <c r="G40" t="n">
-        <v>6657.175491885746</v>
+        <v>2832.858851026715</v>
       </c>
       <c r="H40" t="n">
-        <v>3.240071477651686e-07</v>
+        <v>2.260536466419701e-07</v>
       </c>
       <c r="I40" t="n">
-        <v>64948.02373506132</v>
+        <v>27350.7345878339</v>
       </c>
       <c r="J40" t="n">
-        <v>64347.83285533027</v>
+        <v>27023.53560162392</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7.245120542902627e-06</v>
+        <v>1.129370669687016e-05</v>
       </c>
       <c r="B41" t="n">
-        <v>1869886483.32057</v>
+        <v>2933036521.346478</v>
       </c>
       <c r="C41" t="n">
-        <v>6.743349307581867e+37</v>
+        <v>7.176544002246517e+29</v>
       </c>
       <c r="D41" t="n">
-        <v>6.574152996227569</v>
+        <v>5.146356227821009</v>
       </c>
       <c r="E41" t="n">
-        <v>27248.20652396843</v>
+        <v>64613.25128201074</v>
       </c>
       <c r="F41" t="n">
-        <v>9.327023171910216e-05</v>
+        <v>0.0001935763785281413</v>
       </c>
       <c r="G41" t="n">
-        <v>2785.517834339075</v>
+        <v>6596.976211869922</v>
       </c>
       <c r="H41" t="n">
-        <v>2.308506767416344e-07</v>
+        <v>4.515559029047436e-07</v>
       </c>
       <c r="I41" t="n">
-        <v>27180.76521069928</v>
+        <v>64462.52785571201</v>
       </c>
       <c r="J41" t="n">
-        <v>26930.97551007539</v>
+        <v>63895.4642825115</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6.10473263824813e-06</v>
+        <v>3.15098103612128e-06</v>
       </c>
       <c r="B42" t="n">
-        <v>7558211369.346231</v>
+        <v>3951716680.71194</v>
       </c>
       <c r="C42" t="n">
-        <v>4467664210.938383</v>
+        <v>1.82332326523023e+23</v>
       </c>
       <c r="D42" t="n">
-        <v>1.013773592334332</v>
+        <v>3.515436547165861</v>
       </c>
       <c r="E42" t="n">
-        <v>77271.59505068914</v>
+        <v>23114.85611564028</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0001637192876804239</v>
+        <v>0.0001487288199906386</v>
       </c>
       <c r="G42" t="n">
-        <v>8013.969746358111</v>
+        <v>2335.872946831884</v>
       </c>
       <c r="H42" t="n">
-        <v>6.751995042438009e-07</v>
+        <v>1.743515357953039e-07</v>
       </c>
       <c r="I42" t="n">
-        <v>76952.91700481225</v>
+        <v>23087.75907645377</v>
       </c>
       <c r="J42" t="n">
-        <v>75932.08758984316</v>
+        <v>22967.31054014546</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6.344839775701451e-06</v>
+        <v>6.65863484901716e-06</v>
       </c>
       <c r="B43" t="n">
-        <v>4850223258.398315</v>
+        <v>2895043838.466399</v>
       </c>
       <c r="C43" t="n">
-        <v>1.187311207940563e+24</v>
+        <v>1.171336956792856e+28</v>
       </c>
       <c r="D43" t="n">
-        <v>3.799992463308844</v>
+        <v>4.621143763235176</v>
       </c>
       <c r="E43" t="n">
-        <v>57720.37793025657</v>
+        <v>37228.16893508669</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0001751899881266408</v>
+        <v>4.751914588270407e-05</v>
       </c>
       <c r="G43" t="n">
-        <v>5869.806337228453</v>
+        <v>3929.429967872503</v>
       </c>
       <c r="H43" t="n">
-        <v>3.297135202549308e-07</v>
+        <v>2.930301048556474e-07</v>
       </c>
       <c r="I43" t="n">
-        <v>57611.74621447568</v>
+        <v>36998.59885246021</v>
       </c>
       <c r="J43" t="n">
-        <v>57179.97283603074</v>
+        <v>36352.32123582825</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3.72797041139364e-06</v>
+        <v>8.193499633987376e-06</v>
       </c>
       <c r="B44" t="n">
-        <v>5076408682.374186</v>
+        <v>2459949194.239463</v>
       </c>
       <c r="C44" t="n">
-        <v>1.290502846435742e+16</v>
+        <v>2.619834059507854e+31</v>
       </c>
       <c r="D44" t="n">
-        <v>2.222548918589796</v>
+        <v>5.353921866996225</v>
       </c>
       <c r="E44" t="n">
-        <v>33439.94970057624</v>
+        <v>39455.9098785934</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0001332986568608472</v>
+        <v>0.0003714184231981508</v>
       </c>
       <c r="G44" t="n">
-        <v>3408.397331626988</v>
+        <v>3975.807497426624</v>
       </c>
       <c r="H44" t="n">
-        <v>2.852459200158745e-07</v>
+        <v>3.160480865453777e-07</v>
       </c>
       <c r="I44" t="n">
-        <v>33368.39152105473</v>
+        <v>39422.33597907419</v>
       </c>
       <c r="J44" t="n">
-        <v>33093.06919942379</v>
+        <v>39262.37135489167</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4.213105414238847e-06</v>
+        <v>6.281330603223756e-06</v>
       </c>
       <c r="B45" t="n">
-        <v>6933645238.718513</v>
+        <v>1949957318.069281</v>
       </c>
       <c r="C45" t="n">
-        <v>298205332454351.2</v>
+        <v>2.907326052297343e+47</v>
       </c>
       <c r="D45" t="n">
-        <v>1.908095261660647</v>
+        <v>8.351422488287287</v>
       </c>
       <c r="E45" t="n">
-        <v>50972.61552823446</v>
+        <v>25297.31130831303</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0001055145957531326</v>
+        <v>6.940910276170522e-05</v>
       </c>
       <c r="G45" t="n">
-        <v>5250.532281235014</v>
+        <v>2581.910014311728</v>
       </c>
       <c r="H45" t="n">
-        <v>3.525269572372783e-07</v>
+        <v>1.590722183583587e-07</v>
       </c>
       <c r="I45" t="n">
-        <v>50802.31471888829</v>
+        <v>25239.33477111256</v>
       </c>
       <c r="J45" t="n">
-        <v>50221.77771940541</v>
+        <v>25020.19752154061</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4.808462662730538e-06</v>
+        <v>4.861117142966528e-06</v>
       </c>
       <c r="B46" t="n">
-        <v>984856453.3263053</v>
+        <v>5881611632.411139</v>
       </c>
       <c r="C46" t="n">
-        <v>2.856245929977432e+54</v>
+        <v>42876021596030.21</v>
       </c>
       <c r="D46" t="n">
-        <v>9.559321528056824</v>
+        <v>1.775001746711011</v>
       </c>
       <c r="E46" t="n">
-        <v>9902.664844574016</v>
+        <v>49565.21439684034</v>
       </c>
       <c r="F46" t="n">
-        <v>6.809843154251682e-05</v>
+        <v>0.0001496358470428497</v>
       </c>
       <c r="G46" t="n">
-        <v>1004.239542830454</v>
+        <v>5082.626081983123</v>
       </c>
       <c r="H46" t="n">
-        <v>1.067662508573554e-07</v>
+        <v>4.230066768506946e-07</v>
       </c>
       <c r="I46" t="n">
-        <v>9887.139224159513</v>
+        <v>49425.09812761914</v>
       </c>
       <c r="J46" t="n">
-        <v>9822.615906279849</v>
+        <v>48924.47755952018</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.95719730700988e-06</v>
+        <v>2.123396245053081e-06</v>
       </c>
       <c r="B47" t="n">
-        <v>7832470697.271846</v>
+        <v>7526952472.115642</v>
       </c>
       <c r="C47" t="n">
-        <v>8669813013.282312</v>
+        <v>8291122826.781999</v>
       </c>
       <c r="D47" t="n">
         <v>1.05980198019802</v>
       </c>
       <c r="E47" t="n">
-        <v>25684.3492252103</v>
+        <v>26817.44821200387</v>
       </c>
       <c r="F47" t="n">
-        <v>9.031985461083066e-05</v>
+        <v>6.068714737201559e-05</v>
       </c>
       <c r="G47" t="n">
-        <v>2622.997979912797</v>
+        <v>2773.732682883481</v>
       </c>
       <c r="H47" t="n">
-        <v>2.131919744214263e-07</v>
+        <v>2.312955553027562e-07</v>
       </c>
       <c r="I47" t="n">
-        <v>25623.72360588611</v>
+        <v>26715.23947680043</v>
       </c>
       <c r="J47" t="n">
-        <v>25396.34017239131</v>
+        <v>26379.97683828893</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1.489115700338444e-05</v>
+        <v>2.143705666111455e-06</v>
       </c>
       <c r="B48" t="n">
-        <v>1631298951.025132</v>
+        <v>7916854119.604332</v>
       </c>
       <c r="C48" t="n">
-        <v>2.064200256720277e+37</v>
+        <v>8870554690802.756</v>
       </c>
       <c r="D48" t="n">
-        <v>6.840289087059374</v>
+        <v>1.584804498026456</v>
       </c>
       <c r="E48" t="n">
-        <v>49207.37272692782</v>
+        <v>29180.13182476966</v>
       </c>
       <c r="F48" t="n">
-        <v>9.346886212558359e-05</v>
+        <v>5.95320569818684e-05</v>
       </c>
       <c r="G48" t="n">
-        <v>5137.236326575962</v>
+        <v>3005.167419010149</v>
       </c>
       <c r="H48" t="n">
-        <v>4.569306295267704e-07</v>
+        <v>1.975648288767191e-07</v>
       </c>
       <c r="I48" t="n">
-        <v>48966.81822261318</v>
+        <v>29083.29378417724</v>
       </c>
       <c r="J48" t="n">
-        <v>48235.91157039408</v>
+        <v>28752.54539880503</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1.311142921004322e-05</v>
+        <v>3.175084250401418e-06</v>
       </c>
       <c r="B49" t="n">
-        <v>1829550097.03091</v>
+        <v>5056234614.359341</v>
       </c>
       <c r="C49" t="n">
-        <v>9.662711666720449e+32</v>
+        <v>5.372086280219578e+16</v>
       </c>
       <c r="D49" t="n">
-        <v>5.880836780814231</v>
+        <v>2.319136021481536</v>
       </c>
       <c r="E49" t="n">
-        <v>47655.32936992825</v>
+        <v>28456.33559369521</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0001238360585286933</v>
+        <v>0.0002051983692481178</v>
       </c>
       <c r="G49" t="n">
-        <v>4926.183074194605</v>
+        <v>2875.159198812732</v>
       </c>
       <c r="H49" t="n">
-        <v>4.638464494526086e-07</v>
+        <v>2.36565676982787e-07</v>
       </c>
       <c r="I49" t="n">
-        <v>47476.82921748183</v>
+        <v>28423.5293276472</v>
       </c>
       <c r="J49" t="n">
-        <v>46888.28969034924</v>
+        <v>28277.15691048966</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4.097292645750295e-06</v>
+        <v>1.266075382947816e-06</v>
       </c>
       <c r="B50" t="n">
-        <v>1605455489.867154</v>
+        <v>9303463326.070517</v>
       </c>
       <c r="C50" t="n">
-        <v>4.310809212136719e+62</v>
+        <v>10569845625.59999</v>
       </c>
       <c r="D50" t="n">
-        <v>10.92565014828944</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E50" t="n">
-        <v>13915.76809683419</v>
+        <v>19738.00312181331</v>
       </c>
       <c r="F50" t="n">
-        <v>4.429435409371074e-05</v>
+        <v>5.500984825594887e-05</v>
       </c>
       <c r="G50" t="n">
-        <v>1414.147750059552</v>
+        <v>2018.335273826693</v>
       </c>
       <c r="H50" t="n">
-        <v>7.982672911377316e-08</v>
+        <v>1.379100153521956e-07</v>
       </c>
       <c r="I50" t="n">
-        <v>13890.68927419404</v>
+        <v>19688.51983109624</v>
       </c>
       <c r="J50" t="n">
-        <v>13789.9308440019</v>
+        <v>19505.86883116751</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>7.023517036257792e-06</v>
+        <v>4.066560096787227e-06</v>
       </c>
       <c r="B51" t="n">
-        <v>2923351325.179805</v>
+        <v>2720951486.418786</v>
       </c>
       <c r="C51" t="n">
-        <v>5.290483127499957e+20</v>
+        <v>1.323579425161085e+32</v>
       </c>
       <c r="D51" t="n">
-        <v>3.220619529627567</v>
+        <v>5.23112261493476</v>
       </c>
       <c r="E51" t="n">
-        <v>37774.80551118204</v>
+        <v>21619.06271574956</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0001525058740117838</v>
+        <v>8.413142859056439e-05</v>
       </c>
       <c r="G51" t="n">
-        <v>3870.222182746339</v>
+        <v>2198.957206405044</v>
       </c>
       <c r="H51" t="n">
-        <v>4.160222489664072e-07</v>
+        <v>1.602057364761799e-07</v>
       </c>
       <c r="I51" t="n">
-        <v>37671.75925381744</v>
+        <v>21577.8950103828</v>
       </c>
       <c r="J51" t="n">
-        <v>37299.97142355145</v>
+        <v>21414.7458275311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4.267971024124427e-06</v>
+        <v>2.859287892128499e-06</v>
       </c>
       <c r="B52" t="n">
-        <v>8939635789.657091</v>
+        <v>8434253727.54586</v>
       </c>
       <c r="C52" t="n">
-        <v>9444579211.914169</v>
+        <v>9126679841.426096</v>
       </c>
       <c r="D52" t="n">
         <v>1.05980198019802</v>
       </c>
       <c r="E52" t="n">
-        <v>64000.01585800864</v>
+        <v>40342.57765676204</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0001322001904398243</v>
+        <v>0.0003863518257094082</v>
       </c>
       <c r="G52" t="n">
-        <v>6602.559032862019</v>
+        <v>4063.527401010376</v>
       </c>
       <c r="H52" t="n">
-        <v>4.648980284959744e-07</v>
+        <v>3.114541538448355e-07</v>
       </c>
       <c r="I52" t="n">
-        <v>63774.95202794068</v>
+        <v>40310.05583972407</v>
       </c>
       <c r="J52" t="n">
-        <v>63019.01570792383</v>
+        <v>40152.32390258309</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4.61412521902998e-06</v>
+        <v>2.768553196758152e-06</v>
       </c>
       <c r="B53" t="n">
-        <v>970668129.2471819</v>
+        <v>5578072131.170348</v>
       </c>
       <c r="C53" t="n">
-        <v>2.006814084391082e+91</v>
+        <v>92281809452674.98</v>
       </c>
       <c r="D53" t="n">
-        <v>16.43096077696319</v>
+        <v>1.804655291372965</v>
       </c>
       <c r="E53" t="n">
-        <v>9711.181512922651</v>
+        <v>26868.38135657579</v>
       </c>
       <c r="F53" t="n">
-        <v>4.587186070937378e-05</v>
+        <v>4.714012486536094e-05</v>
       </c>
       <c r="G53" t="n">
-        <v>982.5925115186564</v>
+        <v>2809.337743508312</v>
       </c>
       <c r="H53" t="n">
-        <v>6.022270460245357e-08</v>
+        <v>2.388038992087956e-07</v>
       </c>
       <c r="I53" t="n">
-        <v>9698.432223782214</v>
+        <v>26732.27068118608</v>
       </c>
       <c r="J53" t="n">
-        <v>9643.196256879068</v>
+        <v>26323.39078529439</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2.118601197278911e-05</v>
+        <v>6.13073485328023e-06</v>
       </c>
       <c r="B54" t="n">
-        <v>2355066981.866176</v>
+        <v>4798569910.079486</v>
       </c>
       <c r="C54" t="n">
-        <v>6.182536877502095e+24</v>
+        <v>2.592534454058708e+32</v>
       </c>
       <c r="D54" t="n">
-        <v>4.330386009146245</v>
+        <v>5.383877764040649</v>
       </c>
       <c r="E54" t="n">
-        <v>95174.99867412631</v>
+        <v>57658.4197326686</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0004515275855927844</v>
+        <v>0.0001753404385079815</v>
       </c>
       <c r="G54" t="n">
-        <v>9704.643844550199</v>
+        <v>5835.473795612519</v>
       </c>
       <c r="H54" t="n">
-        <v>9.864946949458965e-07</v>
+        <v>2.352797797173521e-07</v>
       </c>
       <c r="I54" t="n">
-        <v>94967.06092175124</v>
+        <v>57581.05104117343</v>
       </c>
       <c r="J54" t="n">
-        <v>94171.28382567933</v>
+        <v>57247.54535196272</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>7.846028303035443e-06</v>
+        <v>7.085560909933697e-06</v>
       </c>
       <c r="B55" t="n">
-        <v>2224543100.976759</v>
+        <v>5052611013.702147</v>
       </c>
       <c r="C55" t="n">
-        <v>1.413017596888114e+31</v>
+        <v>5.513022468360882e+23</v>
       </c>
       <c r="D55" t="n">
-        <v>5.294192262981406</v>
+        <v>3.758206276027369</v>
       </c>
       <c r="E55" t="n">
-        <v>34195.58257607574</v>
+        <v>67305.95816458848</v>
       </c>
       <c r="F55" t="n">
-        <v>9.825204682524447e-05</v>
+        <v>6.647666394055953e-05</v>
       </c>
       <c r="G55" t="n">
-        <v>3515.331243550878</v>
+        <v>7069.162412737804</v>
       </c>
       <c r="H55" t="n">
-        <v>3.057539792054377e-07</v>
+        <v>3.715500323875517e-07</v>
       </c>
       <c r="I55" t="n">
-        <v>34089.16814724985</v>
+        <v>66929.77305761185</v>
       </c>
       <c r="J55" t="n">
-        <v>33719.0013084842</v>
+        <v>65835.3115968811</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.99558981611416e-06</v>
+        <v>2.432520036101256e-06</v>
       </c>
       <c r="B56" t="n">
-        <v>5379314537.775192</v>
+        <v>8469356591.277208</v>
       </c>
       <c r="C56" t="n">
-        <v>5947485084.446679</v>
+        <v>69835332474.43846</v>
       </c>
       <c r="D56" t="n">
-        <v>1.05980198019802</v>
+        <v>1.214449539881482</v>
       </c>
       <c r="E56" t="n">
-        <v>17986.69616008742</v>
+        <v>34846.12805294045</v>
       </c>
       <c r="F56" t="n">
-        <v>9.050594556303678e-05</v>
+        <v>5.757951363967874e-05</v>
       </c>
       <c r="G56" t="n">
-        <v>1837.54944257585</v>
+        <v>3621.815099680578</v>
       </c>
       <c r="H56" t="n">
-        <v>2.173739619960152e-07</v>
+        <v>2.519024134721117e-07</v>
       </c>
       <c r="I56" t="n">
-        <v>17943.49635279063</v>
+        <v>34693.68105917764</v>
       </c>
       <c r="J56" t="n">
-        <v>17782.21109110923</v>
+        <v>34214.08788163668</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3.836864239484918e-06</v>
+        <v>5.900022385694448e-06</v>
       </c>
       <c r="B57" t="n">
-        <v>8923897544.918446</v>
+        <v>2886035109.225675</v>
       </c>
       <c r="C57" t="n">
-        <v>5275645813182.299</v>
+        <v>5.353085525990016e+34</v>
       </c>
       <c r="D57" t="n">
-        <v>1.561083876533692</v>
+        <v>5.852817139480714</v>
       </c>
       <c r="E57" t="n">
-        <v>58764.08703099637</v>
+        <v>33716.51953983164</v>
       </c>
       <c r="F57" t="n">
-        <v>0.000136702182557034</v>
+        <v>0.0001986014650574254</v>
       </c>
       <c r="G57" t="n">
-        <v>6014.212180386407</v>
+        <v>3403.685770316991</v>
       </c>
       <c r="H57" t="n">
-        <v>3.561895077385821e-07</v>
+        <v>2.096553177330514e-07</v>
       </c>
       <c r="I57" t="n">
-        <v>58610.9720562333</v>
+        <v>33680.92641057183</v>
       </c>
       <c r="J57" t="n">
-        <v>58051.62018795902</v>
+        <v>33518.99567315193</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4.9911570772831e-06</v>
+        <v>3.85358379585559e-06</v>
       </c>
       <c r="B58" t="n">
-        <v>9984354361.444616</v>
+        <v>4519253537.022623</v>
       </c>
       <c r="C58" t="n">
-        <v>2016733712032.083</v>
+        <v>2746192009593500</v>
       </c>
       <c r="D58" t="n">
-        <v>1.48602287747167</v>
+        <v>2.112040803935159</v>
       </c>
       <c r="E58" t="n">
-        <v>85139.0773496558</v>
+        <v>30621.1543944771</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0003033991046688659</v>
+        <v>0.000153719009812664</v>
       </c>
       <c r="G58" t="n">
-        <v>8633.674827681147</v>
+        <v>3116.638639665211</v>
       </c>
       <c r="H58" t="n">
-        <v>4.742205319925126e-07</v>
+        <v>3.041199064643831e-07</v>
       </c>
       <c r="I58" t="n">
-        <v>85006.00280219408</v>
+        <v>30560.5730609021</v>
       </c>
       <c r="J58" t="n">
-        <v>84452.55660395786</v>
+        <v>30322.78067282625</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.230346296972792e-05</v>
+        <v>1.129232689752687e-06</v>
       </c>
       <c r="B59" t="n">
-        <v>2269330732.122569</v>
+        <v>8899161118.441582</v>
       </c>
       <c r="C59" t="n">
-        <v>3.665450344423184e+29</v>
+        <v>10179906628.77111</v>
       </c>
       <c r="D59" t="n">
-        <v>5.141055148240159</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E59" t="n">
-        <v>54561.40877799818</v>
+        <v>16871.18001695865</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0001149445574893499</v>
+        <v>2.811687678692873e-05</v>
       </c>
       <c r="G59" t="n">
-        <v>5666.492787812773</v>
+        <v>1753.544380104243</v>
       </c>
       <c r="H59" t="n">
-        <v>4.923872376100195e-07</v>
+        <v>1.230041273035422e-07</v>
       </c>
       <c r="I59" t="n">
-        <v>54327.68443353933</v>
+        <v>16797.37292983823</v>
       </c>
       <c r="J59" t="n">
-        <v>53587.61395361676</v>
+        <v>16565.17632544323</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.575344018286131e-06</v>
+        <v>5.188177207194669e-06</v>
       </c>
       <c r="B60" t="n">
-        <v>12594438599.18532</v>
+        <v>3890793879.676566</v>
       </c>
       <c r="C60" t="n">
-        <v>14122990028.26291</v>
+        <v>1.377471214545842e+28</v>
       </c>
       <c r="D60" t="n">
-        <v>1.05980198019802</v>
+        <v>4.536385208410741</v>
       </c>
       <c r="E60" t="n">
-        <v>33226.24434915128</v>
+        <v>38715.6338667057</v>
       </c>
       <c r="F60" t="n">
-        <v>9.117086532522473e-05</v>
+        <v>0.0001396241467737814</v>
       </c>
       <c r="G60" t="n">
-        <v>3378.907706999938</v>
+        <v>3929.472302649844</v>
       </c>
       <c r="H60" t="n">
-        <v>1.715977742502118e-07</v>
+        <v>2.320476015806917e-07</v>
       </c>
       <c r="I60" t="n">
-        <v>33163.70738016816</v>
+        <v>38651.29062672873</v>
       </c>
       <c r="J60" t="n">
-        <v>32915.14912921555</v>
+        <v>38387.61211381839</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2.428431383085002e-06</v>
+        <v>5.678445048416077e-06</v>
       </c>
       <c r="B61" t="n">
-        <v>7126728948.893823</v>
+        <v>3631029672.401825</v>
       </c>
       <c r="C61" t="n">
-        <v>30253708177.27902</v>
+        <v>1.146668784050874e+24</v>
       </c>
       <c r="D61" t="n">
-        <v>1.163623351316804</v>
+        <v>3.795385375884316</v>
       </c>
       <c r="E61" t="n">
-        <v>29142.70654101423</v>
+        <v>38654.23532607933</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0001079920101589257</v>
+        <v>0.0001901767241984878</v>
       </c>
       <c r="G61" t="n">
-        <v>2976.364239076627</v>
+        <v>3919.456578521726</v>
       </c>
       <c r="H61" t="n">
-        <v>2.556618735618976e-07</v>
+        <v>2.953773681997352e-07</v>
       </c>
       <c r="I61" t="n">
-        <v>29073.71366881956</v>
+        <v>38594.19860839734</v>
       </c>
       <c r="J61" t="n">
-        <v>28815.14957100108</v>
+        <v>38344.13344221762</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3.406496304373198e-06</v>
+        <v>4.020862318317055e-06</v>
       </c>
       <c r="B62" t="n">
-        <v>3300788932.341217</v>
+        <v>2384285535.266783</v>
       </c>
       <c r="C62" t="n">
-        <v>8.874048406003807e+22</v>
+        <v>2.556439752935066e+35</v>
       </c>
       <c r="D62" t="n">
-        <v>3.488300583870213</v>
+        <v>5.844290646348572</v>
       </c>
       <c r="E62" t="n">
-        <v>20873.59104497406</v>
+        <v>18989.8033804579</v>
       </c>
       <c r="F62" t="n">
-        <v>8.850047713578944e-05</v>
+        <v>8.9700895196611e-05</v>
       </c>
       <c r="G62" t="n">
-        <v>2127.616617352091</v>
+        <v>1926.240336052799</v>
       </c>
       <c r="H62" t="n">
-        <v>1.89650011094742e-07</v>
+        <v>1.43073637718818e-07</v>
       </c>
       <c r="I62" t="n">
-        <v>20828.86047513552</v>
+        <v>18959.51449378344</v>
       </c>
       <c r="J62" t="n">
-        <v>20656.82094596701</v>
+        <v>18834.15481666237</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.110167730644319e-05</v>
+        <v>2.884851357938915e-06</v>
       </c>
       <c r="B63" t="n">
-        <v>2151552162.334291</v>
+        <v>3855613151.995156</v>
       </c>
       <c r="C63" t="n">
-        <v>1.453680587325648e+30</v>
+        <v>1.628538129079032e+21</v>
       </c>
       <c r="D63" t="n">
-        <v>5.228740802071007</v>
+        <v>3.132811441293186</v>
       </c>
       <c r="E63" t="n">
-        <v>46672.80981556957</v>
+        <v>20386.24521138782</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0002142881736528437</v>
+        <v>7.995771167655614e-05</v>
       </c>
       <c r="G63" t="n">
-        <v>4753.049349721923</v>
+        <v>2078.664031462292</v>
       </c>
       <c r="H63" t="n">
-        <v>4.375411399742524e-07</v>
+        <v>1.744895251632879e-07</v>
       </c>
       <c r="I63" t="n">
-        <v>46577.51162871961</v>
+        <v>20341.75686658392</v>
       </c>
       <c r="J63" t="n">
-        <v>46206.42639518439</v>
+        <v>20171.44917691391</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2.608066499420685e-06</v>
+        <v>1.171632719250719e-06</v>
       </c>
       <c r="B64" t="n">
-        <v>5725197051.28875</v>
+        <v>14055746345.08317</v>
       </c>
       <c r="C64" t="n">
-        <v>2.421767692719088e+17</v>
+        <v>16043212020.3137</v>
       </c>
       <c r="D64" t="n">
-        <v>2.405653934485956</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E64" t="n">
-        <v>26776.56742590687</v>
+        <v>27580.65857409471</v>
       </c>
       <c r="F64" t="n">
-        <v>2.086916645169204e-05</v>
+        <v>6.524177381370562e-05</v>
       </c>
       <c r="G64" t="n">
-        <v>2896.841415923794</v>
+        <v>2806.622551952805</v>
       </c>
       <c r="H64" t="n">
-        <v>1.898094686335797e-07</v>
+        <v>1.276226427551203e-07</v>
       </c>
       <c r="I64" t="n">
-        <v>26533.0288999812</v>
+        <v>27526.70669126878</v>
       </c>
       <c r="J64" t="n">
-        <v>25936.80342389093</v>
+        <v>27314.33142692937</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6.798719738023104e-06</v>
+        <v>5.69149469894726e-06</v>
       </c>
       <c r="B65" t="n">
-        <v>3565685367.807933</v>
+        <v>2316389938.203597</v>
       </c>
       <c r="C65" t="n">
-        <v>5.937242820830379e+29</v>
+        <v>2.980030743509963e+38</v>
       </c>
       <c r="D65" t="n">
-        <v>4.938198558128478</v>
+        <v>6.568085495003019</v>
       </c>
       <c r="E65" t="n">
-        <v>47076.04217725175</v>
+        <v>26486.83234648903</v>
       </c>
       <c r="F65" t="n">
-        <v>8.909549281746078e-05</v>
+        <v>0.0001234313566967591</v>
       </c>
       <c r="G65" t="n">
-        <v>4841.759595737913</v>
+        <v>2683.737316845395</v>
       </c>
       <c r="H65" t="n">
-        <v>2.821118760520655e-07</v>
+        <v>1.815062445902537e-07</v>
       </c>
       <c r="I65" t="n">
-        <v>46926.98064612649</v>
+        <v>26447.88336627071</v>
       </c>
       <c r="J65" t="n">
-        <v>46411.00310969088</v>
+        <v>26283.5356217414</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6.304332699115388e-06</v>
+        <v>1.903006058087328e-06</v>
       </c>
       <c r="B66" t="n">
-        <v>3552960466.178642</v>
+        <v>9415271298.687778</v>
       </c>
       <c r="C66" t="n">
-        <v>2.40805628257263e+20</v>
+        <v>10439339998.19713</v>
       </c>
       <c r="D66" t="n">
-        <v>3.119360395351765</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E66" t="n">
-        <v>41134.31360723434</v>
+        <v>30071.16867262626</v>
       </c>
       <c r="F66" t="n">
-        <v>8.24015379412926e-05</v>
+        <v>5.100975462084469e-05</v>
       </c>
       <c r="G66" t="n">
-        <v>4285.301084368695</v>
+        <v>3117.097444492025</v>
       </c>
       <c r="H66" t="n">
-        <v>3.825497582583737e-07</v>
+        <v>2.072890747430019e-07</v>
       </c>
       <c r="I66" t="n">
-        <v>40943.3472476285</v>
+        <v>29948.96803126026</v>
       </c>
       <c r="J66" t="n">
-        <v>40353.56825834756</v>
+        <v>29555.76469166531</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4.009496853391559e-06</v>
+        <v>5.218302210727821e-06</v>
       </c>
       <c r="B67" t="n">
-        <v>2550847795.600993</v>
+        <v>5411657557.981539</v>
       </c>
       <c r="C67" t="n">
-        <v>1.279121342274326e+30</v>
+        <v>2.176163302879067e+25</v>
       </c>
       <c r="D67" t="n">
-        <v>4.859951229990035</v>
+        <v>3.983910486962759</v>
       </c>
       <c r="E67" t="n">
-        <v>19788.51194774975</v>
+        <v>53265.61303110953</v>
       </c>
       <c r="F67" t="n">
-        <v>0.000108162911246111</v>
+        <v>0.0001671542340081538</v>
       </c>
       <c r="G67" t="n">
-        <v>2006.638754134372</v>
+        <v>5401.350260620742</v>
       </c>
       <c r="H67" t="n">
-        <v>1.687614019393641e-07</v>
+        <v>2.607746806455104e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>19757.63688179486</v>
+        <v>53182.51418943197</v>
       </c>
       <c r="J67" t="n">
-        <v>19629.17553084892</v>
+        <v>52836.75732154575</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3.549441119749793e-06</v>
+        <v>1.360758378887815e-05</v>
       </c>
       <c r="B68" t="n">
-        <v>1915321495.486168</v>
+        <v>2730440279.609994</v>
       </c>
       <c r="C68" t="n">
-        <v>2.258976981133836e+36</v>
+        <v>3.212462090210398e+28</v>
       </c>
       <c r="D68" t="n">
-        <v>5.986692607138855</v>
+        <v>4.945547209948804</v>
       </c>
       <c r="E68" t="n">
-        <v>13541.65758685235</v>
+        <v>72051.56096278019</v>
       </c>
       <c r="F68" t="n">
-        <v>2.95295772979468e-05</v>
+        <v>0.0003530342400999035</v>
       </c>
       <c r="G68" t="n">
-        <v>1405.1369076962</v>
+        <v>7308.733917327568</v>
       </c>
       <c r="H68" t="n">
-        <v>1.235001020641366e-07</v>
+        <v>5.638942886765981e-07</v>
       </c>
       <c r="I68" t="n">
-        <v>13485.02297684016</v>
+        <v>71936.47449494737</v>
       </c>
       <c r="J68" t="n">
-        <v>13304.37393445276</v>
+        <v>71460.3170846491</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.399720136497225e-06</v>
+        <v>2.14543094854938e-06</v>
       </c>
       <c r="B69" t="n">
-        <v>8908697759.093161</v>
+        <v>11131432794.92159</v>
       </c>
       <c r="C69" t="n">
-        <v>10060786913.63093</v>
+        <v>152713059743.862</v>
       </c>
       <c r="D69" t="n">
-        <v>1.05980198019802</v>
+        <v>1.250998354074125</v>
       </c>
       <c r="E69" t="n">
-        <v>20862.39491804246</v>
+        <v>40356.39804616239</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0001656680172062921</v>
+        <v>0.0001282433379563329</v>
       </c>
       <c r="G69" t="n">
-        <v>2103.519559910288</v>
+        <v>4097.825572899468</v>
       </c>
       <c r="H69" t="n">
-        <v>1.524675608680292e-07</v>
+        <v>2.195689430541157e-07</v>
       </c>
       <c r="I69" t="n">
-        <v>20843.19484236908</v>
+        <v>40287.30274806992</v>
       </c>
       <c r="J69" t="n">
-        <v>20753.09620949982</v>
+        <v>40006.19097208697</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>9.886996149550922e-06</v>
+        <v>3.851042150640746e-06</v>
       </c>
       <c r="B70" t="n">
-        <v>1858022155.107461</v>
+        <v>6053840787.802942</v>
       </c>
       <c r="C70" t="n">
-        <v>2.043794925646221e+42</v>
+        <v>1.594349749266789e+16</v>
       </c>
       <c r="D70" t="n">
-        <v>7.617251385741232</v>
+        <v>2.228513487473129</v>
       </c>
       <c r="E70" t="n">
-        <v>37554.95025312097</v>
+        <v>41263.58792732758</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0001483270427515913</v>
+        <v>8.309159335794658e-05</v>
       </c>
       <c r="G70" t="n">
-        <v>3817.85780685703</v>
+        <v>4257.83866196259</v>
       </c>
       <c r="H70" t="n">
-        <v>2.736756229346753e-07</v>
+        <v>2.941757391001566e-07</v>
       </c>
       <c r="I70" t="n">
-        <v>37485.65827362661</v>
+        <v>41117.49918373887</v>
       </c>
       <c r="J70" t="n">
-        <v>37208.88410436144</v>
+        <v>40627.78313456759</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2.045807680394766e-06</v>
+        <v>7.099714574511948e-06</v>
       </c>
       <c r="B71" t="n">
-        <v>10610391991.07631</v>
+        <v>2183304687.342275</v>
       </c>
       <c r="C71" t="n">
-        <v>11713653610.60887</v>
+        <v>3.36199147459814e+33</v>
       </c>
       <c r="D71" t="n">
-        <v>1.05980198019802</v>
+        <v>5.7192225499587</v>
       </c>
       <c r="E71" t="n">
-        <v>36339.07249594975</v>
+        <v>30700.91320287912</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0001448286782584842</v>
+        <v>6.154704205228472e-05</v>
       </c>
       <c r="G71" t="n">
-        <v>3684.229821312211</v>
+        <v>3185.802806113995</v>
       </c>
       <c r="H71" t="n">
-        <v>2.22844052108476e-07</v>
+        <v>2.577447646809691e-07</v>
       </c>
       <c r="I71" t="n">
-        <v>36283.15852737505</v>
+        <v>30572.34488529459</v>
       </c>
       <c r="J71" t="n">
-        <v>36049.74468136064</v>
+        <v>30162.4115608075</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>8.541204139752655e-06</v>
+        <v>5.872556769993132e-06</v>
       </c>
       <c r="B72" t="n">
-        <v>3789410022.1747</v>
+        <v>3301737452.873795</v>
       </c>
       <c r="C72" t="n">
-        <v>1.080191297461213e+21</v>
+        <v>7.438040334960571e+23</v>
       </c>
       <c r="D72" t="n">
-        <v>3.296177838851641</v>
+        <v>3.775279637950889</v>
       </c>
       <c r="E72" t="n">
-        <v>59854.19589954857</v>
+        <v>36375.70291762448</v>
       </c>
       <c r="F72" t="n">
-        <v>9.708693077834375e-05</v>
+        <v>0.0001053275847530683</v>
       </c>
       <c r="G72" t="n">
-        <v>6261.186624219298</v>
+        <v>3732.932087091528</v>
       </c>
       <c r="H72" t="n">
-        <v>4.970110108443792e-07</v>
+        <v>3.068051466012425e-07</v>
       </c>
       <c r="I72" t="n">
-        <v>59547.78808369918</v>
+        <v>36269.74536725882</v>
       </c>
       <c r="J72" t="n">
-        <v>58630.43145904878</v>
+        <v>35894.29051568102</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1.282255617887248e-05</v>
+        <v>7.2028383280806e-06</v>
       </c>
       <c r="B73" t="n">
-        <v>2265814731.563877</v>
+        <v>2605471529.785024</v>
       </c>
       <c r="C73" t="n">
-        <v>7.429921397309086e+29</v>
+        <v>9.06214353818558e+17</v>
       </c>
       <c r="D73" t="n">
-        <v>5.218714373657768</v>
+        <v>2.701475454810566</v>
       </c>
       <c r="E73" t="n">
-        <v>56872.62475427108</v>
+        <v>34102.82635313582</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0001241166200751542</v>
+        <v>4.742278118784276e-05</v>
       </c>
       <c r="G73" t="n">
-        <v>5896.036632545985</v>
+        <v>3724.135369904301</v>
       </c>
       <c r="H73" t="n">
-        <v>5.062451761007495e-07</v>
+        <v>4.849311185980072e-07</v>
       </c>
       <c r="I73" t="n">
-        <v>56640.65346858343</v>
+        <v>33754.10109247947</v>
       </c>
       <c r="J73" t="n">
-        <v>55895.07882233625</v>
+        <v>32938.23470090162</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4.435135066932549e-06</v>
+        <v>1.407093345539822e-05</v>
       </c>
       <c r="B74" t="n">
-        <v>2345702607.913626</v>
+        <v>1011476835.010214</v>
       </c>
       <c r="C74" t="n">
-        <v>1.214397989519475e+38</v>
+        <v>3.987536112858301e+63</v>
       </c>
       <c r="D74" t="n">
-        <v>6.382195761854057</v>
+        <v>12.26074249046263</v>
       </c>
       <c r="E74" t="n">
-        <v>20815.5006110513</v>
+        <v>30400.13851634714</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0001786002301399802</v>
+        <v>8.395679666318286e-05</v>
       </c>
       <c r="G74" t="n">
-        <v>2096.794109931537</v>
+        <v>3119.798692372622</v>
       </c>
       <c r="H74" t="n">
-        <v>1.453292310878487e-07</v>
+        <v>2.448263570697963e-07</v>
       </c>
       <c r="I74" t="n">
-        <v>20798.56277902196</v>
+        <v>30311.48869330501</v>
       </c>
       <c r="J74" t="n">
-        <v>20717.10551669217</v>
+        <v>29997.45702705808</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>5.107399630190671e-06</v>
+        <v>7.515421763204455e-06</v>
       </c>
       <c r="B75" t="n">
-        <v>2566156959.055822</v>
+        <v>8610540195.680521</v>
       </c>
       <c r="C75" t="n">
-        <v>1.154159412785191e+42</v>
+        <v>8794232279.807817</v>
       </c>
       <c r="D75" t="n">
-        <v>7.18631755709253</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E75" t="n">
-        <v>26617.12952161649</v>
+        <v>108557.20463992</v>
       </c>
       <c r="F75" t="n">
-        <v>8.54328876024044e-05</v>
+        <v>0.0002274328525933256</v>
       </c>
       <c r="G75" t="n">
-        <v>2703.634586397697</v>
+        <v>11207.39227895623</v>
       </c>
       <c r="H75" t="n">
-        <v>1.495063237749771e-07</v>
+        <v>8.186336648680188e-07</v>
       </c>
       <c r="I75" t="n">
-        <v>26570.54992802088</v>
+        <v>108166.4581788487</v>
       </c>
       <c r="J75" t="n">
-        <v>26382.05293958833</v>
+        <v>106862.9257889577</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2.355150008314258e-06</v>
+        <v>3.219614930649564e-06</v>
       </c>
       <c r="B76" t="n">
-        <v>8932892121.907604</v>
+        <v>4490570521.767177</v>
       </c>
       <c r="C76" t="n">
-        <v>9779033212.488623</v>
+        <v>2.041606283871838e+18</v>
       </c>
       <c r="D76" t="n">
-        <v>1.05980198019802</v>
+        <v>2.615041396954301</v>
       </c>
       <c r="E76" t="n">
-        <v>35224.13582374471</v>
+        <v>26034.12333243746</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0001546913860540007</v>
+        <v>4.793493351093676e-05</v>
       </c>
       <c r="G76" t="n">
-        <v>3574.98764547998</v>
+        <v>2711.762924415588</v>
       </c>
       <c r="H76" t="n">
-        <v>2.565398381312104e-07</v>
+        <v>2.216654195372748e-07</v>
       </c>
       <c r="I76" t="n">
-        <v>35165.72019807191</v>
+        <v>25913.73378669096</v>
       </c>
       <c r="J76" t="n">
-        <v>34926.20984206545</v>
+        <v>25541.46568677525</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1.79720219814648e-06</v>
+        <v>1.10961672255914e-05</v>
       </c>
       <c r="B77" t="n">
-        <v>10434008715.14014</v>
+        <v>888631968.3626577</v>
       </c>
       <c r="C77" t="n">
-        <v>11608525859.77732</v>
+        <v>1.636224860137346e+61</v>
       </c>
       <c r="D77" t="n">
-        <v>1.05980198019802</v>
+        <v>11.55671590075302</v>
       </c>
       <c r="E77" t="n">
-        <v>31378.79667876631</v>
+        <v>21149.66452858451</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0001774815507563969</v>
+        <v>1.818636572538166e-05</v>
       </c>
       <c r="G77" t="n">
-        <v>3169.029718955867</v>
+        <v>2329.11279513396</v>
       </c>
       <c r="H77" t="n">
-        <v>1.95764159129533e-07</v>
+        <v>2.046023364216989e-07</v>
       </c>
       <c r="I77" t="n">
-        <v>31344.18551090049</v>
+        <v>20911.72414827838</v>
       </c>
       <c r="J77" t="n">
-        <v>31188.23595542648</v>
+        <v>20375.91255605582</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1.870259611548814e-06</v>
+        <v>3.911773493636431e-06</v>
       </c>
       <c r="B78" t="n">
-        <v>13000216740.86377</v>
+        <v>1939408009.250391</v>
       </c>
       <c r="C78" t="n">
-        <v>14429178316.35742</v>
+        <v>5.635904320765717e+36</v>
       </c>
       <c r="D78" t="n">
-        <v>1.05980198019802</v>
+        <v>6.097627620105548</v>
       </c>
       <c r="E78" t="n">
-        <v>40755.95258566954</v>
+        <v>15111.95826435477</v>
       </c>
       <c r="F78" t="n">
-        <v>7.205023952347994e-05</v>
+        <v>6.900298417625891e-05</v>
       </c>
       <c r="G78" t="n">
-        <v>4179.308991596299</v>
+        <v>1537.566731503606</v>
       </c>
       <c r="H78" t="n">
-        <v>2.037220968160308e-07</v>
+        <v>1.337918483199491e-07</v>
       </c>
       <c r="I78" t="n">
-        <v>40640.71510452581</v>
+        <v>15082.65725872351</v>
       </c>
       <c r="J78" t="n">
-        <v>40229.00741655332</v>
+        <v>14967.06014804323</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>6.482355621209123e-06</v>
+        <v>6.390279905832103e-06</v>
       </c>
       <c r="B79" t="n">
-        <v>1977566520.14719</v>
+        <v>3534404915.328825</v>
       </c>
       <c r="C79" t="n">
-        <v>6.017867976438455e+37</v>
+        <v>1.210501905941191e+23</v>
       </c>
       <c r="D79" t="n">
-        <v>6.508258754230982</v>
+        <v>3.638343555253461</v>
       </c>
       <c r="E79" t="n">
-        <v>25705.19867382592</v>
+        <v>42213.77021615933</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0003236234075084104</v>
+        <v>9.154300427949524e-05</v>
       </c>
       <c r="G79" t="n">
-        <v>2585.42657565991</v>
+        <v>4364.149374712564</v>
       </c>
       <c r="H79" t="n">
-        <v>2.085250358477307e-07</v>
+        <v>3.440112357121958e-07</v>
       </c>
       <c r="I79" t="n">
-        <v>25688.6356646289</v>
+        <v>42055.13426827418</v>
       </c>
       <c r="J79" t="n">
-        <v>25605.12021722161</v>
+        <v>41532.59793906683</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4.970915240843809e-06</v>
+        <v>1.157418566669284e-05</v>
       </c>
       <c r="B80" t="n">
-        <v>3424494951.347258</v>
+        <v>1056301379.714429</v>
       </c>
       <c r="C80" t="n">
-        <v>4.699375658853646e+28</v>
+        <v>1.867888919892842e+80</v>
       </c>
       <c r="D80" t="n">
-        <v>4.634405932467148</v>
+        <v>15.4379370841756</v>
       </c>
       <c r="E80" t="n">
-        <v>32864.81070028093</v>
+        <v>26431.46224644595</v>
       </c>
       <c r="F80" t="n">
-        <v>3.970765239276479e-05</v>
+        <v>0.0001173866437117625</v>
       </c>
       <c r="G80" t="n">
-        <v>3449.024791672007</v>
+        <v>2675.692100663988</v>
       </c>
       <c r="H80" t="n">
-        <v>2.18208048877157e-07</v>
+        <v>1.606020009602323e-07</v>
       </c>
       <c r="I80" t="n">
-        <v>32684.20656512103</v>
+        <v>26395.30016197995</v>
       </c>
       <c r="J80" t="n">
-        <v>32155.82346971353</v>
+        <v>26240.11464133796</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3.609928967089435e-06</v>
+        <v>8.438432800220167e-06</v>
       </c>
       <c r="B81" t="n">
-        <v>7151377793.093711</v>
+        <v>4269625891.178151</v>
       </c>
       <c r="C81" t="n">
-        <v>9.509756949872517e+21</v>
+        <v>957154997868876.4</v>
       </c>
       <c r="D81" t="n">
-        <v>3.261526985251812</v>
+        <v>2.10140036536167</v>
       </c>
       <c r="E81" t="n">
-        <v>47531.56612416225</v>
+        <v>63264.98728304538</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0001064710158427139</v>
+        <v>0.0006004984119442384</v>
       </c>
       <c r="G81" t="n">
-        <v>4838.244019739586</v>
+        <v>6389.833424690118</v>
       </c>
       <c r="H81" t="n">
-        <v>2.11773714743965e-07</v>
+        <v>6.679556406550265e-07</v>
       </c>
       <c r="I81" t="n">
-        <v>47437.02456046962</v>
+        <v>63194.61539817251</v>
       </c>
       <c r="J81" t="n">
-        <v>47066.43293337614</v>
+        <v>62878.12687200471</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2.849008969840443e-06</v>
+        <v>6.157361152228287e-06</v>
       </c>
       <c r="B82" t="n">
-        <v>3749376433.010259</v>
+        <v>3232702623.052841</v>
       </c>
       <c r="C82" t="n">
-        <v>4.664043630126341e+19</v>
+        <v>2245861748119174</v>
       </c>
       <c r="D82" t="n">
-        <v>2.856769064968423</v>
+        <v>2.166106022444916</v>
       </c>
       <c r="E82" t="n">
-        <v>19395.31742353888</v>
+        <v>35273.2081017387</v>
       </c>
       <c r="F82" t="n">
-        <v>5.560026018811023e-05</v>
+        <v>6.449162064525351e-05</v>
       </c>
       <c r="G82" t="n">
-        <v>1997.422350422929</v>
+        <v>3762.911232768154</v>
       </c>
       <c r="H82" t="n">
-        <v>1.84393468725731e-07</v>
+        <v>4.786008348754722e-07</v>
       </c>
       <c r="I82" t="n">
-        <v>19330.99452568438</v>
+        <v>35011.44096552282</v>
       </c>
       <c r="J82" t="n">
-        <v>19111.25849453102</v>
+        <v>34320.60799257916</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>8.242500096203821e-06</v>
+        <v>4.251546501828051e-06</v>
       </c>
       <c r="B83" t="n">
-        <v>3922146547.077455</v>
+        <v>4604934292.195121</v>
       </c>
       <c r="C83" t="n">
-        <v>8.944489091833796e+18</v>
+        <v>2.59029417070604e+20</v>
       </c>
       <c r="D83" t="n">
-        <v>2.88014723758024</v>
+        <v>3.037420166741165</v>
       </c>
       <c r="E83" t="n">
-        <v>58699.20355880319</v>
+        <v>35785.0171686438</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0002190570531930158</v>
+        <v>8.708393908135724e-05</v>
       </c>
       <c r="G83" t="n">
-        <v>5997.825183196284</v>
+        <v>3675.824199461365</v>
       </c>
       <c r="H83" t="n">
-        <v>5.303584084867285e-07</v>
+        <v>2.631525027416174e-07</v>
       </c>
       <c r="I83" t="n">
-        <v>58557.08708400768</v>
+        <v>35676.88107686937</v>
       </c>
       <c r="J83" t="n">
-        <v>58027.62342697538</v>
+        <v>35297.60819143554</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.323863036535314e-06</v>
+        <v>3.556838948978036e-06</v>
       </c>
       <c r="B84" t="n">
-        <v>15176375033.50193</v>
+        <v>2995891540.254252</v>
       </c>
       <c r="C84" t="n">
-        <v>17196215277.8832</v>
+        <v>5.921988864477946e+22</v>
       </c>
       <c r="D84" t="n">
-        <v>1.05980198019802</v>
+        <v>3.472464426073452</v>
       </c>
       <c r="E84" t="n">
-        <v>33600.54888625658</v>
+        <v>19988.32713519023</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0002766790893580762</v>
+        <v>1.527667763078186e-05</v>
       </c>
       <c r="G84" t="n">
-        <v>3375.816181618739</v>
+        <v>2232.8563734903</v>
       </c>
       <c r="H84" t="n">
-        <v>1.442046612324936e-07</v>
+        <v>1.98732878621098e-07</v>
       </c>
       <c r="I84" t="n">
-        <v>33583.03633848648</v>
+        <v>19728.30084633326</v>
       </c>
       <c r="J84" t="n">
-        <v>33485.99192373411</v>
+        <v>19177.0249561625</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2.568086311849477e-06</v>
+        <v>1.144926587967269e-06</v>
       </c>
       <c r="B85" t="n">
-        <v>5010222515.153585</v>
+        <v>11283854596.35976</v>
       </c>
       <c r="C85" t="n">
-        <v>1.55541929899787e+18</v>
+        <v>12897149710.17609</v>
       </c>
       <c r="D85" t="n">
-        <v>2.557516707052066</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E85" t="n">
-        <v>23049.19613202176</v>
+        <v>21652.45867411136</v>
       </c>
       <c r="F85" t="n">
-        <v>9.974700551044669e-05</v>
+        <v>4.662394774668736e-05</v>
       </c>
       <c r="G85" t="n">
-        <v>2342.248441451554</v>
+        <v>2217.371887553094</v>
       </c>
       <c r="H85" t="n">
-        <v>1.794923449709753e-07</v>
+        <v>1.247136193076199e-07</v>
       </c>
       <c r="I85" t="n">
-        <v>23007.71965618912</v>
+        <v>21594.54087395363</v>
       </c>
       <c r="J85" t="n">
-        <v>22841.02114380627</v>
+        <v>21384.45597694451</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7.664413358424158e-06</v>
+        <v>8.747622229903298e-06</v>
       </c>
       <c r="B86" t="n">
-        <v>4086681065.964694</v>
+        <v>2298040877.829451</v>
       </c>
       <c r="C86" t="n">
-        <v>1.091935876155669e+21</v>
+        <v>1.816588474270295e+28</v>
       </c>
       <c r="D86" t="n">
-        <v>3.26977482503503</v>
+        <v>4.762698887288253</v>
       </c>
       <c r="E86" t="n">
-        <v>57748.44620478991</v>
+        <v>38798.21683181628</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0001466133114622527</v>
+        <v>0.0002223226639031686</v>
       </c>
       <c r="G86" t="n">
-        <v>5933.926440640052</v>
+        <v>3938.697588924165</v>
       </c>
       <c r="H86" t="n">
-        <v>4.487569022789501e-07</v>
+        <v>3.748582415851556e-07</v>
       </c>
       <c r="I86" t="n">
-        <v>57571.68862683317</v>
+        <v>38732.79915876901</v>
       </c>
       <c r="J86" t="n">
-        <v>56953.95962453196</v>
+        <v>38465.65510673587</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4.587891556554006e-06</v>
+        <v>4.382426126587078e-06</v>
       </c>
       <c r="B87" t="n">
-        <v>3232218558.593748</v>
+        <v>2755298741.385623</v>
       </c>
       <c r="C87" t="n">
-        <v>3.376198888610927e+23</v>
+        <v>4.573810990196929e+26</v>
       </c>
       <c r="D87" t="n">
-        <v>3.657805078692776</v>
+        <v>4.241666537473982</v>
       </c>
       <c r="E87" t="n">
-        <v>27670.27921382385</v>
+        <v>22959.84520283685</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0001695046345685114</v>
+        <v>0.0001262384684377111</v>
       </c>
       <c r="G87" t="n">
-        <v>2803.158344541355</v>
+        <v>2329.98476013721</v>
       </c>
       <c r="H87" t="n">
-        <v>2.459226750133515e-07</v>
+        <v>2.07712308535251e-07</v>
       </c>
       <c r="I87" t="n">
-        <v>27630.13429920276</v>
+        <v>22922.06715855515</v>
       </c>
       <c r="J87" t="n">
-        <v>27460.20341045213</v>
+        <v>22766.87769043597</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>9.92382902342357e-06</v>
+        <v>6.248407320006229e-06</v>
       </c>
       <c r="B88" t="n">
-        <v>2489523187.31364</v>
+        <v>3626940424.359356</v>
       </c>
       <c r="C88" t="n">
-        <v>2.837697533033391e+36</v>
+        <v>6.332936633440312e+26</v>
       </c>
       <c r="D88" t="n">
-        <v>6.427061658145814</v>
+        <v>4.341248289839321</v>
       </c>
       <c r="E88" t="n">
-        <v>49956.56792054175</v>
+        <v>43236.68560294834</v>
       </c>
       <c r="F88" t="n">
-        <v>3.082018306449411e-05</v>
+        <v>0.0001429772710357483</v>
       </c>
       <c r="G88" t="n">
-        <v>5466.911113855975</v>
+        <v>4402.683098457917</v>
       </c>
       <c r="H88" t="n">
-        <v>3.230393713854884e-07</v>
+        <v>2.903214373309653e-07</v>
       </c>
       <c r="I88" t="n">
-        <v>49432.95200742864</v>
+        <v>43148.89167165603</v>
       </c>
       <c r="J88" t="n">
-        <v>48219.82747843143</v>
+        <v>42806.54567426418</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>6.968091249740581e-06</v>
+        <v>4.27618563148119e-06</v>
       </c>
       <c r="B89" t="n">
-        <v>3100472548.505892</v>
+        <v>9876313281.282448</v>
       </c>
       <c r="C89" t="n">
-        <v>1.412059337080039e+34</v>
+        <v>10432963919.82084</v>
       </c>
       <c r="D89" t="n">
-        <v>5.802758235334235</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E89" t="n">
-        <v>42724.95621086025</v>
+        <v>70716.01438011775</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0002875193388463503</v>
+        <v>0.0002672787426730811</v>
       </c>
       <c r="G89" t="n">
-        <v>4305.875626250329</v>
+        <v>7182.516022697542</v>
       </c>
       <c r="H89" t="n">
-        <v>2.495912320908921e-07</v>
+        <v>4.657928224726536e-07</v>
       </c>
       <c r="I89" t="n">
-        <v>42687.86731623325</v>
+        <v>70592.77595268913</v>
       </c>
       <c r="J89" t="n">
-        <v>42511.89486629768</v>
+        <v>70093.55029322908</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4.594405317875789e-06</v>
+        <v>5.870334126337893e-06</v>
       </c>
       <c r="B90" t="n">
-        <v>2550683653.728129</v>
+        <v>2446399999.071331</v>
       </c>
       <c r="C90" t="n">
-        <v>5.614400073153928e+37</v>
+        <v>1.348682252921788e+22</v>
       </c>
       <c r="D90" t="n">
-        <v>6.328246969846115</v>
+        <v>3.469322788579481</v>
       </c>
       <c r="E90" t="n">
-        <v>23472.4677747282</v>
+        <v>26638.31390492601</v>
       </c>
       <c r="F90" t="n">
-        <v>5.212789167933043e-05</v>
+        <v>0.0001649920334435949</v>
       </c>
       <c r="G90" t="n">
-        <v>2408.747501543719</v>
+        <v>2711.525491943376</v>
       </c>
       <c r="H90" t="n">
-        <v>1.517571382086255e-07</v>
+        <v>3.282300995189762e-07</v>
       </c>
       <c r="I90" t="n">
-        <v>23404.13363687164</v>
+        <v>26585.32045886959</v>
       </c>
       <c r="J90" t="n">
-        <v>23161.95686613785</v>
+        <v>26377.60175608772</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4.370407984837527e-06</v>
+        <v>4.87460351264533e-06</v>
       </c>
       <c r="B91" t="n">
-        <v>2640755852.553349</v>
+        <v>2146974882.985356</v>
       </c>
       <c r="C91" t="n">
-        <v>8.057278009646429e+30</v>
+        <v>1.797470424144576e+28</v>
       </c>
       <c r="D91" t="n">
-        <v>5.032384569148459</v>
+        <v>4.588441165654902</v>
       </c>
       <c r="E91" t="n">
-        <v>22444.38393780284</v>
+        <v>20106.46089430291</v>
       </c>
       <c r="F91" t="n">
-        <v>8.150585913897968e-05</v>
+        <v>0.0001142661654830823</v>
       </c>
       <c r="G91" t="n">
-        <v>2288.628258897407</v>
+        <v>2044.830690543642</v>
       </c>
       <c r="H91" t="n">
-        <v>1.783040906599146e-07</v>
+        <v>2.158589336767269e-07</v>
       </c>
       <c r="I91" t="n">
-        <v>22395.2840876727</v>
+        <v>20068.47800417696</v>
       </c>
       <c r="J91" t="n">
-        <v>22207.44106305349</v>
+        <v>19917.6500896157</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>5.211273622048677e-06</v>
+        <v>3.724729157431353e-06</v>
       </c>
       <c r="B92" t="n">
-        <v>1662968311.435907</v>
+        <v>2810141232.264959</v>
       </c>
       <c r="C92" t="n">
-        <v>3.546951379905081e+60</v>
+        <v>3.93280244370612e+37</v>
       </c>
       <c r="D92" t="n">
-        <v>10.72464433072561</v>
+        <v>6.203015150536508</v>
       </c>
       <c r="E92" t="n">
-        <v>18315.27625101465</v>
+        <v>20902.21840942793</v>
       </c>
       <c r="F92" t="n">
-        <v>4.489271617271129e-05</v>
+        <v>5.338680738987222e-05</v>
       </c>
       <c r="G92" t="n">
-        <v>1869.492163640048</v>
+        <v>2134.396815299177</v>
       </c>
       <c r="H92" t="n">
-        <v>1.033946398916365e-07</v>
+        <v>1.253647287692805e-07</v>
       </c>
       <c r="I92" t="n">
-        <v>18273.09343041623</v>
+        <v>20853.1351045875</v>
       </c>
       <c r="J92" t="n">
-        <v>18113.85839868793</v>
+        <v>20668.79073836565</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4.174676950520057e-06</v>
+        <v>1.992701825215781e-06</v>
       </c>
       <c r="B93" t="n">
-        <v>4146405682.561856</v>
+        <v>8635429861.653545</v>
       </c>
       <c r="C93" t="n">
-        <v>2.053053385586421e+17</v>
+        <v>5657498891147.627</v>
       </c>
       <c r="D93" t="n">
-        <v>2.471165684454101</v>
+        <v>1.54110729329549</v>
       </c>
       <c r="E93" t="n">
-        <v>30876.25072137923</v>
+        <v>29551.87720639768</v>
       </c>
       <c r="F93" t="n">
-        <v>0.000277626857068088</v>
+        <v>4.465011727172301e-05</v>
       </c>
       <c r="G93" t="n">
-        <v>3117.50634349377</v>
+        <v>3066.059786162569</v>
       </c>
       <c r="H93" t="n">
-        <v>2.985337798434441e-07</v>
+        <v>1.861303351457384e-07</v>
       </c>
       <c r="I93" t="n">
-        <v>30843.04930876162</v>
+        <v>29428.68602248345</v>
       </c>
       <c r="J93" t="n">
-        <v>30692.60986443211</v>
+        <v>29035.35117340942</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>3.488085860816901e-06</v>
+        <v>1.03272956674941e-05</v>
       </c>
       <c r="B94" t="n">
-        <v>2885176410.875945</v>
+        <v>1885514139.444468</v>
       </c>
       <c r="C94" t="n">
-        <v>3.440244296992651e+24</v>
+        <v>2.466471646882154e+34</v>
       </c>
       <c r="D94" t="n">
-        <v>3.792724898609005</v>
+        <v>6.058190387190446</v>
       </c>
       <c r="E94" t="n">
-        <v>18911.77389564573</v>
+        <v>38783.23545388658</v>
       </c>
       <c r="F94" t="n">
-        <v>4.519668394516483e-05</v>
+        <v>0.0001355549828833002</v>
       </c>
       <c r="G94" t="n">
-        <v>1959.545345420223</v>
+        <v>3969.829561413046</v>
       </c>
       <c r="H94" t="n">
-        <v>1.815450411318309e-07</v>
+        <v>3.553682206224092e-07</v>
       </c>
       <c r="I94" t="n">
-        <v>18835.80950025056</v>
+        <v>38681.56210274838</v>
       </c>
       <c r="J94" t="n">
-        <v>18590.52060061644</v>
+        <v>38310.74707961096</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4.438984142041004e-06</v>
+        <v>4.413490959903755e-06</v>
       </c>
       <c r="B95" t="n">
-        <v>4429462804.104851</v>
+        <v>3335843186.729012</v>
       </c>
       <c r="C95" t="n">
-        <v>5.042411596114895e+23</v>
+        <v>9.136755215963197e+16</v>
       </c>
       <c r="D95" t="n">
-        <v>3.657670506634589</v>
+        <v>2.430153393326568</v>
       </c>
       <c r="E95" t="n">
-        <v>36700.49122378264</v>
+        <v>26248.71172968821</v>
       </c>
       <c r="F95" t="n">
-        <v>0.000134314224502145</v>
+        <v>0.000139026852312371</v>
       </c>
       <c r="G95" t="n">
-        <v>3728.565076902693</v>
+        <v>2679.092616202802</v>
       </c>
       <c r="H95" t="n">
-        <v>2.379479217632793e-07</v>
+        <v>3.190944572519997e-07</v>
       </c>
       <c r="I95" t="n">
-        <v>36635.47349653327</v>
+        <v>26188.46568165046</v>
       </c>
       <c r="J95" t="n">
-        <v>36373.15260302457</v>
+        <v>25960.83914533764</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.586835863660611e-06</v>
+        <v>2.028342030646927e-05</v>
       </c>
       <c r="B96" t="n">
-        <v>4596635459.601551</v>
+        <v>1083938963.915483</v>
       </c>
       <c r="C96" t="n">
-        <v>1537208197109.66</v>
+        <v>3.409994879483989e+42</v>
       </c>
       <c r="D96" t="n">
-        <v>1.482111049816301</v>
+        <v>8.153071202395843</v>
       </c>
       <c r="E96" t="n">
-        <v>12452.80251508037</v>
+        <v>45315.31235822103</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0001470155337119163</v>
+        <v>0.0001937044595282755</v>
       </c>
       <c r="G96" t="n">
-        <v>1256.787874911181</v>
+        <v>4642.231502581854</v>
       </c>
       <c r="H96" t="n">
-        <v>1.509521334495018e-07</v>
+        <v>5.257760499934763e-07</v>
       </c>
       <c r="I96" t="n">
-        <v>12440.01626685465</v>
+        <v>45192.31206182131</v>
       </c>
       <c r="J96" t="n">
-        <v>12381.49176760674</v>
+        <v>44747.92585914543</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>8.562198591445636e-06</v>
+        <v>3.371626405837405e-06</v>
       </c>
       <c r="B97" t="n">
-        <v>1809680269.154519</v>
+        <v>4195040380.739286</v>
       </c>
       <c r="C97" t="n">
-        <v>2.775534913732903e+38</v>
+        <v>4.658439518050506e+33</v>
       </c>
       <c r="D97" t="n">
-        <v>6.777319058990563</v>
+        <v>5.415632254625293</v>
       </c>
       <c r="E97" t="n">
-        <v>31242.69365018229</v>
+        <v>27813.55406929293</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0001942196187606583</v>
+        <v>3.292566022717369e-05</v>
       </c>
       <c r="G97" t="n">
-        <v>3162.642404394491</v>
+        <v>2879.201157177503</v>
       </c>
       <c r="H97" t="n">
-        <v>2.650503101725254e-07</v>
+        <v>1.286996787936675e-07</v>
       </c>
       <c r="I97" t="n">
-        <v>31200.05693976422</v>
+        <v>27704.83656901714</v>
       </c>
       <c r="J97" t="n">
-        <v>31016.98340547877</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>5.633980028832379e-06</v>
-      </c>
-      <c r="B98" t="n">
-        <v>1832699184.111412</v>
-      </c>
-      <c r="C98" t="n">
-        <v>4.118316882710075e+35</v>
-      </c>
-      <c r="D98" t="n">
-        <v>6.039935927334142</v>
-      </c>
-      <c r="E98" t="n">
-        <v>20618.42819347581</v>
-      </c>
-      <c r="F98" t="n">
-        <v>3.493998086849626e-05</v>
-      </c>
-      <c r="G98" t="n">
-        <v>2165.096998607803</v>
-      </c>
-      <c r="H98" t="n">
-        <v>1.944161048602342e-07</v>
-      </c>
-      <c r="I98" t="n">
-        <v>20503.70132763112</v>
-      </c>
-      <c r="J98" t="n">
-        <v>20169.42675859095</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>1.839246122242665e-06</v>
-      </c>
-      <c r="B99" t="n">
-        <v>6978118840.349827</v>
-      </c>
-      <c r="C99" t="n">
-        <v>7752890562.662872</v>
-      </c>
-      <c r="D99" t="n">
-        <v>1.05980198019802</v>
-      </c>
-      <c r="E99" t="n">
-        <v>21503.85278670231</v>
-      </c>
-      <c r="F99" t="n">
-        <v>8.463866592227069e-05</v>
-      </c>
-      <c r="G99" t="n">
-        <v>2196.195888124253</v>
-      </c>
-      <c r="H99" t="n">
-        <v>2.003438850255308e-07</v>
-      </c>
-      <c r="I99" t="n">
-        <v>21452.95210953117</v>
-      </c>
-      <c r="J99" t="n">
-        <v>21262.18437416603</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>2.701727851504217e-06</v>
-      </c>
-      <c r="B100" t="n">
-        <v>9053369834.412766</v>
-      </c>
-      <c r="C100" t="n">
-        <v>9829886848.8634</v>
-      </c>
-      <c r="D100" t="n">
-        <v>1.05980198019802</v>
-      </c>
-      <c r="E100" t="n">
-        <v>41070.43775199963</v>
-      </c>
-      <c r="F100" t="n">
-        <v>6.507059649218134e-05</v>
-      </c>
-      <c r="G100" t="n">
-        <v>4274.216297617553</v>
-      </c>
-      <c r="H100" t="n">
-        <v>2.942915836582206e-07</v>
-      </c>
-      <c r="I100" t="n">
-        <v>40884.69050486897</v>
-      </c>
-      <c r="J100" t="n">
-        <v>40306.32258426701</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>4.416349625033305e-06</v>
-      </c>
-      <c r="B101" t="n">
-        <v>3288413395.827895</v>
-      </c>
-      <c r="C101" t="n">
-        <v>6.466147251216041e+24</v>
-      </c>
-      <c r="D101" t="n">
-        <v>3.886130076185295</v>
-      </c>
-      <c r="E101" t="n">
-        <v>27394.12879523556</v>
-      </c>
-      <c r="F101" t="n">
-        <v>4.764157270051151e-05</v>
-      </c>
-      <c r="G101" t="n">
-        <v>2856.007827147475</v>
-      </c>
-      <c r="H101" t="n">
-        <v>2.253024002680702e-07</v>
-      </c>
-      <c r="I101" t="n">
-        <v>27264.5788534312</v>
-      </c>
-      <c r="J101" t="n">
-        <v>26866.79641461041</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>1.028193293135666e-05</v>
-      </c>
-      <c r="B102" t="n">
-        <v>1960219300.336402</v>
-      </c>
-      <c r="C102" t="n">
-        <v>1.886027671688805e+36</v>
-      </c>
-      <c r="D102" t="n">
-        <v>6.429048326641047</v>
-      </c>
-      <c r="E102" t="n">
-        <v>40384.62553674074</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.0002426231781610949</v>
-      </c>
-      <c r="G102" t="n">
-        <v>4088.587110415034</v>
-      </c>
-      <c r="H102" t="n">
-        <v>3.345987103528314e-07</v>
-      </c>
-      <c r="I102" t="n">
-        <v>40328.93158480633</v>
-      </c>
-      <c r="J102" t="n">
-        <v>40090.37409814701</v>
+        <v>27350.90210405471</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,386 +482,5154 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.817761155638728e-06</v>
+        <v>4.984835199939135e-06</v>
       </c>
       <c r="B2" t="n">
-        <v>7041471467.043752</v>
+        <v>3769564856.362882</v>
       </c>
       <c r="C2" t="n">
-        <v>13212984816459.89</v>
+        <v>8.816645284336236e+22</v>
       </c>
       <c r="D2" t="n">
-        <v>1.652478103761136</v>
+        <v>3.554018752326852</v>
       </c>
       <c r="E2" t="n">
-        <v>46366.76809245747</v>
+        <v>34978.92232868962</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000103275161481378</v>
+        <v>0.0001048267357680382</v>
       </c>
       <c r="G2" t="n">
-        <v>4775.945218928787</v>
+        <v>3580.010236410095</v>
       </c>
       <c r="H2" t="n">
-        <v>3.446665716989919e-07</v>
+        <v>2.734396629590559e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>46212.02541503187</v>
+        <v>34887.68010253281</v>
       </c>
       <c r="J2" t="n">
-        <v>45684.35791919021</v>
+        <v>34554.45840458442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.435475033068382e-06</v>
+        <v>1.875431132209394e-06</v>
       </c>
       <c r="B3" t="n">
-        <v>2415253433.432325</v>
+        <v>8256440397.91818</v>
       </c>
       <c r="C3" t="n">
-        <v>2.44067618254698e+36</v>
+        <v>9162461052.596571</v>
       </c>
       <c r="D3" t="n">
-        <v>6.148629330008512</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E3" t="n">
-        <v>26204.59880723685</v>
+        <v>25930.71570992833</v>
       </c>
       <c r="F3" t="n">
-        <v>6.183168525097499e-05</v>
+        <v>0.0001094063867734516</v>
       </c>
       <c r="G3" t="n">
-        <v>2690.818013650521</v>
+        <v>2636.648006344709</v>
       </c>
       <c r="H3" t="n">
-        <v>1.844613425800209e-07</v>
+        <v>2.042854159542911e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>26126.42310398481</v>
+        <v>25882.29744842624</v>
       </c>
       <c r="J3" t="n">
-        <v>25851.24662182675</v>
+        <v>25689.47269486717</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.995002017071434e-05</v>
+        <v>1.8657910106372e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>2005309106.040979</v>
+        <v>8309445459.894715</v>
       </c>
       <c r="C4" t="n">
-        <v>7.664055860321331e+37</v>
+        <v>9224124951.507225</v>
       </c>
       <c r="D4" t="n">
-        <v>7.099371243866748</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E4" t="n">
-        <v>81157.47629967256</v>
+        <v>25968.62433712312</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002882133437247341</v>
+        <v>9.76251927388389e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>8265.480851202019</v>
+        <v>2645.517580548656</v>
       </c>
       <c r="H4" t="n">
-        <v>5.908281901964999e-07</v>
+        <v>2.032353447405828e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>80991.10605385616</v>
+        <v>25914.56306286052</v>
       </c>
       <c r="J4" t="n">
-        <v>80343.92458220787</v>
+        <v>25705.08861187599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3.523919891298276e-06</v>
+        <v>4.41756017164473e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>5075745108.69827</v>
+        <v>5758376374.249015</v>
       </c>
       <c r="C5" t="n">
-        <v>5.210787928405287e+22</v>
+        <v>4014945251560.878</v>
       </c>
       <c r="D5" t="n">
-        <v>3.418829569927147</v>
+        <v>1.580669328172041</v>
       </c>
       <c r="E5" t="n">
-        <v>33104.56199967252</v>
+        <v>43812.85770952214</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001269830491195245</v>
+        <v>7.797093382898866e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3357.222282794387</v>
+        <v>4587.43817728013</v>
       </c>
       <c r="H5" t="n">
-        <v>1.99317940021028e-07</v>
+        <v>4.076402446628842e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>33052.59968542014</v>
+        <v>43583.7994802689</v>
       </c>
       <c r="J5" t="n">
-        <v>32836.71053736185</v>
+        <v>42902.66717883011</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.066013920504416e-06</v>
+        <v>5.460158937557678e-06</v>
       </c>
       <c r="B6" t="n">
-        <v>9953593836.16169</v>
+        <v>2297500362.335032</v>
       </c>
       <c r="C6" t="n">
-        <v>541260447442847.8</v>
+        <v>2.419649766575982e+43</v>
       </c>
       <c r="D6" t="n">
-        <v>1.835064166976425</v>
+        <v>7.479817559208118</v>
       </c>
       <c r="E6" t="n">
-        <v>18418.03285807096</v>
+        <v>25575.43351943724</v>
       </c>
       <c r="F6" t="n">
-        <v>6.54570622326894e-05</v>
+        <v>0.0001373631682320431</v>
       </c>
       <c r="G6" t="n">
-        <v>1864.880253345895</v>
+        <v>2583.317280250313</v>
       </c>
       <c r="H6" t="n">
-        <v>9.112750844476581e-08</v>
+        <v>1.538102938286854e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>18392.39178302786</v>
+        <v>25546.7958213188</v>
       </c>
       <c r="J6" t="n">
-        <v>18282.80252483383</v>
+        <v>25418.19026460578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7.531072930847813e-06</v>
+        <v>2.892210388907534e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>1022128688.839141</v>
+        <v>2616847939.310946</v>
       </c>
       <c r="C7" t="n">
-        <v>4.939351059448636e+60</v>
+        <v>7.5627571805322e+34</v>
       </c>
       <c r="D7" t="n">
-        <v>11.09703522433316</v>
+        <v>5.617237133993083</v>
       </c>
       <c r="E7" t="n">
-        <v>16366.70639050945</v>
+        <v>14927.72701233823</v>
       </c>
       <c r="F7" t="n">
-        <v>2.578571732390493e-05</v>
+        <v>4.663914217326232e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1719.218621837328</v>
+        <v>1523.525150826194</v>
       </c>
       <c r="H7" t="n">
-        <v>1.445046696222367e-07</v>
+        <v>1.067564381316267e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>16274.98640963569</v>
+        <v>14893.55762390227</v>
       </c>
       <c r="J7" t="n">
-        <v>16008.37328106172</v>
+        <v>14764.36424559891</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3.669141299908964e-06</v>
+        <v>3.509037456894424e-06</v>
       </c>
       <c r="B8" t="n">
-        <v>4008904243.267509</v>
+        <v>4909254854.096014</v>
       </c>
       <c r="C8" t="n">
-        <v>23514363770070.89</v>
+        <v>1.9735758683921e+18</v>
       </c>
       <c r="D8" t="n">
-        <v>1.740563536536275</v>
+        <v>2.616303789238016</v>
       </c>
       <c r="E8" t="n">
-        <v>25453.08169511605</v>
+        <v>30983.52834897685</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000125748948590124</v>
+        <v>7.096575988924308e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2604.072706800864</v>
+        <v>3193.2522738863</v>
       </c>
       <c r="H8" t="n">
-        <v>3.22579528309457e-07</v>
+        <v>2.415122256443974e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>25387.78776479465</v>
+        <v>30878.08452787839</v>
       </c>
       <c r="J8" t="n">
-        <v>25148.25581249368</v>
+        <v>30520.54217312479</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5.211512695083337e-06</v>
+        <v>9.190113604862866e-06</v>
       </c>
       <c r="B9" t="n">
-        <v>6809946003.438034</v>
+        <v>1812606311.105507</v>
       </c>
       <c r="C9" t="n">
-        <v>31214361469289.66</v>
+        <v>1.067451560854188e+39</v>
       </c>
       <c r="D9" t="n">
-        <v>1.741643343098462</v>
+        <v>6.928088588974071</v>
       </c>
       <c r="E9" t="n">
-        <v>61530.61666427727</v>
+        <v>33975.22439520506</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001034206102723944</v>
+        <v>2.732009335805661e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>6398.319342079777</v>
+        <v>3709.331336842527</v>
       </c>
       <c r="H9" t="n">
-        <v>4.580321123045037e-07</v>
+        <v>2.78590202659969e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>61258.10813577499</v>
+        <v>33628.77006484726</v>
       </c>
       <c r="J9" t="n">
-        <v>60404.04764392214</v>
+        <v>32817.321389072</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.154650051306849e-06</v>
+        <v>7.870890962395305e-06</v>
       </c>
       <c r="B10" t="n">
-        <v>4322367164.133391</v>
+        <v>2986507312.736033</v>
       </c>
       <c r="C10" t="n">
-        <v>4319604415466609</v>
+        <v>5.067619202480721e+21</v>
       </c>
       <c r="D10" t="n">
-        <v>2.133545709226545</v>
+        <v>3.430964510675726</v>
       </c>
       <c r="E10" t="n">
-        <v>23985.4975555879</v>
+        <v>43640.76204058265</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0001681828770773384</v>
+        <v>0.0001050706515088921</v>
       </c>
       <c r="G10" t="n">
-        <v>2430.311787845918</v>
+        <v>4530.031529331838</v>
       </c>
       <c r="H10" t="n">
-        <v>2.474564732984344e-07</v>
+        <v>4.439538055843085e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>23950.20640860219</v>
+        <v>43456.36723472313</v>
       </c>
       <c r="J10" t="n">
-        <v>23801.31397209894</v>
+        <v>42870.03549780516</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6.165969091457313e-06</v>
+        <v>7.261610774316377e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>2121969099.682878</v>
+        <v>2316996661.423347</v>
       </c>
       <c r="C11" t="n">
-        <v>1.725175751595072e+31</v>
+        <v>4.411059297222786e+31</v>
       </c>
       <c r="D11" t="n">
-        <v>5.228819253619148</v>
+        <v>5.358563768975928</v>
       </c>
       <c r="E11" t="n">
-        <v>25591.026255219</v>
+        <v>33009.4420241759</v>
       </c>
       <c r="F11" t="n">
-        <v>8.064414716466301e-05</v>
+        <v>9.472459816207918e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>2628.506399263875</v>
+        <v>3388.723333084</v>
       </c>
       <c r="H11" t="n">
-        <v>2.430108849533566e-07</v>
+        <v>2.798809596257184e-07</v>
       </c>
       <c r="I11" t="n">
-        <v>25513.91095106124</v>
+        <v>32911.90965676878</v>
       </c>
       <c r="J11" t="n">
-        <v>25243.22723608387</v>
+        <v>32567.67445935337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.324024352572786e-06</v>
+        <v>5.855272732472012e-06</v>
       </c>
       <c r="B12" t="n">
-        <v>4036777358.126885</v>
+        <v>3283149980.285232</v>
       </c>
       <c r="C12" t="n">
-        <v>1.524710934422093e+28</v>
+        <v>5.075976914165194e+29</v>
       </c>
       <c r="D12" t="n">
-        <v>4.41735066951629</v>
+        <v>4.883489658630973</v>
       </c>
       <c r="E12" t="n">
-        <v>25697.27907041573</v>
+        <v>37253.31695958079</v>
       </c>
       <c r="F12" t="n">
-        <v>4.241846549142105e-05</v>
+        <v>9.730260281100608e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>2652.681703840211</v>
+        <v>3809.88761090344</v>
       </c>
       <c r="H12" t="n">
-        <v>1.521463618014956e-07</v>
+        <v>2.453923354641978e-07</v>
       </c>
       <c r="I12" t="n">
-        <v>25605.10818508391</v>
+        <v>37159.36594297483</v>
       </c>
       <c r="J12" t="n">
-        <v>25297.30831151704</v>
+        <v>36813.12769268435</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5.450803035501284e-06</v>
+        <v>1.6355208209081e-06</v>
       </c>
       <c r="B13" t="n">
-        <v>2813243141.638292</v>
+        <v>7858561727.349974</v>
       </c>
       <c r="C13" t="n">
-        <v>1.498422862131791e+36</v>
+        <v>8792599498.723585</v>
       </c>
       <c r="D13" t="n">
-        <v>6.097179708333048</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E13" t="n">
-        <v>30535.39131061226</v>
+        <v>21502.97176662271</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0001149977674434651</v>
+        <v>0.0001982287221124055</v>
       </c>
       <c r="G13" t="n">
-        <v>3098.094792232655</v>
+        <v>2167.689865699025</v>
       </c>
       <c r="H13" t="n">
-        <v>1.864430944539621e-07</v>
+        <v>1.781526633865279e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>30485.88502042177</v>
+        <v>21483.64655658187</v>
       </c>
       <c r="J13" t="n">
-        <v>30281.79033881798</v>
+        <v>21392.44412331548</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3.241152126531787e-06</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4354232732.416034</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.479044509346111e+18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.59301645672442</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25417.19138216745</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.940695361825226e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2672.00234249597</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.244353311493437e-07</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25272.43226630164</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24853.88927522643</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.486209913281607e-05</v>
+      </c>
+      <c r="B15" t="n">
+        <v>833212293.0648084</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.74837040511762e+77</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15.22541537556792</v>
+      </c>
+      <c r="E15" t="n">
+        <v>26741.15983293475</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0002268484458205106</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2696.294899553296</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.090515443008465e-07</v>
+      </c>
+      <c r="I15" t="n">
+        <v>26716.51659264606</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26601.06152595478</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4.432610104531841e-06</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5051783695.858262</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.11692239690603e+21</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.23707895688099</v>
+      </c>
+      <c r="E16" t="n">
+        <v>41145.92779162651</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0002984821009776922</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4147.040480817536</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.615368351853205e-07</v>
+      </c>
+      <c r="I16" t="n">
+        <v>41109.87478978775</v>
+      </c>
+      <c r="J16" t="n">
+        <v>40939.15285428576</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7.094748346854988e-06</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2713577821.447883</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9.221101553975188e+32</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.592043246519447</v>
+      </c>
+      <c r="E17" t="n">
+        <v>37955.19292453487</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0001090842347736051</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3877.86697464605</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.629660339880838e-07</v>
+      </c>
+      <c r="I17" t="n">
+        <v>37863.69549987646</v>
+      </c>
+      <c r="J17" t="n">
+        <v>37522.42621593997</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4.945237698251905e-06</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2695344128.050301</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6.460396282770609e+33</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.616179052502309</v>
+      </c>
+      <c r="E18" t="n">
+        <v>26262.57501868518</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0001426580650354853</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2656.506448343314</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.825688866459952e-07</v>
+      </c>
+      <c r="I18" t="n">
+        <v>26228.96507815762</v>
+      </c>
+      <c r="J18" t="n">
+        <v>26082.50141017721</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1.271708312307658e-05</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1085399895.106679</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8.294454980855011e+80</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15.6882414062901</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30045.40607413334</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.360767351732626e-05</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3203.49572700875</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.736951620054375e-07</v>
+      </c>
+      <c r="I19" t="n">
+        <v>29824.34483013843</v>
+      </c>
+      <c r="J19" t="n">
+        <v>29239.14208329035</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5.377564163807374e-06</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3191024256.986775</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.255625540535362e+19</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.936982750551315</v>
+      </c>
+      <c r="E20" t="n">
+        <v>31263.49031254638</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.452473242475759e-05</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3227.901901207146</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.411596708870211e-07</v>
+      </c>
+      <c r="I20" t="n">
+        <v>31150.65379037691</v>
+      </c>
+      <c r="J20" t="n">
+        <v>30774.52903040934</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1.729199509968751e-06</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9044908530.80798</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10086299280.05347</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E21" t="n">
+        <v>26191.09032891695</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0001029329749062116</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2662.243348245743</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.88356818384351e-07</v>
+      </c>
+      <c r="I21" t="n">
+        <v>26143.1633118569</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25951.33595120479</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2.731419500327691e-06</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3771452281.906415</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.30821769471287e+24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.643991024474111</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19243.01525369994</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.875757797807911e-05</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1976.46568279874</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.46858364506157e-07</v>
+      </c>
+      <c r="I22" t="n">
+        <v>19185.05507877911</v>
+      </c>
+      <c r="J22" t="n">
+        <v>18981.58209303927</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9.588503973754878e-06</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1784219254.950021</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.641723520512505e+30</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.270589420959043</v>
+      </c>
+      <c r="E23" t="n">
+        <v>33458.58895224404</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0001963806373390978</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3403.388197759244</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.751782410984615e-07</v>
+      </c>
+      <c r="I23" t="n">
+        <v>33394.66750498311</v>
+      </c>
+      <c r="J23" t="n">
+        <v>33141.55144411985</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7.580752651571538e-06</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1424668059.413173</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.331962678010052e+52</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9.48110163343487</v>
+      </c>
+      <c r="E24" t="n">
+        <v>22563.19498029839</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0001209886005587331</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2284.798375812805</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.696774854138903e-07</v>
+      </c>
+      <c r="I24" t="n">
+        <v>22531.55178276176</v>
+      </c>
+      <c r="J24" t="n">
+        <v>22396.54033670566</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6.050496212920266e-06</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5810081797.147509</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3578175720911.05</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.585488669273701</v>
+      </c>
+      <c r="E25" t="n">
+        <v>60360.21639432131</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0002892072277793654</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6140.741400511492</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.574995070268206e-07</v>
+      </c>
+      <c r="I25" t="n">
+        <v>60243.86110423312</v>
+      </c>
+      <c r="J25" t="n">
+        <v>59784.15257075681</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3.02324451436337e-06</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5860529974.389969</v>
+      </c>
+      <c r="C26" t="n">
+        <v>20282943441635.77</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.688300039123629</v>
+      </c>
+      <c r="E26" t="n">
+        <v>30577.44487655753</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0001181317516438774</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3120.642662102596</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.699982709697044e-07</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30507.55801606103</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30243.21555084952</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2.073185266345119e-06</v>
+      </c>
+      <c r="B27" t="n">
+        <v>6951191883.302405</v>
+      </c>
+      <c r="C27" t="n">
+        <v>41106890917576.48</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.709189695553993</v>
+      </c>
+      <c r="E27" t="n">
+        <v>24886.55207288289</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.358408984770904e-05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2532.690455103275</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.839904260972853e-07</v>
+      </c>
+      <c r="I27" t="n">
+        <v>24837.62401975512</v>
+      </c>
+      <c r="J27" t="n">
+        <v>24645.26903866991</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5.388781360697307e-06</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4887035392.337063</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.904633648453378e+20</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.10561761160781</v>
+      </c>
+      <c r="E28" t="n">
+        <v>48159.72415051453</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0003417920205550455</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4857.576923748059</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.280770243056253e-07</v>
+      </c>
+      <c r="I28" t="n">
+        <v>48113.49691862941</v>
+      </c>
+      <c r="J28" t="n">
+        <v>47898.80210647309</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5.230662336138732e-06</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2209942775.774018</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.106179444338609e+36</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.159460147329364</v>
+      </c>
+      <c r="E29" t="n">
+        <v>23043.27878198095</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0001216736077922691</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2334.534242421822</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.772180921995296e-07</v>
+      </c>
+      <c r="I29" t="n">
+        <v>23009.7161550657</v>
+      </c>
+      <c r="J29" t="n">
+        <v>22867.77783730239</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6.151517582505285e-06</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2491371166.594755</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.563175162524755e+29</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4.913434007225597</v>
+      </c>
+      <c r="E30" t="n">
+        <v>29693.860793727</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.000165303085893488</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3010.839052615166</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.564055783951204e-07</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29647.8019345687</v>
+      </c>
+      <c r="J30" t="n">
+        <v>29455.89683441269</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1.15685204387662e-05</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1291603874.13574</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.040560778162654e+46</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8.489345000508731</v>
+      </c>
+      <c r="E31" t="n">
+        <v>30913.33619881789</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0001239364192732774</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3156.063769049159</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.883481476240897e-07</v>
+      </c>
+      <c r="I31" t="n">
+        <v>30841.41381085414</v>
+      </c>
+      <c r="J31" t="n">
+        <v>30570.63365959517</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4.632273417369927e-06</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4339067262.610166</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5.792284237389445e+27</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.424964499600764</v>
+      </c>
+      <c r="E32" t="n">
+        <v>38430.99475855025</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0001199112148602874</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3904.166748853376</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.117113757164804e-07</v>
+      </c>
+      <c r="I32" t="n">
+        <v>38363.14223299653</v>
+      </c>
+      <c r="J32" t="n">
+        <v>38089.15543541405</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9.008821480833015e-06</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1642283094.101633</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.298960144142185e+46</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8.326908140198112</v>
+      </c>
+      <c r="E33" t="n">
+        <v>30559.41229474531</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8.583654570496832e-05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3129.251376845101</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.287962054126976e-07</v>
+      </c>
+      <c r="I33" t="n">
+        <v>30477.95657544467</v>
+      </c>
+      <c r="J33" t="n">
+        <v>30182.20996173148</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>4.70584907539615e-06</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4684626035.593358</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7.029021587020399e+19</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.947274718548396</v>
+      </c>
+      <c r="E34" t="n">
+        <v>40238.15128465561</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.888823834085665e-05</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4206.943848656007</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.977861495270748e-07</v>
+      </c>
+      <c r="I34" t="n">
+        <v>40034.67492888845</v>
+      </c>
+      <c r="J34" t="n">
+        <v>39423.07607211146</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.83943770123425e-06</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5130408072.302237</v>
+      </c>
+      <c r="C35" t="n">
+        <v>818110396265066.1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.053781326335673</v>
+      </c>
+      <c r="E35" t="n">
+        <v>61610.67089574496</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0001754500052105336</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6334.496123426754</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.487527918035455e-07</v>
+      </c>
+      <c r="I35" t="n">
+        <v>61417.97196924244</v>
+      </c>
+      <c r="J35" t="n">
+        <v>60748.61862411042</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3.44643486994436e-06</v>
+      </c>
+      <c r="B36" t="n">
+        <v>6252927086.513662</v>
+      </c>
+      <c r="C36" t="n">
+        <v>282607679435379.4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.897641379911786</v>
+      </c>
+      <c r="E36" t="n">
+        <v>37651.31487574788</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.698120718901079e-05</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3937.150088604631</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.892573481457998e-07</v>
+      </c>
+      <c r="I36" t="n">
+        <v>37460.18309682584</v>
+      </c>
+      <c r="J36" t="n">
+        <v>36886.40100231022</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>7.069809321520528e-06</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2197987832.33008</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.35355677606249e+42</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.381851003825635</v>
+      </c>
+      <c r="E37" t="n">
+        <v>31805.6856476692</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.098981153169244e-05</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3366.870420950839</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.016920802253279e-07</v>
+      </c>
+      <c r="I37" t="n">
+        <v>31598.68358524262</v>
+      </c>
+      <c r="J37" t="n">
+        <v>31026.59391875274</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3.976570476892584e-06</v>
+      </c>
+      <c r="B38" t="n">
+        <v>9104513765.996311</v>
+      </c>
+      <c r="C38" t="n">
+        <v>9659535206.67663</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E38" t="n">
+        <v>60719.42333666407</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0001296543389931715</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6254.511746347051</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.331565899658187e-07</v>
+      </c>
+      <c r="I38" t="n">
+        <v>60516.56843368559</v>
+      </c>
+      <c r="J38" t="n">
+        <v>59825.04765966592</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.442026548892783e-06</v>
+      </c>
+      <c r="B39" t="n">
+        <v>7799526631.361507</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6135008142.150391</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.036936851316268</v>
+      </c>
+      <c r="E39" t="n">
+        <v>71229.91323266733</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0001178933130689001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7447.77968843773</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.972892673018183e-07</v>
+      </c>
+      <c r="I39" t="n">
+        <v>70869.03727136622</v>
+      </c>
+      <c r="J39" t="n">
+        <v>69784.99280153197</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3.530484856892447e-06</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4840224622.204686</v>
+      </c>
+      <c r="C40" t="n">
+        <v>859893218740.2922</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.462643923568946</v>
+      </c>
+      <c r="E40" t="n">
+        <v>29255.52095660166</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.157297086712361e-05</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3049.853408558628</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.378892809867421e-07</v>
+      </c>
+      <c r="I40" t="n">
+        <v>29117.40838671448</v>
+      </c>
+      <c r="J40" t="n">
+        <v>28693.10203376749</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2.473062826841745e-06</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7774382366.57118</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8485959120.812866</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E41" t="n">
+        <v>32217.62317831662</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0001081008067353521</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3294.019074488745</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.693837484009804e-07</v>
+      </c>
+      <c r="I41" t="n">
+        <v>32137.33789314208</v>
+      </c>
+      <c r="J41" t="n">
+        <v>31840.51528166633</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3.799182140636718e-06</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5436808758.742797</v>
+      </c>
+      <c r="C42" t="n">
+        <v>931203001625.7512</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.462435700115939</v>
+      </c>
+      <c r="E42" t="n">
+        <v>35280.81014007789</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0001497619662859364</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3605.178089422815</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.636288888179229e-07</v>
+      </c>
+      <c r="I42" t="n">
+        <v>35195.14672295008</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34876.2445863912</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>6.893335117909527e-06</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2030013499.84119</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.749405373606145e+35</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6.044824714181156</v>
+      </c>
+      <c r="E43" t="n">
+        <v>27873.59618518443</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.980137693485246e-05</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2862.080690782072</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.376938620043743e-07</v>
+      </c>
+      <c r="I43" t="n">
+        <v>27790.57277155818</v>
+      </c>
+      <c r="J43" t="n">
+        <v>27498.20347756969</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7.384524190619949e-06</v>
+      </c>
+      <c r="B44" t="n">
+        <v>836950226.0772754</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.488856944939052e+62</v>
+      </c>
+      <c r="D44" t="n">
+        <v>11.3850551167524</v>
+      </c>
+      <c r="E44" t="n">
+        <v>13132.43107899979</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.575754643283525e-05</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1348.934224381738</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.381768293767046e-07</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13092.77428290894</v>
+      </c>
+      <c r="J44" t="n">
+        <v>12953.6563027213</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>7.432245846907087e-06</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2704536236.55074</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.119338511040356e+29</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4.850491298067976</v>
+      </c>
+      <c r="E45" t="n">
+        <v>38945.48239377638</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9.789217525545731e-05</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4006.752171693397</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.133693087385876e-07</v>
+      </c>
+      <c r="I45" t="n">
+        <v>38820.81135786998</v>
+      </c>
+      <c r="J45" t="n">
+        <v>38390.59718894291</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1.208719194255362e-06</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8840489942.244511</v>
+      </c>
+      <c r="C46" t="n">
+        <v>10071737323.41901</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E46" t="n">
+        <v>17879.20131894041</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0001307609431272651</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1804.122341285729</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.316623677242139e-07</v>
+      </c>
+      <c r="I46" t="n">
+        <v>17861.19886406075</v>
+      </c>
+      <c r="J46" t="n">
+        <v>17778.44379277641</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8.988092730693354e-06</v>
+      </c>
+      <c r="B47" t="n">
+        <v>813694406.7188741</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.272853061091479e+47</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8.581737389299434</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15151.78409481673</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8.5061634063866e-05</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1550.718096222942</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.216874124021421e-07</v>
+      </c>
+      <c r="I47" t="n">
+        <v>15112.2955539931</v>
+      </c>
+      <c r="J47" t="n">
+        <v>14968.04544009373</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1.178007355384679e-05</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1590942660.820812</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.98423189969331e+37</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.718827827870607</v>
+      </c>
+      <c r="E48" t="n">
+        <v>37759.50123242805</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0002284557125052802</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3830.643529475859</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.676784998179831e-07</v>
+      </c>
+      <c r="I48" t="n">
+        <v>37698.730781058</v>
+      </c>
+      <c r="J48" t="n">
+        <v>37447.75476483896</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.349447554922331e-06</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3241996743.349532</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1.520413417344563e+17</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.471650754624729</v>
+      </c>
+      <c r="E49" t="n">
+        <v>25281.17721696943</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.056606228890385e-05</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2668.053633873374</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3.109914977824515e-07</v>
+      </c>
+      <c r="I49" t="n">
+        <v>25125.69287010673</v>
+      </c>
+      <c r="J49" t="n">
+        <v>24687.58359995182</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6.459520915092858e-06</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2827736546.822832</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4.734293077319169e+19</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3.007564781499801</v>
+      </c>
+      <c r="E50" t="n">
+        <v>33422.42894715018</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7.711077276425699e-05</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3499.348743878344</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.027419715307254e-07</v>
+      </c>
+      <c r="I50" t="n">
+        <v>33247.86689252427</v>
+      </c>
+      <c r="J50" t="n">
+        <v>32728.61811624772</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3.402920269722651e-06</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5633851614.347816</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.085106096101426e+17</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.373157730510949</v>
+      </c>
+      <c r="E51" t="n">
+        <v>34095.19889359052</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0001143052698400421</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3476.590791672979</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.498415494195635e-07</v>
+      </c>
+      <c r="I51" t="n">
+        <v>34020.67566879727</v>
+      </c>
+      <c r="J51" t="n">
+        <v>33735.50727441063</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5.448954253408636e-06</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1666608009.954901</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5.49393616453964e+29</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.922715876293775</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17702.28370238582</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.083299143038452e-05</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1887.389197859348</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.267390313865413e-07</v>
+      </c>
+      <c r="I52" t="n">
+        <v>17572.10500502941</v>
+      </c>
+      <c r="J52" t="n">
+        <v>17227.42671744608</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.299646946653002e-06</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3514318224.13512</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9.368687972290929e+24</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.904388291183805</v>
+      </c>
+      <c r="E53" t="n">
+        <v>28488.9291973809</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.951828591726439e-05</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2943.020887172149</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.184995067045316e-07</v>
+      </c>
+      <c r="I53" t="n">
+        <v>28384.34256689862</v>
+      </c>
+      <c r="J53" t="n">
+        <v>28037.45474491963</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.337180321806985e-06</v>
+      </c>
+      <c r="B54" t="n">
+        <v>7344250145.105207</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2491590460160268</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.075834889691397</v>
+      </c>
+      <c r="E54" t="n">
+        <v>56066.64502408127</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7.502136979705234e-05</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5839.260203908662</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.458116304262476e-07</v>
+      </c>
+      <c r="I54" t="n">
+        <v>55808.20535574734</v>
+      </c>
+      <c r="J54" t="n">
+        <v>55008.25624242162</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1.975107837310379e-06</v>
+      </c>
+      <c r="B55" t="n">
+        <v>13734096405.79121</v>
+      </c>
+      <c r="C55" t="n">
+        <v>15194081616.88553</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E55" t="n">
+        <v>45433.57779632717</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.000106625368783336</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4625.863860017233</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.151429178976013e-07</v>
+      </c>
+      <c r="I55" t="n">
+        <v>45341.9043736777</v>
+      </c>
+      <c r="J55" t="n">
+        <v>44983.85700715982</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.724500805380013e-06</v>
+      </c>
+      <c r="B56" t="n">
+        <v>6446077521.564322</v>
+      </c>
+      <c r="C56" t="n">
+        <v>7.265316087400374e+18</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.738525592443485</v>
+      </c>
+      <c r="E56" t="n">
+        <v>55054.01145795922</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8.792021767337783e-05</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5682.963374139534</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.150705876146029e-07</v>
+      </c>
+      <c r="I56" t="n">
+        <v>54856.72009313299</v>
+      </c>
+      <c r="J56" t="n">
+        <v>54197.70374228277</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3.299530364069592e-06</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3942649760.392572</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2.658786606908581e+21</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.192131904383524</v>
+      </c>
+      <c r="E57" t="n">
+        <v>23904.44934567944</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.689059529208761e-05</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2445.49973533587</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.967646898197501e-07</v>
+      </c>
+      <c r="I57" t="n">
+        <v>23843.27734482619</v>
+      </c>
+      <c r="J57" t="n">
+        <v>23618.71985820847</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3.307386977100087e-06</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2413564800.821003</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1.575284439761085e+30</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4.822142715230667</v>
+      </c>
+      <c r="E58" t="n">
+        <v>15435.57157454491</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.131683787319797e-05</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1570.863145292876</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.401795772139323e-07</v>
+      </c>
+      <c r="I58" t="n">
+        <v>15405.23158805782</v>
+      </c>
+      <c r="J58" t="n">
+        <v>15285.94638030246</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5.452348712753393e-06</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2072198194.548035</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2.047680494526544e+31</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5.202126250287017</v>
+      </c>
+      <c r="E59" t="n">
+        <v>22048.44973364638</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0001536344533798445</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2232.728970772097</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2.158853067016659e-07</v>
+      </c>
+      <c r="I59" t="n">
+        <v>22017.46751430476</v>
+      </c>
+      <c r="J59" t="n">
+        <v>21885.33696046134</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>7.328716189762455e-06</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1965951197.973393</v>
+      </c>
+      <c r="C60" t="n">
+        <v>7.025709973165623e+44</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7.937992575167885</v>
+      </c>
+      <c r="E60" t="n">
+        <v>29568.04850013707</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0001595014352056429</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2989.330025836641</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.949481314094751e-07</v>
+      </c>
+      <c r="I60" t="n">
+        <v>29531.90941588937</v>
+      </c>
+      <c r="J60" t="n">
+        <v>29372.76992029918</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1.25230341931825e-05</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2369542105.858871</v>
+      </c>
+      <c r="C61" t="n">
+        <v>8.881374917458846e+25</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4.410297901728083</v>
+      </c>
+      <c r="E61" t="n">
+        <v>56778.3200354263</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.0001965777363043879</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5827.042026277959</v>
+      </c>
+      <c r="H61" t="n">
+        <v>5.739939016812585e-07</v>
+      </c>
+      <c r="I61" t="n">
+        <v>56612.53112127593</v>
+      </c>
+      <c r="J61" t="n">
+        <v>56025.46177623532</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3.623567675307397e-06</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7264972312.704322</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4500092507904.711</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.562234964078664</v>
+      </c>
+      <c r="E62" t="n">
+        <v>45280.45671196604</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7.074194755366786e-05</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4721.760892539719</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.362694789982438e-07</v>
+      </c>
+      <c r="I62" t="n">
+        <v>45065.21757714035</v>
+      </c>
+      <c r="J62" t="n">
+        <v>44405.3967884829</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2.855471811214435e-06</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3480667995.130036</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4.611440416859244e+21</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3.220005548005912</v>
+      </c>
+      <c r="E63" t="n">
+        <v>18286.57099844441</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.023752114581437e-05</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1874.875037639375</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.691620227442716e-07</v>
+      </c>
+      <c r="I63" t="n">
+        <v>18235.21773422782</v>
+      </c>
+      <c r="J63" t="n">
+        <v>18051.40342107141</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1.99512111818996e-06</v>
+      </c>
+      <c r="B64" t="n">
+        <v>6247515667.674904</v>
+      </c>
+      <c r="C64" t="n">
+        <v>6907483832.975375</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20892.35915270145</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7.862892919374828e-05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2141.205965789414</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2.173229080549998e-07</v>
+      </c>
+      <c r="I64" t="n">
+        <v>20834.61465212449</v>
+      </c>
+      <c r="J64" t="n">
+        <v>20627.01926035082</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1.723352936057902e-05</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1145198602.935472</v>
+      </c>
+      <c r="C65" t="n">
+        <v>9.053189479768825e+54</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10.64503683995501</v>
+      </c>
+      <c r="E65" t="n">
+        <v>41970.57410388313</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.787006425171598e-05</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4540.607301455634</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.444279904875805e-07</v>
+      </c>
+      <c r="I65" t="n">
+        <v>41588.85200269721</v>
+      </c>
+      <c r="J65" t="n">
+        <v>40654.31927367012</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.651532735422679e-06</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2839247462.63577</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1.01725042059392e+36</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6.20982891397899</v>
+      </c>
+      <c r="E66" t="n">
+        <v>43474.11620272432</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5.980563769671499e-05</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4515.722691697969</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.572654933616908e-07</v>
+      </c>
+      <c r="I66" t="n">
+        <v>43287.10390114039</v>
+      </c>
+      <c r="J66" t="n">
+        <v>42695.70644107642</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3.806491048067244e-06</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6188562674.193564</v>
+      </c>
+      <c r="C67" t="n">
+        <v>367887137815709.9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.926465757739394</v>
+      </c>
+      <c r="E67" t="n">
+        <v>41160.83719012157</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8.139102676407843e-05</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4260.276321747195</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.168055632369736e-07</v>
+      </c>
+      <c r="I67" t="n">
+        <v>41000.62318708263</v>
+      </c>
+      <c r="J67" t="n">
+        <v>40478.38248804088</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.780976326519378e-06</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7168832422.572708</v>
+      </c>
+      <c r="C68" t="n">
+        <v>7522518594.531461</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E68" t="n">
+        <v>57603.29109205442</v>
+      </c>
+      <c r="F68" t="n">
+        <v>9.555386782980136e-05</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6042.878497079329</v>
+      </c>
+      <c r="H68" t="n">
+        <v>5.207782470689956e-07</v>
+      </c>
+      <c r="I68" t="n">
+        <v>57289.3473277501</v>
+      </c>
+      <c r="J68" t="n">
+        <v>56368.36630427754</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1.952362699624528e-06</v>
+      </c>
+      <c r="B69" t="n">
+        <v>6360041552.524378</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3204926718.472374</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.000586918521727</v>
+      </c>
+      <c r="E69" t="n">
+        <v>20764.16714757587</v>
+      </c>
+      <c r="F69" t="n">
+        <v>6.584325384457639e-05</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2137.973902614781</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.168867548081979e-07</v>
+      </c>
+      <c r="I69" t="n">
+        <v>20695.77027217899</v>
+      </c>
+      <c r="J69" t="n">
+        <v>20461.66270557591</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1.675926059456666e-05</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1216588080.426728</v>
+      </c>
+      <c r="C70" t="n">
+        <v>5.716384821634688e+60</v>
+      </c>
+      <c r="D70" t="n">
+        <v>11.82805148533929</v>
+      </c>
+      <c r="E70" t="n">
+        <v>43385.12930108589</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.000184397025840297</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4402.476603803221</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3.020674334249431e-07</v>
+      </c>
+      <c r="I70" t="n">
+        <v>43314.0585525363</v>
+      </c>
+      <c r="J70" t="n">
+        <v>43021.78898974863</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>6.157895773712314e-06</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2930973564.523913</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1.691344865215773e+27</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4.436265161472607</v>
+      </c>
+      <c r="E71" t="n">
+        <v>34509.42428833988</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.0001944346492343289</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3495.799349725433</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2.808166773480231e-07</v>
+      </c>
+      <c r="I71" t="n">
+        <v>34459.58326512716</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34248.38475242396</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>6.267486051844682e-06</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2358381617.252433</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.648123931010451e+40</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.945125965000455</v>
+      </c>
+      <c r="E72" t="n">
+        <v>29894.4040752706</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.000122634791672939</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3031.025711772741</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.895488574451811e-07</v>
+      </c>
+      <c r="I72" t="n">
+        <v>29848.19818166428</v>
+      </c>
+      <c r="J72" t="n">
+        <v>29655.51694437187</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3.563432120223286e-06</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8650678214.263084</v>
+      </c>
+      <c r="C73" t="n">
+        <v>9238439270.22521</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E73" t="n">
+        <v>51604.64179593918</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.000255118932883924</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5231.127382759471</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.881545957100057e-07</v>
+      </c>
+      <c r="I73" t="n">
+        <v>51526.12712575521</v>
+      </c>
+      <c r="J73" t="n">
+        <v>51197.48891751603</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2.614064054032443e-06</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3819037662.719495</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.420504125279916e+21</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3.106759605886101</v>
+      </c>
+      <c r="E74" t="n">
+        <v>18274.03352722358</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8.488057005480418e-05</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1858.231727646526</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.591043277353899e-07</v>
+      </c>
+      <c r="I74" t="n">
+        <v>18239.77977730784</v>
+      </c>
+      <c r="J74" t="n">
+        <v>18103.49621736157</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3.330706995657855e-06</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2288918796.388811</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.354840484577935e+37</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6.089070604710126</v>
+      </c>
+      <c r="E75" t="n">
+        <v>15194.14921819726</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.314532060905656e-05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1555.568254320773</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.140678193840092e-07</v>
+      </c>
+      <c r="I75" t="n">
+        <v>15153.97884875165</v>
+      </c>
+      <c r="J75" t="n">
+        <v>15007.80672206026</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>7.704352826422585e-06</v>
+      </c>
+      <c r="B76" t="n">
+        <v>4554838180.944698</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4.827256581202417e+21</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3.386904569725495</v>
+      </c>
+      <c r="E76" t="n">
+        <v>64894.72705657646</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.0002349417002085595</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6598.60004606592</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4.389769923903196e-07</v>
+      </c>
+      <c r="I76" t="n">
+        <v>64773.47445612283</v>
+      </c>
+      <c r="J76" t="n">
+        <v>64290.66724307533</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1.402409946214172e-05</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1380185152.840949</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1.169260134605782e+35</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6.362656824027266</v>
+      </c>
+      <c r="E77" t="n">
+        <v>38823.870774091</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.0001257810392042911</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4010.414345472951</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4.608677457244518e-07</v>
+      </c>
+      <c r="I77" t="n">
+        <v>38681.61825402005</v>
+      </c>
+      <c r="J77" t="n">
+        <v>38209.53300903998</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1.372379628111229e-05</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1452013120.77163</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2.197386834051423e+40</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7.428782106451888</v>
+      </c>
+      <c r="E78" t="n">
+        <v>40732.22804690889</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8.689638658656181e-05</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4237.391717667733</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3.891454564376059e-07</v>
+      </c>
+      <c r="I78" t="n">
+        <v>40549.81814360128</v>
+      </c>
+      <c r="J78" t="n">
+        <v>39980.09669067634</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2.029334566057613e-06</v>
+      </c>
+      <c r="B79" t="n">
+        <v>9573215992.691996</v>
+      </c>
+      <c r="C79" t="n">
+        <v>10573743715.9444</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E79" t="n">
+        <v>32573.25768257957</v>
+      </c>
+      <c r="F79" t="n">
+        <v>7.170842796264614e-05</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3347.695584190374</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.210496822931133e-07</v>
+      </c>
+      <c r="I79" t="n">
+        <v>32472.846775988</v>
+      </c>
+      <c r="J79" t="n">
+        <v>32122.63224166994</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.601384546497187e-06</v>
+      </c>
+      <c r="B80" t="n">
+        <v>5653625619.491875</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1.061317159211048e+17</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2.404496779272574</v>
+      </c>
+      <c r="E80" t="n">
+        <v>46280.98191094749</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.0002745107192998729</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4678.926887478824</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3.349833375118031e-07</v>
+      </c>
+      <c r="I80" t="n">
+        <v>46224.50558163185</v>
+      </c>
+      <c r="J80" t="n">
+        <v>45975.72138482513</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>6.387979276453976e-06</v>
+      </c>
+      <c r="B81" t="n">
+        <v>4077472992.660203</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2.493091756191016e+28</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4.642980900641378</v>
+      </c>
+      <c r="E81" t="n">
+        <v>50110.33897089762</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.000159199121827849</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5090.342772049903</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.799578225461805e-07</v>
+      </c>
+      <c r="I81" t="n">
+        <v>50022.21799871969</v>
+      </c>
+      <c r="J81" t="n">
+        <v>49666.03769352227</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>5.562886440105671e-06</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3103098343.451736</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2.357578154336589e+26</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4.240976252018994</v>
+      </c>
+      <c r="E82" t="n">
+        <v>32863.53139932991</v>
+      </c>
+      <c r="F82" t="n">
+        <v>9.123695718901744e-05</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3371.83896559121</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.636988068112538e-07</v>
+      </c>
+      <c r="I82" t="n">
+        <v>32768.54714859855</v>
+      </c>
+      <c r="J82" t="n">
+        <v>32431.24779906262</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1.901582332920214e-06</v>
+      </c>
+      <c r="B83" t="n">
+        <v>6473959040.346717</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3.889970763132591e+21</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3.092378680380957</v>
+      </c>
+      <c r="E83" t="n">
+        <v>22540.43396683432</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.3479966525405e-05</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2308.231350330461</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.161414300146499e-07</v>
+      </c>
+      <c r="I83" t="n">
+        <v>22480.22512944873</v>
+      </c>
+      <c r="J83" t="n">
+        <v>22261.74712042259</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>9.332892432397317e-06</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1941085095.095613</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1.569750725678093e+44</v>
+      </c>
+      <c r="D84" t="n">
+        <v>7.954467237508033</v>
+      </c>
+      <c r="E84" t="n">
+        <v>37231.070161831</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.0001018547958885567</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3804.615681018382</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2.47763446075794e-07</v>
+      </c>
+      <c r="I84" t="n">
+        <v>37140.50497868069</v>
+      </c>
+      <c r="J84" t="n">
+        <v>36803.51938757899</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>5.982352635616083e-06</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2072166972.717406</v>
+      </c>
+      <c r="C85" t="n">
+        <v>7.410928480607636e+37</v>
+      </c>
+      <c r="D85" t="n">
+        <v>6.485003127379274</v>
+      </c>
+      <c r="E85" t="n">
+        <v>24886.20171116486</v>
+      </c>
+      <c r="F85" t="n">
+        <v>8.642050033465468e-05</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2538.664091599941</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.930931979934832e-07</v>
+      </c>
+      <c r="I85" t="n">
+        <v>24830.59735507214</v>
+      </c>
+      <c r="J85" t="n">
+        <v>24619.0311821481</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>6.552601285972407e-06</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2843017948.01109</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1.232790310009922e+17</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2.515213508981284</v>
+      </c>
+      <c r="E86" t="n">
+        <v>33340.40607330795</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.0001790740061049604</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3411.643977880766</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.631266144974399e-07</v>
+      </c>
+      <c r="I86" t="n">
+        <v>33254.18010603021</v>
+      </c>
+      <c r="J86" t="n">
+        <v>32938.54979410039</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1.050599277960142e-05</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1848187693.722099</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3.337134163144032e+27</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4.694396036927373</v>
+      </c>
+      <c r="E87" t="n">
+        <v>37503.66242002649</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.0001063156533569239</v>
+      </c>
+      <c r="G87" t="n">
+        <v>3895.135177335377</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.559911383026975e-07</v>
+      </c>
+      <c r="I87" t="n">
+        <v>37342.80804743458</v>
+      </c>
+      <c r="J87" t="n">
+        <v>36833.67013855507</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3.956122847381924e-06</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2655956021.679125</v>
+      </c>
+      <c r="C88" t="n">
+        <v>7.187149727092068e+22</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3.518532556108561</v>
+      </c>
+      <c r="E88" t="n">
+        <v>19553.75123911834</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6.169645404161847e-05</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2017.771422571522</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.187491815962552e-07</v>
+      </c>
+      <c r="I88" t="n">
+        <v>19484.42201838536</v>
+      </c>
+      <c r="J88" t="n">
+        <v>19252.11727747215</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>9.080539943053419e-06</v>
+      </c>
+      <c r="B89" t="n">
+        <v>4776831318.220537</v>
+      </c>
+      <c r="C89" t="n">
+        <v>2.436949769777494e+16</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2.374800317188734</v>
+      </c>
+      <c r="E89" t="n">
+        <v>77298.17346100132</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.0001609473587365567</v>
+      </c>
+      <c r="G89" t="n">
+        <v>8017.861594632235</v>
+      </c>
+      <c r="H89" t="n">
+        <v>6.663943722333881e-07</v>
+      </c>
+      <c r="I89" t="n">
+        <v>76978.12429596564</v>
+      </c>
+      <c r="J89" t="n">
+        <v>75954.1323519688</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1.897023349559627e-05</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1542580284.706867</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1.50243404657576e+42</v>
+      </c>
+      <c r="D90" t="n">
+        <v>8.001595045457899</v>
+      </c>
+      <c r="E90" t="n">
+        <v>60266.13312585736</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.0001287059352146413</v>
+      </c>
+      <c r="G90" t="n">
+        <v>6237.636772700746</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5.00741376026828e-07</v>
+      </c>
+      <c r="I90" t="n">
+        <v>60031.66261461846</v>
+      </c>
+      <c r="J90" t="n">
+        <v>59267.26309031458</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2.893811523453064e-06</v>
+      </c>
+      <c r="B91" t="n">
+        <v>7248303201.331181</v>
+      </c>
+      <c r="C91" t="n">
+        <v>7837738994.438705</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E91" t="n">
+        <v>35120.2292861663</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.0001846794383081957</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3565.972474193771</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3.152147154907771e-07</v>
+      </c>
+      <c r="I91" t="n">
+        <v>35060.28534663614</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34816.22085961667</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2.880978607819951e-06</v>
+      </c>
+      <c r="B92" t="n">
+        <v>6720482457.936364</v>
+      </c>
+      <c r="C92" t="n">
+        <v>595503806164.8562</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1.401396425448878</v>
+      </c>
+      <c r="E92" t="n">
+        <v>33136.98527085414</v>
+      </c>
+      <c r="F92" t="n">
+        <v>3.864385911485391e-05</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3530.612829461411</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2.810691461686811e-07</v>
+      </c>
+      <c r="I92" t="n">
+        <v>32895.96937932526</v>
+      </c>
+      <c r="J92" t="n">
+        <v>32255.31556693533</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>6.848546225013914e-06</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1702329291.842941</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2.927752676230072e+44</v>
+      </c>
+      <c r="D93" t="n">
+        <v>7.837205054741013</v>
+      </c>
+      <c r="E93" t="n">
+        <v>23929.78805202318</v>
+      </c>
+      <c r="F93" t="n">
+        <v>6.676790092166067e-05</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2452.471456421925</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1.844376943991362e-07</v>
+      </c>
+      <c r="I93" t="n">
+        <v>23863.68510622362</v>
+      </c>
+      <c r="J93" t="n">
+        <v>23626.00418217558</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>6.348689616942384e-06</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2658181936.720685</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2.88679255111248e+37</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6.412903801306122</v>
+      </c>
+      <c r="E94" t="n">
+        <v>33805.08097417351</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.0001481071745497214</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3423.049564710481</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.070923574673558e-07</v>
+      </c>
+      <c r="I94" t="n">
+        <v>33757.81267718114</v>
+      </c>
+      <c r="J94" t="n">
+        <v>33555.99410108497</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>8.860068056743548e-06</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2935012631.077309</v>
+      </c>
+      <c r="C95" t="n">
+        <v>6.850082588688051e+22</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3.679189655133222</v>
+      </c>
+      <c r="E95" t="n">
+        <v>48921.70112727676</v>
+      </c>
+      <c r="F95" t="n">
+        <v>5.325466538148999e-05</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5282.978340021494</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4.726909620270161e-07</v>
+      </c>
+      <c r="I95" t="n">
+        <v>48487.46976361696</v>
+      </c>
+      <c r="J95" t="n">
+        <v>47414.51680285023</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>6.76276227292619e-06</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9353554406.286764</v>
+      </c>
+      <c r="C96" t="n">
+        <v>9613574356.822214</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E96" t="n">
+        <v>106176.1488771944</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.0001764095262437803</v>
+      </c>
+      <c r="G96" t="n">
+        <v>11016.64696419632</v>
+      </c>
+      <c r="H96" t="n">
+        <v>7.366485925277177e-07</v>
+      </c>
+      <c r="I96" t="n">
+        <v>105732.7799033312</v>
+      </c>
+      <c r="J96" t="n">
+        <v>104317.8936110217</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1.265854613581787e-06</v>
+      </c>
+      <c r="B97" t="n">
+        <v>14684523995.51935</v>
+      </c>
+      <c r="C97" t="n">
+        <v>16683547294.93893</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E97" t="n">
+        <v>31142.69763072752</v>
+      </c>
+      <c r="F97" t="n">
+        <v>5.973286123154265e-05</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3178.969943447189</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1.378859675687314e-07</v>
+      </c>
+      <c r="I97" t="n">
+        <v>31070.8085414226</v>
+      </c>
+      <c r="J97" t="n">
+        <v>30799.59769299501</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2.154555419368721e-06</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3483058374.508049</v>
+      </c>
+      <c r="C98" t="n">
+        <v>7.173301261249553e+18</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2.68057146532019</v>
+      </c>
+      <c r="E98" t="n">
+        <v>13560.57612205806</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.660739062339685e-05</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1422.952095143366</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.458384152257202e-07</v>
+      </c>
+      <c r="I98" t="n">
+        <v>13486.2489187941</v>
+      </c>
+      <c r="J98" t="n">
+        <v>13268.60932177758</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>6.021264311564725e-06</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2604558533.683782</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4.435480584629233e+38</v>
+      </c>
+      <c r="D99" t="n">
+        <v>6.617341807683788</v>
+      </c>
+      <c r="E99" t="n">
+        <v>31656.60580188291</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3.605790352316313e-05</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3316.316281953414</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1.906686042597402e-07</v>
+      </c>
+      <c r="I99" t="n">
+        <v>31489.21057769944</v>
+      </c>
+      <c r="J99" t="n">
+        <v>30993.2727301803</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9.950904990312835e-06</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1716760670.700364</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2.976131073172509e+31</v>
+      </c>
+      <c r="D100" t="n">
+        <v>5.469136484645685</v>
+      </c>
+      <c r="E100" t="n">
+        <v>33643.54055019871</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9.065052075062309e-05</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3490.091825852203</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3.764366128458642e-07</v>
+      </c>
+      <c r="I100" t="n">
+        <v>33503.83191594057</v>
+      </c>
+      <c r="J100" t="n">
+        <v>33057.23245151088</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1.22784202418103e-05</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1869149274.251131</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1.717357094819927e+41</v>
+      </c>
+      <c r="D101" t="n">
+        <v>7.524733058310441</v>
+      </c>
+      <c r="E101" t="n">
+        <v>46944.64509419882</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9.149741247140437e-05</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4853.261400581289</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.438921313156795e-07</v>
+      </c>
+      <c r="I101" t="n">
+        <v>46768.20410401949</v>
+      </c>
+      <c r="J101" t="n">
+        <v>46187.04413829723</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2.378021459991253e-06</v>
+      </c>
+      <c r="B102" t="n">
+        <v>7734115326.091311</v>
+      </c>
+      <c r="C102" t="n">
+        <v>8461814002.785586</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E102" t="n">
+        <v>30788.33625662694</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.0001729460855996911</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3120.335719252762</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.590311607604818e-07</v>
+      </c>
+      <c r="I102" t="n">
+        <v>30742.22281930464</v>
+      </c>
+      <c r="J102" t="n">
+        <v>30548.48647169976</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3.614938154608817e-06</v>
+      </c>
+      <c r="B103" t="n">
+        <v>7017162481.673064</v>
+      </c>
+      <c r="C103" t="n">
+        <v>6.362065952002529e+18</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2.68446670878568</v>
+      </c>
+      <c r="E103" t="n">
+        <v>45738.56893756427</v>
+      </c>
+      <c r="F103" t="n">
+        <v>7.707599792128108e-05</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4704.409284816347</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.444437315933156e-07</v>
+      </c>
+      <c r="I103" t="n">
+        <v>45593.51072527547</v>
+      </c>
+      <c r="J103" t="n">
+        <v>45091.61859205442</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2.718471011335598e-06</v>
+      </c>
+      <c r="B104" t="n">
+        <v>5997644575.664777</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1.364719366048121e+20</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2.896780389742247</v>
+      </c>
+      <c r="E104" t="n">
+        <v>29674.20205624754</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4.219584811380022e-05</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3077.671782233504</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1.741939110039698e-07</v>
+      </c>
+      <c r="I104" t="n">
+        <v>29551.70030446004</v>
+      </c>
+      <c r="J104" t="n">
+        <v>29159.40577820168</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>3.943977839102977e-06</v>
+      </c>
+      <c r="B105" t="n">
+        <v>4656310680.739011</v>
+      </c>
+      <c r="C105" t="n">
+        <v>5.304962101975748e+27</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4.368274000593987</v>
+      </c>
+      <c r="E105" t="n">
+        <v>35057.96980570808</v>
+      </c>
+      <c r="F105" t="n">
+        <v>9.842076848487849e-05</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3564.230940971509</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1.822731930420353e-07</v>
+      </c>
+      <c r="I105" t="n">
+        <v>34993.04318304063</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34733.94704864243</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2.817638628367931e-06</v>
+      </c>
+      <c r="B106" t="n">
+        <v>6383042978.0349</v>
+      </c>
+      <c r="C106" t="n">
+        <v>6913134659.890673</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E106" t="n">
+        <v>30106.32661284831</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0002097808197014724</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3050.274704900966</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3.069174171844528e-07</v>
+      </c>
+      <c r="I106" t="n">
+        <v>30062.27989771927</v>
+      </c>
+      <c r="J106" t="n">
+        <v>29876.19975522493</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2.19908679106328e-06</v>
+      </c>
+      <c r="B107" t="n">
+        <v>8673895209.790394</v>
+      </c>
+      <c r="C107" t="n">
+        <v>9534516593.786968</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E107" t="n">
+        <v>31964.32889664964</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9.46765673842641e-05</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3269.218278861479</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2.395403126867744e-07</v>
+      </c>
+      <c r="I107" t="n">
+        <v>31883.45624198685</v>
+      </c>
+      <c r="J107" t="n">
+        <v>31585.67281331352</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2.595907601605128e-06</v>
+      </c>
+      <c r="B108" t="n">
+        <v>3977429969.080467</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1.542888864994979e+21</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3.108868382382296</v>
+      </c>
+      <c r="E108" t="n">
+        <v>18921.93277531528</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5.324201763866217e-05</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1942.704504155173</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.579190109864322e-07</v>
+      </c>
+      <c r="I108" t="n">
+        <v>18865.8091901779</v>
+      </c>
+      <c r="J108" t="n">
+        <v>18667.93602426305</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1.593795774719974e-05</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1137729982.416018</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1.145235116373e+57</v>
+      </c>
+      <c r="D109" t="n">
+        <v>11.01502934970468</v>
+      </c>
+      <c r="E109" t="n">
+        <v>38452.6021482311</v>
+      </c>
+      <c r="F109" t="n">
+        <v>8.6639516398164e-05</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3968.306329972664</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3.080460768048441e-07</v>
+      </c>
+      <c r="I109" t="n">
+        <v>38315.88424250938</v>
+      </c>
+      <c r="J109" t="n">
+        <v>37858.1454233721</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1.310476365993396e-06</v>
+      </c>
+      <c r="B110" t="n">
+        <v>15580482841.51775</v>
+      </c>
+      <c r="C110" t="n">
+        <v>17664839399.70582</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E110" t="n">
+        <v>34206.69293003367</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.255712198003629e-05</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3490.918637059401</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.427464890218846e-07</v>
+      </c>
+      <c r="I110" t="n">
+        <v>34128.63810330474</v>
+      </c>
+      <c r="J110" t="n">
+        <v>33833.27556435014</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2.735664118301497e-06</v>
+      </c>
+      <c r="B111" t="n">
+        <v>4972540297.640258</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3.50355719316613e+21</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3.163689889364316</v>
+      </c>
+      <c r="E111" t="n">
+        <v>24955.67750641398</v>
+      </c>
+      <c r="F111" t="n">
+        <v>8.31373280704177e-05</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2539.9404085404</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1.64247826801364e-07</v>
+      </c>
+      <c r="I111" t="n">
+        <v>24906.37455319287</v>
+      </c>
+      <c r="J111" t="n">
+        <v>24712.78259035696</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1.989971148124596e-05</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1191965229.272493</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1.962668902559906e+45</v>
+      </c>
+      <c r="D112" t="n">
+        <v>8.717417986255558</v>
+      </c>
+      <c r="E112" t="n">
+        <v>49397.74186847982</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7.755991549319015e-05</v>
+      </c>
+      <c r="G112" t="n">
+        <v>5216.857671770013</v>
+      </c>
+      <c r="H112" t="n">
+        <v>4.83390780006129e-07</v>
+      </c>
+      <c r="I112" t="n">
+        <v>49089.87132967755</v>
+      </c>
+      <c r="J112" t="n">
+        <v>48226.28499266251</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>7.38185564961965e-06</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1857302521.006657</v>
+      </c>
+      <c r="C113" t="n">
+        <v>6.787436633180177e+27</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4.644000715113846</v>
+      </c>
+      <c r="E113" t="n">
+        <v>26495.18985492994</v>
+      </c>
+      <c r="F113" t="n">
+        <v>5.222364264223953e-05</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2797.209710158211</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3.234527419555794e-07</v>
+      </c>
+      <c r="I113" t="n">
+        <v>26331.08904974637</v>
+      </c>
+      <c r="J113" t="n">
+        <v>25869.80237957975</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1.515267892145295e-05</v>
+      </c>
+      <c r="B114" t="n">
+        <v>806671395.4694394</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1.150337891797602e+97</v>
+      </c>
+      <c r="D114" t="n">
+        <v>19.29463187498571</v>
+      </c>
+      <c r="E114" t="n">
+        <v>26960.20951607989</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.422493354961716e-05</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2984.132565299196</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1.689060628893771e-07</v>
+      </c>
+      <c r="I114" t="n">
+        <v>26640.08550086744</v>
+      </c>
+      <c r="J114" t="n">
+        <v>25934.91303438015</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2.454980392723419e-06</v>
+      </c>
+      <c r="B115" t="n">
+        <v>10210237199.36193</v>
+      </c>
+      <c r="C115" t="n">
+        <v>11149655949.64705</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E115" t="n">
+        <v>42046.58445672441</v>
+      </c>
+      <c r="F115" t="n">
+        <v>7.564461736114994e-05</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4338.4348355855</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.67414079927483e-07</v>
+      </c>
+      <c r="I115" t="n">
+        <v>41897.94402348767</v>
+      </c>
+      <c r="J115" t="n">
+        <v>41399.45889733946</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1.440950832991057e-06</v>
+      </c>
+      <c r="B116" t="n">
+        <v>12221236000.03175</v>
+      </c>
+      <c r="C116" t="n">
+        <v>13777768265.69586</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E116" t="n">
+        <v>29485.9340186063</v>
+      </c>
+      <c r="F116" t="n">
+        <v>9.197860054304694e-05</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2993.878572225814</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1.56958704178317e-07</v>
+      </c>
+      <c r="I116" t="n">
+        <v>29435.61716264499</v>
+      </c>
+      <c r="J116" t="n">
+        <v>29230.73953004076</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1.046021768576762e-05</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1247920756.561033</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4.415759317534574e+48</v>
+      </c>
+      <c r="D117" t="n">
+        <v>8.953192302257102</v>
+      </c>
+      <c r="E117" t="n">
+        <v>27237.27113886363</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4.458299876828568e-05</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2859.856066883008</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.475789276978293e-07</v>
+      </c>
+      <c r="I117" t="n">
+        <v>27086.01674664513</v>
+      </c>
+      <c r="J117" t="n">
+        <v>26645.02408171707</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2.665251099658117e-06</v>
+      </c>
+      <c r="B118" t="n">
+        <v>4431538846.940591</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3.624388693181797e+22</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3.348975436969365</v>
+      </c>
+      <c r="E118" t="n">
+        <v>21793.10259952753</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.0001561696610783818</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2198.550660274977</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1.531966253803741e-07</v>
+      </c>
+      <c r="I118" t="n">
+        <v>21771.72437694728</v>
+      </c>
+      <c r="J118" t="n">
+        <v>21672.90005672205</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2.914505994320712e-06</v>
+      </c>
+      <c r="B119" t="n">
+        <v>11905747484.33926</v>
+      </c>
+      <c r="C119" t="n">
+        <v>21476681942.84808</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.099538095242875</v>
+      </c>
+      <c r="E119" t="n">
+        <v>58280.16047513141</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.0001085246689119565</v>
+      </c>
+      <c r="G119" t="n">
+        <v>5979.458386738759</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3.133376128480754e-07</v>
+      </c>
+      <c r="I119" t="n">
+        <v>58111.89120932517</v>
+      </c>
+      <c r="J119" t="n">
+        <v>57514.17760764501</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1.177835372091057e-05</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2074659345.482962</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.102070944771221e+32</v>
+      </c>
+      <c r="D120" t="n">
+        <v>5.633435993302126</v>
+      </c>
+      <c r="E120" t="n">
+        <v>48224.36995325291</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.0001733924780148547</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4930.973199656505</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4.33606527192201e-07</v>
+      </c>
+      <c r="I120" t="n">
+        <v>48103.77417066268</v>
+      </c>
+      <c r="J120" t="n">
+        <v>47658.33671399317</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2.502311564124811e-06</v>
+      </c>
+      <c r="B121" t="n">
+        <v>4376566111.639027</v>
+      </c>
+      <c r="C121" t="n">
+        <v>7.111604051209849e+22</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3.390424662451486</v>
+      </c>
+      <c r="E121" t="n">
+        <v>20265.03923270485</v>
+      </c>
+      <c r="F121" t="n">
+        <v>6.013113486826694e-05</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2069.714049031239</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1.424606666989647e-07</v>
+      </c>
+      <c r="I121" t="n">
+        <v>20217.02798185957</v>
+      </c>
+      <c r="J121" t="n">
+        <v>20037.13139976161</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>5.081509992471093e-06</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1340457943.104717</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.454506499734342e+35</v>
+      </c>
+      <c r="D122" t="n">
+        <v>6.02940098533769</v>
+      </c>
+      <c r="E122" t="n">
+        <v>13562.56537831151</v>
+      </c>
+      <c r="F122" t="n">
+        <v>6.044533883046298e-05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1391.724774017974</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1.756378264755584e-07</v>
+      </c>
+      <c r="I122" t="n">
+        <v>13523.15622699282</v>
+      </c>
+      <c r="J122" t="n">
+        <v>13383.41709366458</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.280464231146059e-06</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1239731507.432336</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2.279633950125505e+53</v>
+      </c>
+      <c r="D123" t="n">
+        <v>9.25616669527184</v>
+      </c>
+      <c r="E123" t="n">
+        <v>11062.6033827947</v>
+      </c>
+      <c r="F123" t="n">
+        <v>6.635354688673989e-05</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1120.977150931192</v>
+      </c>
+      <c r="H123" t="n">
+        <v>9.807945687923202e-08</v>
+      </c>
+      <c r="I123" t="n">
+        <v>11046.25136873723</v>
+      </c>
+      <c r="J123" t="n">
+        <v>10977.33737512224</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>3.702237419250914e-06</v>
+      </c>
+      <c r="B124" t="n">
+        <v>9180384586.766308</v>
+      </c>
+      <c r="C124" t="n">
+        <v>9781756906.082798</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E124" t="n">
+        <v>56892.51650672299</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.0002821621106522521</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5762.432840542043</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4.032742648684852e-07</v>
+      </c>
+      <c r="I124" t="n">
+        <v>56811.20407353439</v>
+      </c>
+      <c r="J124" t="n">
+        <v>56465.80088698192</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>6.654220129720017e-06</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1347662085.378379</v>
+      </c>
+      <c r="C125" t="n">
+        <v>9.380955891530274e+48</v>
+      </c>
+      <c r="D125" t="n">
+        <v>8.708651658707701</v>
+      </c>
+      <c r="E125" t="n">
+        <v>18596.27476212152</v>
+      </c>
+      <c r="F125" t="n">
+        <v>7.733308607420187e-05</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1894.644300982854</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.617981832190378e-07</v>
+      </c>
+      <c r="I125" t="n">
+        <v>18557.36717904296</v>
+      </c>
+      <c r="J125" t="n">
+        <v>18406.80163810643</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1.800242751727267e-06</v>
+      </c>
+      <c r="B126" t="n">
+        <v>4355180020.993597</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.221962676749709e+26</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3.891247567890579</v>
+      </c>
+      <c r="E126" t="n">
+        <v>14751.84292901079</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4.489784311679846e-05</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1502.312685864002</v>
+      </c>
+      <c r="H126" t="n">
+        <v>9.174042691340005e-08</v>
+      </c>
+      <c r="I126" t="n">
+        <v>14721.70027016309</v>
+      </c>
+      <c r="J126" t="n">
+        <v>14604.34822389633</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1.914748417935043e-06</v>
+      </c>
+      <c r="B127" t="n">
+        <v>16104863866.36523</v>
+      </c>
+      <c r="C127" t="n">
+        <v>17849970303.05365</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E127" t="n">
+        <v>51607.70939479864</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.0001687968592070095</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5218.161529925604</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2.08568136834154e-07</v>
+      </c>
+      <c r="I127" t="n">
+        <v>51543.94207208117</v>
+      </c>
+      <c r="J127" t="n">
+        <v>51263.83256704549</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.221075213060228e-05</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1638660115.305315</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2.523975641512583e+23</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3.92022385192057</v>
+      </c>
+      <c r="E128" t="n">
+        <v>37754.78407480365</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.0001569729547411843</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3909.351253403461</v>
+      </c>
+      <c r="H128" t="n">
+        <v>6.184474865349697e-07</v>
+      </c>
+      <c r="I128" t="n">
+        <v>37606.03646822244</v>
+      </c>
+      <c r="J128" t="n">
+        <v>37122.92765294159</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1.375579551326686e-05</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1454587225.327064</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.183706209690586e+40</v>
+      </c>
+      <c r="D129" t="n">
+        <v>7.462983297302178</v>
+      </c>
+      <c r="E129" t="n">
+        <v>41122.93523898342</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4.140962735573008e-05</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4459.375256269434</v>
+      </c>
+      <c r="H129" t="n">
+        <v>3.883349364788254e-07</v>
+      </c>
+      <c r="I129" t="n">
+        <v>40737.2888696822</v>
+      </c>
+      <c r="J129" t="n">
+        <v>39804.12705199773</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>6.368908875013459e-06</v>
+      </c>
+      <c r="B130" t="n">
+        <v>2107243136.388333</v>
+      </c>
+      <c r="C130" t="n">
+        <v>2.567043514602377e+28</v>
+      </c>
+      <c r="D130" t="n">
+        <v>4.699379181068364</v>
+      </c>
+      <c r="E130" t="n">
+        <v>25849.49219733776</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.0002036882860396445</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2616.492476727613</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2.761709937464776e-07</v>
+      </c>
+      <c r="I130" t="n">
+        <v>25814.44413401128</v>
+      </c>
+      <c r="J130" t="n">
+        <v>25663.72761263267</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1.457689252110273e-05</v>
+      </c>
+      <c r="B131" t="n">
+        <v>981646020.5183604</v>
+      </c>
+      <c r="C131" t="n">
+        <v>2.256920081756553e+65</v>
+      </c>
+      <c r="D131" t="n">
+        <v>12.66117196769394</v>
+      </c>
+      <c r="E131" t="n">
+        <v>30663.6310992815</v>
+      </c>
+      <c r="F131" t="n">
+        <v>6.164855934797148e-05</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3176.375508014167</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2.457527989739761e-07</v>
+      </c>
+      <c r="I131" t="n">
+        <v>30541.39510140815</v>
+      </c>
+      <c r="J131" t="n">
+        <v>30145.78654238112</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1.485805514288593e-06</v>
+      </c>
+      <c r="B132" t="n">
+        <v>5280324984.816464</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1551797910901946</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.980115260650833</v>
+      </c>
+      <c r="E132" t="n">
+        <v>13736.93656335972</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3.405621258424593e-05</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1417.8936817503</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1.217549046847803e-07</v>
+      </c>
+      <c r="I132" t="n">
+        <v>13687.82542401046</v>
+      </c>
+      <c r="J132" t="n">
+        <v>13523.66467236981</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1.904726741211411e-06</v>
+      </c>
+      <c r="B133" t="n">
+        <v>8166776088.144678</v>
+      </c>
+      <c r="C133" t="n">
+        <v>9054560594.826979</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E133" t="n">
+        <v>26061.00282105781</v>
+      </c>
+      <c r="F133" t="n">
+        <v>9.030503414930355e-05</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2659.988099366848</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2.074765038955268e-07</v>
+      </c>
+      <c r="I133" t="n">
+        <v>26001.12746854551</v>
+      </c>
+      <c r="J133" t="n">
+        <v>25774.96086704244</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1.089018937909456e-05</v>
+      </c>
+      <c r="B134" t="n">
+        <v>923669624.8317542</v>
+      </c>
+      <c r="C134" t="n">
+        <v>8.854250711337222e+58</v>
+      </c>
+      <c r="D134" t="n">
+        <v>11.07989014904094</v>
+      </c>
+      <c r="E134" t="n">
+        <v>21329.97281835128</v>
+      </c>
+      <c r="F134" t="n">
+        <v>6.832828597221852e-05</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2191.793729493319</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2.092756998151886e-07</v>
+      </c>
+      <c r="I134" t="n">
+        <v>21264.6434320644</v>
+      </c>
+      <c r="J134" t="n">
+        <v>21036.36902917067</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2.03071109038174e-06</v>
+      </c>
+      <c r="B135" t="n">
+        <v>15074978178.38526</v>
+      </c>
+      <c r="C135" t="n">
+        <v>16649837660.85507</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E135" t="n">
+        <v>51270.15309316716</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.0001130058539559215</v>
+      </c>
+      <c r="G135" t="n">
+        <v>5217.336689437599</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2.211996231996579e-07</v>
+      </c>
+      <c r="I135" t="n">
+        <v>51169.79600414397</v>
+      </c>
+      <c r="J135" t="n">
+        <v>50774.81643151509</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.726748619565864e-06</v>
+      </c>
+      <c r="B136" t="n">
+        <v>4495903292.149563</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.11136038860537e+20</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2.98836189377126</v>
+      </c>
+      <c r="E136" t="n">
+        <v>38696.44435816973</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.0002653840129667086</v>
+      </c>
+      <c r="G136" t="n">
+        <v>3908.501707807097</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2.96096649610903e-07</v>
+      </c>
+      <c r="I136" t="n">
+        <v>38653.26961151404</v>
+      </c>
+      <c r="J136" t="n">
+        <v>38459.22768502562</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1.639551790977639e-06</v>
+      </c>
+      <c r="B137" t="n">
+        <v>6371292150.712802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>7127509592.616973</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E137" t="n">
+        <v>17518.37033045036</v>
+      </c>
+      <c r="F137" t="n">
+        <v>5.424514035188646e-05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1803.74532722425</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1.785917455704654e-07</v>
+      </c>
+      <c r="I137" t="n">
+        <v>17460.69444802901</v>
+      </c>
+      <c r="J137" t="n">
+        <v>17263.25363299957</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>5.498182437331141e-06</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2081590937.26846</v>
+      </c>
+      <c r="C138" t="n">
+        <v>5.062077801890393e+39</v>
+      </c>
+      <c r="D138" t="n">
+        <v>6.79415345543451</v>
+      </c>
+      <c r="E138" t="n">
+        <v>23092.86531884698</v>
+      </c>
+      <c r="F138" t="n">
+        <v>9.60654759514494e-05</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2346.022423037077</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.697999610282584e-07</v>
+      </c>
+      <c r="I138" t="n">
+        <v>23052.047662011</v>
+      </c>
+      <c r="J138" t="n">
+        <v>22887.27174549463</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1.584416474993845e-06</v>
+      </c>
+      <c r="B139" t="n">
+        <v>12791822549.67047</v>
+      </c>
+      <c r="C139" t="n">
+        <v>14339404718.86368</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E139" t="n">
+        <v>33932.33194917566</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.0001066934306665164</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3442.632874080527</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1.725860113336388e-07</v>
+      </c>
+      <c r="I139" t="n">
+        <v>33877.44341677237</v>
+      </c>
+      <c r="J139" t="n">
+        <v>33651.03687256025</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2.764955758524523e-06</v>
+      </c>
+      <c r="B140" t="n">
+        <v>5711029815.893266</v>
+      </c>
+      <c r="C140" t="n">
+        <v>6192298431.995183</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.059801980198021</v>
+      </c>
+      <c r="E140" t="n">
+        <v>26504.90666149347</v>
+      </c>
+      <c r="F140" t="n">
+        <v>7.222443201033895e-05</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2749.964551711819</v>
+      </c>
+      <c r="H140" t="n">
+        <v>3.011788209786044e-07</v>
+      </c>
+      <c r="I140" t="n">
+        <v>26394.38012197962</v>
+      </c>
+      <c r="J140" t="n">
+        <v>26041.51795830965</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>3.902044582359818e-06</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2112159112.963531</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.767593233428585e+36</v>
+      </c>
+      <c r="D141" t="n">
+        <v>6.057568217432631</v>
+      </c>
+      <c r="E141" t="n">
+        <v>16396.59591835319</v>
+      </c>
+      <c r="F141" t="n">
+        <v>8.941203698095832e-05</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1661.822467923597</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1.342845054395595e-07</v>
+      </c>
+      <c r="I141" t="n">
+        <v>16371.97050047732</v>
+      </c>
+      <c r="J141" t="n">
+        <v>16268.57849056039</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>6.917839833655508e-06</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2563902039.749474</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4.575853581911409e+30</v>
+      </c>
+      <c r="D142" t="n">
+        <v>5.142567493204371</v>
+      </c>
+      <c r="E142" t="n">
+        <v>34600.82557446903</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.000109202963637102</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3539.010188125141</v>
+      </c>
+      <c r="H142" t="n">
+        <v>2.767798821693743e-07</v>
+      </c>
+      <c r="I142" t="n">
+        <v>34513.12820704877</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34190.36740932654</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>3.542695122945178e-06</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3761497747.451452</v>
+      </c>
+      <c r="C143" t="n">
+        <v>6.107495702682723e+27</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4.367708097140294</v>
+      </c>
+      <c r="E143" t="n">
+        <v>25409.9167172301</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.0002290592018422405</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2557.339822467948</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1.6374597204637e-07</v>
+      </c>
+      <c r="I143" t="n">
+        <v>25391.75210529128</v>
+      </c>
+      <c r="J143" t="n">
+        <v>25302.04610227095</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>5.310962457727114e-06</v>
+      </c>
+      <c r="B144" t="n">
+        <v>5864810867.176059</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1.549511086251263e+16</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2.26097955671381</v>
+      </c>
+      <c r="E144" t="n">
+        <v>55100.74688684217</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.0002464189920619325</v>
+      </c>
+      <c r="G144" t="n">
+        <v>5590.989700042729</v>
+      </c>
+      <c r="H144" t="n">
+        <v>4.020714916299342e-07</v>
+      </c>
+      <c r="I144" t="n">
+        <v>55010.84131866603</v>
+      </c>
+      <c r="J144" t="n">
+        <v>54640.76780987055</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>3.957365628363408e-06</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8285789364.41119</v>
+      </c>
+      <c r="C145" t="n">
+        <v>8793445892.50456</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E145" t="n">
+        <v>54958.54630786697</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.00015802241294547</v>
+      </c>
+      <c r="G145" t="n">
+        <v>5630.782442456264</v>
+      </c>
+      <c r="H145" t="n">
+        <v>4.3106466006088e-07</v>
+      </c>
+      <c r="I145" t="n">
+        <v>54808.626517123</v>
+      </c>
+      <c r="J145" t="n">
+        <v>54267.71865768848</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1.840818435038785e-06</v>
+      </c>
+      <c r="B146" t="n">
+        <v>6066640022.27399</v>
+      </c>
+      <c r="C146" t="n">
+        <v>311659389972.1312</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.347062469808586</v>
+      </c>
+      <c r="E146" t="n">
+        <v>18968.61710778504</v>
+      </c>
+      <c r="F146" t="n">
+        <v>8.027816783454428e-05</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1935.714348386345</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1.82700518497581e-07</v>
+      </c>
+      <c r="I146" t="n">
+        <v>18925.44751044299</v>
+      </c>
+      <c r="J146" t="n">
+        <v>18761.97941504342</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1.247309887441523e-05</v>
+      </c>
+      <c r="B147" t="n">
+        <v>936120253.0342906</v>
+      </c>
+      <c r="C147" t="n">
+        <v>2.261055396084107e+68</v>
+      </c>
+      <c r="D147" t="n">
+        <v>13.11590200231777</v>
+      </c>
+      <c r="E147" t="n">
+        <v>25095.12767398616</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4.364198968171605e-05</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2614.633508390838</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2.031239048700318e-07</v>
+      </c>
+      <c r="I147" t="n">
+        <v>24978.32685066147</v>
+      </c>
+      <c r="J147" t="n">
+        <v>24617.88653657761</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>3.133816744057326e-06</v>
+      </c>
+      <c r="B148" t="n">
+        <v>15721580520.45646</v>
+      </c>
+      <c r="C148" t="n">
+        <v>16919257502.4929</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E148" t="n">
+        <v>82415.03391898068</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.0004524443133828943</v>
+      </c>
+      <c r="G148" t="n">
+        <v>8297.465447148654</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3.413578062608353e-07</v>
+      </c>
+      <c r="I148" t="n">
+        <v>82352.85385759115</v>
+      </c>
+      <c r="J148" t="n">
+        <v>82045.88302314977</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.770493557930055e-06</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1753566086.955728</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2.219016769438167e+52</v>
+      </c>
+      <c r="D149" t="n">
+        <v>9.111042986454077</v>
+      </c>
+      <c r="E149" t="n">
+        <v>17403.20658352141</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.0001214904638730037</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1754.631704356688</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1.110048062602834e-07</v>
+      </c>
+      <c r="I149" t="n">
+        <v>17387.30542129413</v>
+      </c>
+      <c r="J149" t="n">
+        <v>17312.67296313947</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2.053497062431998e-06</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3715799880.744454</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1.036445747658854e+19</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2.697433792896754</v>
+      </c>
+      <c r="E150" t="n">
+        <v>13786.83929698489</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.935977986922835e-05</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1437.173213786929</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1.383954709394398e-07</v>
+      </c>
+      <c r="I150" t="n">
+        <v>13721.85120355329</v>
+      </c>
+      <c r="J150" t="n">
+        <v>13522.10113643516</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2.849152949269938e-06</v>
+      </c>
+      <c r="B151" t="n">
+        <v>5609900228.051073</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1.587054430238244e+16</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2.205338425221782</v>
+      </c>
+      <c r="E151" t="n">
+        <v>28277.14381434503</v>
+      </c>
+      <c r="F151" t="n">
+        <v>5.35621302575915e-05</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2931.792557544032</v>
+      </c>
+      <c r="H151" t="n">
+        <v>2.190480867340055e-07</v>
+      </c>
+      <c r="I151" t="n">
+        <v>28161.50139644556</v>
+      </c>
+      <c r="J151" t="n">
+        <v>27790.11546432624</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>5.799406436887279e-06</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2251716333.231744</v>
+      </c>
+      <c r="C152" t="n">
+        <v>2.5248802267194e+33</v>
+      </c>
+      <c r="D152" t="n">
+        <v>5.61418344027389</v>
+      </c>
+      <c r="E152" t="n">
+        <v>25727.14474334479</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.0001742675309122899</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2601.171074243837</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2.141733286782609e-07</v>
+      </c>
+      <c r="I152" t="n">
+        <v>25695.52629900106</v>
+      </c>
+      <c r="J152" t="n">
+        <v>25556.46730399879</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1.572349247681257e-06</v>
+      </c>
+      <c r="B153" t="n">
+        <v>6510172620.708665</v>
+      </c>
+      <c r="C153" t="n">
+        <v>39757774338524.95</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1.697039720622282</v>
+      </c>
+      <c r="E153" t="n">
+        <v>17663.41565051967</v>
+      </c>
+      <c r="F153" t="n">
+        <v>7.989309165244081e-05</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1794.209271741187</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1.400532722370872e-07</v>
+      </c>
+      <c r="I153" t="n">
+        <v>17632.4515319761</v>
+      </c>
+      <c r="J153" t="n">
+        <v>17507.19986399986</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>3.888113628151026e-06</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2052059778.148011</v>
+      </c>
+      <c r="C154" t="n">
+        <v>2.300198192054708e+35</v>
+      </c>
+      <c r="D154" t="n">
+        <v>5.834839580895774</v>
+      </c>
+      <c r="E154" t="n">
+        <v>15824.20973445628</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4.527687748715865e-05</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1626.004285150809</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1.385581753580318e-07</v>
+      </c>
+      <c r="I154" t="n">
+        <v>15775.78383256163</v>
+      </c>
+      <c r="J154" t="n">
+        <v>15606.5368665729</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1.946051611816754e-06</v>
+      </c>
+      <c r="B155" t="n">
+        <v>15718070086.85243</v>
+      </c>
+      <c r="C155" t="n">
+        <v>17404377609.05661</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E155" t="n">
+        <v>51387.84755621927</v>
+      </c>
+      <c r="F155" t="n">
+        <v>4.199000359636186e-05</v>
+      </c>
+      <c r="G155" t="n">
+        <v>5372.263646216747</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2.119779053257805e-07</v>
+      </c>
+      <c r="I155" t="n">
+        <v>51128.42656666946</v>
+      </c>
+      <c r="J155" t="n">
+        <v>50348.25080535033</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2.157730148053644e-06</v>
+      </c>
+      <c r="B156" t="n">
+        <v>8672105882.538345</v>
+      </c>
+      <c r="C156" t="n">
+        <v>9543378776.423321</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E156" t="n">
+        <v>31376.02542664848</v>
+      </c>
+      <c r="F156" t="n">
+        <v>7.476766999024316e-05</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3226.37126370932</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2.350354503782642e-07</v>
+      </c>
+      <c r="I156" t="n">
+        <v>31277.39351437685</v>
+      </c>
+      <c r="J156" t="n">
+        <v>30935.27793159528</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1.258478130411947e-05</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1438600007.262705</v>
+      </c>
+      <c r="C157" t="n">
+        <v>6.82598140075148e+57</v>
+      </c>
+      <c r="D157" t="n">
+        <v>10.94287471925631</v>
+      </c>
+      <c r="E157" t="n">
+        <v>38297.01834319554</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.0001527368104257357</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3884.946483606265</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2.448084846688825e-07</v>
+      </c>
+      <c r="I157" t="n">
+        <v>38235.63539954363</v>
+      </c>
+      <c r="J157" t="n">
+        <v>37981.87838071688</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1.177371350576386e-05</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2044491433.003585</v>
+      </c>
+      <c r="C158" t="n">
+        <v>9.04202151712955e+36</v>
+      </c>
+      <c r="D158" t="n">
+        <v>6.627528353931838</v>
+      </c>
+      <c r="E158" t="n">
+        <v>48417.14730041652</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.0002376147589494071</v>
+      </c>
+      <c r="G158" t="n">
+        <v>4909.986324275799</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3.722817525870626e-07</v>
+      </c>
+      <c r="I158" t="n">
+        <v>48341.28997348969</v>
+      </c>
+      <c r="J158" t="n">
+        <v>48025.98447541803</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>9.163106169596017e-06</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1430701847.864327</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2.130750287771173e+52</v>
+      </c>
+      <c r="D159" t="n">
+        <v>9.580618841883245</v>
+      </c>
+      <c r="E159" t="n">
+        <v>27433.10353061616</v>
+      </c>
+      <c r="F159" t="n">
+        <v>9.766846105857329e-05</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2794.630710854091</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2.03014271141126e-07</v>
+      </c>
+      <c r="I159" t="n">
+        <v>27376.08091084674</v>
+      </c>
+      <c r="J159" t="n">
+        <v>27155.04514691816</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2.318667058289539e-06</v>
+      </c>
+      <c r="B160" t="n">
+        <v>5832977747.896509</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1411547092989620</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1.998587468193929</v>
+      </c>
+      <c r="E160" t="n">
+        <v>23692.69568632255</v>
+      </c>
+      <c r="F160" t="n">
+        <v>5.794630362801674e-05</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2438.817667608242</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1.889966104776423e-07</v>
+      </c>
+      <c r="I160" t="n">
+        <v>23615.42002079367</v>
+      </c>
+      <c r="J160" t="n">
+        <v>23350.17375682316</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2.817121969802659e-05</v>
+      </c>
+      <c r="B161" t="n">
+        <v>533583104.6058289</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3.721817571731184e+99</v>
+      </c>
+      <c r="D161" t="n">
+        <v>20.96797600045242</v>
+      </c>
+      <c r="E161" t="n">
+        <v>32971.63441100034</v>
+      </c>
+      <c r="F161" t="n">
+        <v>7.904077955893898e-05</v>
+      </c>
+      <c r="G161" t="n">
+        <v>3405.813357485918</v>
+      </c>
+      <c r="H161" t="n">
+        <v>2.893993998701685e-07</v>
+      </c>
+      <c r="I161" t="n">
+        <v>32850.91228168269</v>
+      </c>
+      <c r="J161" t="n">
+        <v>32450.17895630378</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2.001149826695999e-06</v>
+      </c>
+      <c r="B162" t="n">
+        <v>7410391136.528933</v>
+      </c>
+      <c r="C162" t="n">
+        <v>33152121569.19927</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1.165190940237617</v>
+      </c>
+      <c r="E162" t="n">
+        <v>24977.33156938372</v>
+      </c>
+      <c r="F162" t="n">
+        <v>8.263030960120603e-05</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2555.018981075008</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2.105707271687616e-07</v>
+      </c>
+      <c r="I162" t="n">
+        <v>24913.68065367635</v>
+      </c>
+      <c r="J162" t="n">
+        <v>24679.76101536419</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,1186 +482,962 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.667031178876705e-06</v>
+        <v>8.403448149405198e-06</v>
       </c>
       <c r="B2" t="n">
-        <v>3081289910.235978</v>
+        <v>4667201256.911844</v>
       </c>
       <c r="C2" t="n">
-        <v>8.727818723857648e+21</v>
+        <v>8.713844062863805e+26</v>
       </c>
       <c r="D2" t="n">
-        <v>3.324318753001945</v>
+        <v>4.431156156448607</v>
       </c>
       <c r="E2" t="n">
-        <v>20849.16690201708</v>
+        <v>74940.1353005407</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001115928444877289</v>
+        <v>0.0004178605713769885</v>
       </c>
       <c r="G2" t="n">
-        <v>2120.562360368803</v>
+        <v>7555.930149064542</v>
       </c>
       <c r="H2" t="n">
-        <v>2.119883119610471e-07</v>
+        <v>3.836026908335675e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>20809.56060183142</v>
+        <v>74871.33905719573</v>
       </c>
       <c r="J2" t="n">
-        <v>20652.5052455757</v>
+        <v>74548.76597002705</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.287555518768828e-06</v>
+        <v>4.340603162646586e-06</v>
       </c>
       <c r="B3" t="n">
-        <v>10329056239.93125</v>
+        <v>3096010541.841296</v>
       </c>
       <c r="C3" t="n">
-        <v>11723241168.54478</v>
+        <v>1.024915092072574e+20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.05980198019802</v>
+        <v>2.998214520422403</v>
       </c>
       <c r="E3" t="n">
-        <v>22257.86658732424</v>
+        <v>24524.54410293533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001112039561216727</v>
+        <v>9.227768975211786e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2251.051002004031</v>
+        <v>2517.335491357446</v>
       </c>
       <c r="H3" t="n">
-        <v>1.402497858751369e-07</v>
+        <v>2.712509940186463e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>22229.79509480024</v>
+        <v>24452.45401286431</v>
       </c>
       <c r="J3" t="n">
-        <v>22107.05854398389</v>
+        <v>24197.65158740982</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3.615997596989913e-06</v>
+        <v>2.184094999386381e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>6100290280.329127</v>
+        <v>8195724534.336205</v>
       </c>
       <c r="C4" t="n">
-        <v>3231022041785144</v>
+        <v>9012588103.180801</v>
       </c>
       <c r="D4" t="n">
-        <v>2.095583423253725</v>
+        <v>1.059801980198021</v>
       </c>
       <c r="E4" t="n">
-        <v>38762.33677368958</v>
+        <v>30098.19108107954</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000136498557933969</v>
+        <v>4.028047433364319e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3949.508221781581</v>
+        <v>3169.810307850998</v>
       </c>
       <c r="H4" t="n">
-        <v>2.86700684739033e-07</v>
+        <v>2.379072991647008e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>38680.92061323112</v>
+        <v>29920.42308136504</v>
       </c>
       <c r="J4" t="n">
-        <v>38366.1691304524</v>
+        <v>29412.64057159039</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.804711149147034e-06</v>
+        <v>7.982255016870326e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>7637125006.692332</v>
+        <v>1879916082.951727</v>
       </c>
       <c r="C5" t="n">
-        <v>1269052006566.318</v>
+        <v>8.918333422981467e+37</v>
       </c>
       <c r="D5" t="n">
-        <v>1.449228686090626</v>
+        <v>6.643286292337121</v>
       </c>
       <c r="E5" t="n">
-        <v>36586.51912430811</v>
+        <v>30226.6134671924</v>
       </c>
       <c r="F5" t="n">
-        <v>8.858434484029704e-05</v>
+        <v>9.255223470126079e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3758.848652639759</v>
+        <v>3096.681689868969</v>
       </c>
       <c r="H5" t="n">
-        <v>2.695547370083375e-07</v>
+        <v>2.518291512028452e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>36475.18941296484</v>
+        <v>30144.36864147048</v>
       </c>
       <c r="J5" t="n">
-        <v>36085.47550387601</v>
+        <v>29847.42298674059</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8.525568158618643e-06</v>
+        <v>1.477110351627712e-06</v>
       </c>
       <c r="B6" t="n">
-        <v>1299810232.605409</v>
+        <v>6027016845.53777</v>
       </c>
       <c r="C6" t="n">
-        <v>5.679913997219084e+29</v>
+        <v>7.588403553199127e+21</v>
       </c>
       <c r="D6" t="n">
-        <v>5.096409300323141</v>
+        <v>3.108000545632082</v>
       </c>
       <c r="E6" t="n">
-        <v>21594.93646458914</v>
+        <v>16294.57930272303</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001314104077698925</v>
+        <v>5.152422848292629e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2210.354754894003</v>
+        <v>1655.039256711742</v>
       </c>
       <c r="H6" t="n">
-        <v>3.438912641007043e-07</v>
+        <v>8.98770678323914e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>21538.42412188349</v>
+        <v>16266.15560667921</v>
       </c>
       <c r="J6" t="n">
-        <v>21332.21709664665</v>
+        <v>16151.04061700295</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.335037051107788e-06</v>
+        <v>9.102525088777863e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>11113462454.42222</v>
+        <v>2944092151.233714</v>
       </c>
       <c r="C7" t="n">
-        <v>12586237337.20059</v>
+        <v>1.222685002548339e+39</v>
       </c>
       <c r="D7" t="n">
-        <v>1.05980198019802</v>
+        <v>6.89321972878093</v>
       </c>
       <c r="E7" t="n">
-        <v>24823.17528929426</v>
+        <v>54193.37411390413</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001557150299406205</v>
+        <v>0.0001203575031428584</v>
       </c>
       <c r="G7" t="n">
-        <v>2503.18159123063</v>
+        <v>5531.697218049677</v>
       </c>
       <c r="H7" t="n">
-        <v>1.454218150781419e-07</v>
+        <v>2.772652562183012e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>24799.99299784848</v>
+        <v>54068.52988428272</v>
       </c>
       <c r="J7" t="n">
-        <v>24691.58237742136</v>
+        <v>53597.28789401611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.459645574061837e-06</v>
+        <v>4.311716514286575e-06</v>
       </c>
       <c r="B8" t="n">
-        <v>3358793166.809647</v>
+        <v>9023192897.158333</v>
       </c>
       <c r="C8" t="n">
-        <v>3.089462786388682e+17</v>
+        <v>6902703890830084</v>
       </c>
       <c r="D8" t="n">
-        <v>2.402770436970912</v>
+        <v>2.14051634621999</v>
       </c>
       <c r="E8" t="n">
-        <v>8723.507111697914</v>
+        <v>68581.96257327804</v>
       </c>
       <c r="F8" t="n">
-        <v>7.274856432803323e-05</v>
+        <v>0.000102574168026858</v>
       </c>
       <c r="G8" t="n">
-        <v>883.8241454833168</v>
+        <v>7061.320087251413</v>
       </c>
       <c r="H8" t="n">
-        <v>1.06312475722024e-07</v>
+        <v>3.375564892490878e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>8710.758851349552</v>
+        <v>68356.26942891847</v>
       </c>
       <c r="J8" t="n">
-        <v>8656.887946355344</v>
+        <v>67583.56086992071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.088639593828035e-06</v>
+        <v>1.769829056384928e-06</v>
       </c>
       <c r="B9" t="n">
-        <v>7053480457.565618</v>
+        <v>6349861862.948016</v>
       </c>
       <c r="C9" t="n">
-        <v>7777253868.281381</v>
+        <v>250199231673031</v>
       </c>
       <c r="D9" t="n">
-        <v>1.059801980198019</v>
+        <v>1.842633182400972</v>
       </c>
       <c r="E9" t="n">
-        <v>24746.80515490449</v>
+        <v>19546.35502787025</v>
       </c>
       <c r="F9" t="n">
-        <v>4.621360570113602e-05</v>
+        <v>4.949450821000035e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2584.32619983305</v>
+        <v>2008.289345953632</v>
       </c>
       <c r="H9" t="n">
-        <v>2.275096114572351e-07</v>
+        <v>1.509557139835757e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>24624.97661674604</v>
+        <v>19486.73964657402</v>
       </c>
       <c r="J9" t="n">
-        <v>24255.63622622042</v>
+        <v>19278.18890268085</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.808880819810449e-06</v>
+        <v>2.642590617657865e-06</v>
       </c>
       <c r="B10" t="n">
-        <v>5604076985.730527</v>
+        <v>3713790616.626796</v>
       </c>
       <c r="C10" t="n">
-        <v>163352729815621</v>
+        <v>6.624908874462798e+21</v>
       </c>
       <c r="D10" t="n">
-        <v>1.869961920154752</v>
+        <v>3.229704187863608</v>
       </c>
       <c r="E10" t="n">
-        <v>37087.07868185965</v>
+        <v>18114.00655332514</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0004074066652668046</v>
+        <v>2.785062527984164e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>3735.111615026612</v>
+        <v>1902.829100228089</v>
       </c>
       <c r="H10" t="n">
-        <v>3.222764379647329e-07</v>
+        <v>1.561921679661565e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>37057.74118537004</v>
+        <v>18012.41939233006</v>
       </c>
       <c r="J10" t="n">
-        <v>36915.82455693195</v>
+        <v>17717.19642939587</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.295579456279827e-05</v>
+        <v>7.619063008233456e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>1321981113.661859</v>
+        <v>2022205034.86113</v>
       </c>
       <c r="C11" t="n">
-        <v>1.739146931864768e+39</v>
+        <v>9.512151730693729e+32</v>
       </c>
       <c r="D11" t="n">
-        <v>7.179593887388886</v>
+        <v>5.647174964795783</v>
       </c>
       <c r="E11" t="n">
-        <v>34829.70766998579</v>
+        <v>30411.86111277529</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001188406628095494</v>
+        <v>0.000117549371701124</v>
       </c>
       <c r="G11" t="n">
-        <v>3583.095242309736</v>
+        <v>3106.349274169251</v>
       </c>
       <c r="H11" t="n">
-        <v>3.795884415740353e-07</v>
+        <v>2.798575064575771e-07</v>
       </c>
       <c r="I11" t="n">
-        <v>34718.4582529734</v>
+        <v>30339.45759845115</v>
       </c>
       <c r="J11" t="n">
-        <v>34334.31792357814</v>
+        <v>30068.51331829963</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.069895161334187e-06</v>
+        <v>3.384949298669451e-06</v>
       </c>
       <c r="B12" t="n">
-        <v>11744080445.9189</v>
+        <v>4251132035.21551</v>
       </c>
       <c r="C12" t="n">
-        <v>12956149772.74445</v>
+        <v>9.200427988599282e+17</v>
       </c>
       <c r="D12" t="n">
-        <v>1.05980198019802</v>
+        <v>2.562976849690681</v>
       </c>
       <c r="E12" t="n">
-        <v>40716.64982395301</v>
+        <v>25796.55889970985</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0001094201375918842</v>
+        <v>0.0001026063470059714</v>
       </c>
       <c r="G12" t="n">
-        <v>4147.174532263894</v>
+        <v>2633.111707133779</v>
       </c>
       <c r="H12" t="n">
-        <v>2.254678333705496e-07</v>
+        <v>2.362462436524175e-07</v>
       </c>
       <c r="I12" t="n">
-        <v>40632.75032409902</v>
+        <v>25737.16354730674</v>
       </c>
       <c r="J12" t="n">
-        <v>40306.80921881279</v>
+        <v>25512.93621006142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.668238882953456e-06</v>
+        <v>4.146577480462725e-06</v>
       </c>
       <c r="B13" t="n">
-        <v>10356602433.70112</v>
+        <v>1560390629.134585</v>
       </c>
       <c r="C13" t="n">
-        <v>11573830064.14553</v>
+        <v>4.290030422709704e+38</v>
       </c>
       <c r="D13" t="n">
-        <v>1.05980198019802</v>
+        <v>6.487348178661075</v>
       </c>
       <c r="E13" t="n">
-        <v>28936.087305337</v>
+        <v>12997.5927125267</v>
       </c>
       <c r="F13" t="n">
-        <v>9.234909988326257e-05</v>
+        <v>4.728730386009993e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>2944.852861253582</v>
+        <v>1332.856926972734</v>
       </c>
       <c r="H13" t="n">
-        <v>1.817165494708331e-07</v>
+        <v>1.337939124324883e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>28879.1493823149</v>
+        <v>12960.8175395044</v>
       </c>
       <c r="J13" t="n">
-        <v>28655.35233136495</v>
+        <v>12829.45492940041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.354748785205157e-06</v>
+        <v>4.741939430278862e-06</v>
       </c>
       <c r="B14" t="n">
-        <v>6228320624.17422</v>
+        <v>8194524182.783033</v>
       </c>
       <c r="C14" t="n">
-        <v>132907601775.2578</v>
+        <v>3891476676853.779</v>
       </c>
       <c r="D14" t="n">
-        <v>1.274905587201847</v>
+        <v>1.552996620325273</v>
       </c>
       <c r="E14" t="n">
-        <v>14284.33324484378</v>
+        <v>66668.14962098698</v>
       </c>
       <c r="F14" t="n">
-        <v>5.795052132585832e-05</v>
+        <v>0.0001663120446812447</v>
       </c>
       <c r="G14" t="n">
-        <v>1458.956244745437</v>
+        <v>6826.027737065367</v>
       </c>
       <c r="H14" t="n">
-        <v>1.375881231554074e-07</v>
+        <v>4.413068858320629e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>14250.41888899815</v>
+        <v>66491.24653769069</v>
       </c>
       <c r="J14" t="n">
-        <v>14123.41468413051</v>
+        <v>65848.16775205244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8.491547735288397e-06</v>
+        <v>1.88846206662477e-05</v>
       </c>
       <c r="B15" t="n">
-        <v>2645379837.529748</v>
+        <v>926084301.3472761</v>
       </c>
       <c r="C15" t="n">
-        <v>9.953473850398849e+29</v>
+        <v>2.879823113906124e+68</v>
       </c>
       <c r="D15" t="n">
-        <v>5.082264772729761</v>
+        <v>13.60071548057132</v>
       </c>
       <c r="E15" t="n">
-        <v>43691.63461798689</v>
+        <v>37581.44991818465</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0003191494650548424</v>
+        <v>0.0001305593542861947</v>
       </c>
       <c r="G15" t="n">
-        <v>4411.471124835749</v>
+        <v>3835.026608148878</v>
       </c>
       <c r="H15" t="n">
-        <v>3.433779116364861e-07</v>
+        <v>2.967662150824579e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>43644.62610350127</v>
+        <v>37496.02590003975</v>
       </c>
       <c r="J15" t="n">
-        <v>43431.65192450321</v>
+        <v>37172.45007605948</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9.108656526703255e-06</v>
+        <v>1.242816187436043e-06</v>
       </c>
       <c r="B16" t="n">
-        <v>1333581791.360858</v>
+        <v>11783023816.99518</v>
       </c>
       <c r="C16" t="n">
-        <v>1.066112930669511e+48</v>
+        <v>13401774777.27381</v>
       </c>
       <c r="D16" t="n">
-        <v>8.730675575850338</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E16" t="n">
-        <v>25176.02565876732</v>
+        <v>24553.11419516072</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001695536412224506</v>
+        <v>4.413817211802082e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>2547.127344851368</v>
+        <v>2523.087725173897</v>
       </c>
       <c r="H16" t="n">
-        <v>2.209347826596219e-07</v>
+        <v>1.353764568822095e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>25143.2203487955</v>
+        <v>24477.80718887425</v>
       </c>
       <c r="J16" t="n">
-        <v>25000.85081522259</v>
+        <v>24214.77746992087</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7.359302119415257e-06</v>
+        <v>3.395716924485127e-06</v>
       </c>
       <c r="B17" t="n">
-        <v>1711468638.998442</v>
+        <v>5998933072.009009</v>
       </c>
       <c r="C17" t="n">
-        <v>6.198011702475512e+28</v>
+        <v>381669504118006.2</v>
       </c>
       <c r="D17" t="n">
-        <v>4.836058402158844</v>
+        <v>1.923485691056994</v>
       </c>
       <c r="E17" t="n">
-        <v>24336.32946718072</v>
+        <v>35505.42038459728</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0003711077805688693</v>
+        <v>0.0001832046866345168</v>
       </c>
       <c r="G17" t="n">
-        <v>2451.995017985163</v>
+        <v>3599.879441345798</v>
       </c>
       <c r="H17" t="n">
-        <v>3.111172867784188e-07</v>
+        <v>2.82862708385051e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>24315.92716577284</v>
+        <v>35450.60104805719</v>
       </c>
       <c r="J17" t="n">
-        <v>24218.41610515145</v>
+        <v>35221.94391343922</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.442842310601704e-06</v>
+        <v>5.474729667407334e-06</v>
       </c>
       <c r="B18" t="n">
-        <v>6715999504.665989</v>
+        <v>2080745246.98526</v>
       </c>
       <c r="C18" t="n">
-        <v>37550709181.23125</v>
+        <v>2.096512879964513e+40</v>
       </c>
       <c r="D18" t="n">
-        <v>1.196852845503568</v>
+        <v>6.909077575706648</v>
       </c>
       <c r="E18" t="n">
-        <v>61724.15425000286</v>
+        <v>23059.96643146284</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001599963516877906</v>
+        <v>5.444114893817384e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>6369.232911993285</v>
+        <v>2369.430209553617</v>
       </c>
       <c r="H18" t="n">
-        <v>5.668603815703784e-07</v>
+        <v>1.663969000477801e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>61505.46815334397</v>
+        <v>22989.48469101025</v>
       </c>
       <c r="J18" t="n">
-        <v>60772.5485200508</v>
+        <v>22743.06716840671</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3.597647918825609e-06</v>
+        <v>3.103777591103834e-06</v>
       </c>
       <c r="B19" t="n">
-        <v>6371289069.004514</v>
+        <v>4435426816.842041</v>
       </c>
       <c r="C19" t="n">
-        <v>1837182639370095</v>
+        <v>4.551169233092393e+18</v>
       </c>
       <c r="D19" t="n">
-        <v>2.047096419971839</v>
+        <v>2.674063348355865</v>
       </c>
       <c r="E19" t="n">
-        <v>40184.74070856647</v>
+        <v>24792.41373772575</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0001533949387729646</v>
+        <v>8.853194156662791e-05</v>
       </c>
       <c r="G19" t="n">
-        <v>4086.660081716096</v>
+        <v>2532.280413467198</v>
       </c>
       <c r="H19" t="n">
-        <v>2.892028935619253e-07</v>
+        <v>2.104429207287536e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>40108.9784742782</v>
+        <v>24733.48147139839</v>
       </c>
       <c r="J19" t="n">
-        <v>39807.98229312344</v>
+        <v>24512.85730736333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1.449014018001992e-06</v>
+        <v>1.887331266779535e-06</v>
       </c>
       <c r="B20" t="n">
-        <v>13646683092.80096</v>
+        <v>12237103293.27728</v>
       </c>
       <c r="C20" t="n">
-        <v>15379631365.04066</v>
+        <v>13574806274.37864</v>
       </c>
       <c r="D20" t="n">
         <v>1.05980198019802</v>
       </c>
       <c r="E20" t="n">
-        <v>33095.24328832372</v>
+        <v>38664.00705152857</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001231378425510187</v>
+        <v>0.0001331132745730682</v>
       </c>
       <c r="G20" t="n">
-        <v>3347.703401565191</v>
+        <v>3920.142526461512</v>
       </c>
       <c r="H20" t="n">
-        <v>1.578370041465674e-07</v>
+        <v>2.055816640003121e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>33052.82209639836</v>
+        <v>38604.29391674117</v>
       </c>
       <c r="J20" t="n">
-        <v>32868.02864087711</v>
+        <v>38355.24122320022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3.544965135381276e-06</v>
+        <v>4.82904997516447e-06</v>
       </c>
       <c r="B21" t="n">
-        <v>7242797653.11934</v>
+        <v>1982074458.337143</v>
       </c>
       <c r="C21" t="n">
-        <v>69522684337345.26</v>
+        <v>1.854122098432059e+28</v>
       </c>
       <c r="D21" t="n">
-        <v>1.777404878801881</v>
+        <v>4.594718240023117</v>
       </c>
       <c r="E21" t="n">
-        <v>44486.37192523578</v>
+        <v>18404.50346627703</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0001416434423323378</v>
+        <v>8.308328448597067e-05</v>
       </c>
       <c r="G21" t="n">
-        <v>4535.770800415328</v>
+        <v>1883.032281227837</v>
       </c>
       <c r="H21" t="n">
-        <v>3.082568044125578e-07</v>
+        <v>2.135858271396814e-07</v>
       </c>
       <c r="I21" t="n">
-        <v>44389.55680535606</v>
+        <v>18357.19020561022</v>
       </c>
       <c r="J21" t="n">
-        <v>44018.67206579962</v>
+        <v>18183.71990900583</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2.904784506799906e-06</v>
+        <v>6.246728141489291e-06</v>
       </c>
       <c r="B22" t="n">
-        <v>2890222019.590757</v>
+        <v>2207782432.330433</v>
       </c>
       <c r="C22" t="n">
-        <v>6.866374192469345e+25</v>
+        <v>9.005187436939933e+31</v>
       </c>
       <c r="D22" t="n">
-        <v>3.986115427503139</v>
+        <v>5.367353490975197</v>
       </c>
       <c r="E22" t="n">
-        <v>15919.18017581696</v>
+        <v>27037.98270091766</v>
       </c>
       <c r="F22" t="n">
-        <v>2.153596056697967e-05</v>
+        <v>0.0001187537775309813</v>
       </c>
       <c r="G22" t="n">
-        <v>1688.44494258808</v>
+        <v>2753.060362119013</v>
       </c>
       <c r="H22" t="n">
-        <v>1.450940191943374e-07</v>
+        <v>2.404049962695164e-07</v>
       </c>
       <c r="I22" t="n">
-        <v>15811.92803692098</v>
+        <v>26983.2470431096</v>
       </c>
       <c r="J22" t="n">
-        <v>15519.04589382273</v>
+        <v>26769.64509732183</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3.82837407627676e-06</v>
+        <v>3.52826139738821e-06</v>
       </c>
       <c r="B23" t="n">
-        <v>3585553549.385788</v>
+        <v>2120657130.623133</v>
       </c>
       <c r="C23" t="n">
-        <v>1375299024049420</v>
+        <v>1.266723947281456e+40</v>
       </c>
       <c r="D23" t="n">
-        <v>2.074922265125828</v>
+        <v>6.661414115856502</v>
       </c>
       <c r="E23" t="n">
-        <v>24112.62500235539</v>
+        <v>15056.85252636523</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0001156428572292737</v>
+        <v>7.778961761793215e-05</v>
       </c>
       <c r="G23" t="n">
-        <v>2468.558884949896</v>
+        <v>1525.026022227765</v>
       </c>
       <c r="H23" t="n">
-        <v>3.053226559681981e-07</v>
+        <v>1.110244630996462e-07</v>
       </c>
       <c r="I23" t="n">
-        <v>24048.96235267277</v>
+        <v>15035.36278237496</v>
       </c>
       <c r="J23" t="n">
-        <v>23817.2213704309</v>
+        <v>14944.04742699166</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7.900790481039985e-06</v>
+        <v>2.095351761330719e-06</v>
       </c>
       <c r="B24" t="n">
-        <v>1753420924.638499</v>
+        <v>4872870322.550197</v>
       </c>
       <c r="C24" t="n">
-        <v>3.940270476293855e+31</v>
+        <v>1.472895273870889e+17</v>
       </c>
       <c r="D24" t="n">
-        <v>5.403765823172555</v>
+        <v>2.356840497652407</v>
       </c>
       <c r="E24" t="n">
-        <v>27254.96248255453</v>
+        <v>18119.85622707646</v>
       </c>
       <c r="F24" t="n">
-        <v>6.480238597864383e-05</v>
+        <v>0.0002062548292368815</v>
       </c>
       <c r="G24" t="n">
-        <v>2839.883239247801</v>
+        <v>1824.203207339059</v>
       </c>
       <c r="H24" t="n">
-        <v>3.021896143364473e-07</v>
+        <v>1.545226776059958e-07</v>
       </c>
       <c r="I24" t="n">
-        <v>27127.86582589637</v>
+        <v>18106.28113304156</v>
       </c>
       <c r="J24" t="n">
-        <v>26735.88991325557</v>
+        <v>18039.87622020418</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6.392536486074355e-06</v>
+        <v>1.766004535009199e-06</v>
       </c>
       <c r="B25" t="n">
-        <v>3494916879.669228</v>
+        <v>9333669750.988598</v>
       </c>
       <c r="C25" t="n">
-        <v>1.159796867018405e+23</v>
+        <v>104202628881.384</v>
       </c>
       <c r="D25" t="n">
-        <v>3.635801050432625</v>
+        <v>1.231955254327451</v>
       </c>
       <c r="E25" t="n">
-        <v>41738.50670034512</v>
+        <v>27829.84920812691</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0001011111701627681</v>
+        <v>0.0001041108662215778</v>
       </c>
       <c r="G25" t="n">
-        <v>4301.774254147392</v>
+        <v>2826.73406515325</v>
       </c>
       <c r="H25" t="n">
-        <v>3.443264133879434e-07</v>
+        <v>1.818495625440536e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>41596.36938466414</v>
+        <v>27781.23904774851</v>
       </c>
       <c r="J25" t="n">
-        <v>41114.49461304459</v>
+        <v>27584.43416512191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6.491629434294466e-06</v>
+        <v>6.042364171173453e-06</v>
       </c>
       <c r="B26" t="n">
-        <v>1740344407.717331</v>
+        <v>2397110274.585873</v>
       </c>
       <c r="C26" t="n">
-        <v>5.057531890303563e+48</v>
+        <v>3.954991794079162e+48</v>
       </c>
       <c r="D26" t="n">
-        <v>8.619744214151494</v>
+        <v>8.527355302117675</v>
       </c>
       <c r="E26" t="n">
-        <v>23430.42863212578</v>
+        <v>29980.26895801043</v>
       </c>
       <c r="F26" t="n">
-        <v>4.963178407786479e-05</v>
+        <v>6.410049543846707e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>2410.77975231713</v>
+        <v>3061.148622259838</v>
       </c>
       <c r="H26" t="n">
-        <v>1.594271898368499e-07</v>
+        <v>1.499554384550966e-07</v>
       </c>
       <c r="I26" t="n">
-        <v>23355.16542200961</v>
+        <v>29910.13370638954</v>
       </c>
       <c r="J26" t="n">
-        <v>23095.70094723373</v>
+        <v>29646.46338664825</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4.278413301298767e-06</v>
+        <v>3.992551585738274e-06</v>
       </c>
       <c r="B27" t="n">
-        <v>3091844000.940776</v>
+        <v>3469126162.866148</v>
       </c>
       <c r="C27" t="n">
-        <v>2.36589054115127e+27</v>
+        <v>6.8723379172298e+26</v>
       </c>
       <c r="D27" t="n">
-        <v>4.358309683945807</v>
+        <v>4.231649447444287</v>
       </c>
       <c r="E27" t="n">
-        <v>25210.7970649346</v>
+        <v>26335.98764451021</v>
       </c>
       <c r="F27" t="n">
-        <v>0.000413569276442103</v>
+        <v>9.816903281878861e-05</v>
       </c>
       <c r="G27" t="n">
-        <v>2531.949134081012</v>
+        <v>2679.380479230403</v>
       </c>
       <c r="H27" t="n">
-        <v>1.98118876128327e-07</v>
+        <v>1.896157675675744e-07</v>
       </c>
       <c r="I27" t="n">
-        <v>25198.71992317065</v>
+        <v>26285.11907253311</v>
       </c>
       <c r="J27" t="n">
-        <v>25134.24497004071</v>
+        <v>26084.2421740973</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6.586015939093114e-06</v>
+        <v>4.345561234064447e-06</v>
       </c>
       <c r="B28" t="n">
-        <v>2460255500.605871</v>
+        <v>3158670502.780784</v>
       </c>
       <c r="C28" t="n">
-        <v>1.001851926330843e+26</v>
+        <v>3.082860713861913e+21</v>
       </c>
       <c r="D28" t="n">
-        <v>4.234605487342838</v>
+        <v>3.270381222521026</v>
       </c>
       <c r="E28" t="n">
-        <v>30817.37106653321</v>
+        <v>25282.15304536305</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0001486017490277738</v>
+        <v>0.0001235752966918327</v>
       </c>
       <c r="G28" t="n">
-        <v>3140.081903663808</v>
+        <v>2575.057926786588</v>
       </c>
       <c r="H28" t="n">
-        <v>3.125992683264494e-07</v>
+        <v>2.543995245278251e-07</v>
       </c>
       <c r="I28" t="n">
-        <v>30752.54351429934</v>
+        <v>25230.10568730719</v>
       </c>
       <c r="J28" t="n">
-        <v>30502.02083439896</v>
+        <v>25027.85915855499</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>9.678269288182025e-06</v>
+        <v>1.788813433121876e-06</v>
       </c>
       <c r="B29" t="n">
-        <v>1621654372.567685</v>
+        <v>9291322190.372814</v>
       </c>
       <c r="C29" t="n">
-        <v>6.288723661586549e+49</v>
+        <v>10340104060.86025</v>
       </c>
       <c r="D29" t="n">
-        <v>9.106735058991182</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E29" t="n">
-        <v>32682.18365170252</v>
+        <v>27827.48830522369</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0001183143693915098</v>
+        <v>0.0001172076217308245</v>
       </c>
       <c r="G29" t="n">
-        <v>3324.231829319054</v>
+        <v>2824.384155072845</v>
       </c>
       <c r="H29" t="n">
-        <v>2.253078639225083e-07</v>
+        <v>1.948503946500156e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>32619.94646931496</v>
+        <v>27781.22683350094</v>
       </c>
       <c r="J29" t="n">
-        <v>32373.3015689883</v>
+        <v>27591.66154397211</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3.118218395527034e-06</v>
+        <v>2.204411480805016e-06</v>
       </c>
       <c r="B30" t="n">
-        <v>7763944651.644887</v>
+        <v>2349987036.08398</v>
       </c>
       <c r="C30" t="n">
-        <v>308245888059695.9</v>
+        <v>1.840310002333156e+24</v>
       </c>
       <c r="D30" t="n">
-        <v>1.880501227326761</v>
+        <v>3.662875186676704</v>
       </c>
       <c r="E30" t="n">
-        <v>42106.73470642843</v>
+        <v>9670.555861213235</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0001971815076849864</v>
+        <v>6.842688314500599e-05</v>
       </c>
       <c r="G30" t="n">
-        <v>4261.223886476741</v>
+        <v>982.0683190225478</v>
       </c>
       <c r="H30" t="n">
-        <v>2.630248865763059e-07</v>
+        <v>1.180300439421107e-07</v>
       </c>
       <c r="I30" t="n">
-        <v>42050.56757772409</v>
+        <v>9653.875046878538</v>
       </c>
       <c r="J30" t="n">
-        <v>41808.12273396521</v>
+        <v>9586.132676138659</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3.571537734488231e-06</v>
+        <v>6.06278911757915e-06</v>
       </c>
       <c r="B31" t="n">
-        <v>1183234772.141279</v>
+        <v>2702626440.944756</v>
       </c>
       <c r="C31" t="n">
-        <v>1.700168890157967e+46</v>
+        <v>5.868039061427119e+24</v>
       </c>
       <c r="D31" t="n">
-        <v>7.83514605786774</v>
+        <v>3.969956430040321</v>
       </c>
       <c r="E31" t="n">
-        <v>8664.677436588854</v>
+        <v>30982.89509046112</v>
       </c>
       <c r="F31" t="n">
-        <v>5.628489872448606e-05</v>
+        <v>6.794148978482817e-05</v>
       </c>
       <c r="G31" t="n">
-        <v>879.79742346811</v>
+        <v>3223.00179388869</v>
       </c>
       <c r="H31" t="n">
-        <v>9.620922078720721e-08</v>
+        <v>3.038643814392668e-07</v>
       </c>
       <c r="I31" t="n">
-        <v>8649.866681245268</v>
+        <v>30844.32588508048</v>
       </c>
       <c r="J31" t="n">
-        <v>8589.585491764408</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>9.67848012975526e-06</v>
-      </c>
-      <c r="B32" t="n">
-        <v>1480451856.036364</v>
-      </c>
-      <c r="C32" t="n">
-        <v>8.92884700136598e+41</v>
-      </c>
-      <c r="D32" t="n">
-        <v>7.553162476474925</v>
-      </c>
-      <c r="E32" t="n">
-        <v>29251.60350707715</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.000194733192684829</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2961.674691786071</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.700917163301176e-07</v>
-      </c>
-      <c r="I32" t="n">
-        <v>29211.03201699009</v>
-      </c>
-      <c r="J32" t="n">
-        <v>29037.47963110052</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>5.288795350880021e-06</v>
-      </c>
-      <c r="B33" t="n">
-        <v>4077939506.965067</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1.095238132513869e+21</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.201413144009628</v>
-      </c>
-      <c r="E33" t="n">
-        <v>39599.80436852141</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.0002200613810519239</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4010.947127489516</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.146985336069695e-07</v>
-      </c>
-      <c r="I33" t="n">
-        <v>39543.17471225766</v>
-      </c>
-      <c r="J33" t="n">
-        <v>39302.65269345899</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1.373132328463737e-05</v>
-      </c>
-      <c r="B34" t="n">
-        <v>2418883255.740611</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.497095037519417e+36</v>
-      </c>
-      <c r="D34" t="n">
-        <v>6.605053030555893</v>
-      </c>
-      <c r="E34" t="n">
-        <v>66759.30671474033</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.0003500640172484659</v>
-      </c>
-      <c r="G34" t="n">
-        <v>6750.691783035287</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4.355809671588178e-07</v>
-      </c>
-      <c r="I34" t="n">
-        <v>66676.23881300561</v>
-      </c>
-      <c r="J34" t="n">
-        <v>66311.92571596307</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1.409314543548663e-05</v>
-      </c>
-      <c r="B35" t="n">
-        <v>1640001336.287345</v>
-      </c>
-      <c r="C35" t="n">
-        <v>9.179315358093739e+45</v>
-      </c>
-      <c r="D35" t="n">
-        <v>8.588867955033411</v>
-      </c>
-      <c r="E35" t="n">
-        <v>47973.04562175144</v>
-      </c>
-      <c r="F35" t="n">
-        <v>7.925650723392621e-05</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4986.510969299277</v>
-      </c>
-      <c r="H35" t="n">
-        <v>3.473209401141937e-07</v>
-      </c>
-      <c r="I35" t="n">
-        <v>47762.8162805024</v>
-      </c>
-      <c r="J35" t="n">
-        <v>47101.78296456249</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>4.244974369026091e-06</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3429165390.543301</v>
-      </c>
-      <c r="C36" t="n">
-        <v>4208983136627.59</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.62405708714971</v>
-      </c>
-      <c r="E36" t="n">
-        <v>25057.63954284161</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0001445948580606555</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2566.053861186624</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3.865581156130041e-07</v>
-      </c>
-      <c r="I36" t="n">
-        <v>24990.65075739444</v>
-      </c>
-      <c r="J36" t="n">
-        <v>24747.62585868469</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>3.276886179220263e-06</v>
-      </c>
-      <c r="B37" t="n">
-        <v>7846333711.518775</v>
-      </c>
-      <c r="C37" t="n">
-        <v>8421558010.081843</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1.05980198019802</v>
-      </c>
-      <c r="E37" t="n">
-        <v>43231.98966815283</v>
-      </c>
-      <c r="F37" t="n">
-        <v>6.053826432005937e-05</v>
-      </c>
-      <c r="G37" t="n">
-        <v>4552.610562998051</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3.56941955724204e-07</v>
-      </c>
-      <c r="I37" t="n">
-        <v>42977.08789461642</v>
-      </c>
-      <c r="J37" t="n">
-        <v>42248.55919276208</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>3.807246759829834e-06</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1554740570.082414</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1.583603949816676e+38</v>
-      </c>
-      <c r="D38" t="n">
-        <v>6.370625860153142</v>
-      </c>
-      <c r="E38" t="n">
-        <v>11858.97092662735</v>
-      </c>
-      <c r="F38" t="n">
-        <v>5.327626309329099e-05</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1210.932564513417</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.249683461138522e-07</v>
-      </c>
-      <c r="I38" t="n">
-        <v>11831.15373568215</v>
-      </c>
-      <c r="J38" t="n">
-        <v>11726.64973628874</v>
+        <v>30411.35776086769</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,38 +478,6 @@
         <is>
           <t>Ipc</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1.19578968203755e-05</v>
-      </c>
-      <c r="B2" t="n">
-        <v>4621705669.169837</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3.277719938228635e+16</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.436643080082072</v>
-      </c>
-      <c r="E2" t="n">
-        <v>98516.37786492333</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.000462201741953264</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10017.19758414594</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8.630491309762619e-07</v>
-      </c>
-      <c r="I2" t="n">
-        <v>98332.42253419709</v>
-      </c>
-      <c r="J2" t="n">
-        <v>97599.82801539893</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,1478 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.288672125651398e-06</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4630488195.524612</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23616739556.88804</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.169450189217972</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10068.96357396152</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.256783477895632e-05</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1044.575150928641</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.354124498429408e-07</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10027.09824781431</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9893.321762809097</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.858832476965101e-06</v>
+      </c>
+      <c r="B3" t="n">
+        <v>16247860932.25778</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17581927482.83089</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E3" t="n">
+        <v>77794.88124318872</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0001579140233160053</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7917.557633931675</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.114045467574364e-07</v>
+      </c>
+      <c r="I3" t="n">
+        <v>77641.47067695227</v>
+      </c>
+      <c r="J3" t="n">
+        <v>77038.81338319767</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6.885755057361809e-06</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1807309793.035128</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8.077287524288523e+41</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.340834356780072</v>
+      </c>
+      <c r="E4" t="n">
+        <v>25387.53665635547</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.138860982441236e-05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2626.565214641719</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.974946950911215e-07</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25289.96826857083</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24970.71953497656</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.84784701673858e-05</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1393087812.612616</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.4301716660468e+35</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.595378393600416</v>
+      </c>
+      <c r="E5" t="n">
+        <v>51862.44516711491</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0001556795601113292</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5362.23514900388</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.869831699499485e-07</v>
+      </c>
+      <c r="I5" t="n">
+        <v>51666.90002012337</v>
+      </c>
+      <c r="J5" t="n">
+        <v>51023.4225193995</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3.81650225491325e-06</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1271919195.754068</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.016747779604768e+32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.376700731137829</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9533.57383161446</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.118356220867834e-05</v>
+      </c>
+      <c r="G6" t="n">
+        <v>983.9094744611485</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.466447799080145e-07</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9499.62706350368</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9386.021530898472</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.238812963571341e-05</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1237842655.545566</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.443775639691273e+31</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.566837474143485</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30341.67978882525</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.993997095667527e-05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3214.192157714053</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.610777403158345e-07</v>
+      </c>
+      <c r="I7" t="n">
+        <v>30141.65292345689</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29591.28891158801</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2.377539143173605e-05</v>
+      </c>
+      <c r="B8" t="n">
+        <v>808274324.8441182</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.769702874992384e+62</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12.66960086487048</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41156.48426372746</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0001190506654570019</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4240.279512552807</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.005690857386687e-07</v>
+      </c>
+      <c r="I8" t="n">
+        <v>41018.00527908294</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40546.89682148917</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.611014382410404e-05</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1274610307.976179</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.545875854382698e+45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.696963069931408</v>
+      </c>
+      <c r="E9" t="n">
+        <v>42582.04985790811</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.000175908906504946</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4343.657392881064</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.922320304661909e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>42487.10273891893</v>
+      </c>
+      <c r="J9" t="n">
+        <v>42125.64825777676</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2.137795881068545e-06</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8384642598.792796</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9232157399.691532</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30042.2494121841</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.634712226003161e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3077.1420712472</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.328640669812117e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>29961.23037881877</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29668.00247662658</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2.69985317511255e-06</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8839127104.241817</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1470107504473.294</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.447977003149377</v>
+      </c>
+      <c r="E11" t="n">
+        <v>40703.65648752257</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0001545798177957547</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4131.882202563802</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.595785817185524e-07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>40635.3047610653</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40355.9031373734</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.159174337141593e-05</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1577137460.478622</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.738376557936015e+31</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.489215798538853</v>
+      </c>
+      <c r="E12" t="n">
+        <v>35953.84498350095</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0001894417464730458</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3670.034705672594</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.370376537610216e-07</v>
+      </c>
+      <c r="I12" t="n">
+        <v>35870.90030869818</v>
+      </c>
+      <c r="J12" t="n">
+        <v>35557.92999371343</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1.565650693303009e-06</v>
+      </c>
+      <c r="B13" t="n">
+        <v>16222708668.5885</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18198328879.40655</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42504.98924066623</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0001445146561853206</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4295.643090965645</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.705419077392275e-07</v>
+      </c>
+      <c r="I13" t="n">
+        <v>42454.82905522288</v>
+      </c>
+      <c r="J13" t="n">
+        <v>42232.19518369313</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3.829917446806675e-06</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3697015498.230899</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7.654806959728745e+18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.757865151427365</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25578.30852107571</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.000120203839823806</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2606.504529063996</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.541547118456457e-07</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25524.2266577908</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25315.50285760668</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.128609683799876e-05</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2438809028.242238</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.887840623839423e+37</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.768898709202589</v>
+      </c>
+      <c r="E15" t="n">
+        <v>55554.79621118663</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0001388640265266232</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5681.422733239508</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.497841341669182e-07</v>
+      </c>
+      <c r="I15" t="n">
+        <v>55414.85941994123</v>
+      </c>
+      <c r="J15" t="n">
+        <v>54898.98207438932</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3.165071734646166e-06</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2341596347.722085</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.152278331819284e+31</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.96768616293292</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14397.23613685938</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.739005387167206e-05</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1475.442549559918</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.306363619004357e-07</v>
+      </c>
+      <c r="I16" t="n">
+        <v>14357.54843033274</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14214.76517765088</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6.577151992360238e-06</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1743084606.943092</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.37539159306307e+54</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.749842081695704</v>
+      </c>
+      <c r="E17" t="n">
+        <v>23996.30352411353</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0001924989961292367</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2415.701661079655</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.43249414413734e-07</v>
+      </c>
+      <c r="I17" t="n">
+        <v>23978.44651448208</v>
+      </c>
+      <c r="J17" t="n">
+        <v>23890.97540153353</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4.418132858777449e-06</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2749140678.070759</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.864858372002077e+24</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.859184687239715</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22868.2463692408</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.059793399356383e-05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2363.818098281853</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.266920502371511e-07</v>
+      </c>
+      <c r="I18" t="n">
+        <v>22782.69807884327</v>
+      </c>
+      <c r="J18" t="n">
+        <v>22500.52922712932</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4.463009687692297e-06</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6249875758.396109</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.241594095432386e+17</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.405601731626761</v>
+      </c>
+      <c r="E19" t="n">
+        <v>49704.28036878176</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0001159984089490863</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5095.68948271271</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.248128131613071e-07</v>
+      </c>
+      <c r="I19" t="n">
+        <v>49565.10098452117</v>
+      </c>
+      <c r="J19" t="n">
+        <v>49066.52521823317</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2.432339678290102e-06</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4322526234.46481</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.592363618362058e+23</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.485550420987809</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19546.22369031183</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.678123543462136e-05</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2019.428928818012</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.355001906701736e-07</v>
+      </c>
+      <c r="I20" t="n">
+        <v>19474.2164016598</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19235.63179794155</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9.712927022126383e-06</v>
+      </c>
+      <c r="B21" t="n">
+        <v>926550869.4272195</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.165130059212148e+54</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10.00755538847455</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18899.79447312144</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0001158075953173685</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1920.268807026748</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.06218463100783e-07</v>
+      </c>
+      <c r="I21" t="n">
+        <v>18866.1396289941</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18730.52523776166</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4.282610744090124e-06</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2688920822.209541</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.62681243488502e+28</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.589429032965815</v>
+      </c>
+      <c r="E22" t="n">
+        <v>22227.7991941109</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.899176860815453e-05</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2353.614253414705</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.896083520515246e-07</v>
+      </c>
+      <c r="I22" t="n">
+        <v>22082.42771188466</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21681.34012037466</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4.152693344488464e-06</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4119217837.576404</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.953267228023183e+17</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.500153769064151</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30584.47396695913</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0001316638123294963</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3120.054011049199</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.946797166587636e-07</v>
+      </c>
+      <c r="I23" t="n">
+        <v>30516.02217323325</v>
+      </c>
+      <c r="J23" t="n">
+        <v>30255.68861368448</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8.151904512753673e-06</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2514358796.860618</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.446327320453256e+36</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6.278142560870144</v>
+      </c>
+      <c r="E24" t="n">
+        <v>40954.095289722</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0001888945224076464</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4148.345153044907</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.712861085842787e-07</v>
+      </c>
+      <c r="I24" t="n">
+        <v>40895.27792964122</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40645.71353076341</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3.563506503128738e-06</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3998892475.156088</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.403932939538714e+24</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.700622410194953</v>
+      </c>
+      <c r="E25" t="n">
+        <v>26630.70835276764</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0001227184533138193</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2700.027290150994</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.892234467755831e-07</v>
+      </c>
+      <c r="I25" t="n">
+        <v>26589.6456251296</v>
+      </c>
+      <c r="J25" t="n">
+        <v>26418.31442092501</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1.058003523867114e-05</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1461868644.627096</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.942019034511177e+40</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.333493677182886</v>
+      </c>
+      <c r="E26" t="n">
+        <v>31482.18133561135</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0001750680879752598</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3197.377722082128</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.037441358503019e-07</v>
+      </c>
+      <c r="I26" t="n">
+        <v>31427.55957058802</v>
+      </c>
+      <c r="J26" t="n">
+        <v>31206.05214278484</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1.388629141321077e-05</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2011089513.337127</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.41650146697491e+57</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10.90761499760477</v>
+      </c>
+      <c r="E27" t="n">
+        <v>59213.6482549689</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.43615016692077e-05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6145.742174426676</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.709822546220707e-07</v>
+      </c>
+      <c r="I27" t="n">
+        <v>58964.34008949135</v>
+      </c>
+      <c r="J27" t="n">
+        <v>58170.72772934684</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5.591650817064009e-06</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3843914374.620783</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9.577436522907017e+22</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.583299002387292</v>
+      </c>
+      <c r="E28" t="n">
+        <v>40060.039834049</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0001077200840164868</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4107.995215598597</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.047232810873744e-07</v>
+      </c>
+      <c r="I28" t="n">
+        <v>39946.71624272267</v>
+      </c>
+      <c r="J28" t="n">
+        <v>39541.89858155933</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3.231621225830685e-06</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3455172931.328835</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.16012704325472e+26</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.08722236604679</v>
+      </c>
+      <c r="E29" t="n">
+        <v>21144.94237071899</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.885954338568585e-05</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2158.177623717121</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.58063437960349e-07</v>
+      </c>
+      <c r="I29" t="n">
+        <v>21096.40527444652</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20913.02365500966</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1.933466266241058e-06</v>
+      </c>
+      <c r="B30" t="n">
+        <v>9420428099.49509</v>
+      </c>
+      <c r="C30" t="n">
+        <v>164606149421.943</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.267227195302306</v>
+      </c>
+      <c r="E30" t="n">
+        <v>30805.12334306776</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0001101527316182431</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3130.057189793903</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.968468076184598e-07</v>
+      </c>
+      <c r="I30" t="n">
+        <v>30750.07350363761</v>
+      </c>
+      <c r="J30" t="n">
+        <v>30528.44342877556</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2.07686693132115e-06</v>
+      </c>
+      <c r="B31" t="n">
+        <v>10403205818.07123</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11474580124.53196</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E31" t="n">
+        <v>36152.61451646413</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0002160476386326151</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3649.331881235994</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.262272485830116e-07</v>
+      </c>
+      <c r="I31" t="n">
+        <v>36114.75848358682</v>
+      </c>
+      <c r="J31" t="n">
+        <v>35942.22625538124</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4.846705579413254e-06</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3227498688.879481</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8.229090555287491e+20</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.181612189756342</v>
+      </c>
+      <c r="E32" t="n">
+        <v>28688.73670177503</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0002851354505395954</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2895.111681002631</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.89753165178691e-07</v>
+      </c>
+      <c r="I32" t="n">
+        <v>28659.58335641378</v>
+      </c>
+      <c r="J32" t="n">
+        <v>28525.84301654431</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2.348234411130611e-06</v>
+      </c>
+      <c r="B33" t="n">
+        <v>6696550352.280573</v>
+      </c>
+      <c r="C33" t="n">
+        <v>327725431711615.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.877403953990098</v>
+      </c>
+      <c r="E33" t="n">
+        <v>27438.44845639951</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.221474983242428e-05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2859.819589689304</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.982556547208445e-07</v>
+      </c>
+      <c r="I33" t="n">
+        <v>27309.58762967801</v>
+      </c>
+      <c r="J33" t="n">
+        <v>26913.05426727684</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>4.847502386140125e-06</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4137541360.647746</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.335129765161754e+19</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.872698077707069</v>
+      </c>
+      <c r="E34" t="n">
+        <v>36430.66118970056</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0001017535665625352</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3743.758623705435</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.124907899111594e-07</v>
+      </c>
+      <c r="I34" t="n">
+        <v>36318.78062888346</v>
+      </c>
+      <c r="J34" t="n">
+        <v>35928.1493012374</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4.8415156988026e-06</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2300998872.192791</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6.829420693362549e+29</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4.876487552102086</v>
+      </c>
+      <c r="E35" t="n">
+        <v>21553.7688960344</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0001857923482680177</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2176.589227007164</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.031658076187416e-07</v>
+      </c>
+      <c r="I35" t="n">
+        <v>21530.19963225248</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21423.79895072364</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2.791731316174039e-06</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11339625867.38326</v>
+      </c>
+      <c r="C36" t="n">
+        <v>12288132339.27859</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E36" t="n">
+        <v>52957.45086552973</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0003819865080217989</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5333.688064918359</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.040954068440613e-07</v>
+      </c>
+      <c r="I36" t="n">
+        <v>52915.29200067931</v>
+      </c>
+      <c r="J36" t="n">
+        <v>52710.14531681745</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>9.087872486388466e-06</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1532172600.637753</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7.738257544743584e+31</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.526062369420263</v>
+      </c>
+      <c r="E37" t="n">
+        <v>27542.58079686482</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.723015384910505e-05</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2932.986367215449</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.405379465763659e-07</v>
+      </c>
+      <c r="I37" t="n">
+        <v>27343.99381072152</v>
+      </c>
+      <c r="J37" t="n">
+        <v>26814.4815709529</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3.403162864888201e-06</v>
+      </c>
+      <c r="B38" t="n">
+        <v>10695848873.21428</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3739354126332.745</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.514508439204624</v>
+      </c>
+      <c r="E38" t="n">
+        <v>62413.6597440364</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8.324330181206859e-05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6457.636913417875</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.204979864873172e-07</v>
+      </c>
+      <c r="I38" t="n">
+        <v>62173.35870068725</v>
+      </c>
+      <c r="J38" t="n">
+        <v>61387.50558536177</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2.617747380187931e-06</v>
+      </c>
+      <c r="B39" t="n">
+        <v>13106818618.47933</v>
+      </c>
+      <c r="C39" t="n">
+        <v>14257903224.4099</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E39" t="n">
+        <v>57651.92839038401</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.445779166813704e-05</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6036.874483682302</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.851438281260439e-07</v>
+      </c>
+      <c r="I39" t="n">
+        <v>57350.05989633523</v>
+      </c>
+      <c r="J39" t="n">
+        <v>56452.85955966441</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1.903341011812373e-06</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4166445915.550479</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.608090877128969e+21</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.059163834568999</v>
+      </c>
+      <c r="E40" t="n">
+        <v>14498.11572820605</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.8254702613812e-05</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1481.499609547564</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.171873961907776e-07</v>
+      </c>
+      <c r="I40" t="n">
+        <v>14462.90679850943</v>
+      </c>
+      <c r="J40" t="n">
+        <v>14331.83994943514</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3.108136022512225e-06</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6933194873.046266</v>
+      </c>
+      <c r="C41" t="n">
+        <v>32021418156612.06</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.712312121843071</v>
+      </c>
+      <c r="E41" t="n">
+        <v>37386.8723643306</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.271404939478953e-05</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3955.77763901253</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.755812874800841e-07</v>
+      </c>
+      <c r="I41" t="n">
+        <v>37145.66080590896</v>
+      </c>
+      <c r="J41" t="n">
+        <v>36477.02070193098</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.980275286226103e-06</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3719555127.396963</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.112010639423776e+23</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.612675549639091</v>
+      </c>
+      <c r="E42" t="n">
+        <v>41692.19897420561</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.357492098049611e-05</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4448.028578139395</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.237766971044161e-07</v>
+      </c>
+      <c r="I42" t="n">
+        <v>41382.41155118468</v>
+      </c>
+      <c r="J42" t="n">
+        <v>40565.21078755809</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1.587152231505506e-06</v>
+      </c>
+      <c r="B43" t="n">
+        <v>12156282778.34054</v>
+      </c>
+      <c r="C43" t="n">
+        <v>13625570172.64042</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.059801980198021</v>
+      </c>
+      <c r="E43" t="n">
+        <v>32328.47067372327</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.112486630975916e-05</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3303.57012571733</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.728840095631315e-07</v>
+      </c>
+      <c r="I43" t="n">
+        <v>32249.88949778437</v>
+      </c>
+      <c r="J43" t="n">
+        <v>31957.43773087271</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7.043397940475845e-06</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4714701581.169619</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.113777285264365e+20</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3.050875939972061</v>
+      </c>
+      <c r="E44" t="n">
+        <v>61062.61149600134</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.120055639724343e-05</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6572.667052322687</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.345310701280411e-07</v>
+      </c>
+      <c r="I44" t="n">
+        <v>60544.3827151985</v>
+      </c>
+      <c r="J44" t="n">
+        <v>59242.15625051902</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.910281606524315e-06</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2525682849.61324</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.957867888267109e+30</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4.99266821395593</v>
+      </c>
+      <c r="E45" t="n">
+        <v>24063.18323124124</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0002173537910074663</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2426.421421752175</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.017597983984382e-07</v>
+      </c>
+      <c r="I45" t="n">
+        <v>24040.84645498785</v>
+      </c>
+      <c r="J45" t="n">
+        <v>23936.36048721694</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3.798544352987502e-06</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6356045646.473345</v>
+      </c>
+      <c r="C46" t="n">
+        <v>21195038064927.37</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.69781237562512</v>
+      </c>
+      <c r="E46" t="n">
+        <v>41686.25229202196</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0001467690637511962</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4255.094394139919</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.382676191116105e-07</v>
+      </c>
+      <c r="I46" t="n">
+        <v>41590.17544209116</v>
+      </c>
+      <c r="J46" t="n">
+        <v>41227.5645989474</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8.953344227903862e-06</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1918346857.032799</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.174539913066847e+40</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7.115632151369266</v>
+      </c>
+      <c r="E47" t="n">
+        <v>34993.14372246555</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.359303328250111e-05</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3690.458682646757</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.64577552395316e-07</v>
+      </c>
+      <c r="I47" t="n">
+        <v>34780.76115535422</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34179.63836010743</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -438,2146 +438,1954 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>5.639151596682141E-06</v>
+        <v>2.256657051398123E-06</v>
       </c>
       <c r="B2">
-        <v>3156546147.088141</v>
+        <v>12739914668.90881</v>
       </c>
       <c r="C2">
-        <v>1.410465291695818E+24</v>
+        <v>13982339979.97377</v>
       </c>
       <c r="D2">
-        <v>3.82231876266452</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E2">
-        <v>33752.86138047086</v>
+        <v>48122.00230910497</v>
       </c>
       <c r="F2">
-        <v>2.432745371466571E-05</v>
+        <v>0.0001772340790388241</v>
       </c>
       <c r="G2">
-        <v>3739.451592916078</v>
+        <v>4872.26789893256</v>
       </c>
       <c r="H2">
-        <v>2.916367806550024E-07</v>
+        <v>2.45811278534102E-07</v>
       </c>
       <c r="I2">
-        <v>33348.2330972831</v>
+        <v>48055.26045574713</v>
       </c>
       <c r="J2">
-        <v>32460.48040309185</v>
+        <v>47769.7571801262</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>1.220690798370938E-06</v>
+        <v>4.557807256545888E-06</v>
       </c>
       <c r="B3">
-        <v>5550605095.334253</v>
+        <v>6691813252.141661</v>
       </c>
       <c r="C3">
-        <v>6319932192.074918</v>
+        <v>96176312600.10886</v>
       </c>
       <c r="D3">
-        <v>1.05980198019802</v>
+        <v>1.269942852270748</v>
       </c>
       <c r="E3">
-        <v>11344.08155542528</v>
+        <v>51634.41385152386</v>
       </c>
       <c r="F3">
-        <v>8.088899246619548E-05</v>
+        <v>0.0001761879667623749</v>
       </c>
       <c r="G3">
-        <v>1151.190952353125</v>
+        <v>5285.726845295714</v>
       </c>
       <c r="H3">
-        <v>1.329664007459489E-07</v>
+        <v>4.636276248112839E-07</v>
       </c>
       <c r="I3">
-        <v>11325.43400341351</v>
+        <v>51498.54111803127</v>
       </c>
       <c r="J3">
-        <v>11248.81351838654</v>
+        <v>51003.49932070971</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>9.877090421362936E-06</v>
+        <v>5.476643209396849E-06</v>
       </c>
       <c r="B4">
-        <v>2516069322.2245</v>
+        <v>6205211723.911633</v>
       </c>
       <c r="C4">
-        <v>4.811561845146648E+33</v>
+        <v>2.445121126183082E+19</v>
       </c>
       <c r="D4">
-        <v>5.87255313141116</v>
+        <v>2.861995782598798</v>
       </c>
       <c r="E4">
-        <v>49389.84008599102</v>
+        <v>61641.9057643331</v>
       </c>
       <c r="F4">
-        <v>8.122012772145131E-05</v>
+        <v>0.0001681700204314984</v>
       </c>
       <c r="G4">
-        <v>5130.470837896034</v>
+        <v>6280.970229519343</v>
       </c>
       <c r="H4">
-        <v>3.498826817956996E-07</v>
+        <v>3.539950515075426E-07</v>
       </c>
       <c r="I4">
-        <v>49177.07694232777</v>
+        <v>61512.15059423751</v>
       </c>
       <c r="J4">
-        <v>48504.54076248574</v>
+        <v>61010.80212482233</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>2.273129947671873E-06</v>
+        <v>1.687761179469438E-06</v>
       </c>
       <c r="B5">
-        <v>5954016793.255564</v>
+        <v>4327936135.222946</v>
       </c>
       <c r="C5">
-        <v>104931104458733.4</v>
+        <v>2.837912287272015E+30</v>
       </c>
       <c r="D5">
-        <v>1.79738305983099</v>
+        <v>4.629972889203504</v>
       </c>
       <c r="E5">
-        <v>23482.24968535084</v>
+        <v>14031.12475423902</v>
       </c>
       <c r="F5">
-        <v>7.433545321388404E-05</v>
+        <v>0.0001293322632996166</v>
       </c>
       <c r="G5">
-        <v>2404.089333383621</v>
+        <v>1410.35247433375</v>
       </c>
       <c r="H5">
-        <v>1.964937079030463E-07</v>
+        <v>7.414986813628295E-08</v>
       </c>
       <c r="I5">
-        <v>23420.17816885246</v>
+        <v>14023.08031100585</v>
       </c>
       <c r="J5">
-        <v>23194.30131837406</v>
+        <v>13981.57928549693</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>6.979089992487488E-06</v>
+        <v>1.720289257116658E-06</v>
       </c>
       <c r="B6">
-        <v>2252001312.620285</v>
+        <v>12384974987.73924</v>
       </c>
       <c r="C6">
-        <v>4.142666887979622E+31</v>
+        <v>13815193692.93708</v>
       </c>
       <c r="D6">
-        <v>5.341185419411947</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E6">
-        <v>30784.03884862971</v>
+        <v>35663.52416295992</v>
       </c>
       <c r="F6">
-        <v>0.0001578017555020668</v>
+        <v>0.0001316091767157524</v>
       </c>
       <c r="G6">
-        <v>3125.771556645599</v>
+        <v>3612.05263865097</v>
       </c>
       <c r="H6">
-        <v>2.697899460207237E-07</v>
+        <v>1.873862497087615E-07</v>
       </c>
       <c r="I6">
-        <v>30731.40810220456</v>
+        <v>35612.74613812105</v>
       </c>
       <c r="J6">
-        <v>30517.20657257281</v>
+        <v>35396.8567633597</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>1.823782146792497E-06</v>
+        <v>7.047755418967829E-07</v>
       </c>
       <c r="B7">
-        <v>5562030709.006808</v>
+        <v>12053807276.42321</v>
       </c>
       <c r="C7">
-        <v>7.794464679895107E+16</v>
+        <v>14182813245.70691</v>
       </c>
       <c r="D7">
-        <v>2.285036756529267</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E7">
-        <v>17944.63528898695</v>
+        <v>14241.68645228369</v>
       </c>
       <c r="F7">
-        <v>0.0002276746386622684</v>
+        <v>2.613660566984872E-05</v>
       </c>
       <c r="G7">
-        <v>1804.193008001678</v>
+        <v>1461.816636594616</v>
       </c>
       <c r="H7">
-        <v>1.371598811486269E-07</v>
+        <v>7.676920909443464E-08</v>
       </c>
       <c r="I7">
-        <v>17933.82475665031</v>
+        <v>14199.85535076564</v>
       </c>
       <c r="J7">
-        <v>17878.58873346953</v>
+        <v>14051.97157109735</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>2.006893313620639E-06</v>
+        <v>4.548326438588888E-06</v>
       </c>
       <c r="B8">
-        <v>7585091142.294609</v>
+        <v>9336109608.606815</v>
       </c>
       <c r="C8">
-        <v>8383406625.74835</v>
+        <v>100475686408656.9</v>
       </c>
       <c r="D8">
-        <v>1.059801980198019</v>
+        <v>1.802199452694152</v>
       </c>
       <c r="E8">
-        <v>25504.40129204485</v>
+        <v>73644.18404643344</v>
       </c>
       <c r="F8">
-        <v>9.307831657245094E-05</v>
+        <v>0.0001961120645742109</v>
       </c>
       <c r="G8">
-        <v>2604.350168790992</v>
+        <v>7497.106737807756</v>
       </c>
       <c r="H8">
-        <v>2.186052200519317E-07</v>
+        <v>3.926052349433208E-07</v>
       </c>
       <c r="I8">
-        <v>25444.50124805983</v>
+        <v>73496.75256513966</v>
       </c>
       <c r="J8">
-        <v>25219.54295941455</v>
+        <v>72919.78419803274</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>5.381416345049777E-06</v>
+        <v>1.149561290935854E-05</v>
       </c>
       <c r="B9">
-        <v>2548497162.142129</v>
+        <v>1916434868.575949</v>
       </c>
       <c r="C9">
-        <v>7.444847269677284E+29</v>
+        <v>1.511640347282036E+37</v>
       </c>
       <c r="D9">
-        <v>4.90879420659622</v>
+        <v>6.666434784839965</v>
       </c>
       <c r="E9">
-        <v>26640.75609714829</v>
+        <v>44359.88433027342</v>
       </c>
       <c r="F9">
-        <v>5.290628670220586E-05</v>
+        <v>0.000186476746570785</v>
       </c>
       <c r="G9">
-        <v>2765.815179164711</v>
+        <v>4513.378973227116</v>
       </c>
       <c r="H9">
-        <v>2.244957484041853E-07</v>
+        <v>3.614761492453601E-07</v>
       </c>
       <c r="I9">
-        <v>26527.71213109286</v>
+        <v>44273.89484116257</v>
       </c>
       <c r="J9">
-        <v>26168.72613624022</v>
+        <v>43934.63137096525</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>7.402882769510614E-06</v>
+        <v>8.276977835471247E-06</v>
       </c>
       <c r="B10">
-        <v>3895470643.872129</v>
+        <v>3547079104.344962</v>
       </c>
       <c r="C10">
-        <v>4.146764395693069E+30</v>
+        <v>1.128550760992706E+29</v>
       </c>
       <c r="D10">
-        <v>5.122686487783747</v>
+        <v>4.86336976166053</v>
       </c>
       <c r="E10">
-        <v>56179.30023751171</v>
+        <v>56942.36679052481</v>
       </c>
       <c r="F10">
-        <v>0.0001797742526575731</v>
+        <v>8.948664049956977E-05</v>
       </c>
       <c r="G10">
-        <v>5701.524071495755</v>
+        <v>5893.626488149792</v>
       </c>
       <c r="H10">
-        <v>2.972240941329139E-07</v>
+        <v>3.481634183951338E-07</v>
       </c>
       <c r="I10">
-        <v>56086.41796223995</v>
+        <v>56720.82255819446</v>
       </c>
       <c r="J10">
-        <v>55705.30770761286</v>
+        <v>55998.57253203546</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>1.238893005328055E-06</v>
+        <v>2.966155101074069E-06</v>
       </c>
       <c r="B11">
-        <v>8267006560.642742</v>
+        <v>5436668973.402788</v>
       </c>
       <c r="C11">
-        <v>9404505310.647741</v>
+        <v>3.468667284591158E+20</v>
       </c>
       <c r="D11">
-        <v>1.05980198019802</v>
+        <v>2.990051126605531</v>
       </c>
       <c r="E11">
-        <v>17147.75888340477</v>
+        <v>29376.6478209759</v>
       </c>
       <c r="F11">
-        <v>8.187238454300924E-05</v>
+        <v>0.0001259845112949367</v>
       </c>
       <c r="G11">
-        <v>1740.213860130169</v>
+        <v>2976.642134895998</v>
       </c>
       <c r="H11">
-        <v>1.349491157364695E-07</v>
+        <v>1.857311507275788E-07</v>
       </c>
       <c r="I11">
-        <v>17119.49447030511</v>
+        <v>29333.33965119989</v>
       </c>
       <c r="J11">
-        <v>17003.43575509281</v>
+        <v>29150.70785023123</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>3.412927647478472E-06</v>
+        <v>5.347609570394546E-06</v>
       </c>
       <c r="B12">
-        <v>4001014460.261916</v>
+        <v>3363979902.58015</v>
       </c>
       <c r="C12">
-        <v>6.855589720122343E+27</v>
+        <v>6.749741810889933E+19</v>
       </c>
       <c r="D12">
-        <v>4.362031469483483</v>
+        <v>2.99136625103958</v>
       </c>
       <c r="E12">
-        <v>26038.909123578</v>
+        <v>32867.34588325315</v>
       </c>
       <c r="F12">
-        <v>0.0001715869923318868</v>
+        <v>7.688350037801967E-05</v>
       </c>
       <c r="G12">
-        <v>2625.459996762603</v>
+        <v>3415.525259281741</v>
       </c>
       <c r="H12">
-        <v>1.579249602887306E-07</v>
+        <v>3.34742155949346E-07</v>
       </c>
       <c r="I12">
-        <v>26014.94347423933</v>
+        <v>32724.24513774602</v>
       </c>
       <c r="J12">
-        <v>25902.63456428233</v>
+        <v>32273.38726966222</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
-        <v>2.775669067741237E-06</v>
+        <v>3.231342566156886E-06</v>
       </c>
       <c r="B13">
-        <v>14185709803.94181</v>
+        <v>8044486466.056783</v>
       </c>
       <c r="C13">
-        <v>15377583183.82827</v>
+        <v>41377268433325.18</v>
       </c>
       <c r="D13">
-        <v>1.05980198019802</v>
+        <v>1.722910350945136</v>
       </c>
       <c r="E13">
-        <v>65973.18678724958</v>
+        <v>44879.72430810134</v>
       </c>
       <c r="F13">
-        <v>0.0001264258951929564</v>
+        <v>0.0002564720534762446</v>
       </c>
       <c r="G13">
-        <v>6739.315251589611</v>
+        <v>4532.950827984954</v>
       </c>
       <c r="H13">
-        <v>3.023457914911421E-07</v>
+        <v>2.855954829723994E-07</v>
       </c>
       <c r="I13">
-        <v>65815.41281739998</v>
+        <v>44829.74831124043</v>
       </c>
       <c r="J13">
-        <v>65225.70034664834</v>
+        <v>44605.04219568798</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
-        <v>3.57855311306535E-06</v>
+        <v>2.055585025922593E-06</v>
       </c>
       <c r="B14">
-        <v>4708013236.625394</v>
+        <v>12523014831.6289</v>
       </c>
       <c r="C14">
-        <v>7.083135661637781E+26</v>
+        <v>13821208382.98229</v>
       </c>
       <c r="D14">
-        <v>4.181789348564387</v>
+        <v>1.059801980198019</v>
       </c>
       <c r="E14">
-        <v>31984.05293296661</v>
+        <v>43107.39933378094</v>
       </c>
       <c r="F14">
-        <v>9.260151468935703E-05</v>
+        <v>0.0001218736609739122</v>
       </c>
       <c r="G14">
-        <v>3251.772111542177</v>
+        <v>4382.018041254272</v>
       </c>
       <c r="H14">
-        <v>1.716775062887904E-07</v>
+        <v>2.239090707400734E-07</v>
       </c>
       <c r="I14">
-        <v>31924.75646824938</v>
+        <v>43028.20143614073</v>
       </c>
       <c r="J14">
-        <v>31688.19019654334</v>
+        <v>42711.52639778993</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>8.091339150270051E-07</v>
+        <v>1.223760293126235E-05</v>
       </c>
       <c r="B15">
-        <v>9700159839.352516</v>
+        <v>3729801552.50725</v>
       </c>
       <c r="C15">
-        <v>11319590912.1318</v>
+        <v>1.312835601441439E+25</v>
       </c>
       <c r="D15">
-        <v>1.05980198019802</v>
+        <v>4.195578444558869</v>
       </c>
       <c r="E15">
-        <v>13138.32282825964</v>
+        <v>86790.53669175172</v>
       </c>
       <c r="F15">
-        <v>6.063043230630174E-05</v>
+        <v>0.0001921099929961272</v>
       </c>
       <c r="G15">
-        <v>1331.021196117399</v>
+        <v>8917.09476858892</v>
       </c>
       <c r="H15">
-        <v>8.813667191249363E-08</v>
+        <v>5.854462387808991E-07</v>
       </c>
       <c r="I15">
-        <v>13119.2240357136</v>
+        <v>86526.04658129202</v>
       </c>
       <c r="J15">
-        <v>13038.41718427818</v>
+        <v>85600.57401483582</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
-        <v>2.544908380798825E-06</v>
+        <v>5.013124947875444E-06</v>
       </c>
       <c r="B16">
-        <v>7613244618.260254</v>
+        <v>3040944677.919991</v>
       </c>
       <c r="C16">
-        <v>114515441420.6537</v>
+        <v>2.813520262394221E+27</v>
       </c>
       <c r="D16">
-        <v>1.261357737770037</v>
+        <v>4.417143481600988</v>
       </c>
       <c r="E16">
-        <v>32765.84546722322</v>
+        <v>29158.74177812421</v>
       </c>
       <c r="F16">
-        <v>0.0001308978488242123</v>
+        <v>9.717783465276577E-05</v>
       </c>
       <c r="G16">
-        <v>3335.065403349468</v>
+        <v>2977.842195327531</v>
       </c>
       <c r="H16">
-        <v>2.595866458141356E-07</v>
+        <v>2.294687399090306E-07</v>
       </c>
       <c r="I16">
-        <v>32700.8667376375</v>
+        <v>29089.88842532964</v>
       </c>
       <c r="J16">
-        <v>32445.96695426945</v>
+        <v>28831.67196306168</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17">
-        <v>6.990305421570131E-06</v>
+        <v>8.422106766323365E-06</v>
       </c>
       <c r="B17">
-        <v>3334561406.121204</v>
+        <v>3839252208.245855</v>
       </c>
       <c r="C17">
-        <v>6.851292796280628E+34</v>
+        <v>3.517872019592862E+27</v>
       </c>
       <c r="D17">
-        <v>5.93043918711495</v>
+        <v>4.56715949517684</v>
       </c>
       <c r="E17">
-        <v>46214.52846141715</v>
+        <v>62029.96354575368</v>
       </c>
       <c r="F17">
-        <v>0.0003525250590265174</v>
+        <v>0.0003651349280358248</v>
       </c>
       <c r="G17">
-        <v>4650.403378914387</v>
+        <v>6260.250748530278</v>
       </c>
       <c r="H17">
-        <v>2.45372291506794E-07</v>
+        <v>3.744709782437233E-07</v>
       </c>
       <c r="I17">
-        <v>46182.36120278084</v>
+        <v>61966.34755247044</v>
       </c>
       <c r="J17">
-        <v>46022.64521817041</v>
+        <v>61675.0931987181</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18">
-        <v>3.058748322048232E-06</v>
+        <v>2.867106044473968E-06</v>
       </c>
       <c r="B18">
-        <v>6426819514.149342</v>
+        <v>7287278531.664982</v>
       </c>
       <c r="C18">
-        <v>4.827274689091424E+18</v>
+        <v>500068137515.005</v>
       </c>
       <c r="D18">
-        <v>2.647786695602912</v>
+        <v>1.381427665720483</v>
       </c>
       <c r="E18">
-        <v>35365.06154040429</v>
+        <v>35556.55932942725</v>
       </c>
       <c r="F18">
-        <v>8.773731861680634E-05</v>
+        <v>0.0001095185161279965</v>
       </c>
       <c r="G18">
-        <v>3612.254472879917</v>
+        <v>3637.903825075897</v>
       </c>
       <c r="H18">
-        <v>2.088047762153502E-07</v>
+        <v>2.814816503608489E-07</v>
       </c>
       <c r="I18">
-        <v>35280.89674169374</v>
+        <v>35465.17278261262</v>
       </c>
       <c r="J18">
-        <v>34965.90912856931</v>
+        <v>35130.09176210016</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19">
-        <v>1.64608215282245E-05</v>
+        <v>4.813585975518217E-06</v>
       </c>
       <c r="B19">
-        <v>935472370.9428865</v>
+        <v>3994948588.039815</v>
       </c>
       <c r="C19">
-        <v>1.328336074446787E+62</v>
+        <v>1.274148169331852E+20</v>
       </c>
       <c r="D19">
-        <v>12.11951599022629</v>
+        <v>3.011942299401699</v>
       </c>
       <c r="E19">
-        <v>32868.69172623328</v>
+        <v>35108.29722630692</v>
       </c>
       <c r="F19">
-        <v>9.544075239405551E-05</v>
+        <v>0.0001057458625763856</v>
       </c>
       <c r="G19">
-        <v>3376.656790181052</v>
+        <v>3600.411369907396</v>
       </c>
       <c r="H19">
-        <v>2.896845777452999E-07</v>
+        <v>2.997989810793051E-07</v>
       </c>
       <c r="I19">
-        <v>32768.92770672469</v>
+        <v>35008.76206266614</v>
       </c>
       <c r="J19">
-        <v>32419.45026816845</v>
+        <v>34653.41631549998</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20">
-        <v>1.728299943429878E-06</v>
+        <v>2.545121055739353E-06</v>
       </c>
       <c r="B20">
-        <v>7015808756.54504</v>
+        <v>5034318572.381765</v>
       </c>
       <c r="C20">
-        <v>7823821396.213886</v>
+        <v>77438393316615.92</v>
       </c>
       <c r="D20">
-        <v>1.05980198019802</v>
+        <v>1.793853458576999</v>
       </c>
       <c r="E20">
-        <v>20303.45119468929</v>
+        <v>22253.21033463352</v>
       </c>
       <c r="F20">
-        <v>0.0001070878265819056</v>
+        <v>5.782991572568478E-05</v>
       </c>
       <c r="G20">
-        <v>2062.468972392832</v>
+        <v>2301.593895410465</v>
       </c>
       <c r="H20">
-        <v>1.882588311421559E-07</v>
+        <v>2.202355481513791E-07</v>
       </c>
       <c r="I20">
-        <v>20267.75802477384</v>
+        <v>22168.46271024783</v>
       </c>
       <c r="J20">
-        <v>20123.47750899533</v>
+        <v>21890.4114522885</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21">
-        <v>1.456378670820924E-05</v>
+        <v>1.529292552451663E-05</v>
       </c>
       <c r="B21">
-        <v>3386013249.666506</v>
+        <v>2174334705.572186</v>
       </c>
       <c r="C21">
-        <v>5.532529700212008E+22</v>
+        <v>1.299468304307375E+38</v>
       </c>
       <c r="D21">
-        <v>3.766088585802484</v>
+        <v>6.993803421100753</v>
       </c>
       <c r="E21">
-        <v>92436.41217873886</v>
+        <v>67401.61037596426</v>
       </c>
       <c r="F21">
-        <v>0.0003195364658605655</v>
+        <v>0.0001548093083130597</v>
       </c>
       <c r="G21">
-        <v>9442.131747955293</v>
+        <v>6920.189012536044</v>
       </c>
       <c r="H21">
-        <v>7.623855024475572E-07</v>
+        <v>4.594352192600095E-07</v>
       </c>
       <c r="I21">
-        <v>92215.86714531505</v>
+        <v>67201.57929269802</v>
       </c>
       <c r="J21">
-        <v>91391.02621209614</v>
+        <v>66496.4441432231</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22">
-        <v>3.33715333225394E-06</v>
+        <v>4.083108115074745E-06</v>
       </c>
       <c r="B22">
-        <v>6501049285.770243</v>
+        <v>6596352812.456501</v>
       </c>
       <c r="C22">
-        <v>63075930216995.09</v>
+        <v>6987417464.798065</v>
       </c>
       <c r="D22">
-        <v>1.774560272102174</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E22">
-        <v>37561.08063336817</v>
+        <v>45160.49229492153</v>
       </c>
       <c r="F22">
-        <v>0.0001878279148988717</v>
+        <v>0.0001427679164939651</v>
       </c>
       <c r="G22">
-        <v>3808.37954241062</v>
+        <v>4642.667879008392</v>
       </c>
       <c r="H22">
-        <v>2.90431915090988E-07</v>
+        <v>4.447614339705094E-07</v>
       </c>
       <c r="I22">
-        <v>37503.00121217505</v>
+        <v>45019.80490657015</v>
       </c>
       <c r="J22">
-        <v>37260.83162795543</v>
+        <v>44530.56857068635</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23">
-        <v>1.56544458411526E-06</v>
+        <v>1.118994713034372E-05</v>
       </c>
       <c r="B23">
-        <v>9413051332.089476</v>
+        <v>2393243786.059372</v>
       </c>
       <c r="C23">
-        <v>10559466737.88247</v>
+        <v>5.004529163250754E+34</v>
       </c>
       <c r="D23">
-        <v>1.05980198019802</v>
+        <v>6.134625701618906</v>
       </c>
       <c r="E23">
-        <v>24667.70718218863</v>
+        <v>53321.46476379972</v>
       </c>
       <c r="F23">
-        <v>0.0001137013451508734</v>
+        <v>0.0005025871254236334</v>
       </c>
       <c r="G23">
-        <v>2500.065765188803</v>
+        <v>5368.48414459152</v>
       </c>
       <c r="H23">
-        <v>1.705194568475748E-07</v>
+        <v>3.805606093768337E-07</v>
       </c>
       <c r="I23">
-        <v>24630.71268555536</v>
+        <v>53281.089576898</v>
       </c>
       <c r="J23">
-        <v>24475.33577852547</v>
+        <v>53084.01674768933</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24">
-        <v>3.168725808579002E-06</v>
+        <v>1.261227564387091E-06</v>
       </c>
       <c r="B24">
-        <v>2952637182.602845</v>
+        <v>7879665829.836873</v>
       </c>
       <c r="C24">
-        <v>2.083965541584884E+27</v>
+        <v>8954295676.219631</v>
       </c>
       <c r="D24">
-        <v>4.272775123286541</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E24">
-        <v>17804.21296106159</v>
+        <v>16626.39548250992</v>
       </c>
       <c r="F24">
-        <v>9.950271015506564E-05</v>
+        <v>0.0001538423887521537</v>
       </c>
       <c r="G24">
-        <v>1804.456619800726</v>
+        <v>1676.002250680173</v>
       </c>
       <c r="H24">
-        <v>1.492518061311361E-07</v>
+        <v>1.373819561693548E-07</v>
       </c>
       <c r="I24">
-        <v>17777.50704584541</v>
+        <v>16611.54803536639</v>
       </c>
       <c r="J24">
-        <v>17665.34651872933</v>
+        <v>16541.36946149052</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25">
-        <v>1.153317922622903E-05</v>
+        <v>2.535256192775147E-06</v>
       </c>
       <c r="B25">
-        <v>1725762947.625911</v>
+        <v>8938681292.631721</v>
       </c>
       <c r="C25">
-        <v>2.248391929212537E+36</v>
+        <v>165387205558.6402</v>
       </c>
       <c r="D25">
-        <v>6.510243176823178</v>
+        <v>1.277180636531821</v>
       </c>
       <c r="E25">
-        <v>40133.15598733992</v>
+        <v>38452.23533620412</v>
       </c>
       <c r="F25">
-        <v>6.028537213150055E-05</v>
+        <v>5.652638487024421E-05</v>
       </c>
       <c r="G25">
-        <v>4235.535563308421</v>
+        <v>4002.745176361067</v>
       </c>
       <c r="H25">
-        <v>3.708934789103959E-07</v>
+        <v>2.572926276832331E-07</v>
       </c>
       <c r="I25">
-        <v>39886.24491559056</v>
+        <v>38277.2112887145</v>
       </c>
       <c r="J25">
-        <v>39190.59937711069</v>
+        <v>37733.31995799686</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26">
-        <v>7.450306021176967E-06</v>
+        <v>3.089738199157271E-06</v>
       </c>
       <c r="B26">
-        <v>6061519858.695403</v>
+        <v>8226675752.56635</v>
       </c>
       <c r="C26">
-        <v>6194055218.101353</v>
+        <v>10858497954.87824</v>
       </c>
       <c r="D26">
-        <v>1.05980198019802</v>
+        <v>1.075645645462612</v>
       </c>
       <c r="E26">
-        <v>75858.19479468463</v>
+        <v>42619.2724403217</v>
       </c>
       <c r="F26">
-        <v>0.0001652548355136828</v>
+        <v>0.0001429846928248074</v>
       </c>
       <c r="G26">
-        <v>7921.094494540765</v>
+        <v>4351.741423985009</v>
       </c>
       <c r="H26">
-        <v>8.115407910126154E-07</v>
+        <v>3.348003587357461E-07</v>
       </c>
       <c r="I26">
-        <v>75485.66700015985</v>
+        <v>42519.47890704076</v>
       </c>
       <c r="J26">
-        <v>74355.40653996663</v>
+        <v>42144.39968365587</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27">
-        <v>4.634856184429072E-06</v>
+        <v>6.621299872177863E-06</v>
       </c>
       <c r="B27">
-        <v>2295992568.747874</v>
+        <v>4793285330.054667</v>
       </c>
       <c r="C27">
-        <v>2.134927117529582E+28</v>
+        <v>5.824277880127428E+20</v>
       </c>
       <c r="D27">
-        <v>4.582284094030346</v>
+        <v>3.176578312171774</v>
       </c>
       <c r="E27">
-        <v>20433.09330463067</v>
+        <v>58198.94281094823</v>
       </c>
       <c r="F27">
-        <v>0.0001365131190769764</v>
+        <v>0.0003726535151885322</v>
       </c>
       <c r="G27">
-        <v>2070.990202728727</v>
+        <v>5875.599739975746</v>
       </c>
       <c r="H27">
-        <v>2.054837738749263E-07</v>
+        <v>3.963194378251115E-07</v>
       </c>
       <c r="I27">
-        <v>20402.33677989104</v>
+        <v>58137.04785663611</v>
       </c>
       <c r="J27">
-        <v>20273.27157660652</v>
+        <v>57855.91430677369</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28">
-        <v>3.93534973280738E-06</v>
+        <v>1.689591565022163E-06</v>
       </c>
       <c r="B28">
-        <v>7168916935.388894</v>
+        <v>8657003466.133289</v>
       </c>
       <c r="C28">
-        <v>7610683227.141737</v>
+        <v>9667119162.717632</v>
       </c>
       <c r="D28">
         <v>1.05980198019802</v>
       </c>
       <c r="E28">
-        <v>47214.76005574208</v>
+        <v>24497.07697918463</v>
       </c>
       <c r="F28">
-        <v>0.0003501192039964721</v>
+        <v>9.345678563315304E-05</v>
       </c>
       <c r="G28">
-        <v>4773.502425278561</v>
+        <v>2493.125107798638</v>
       </c>
       <c r="H28">
-        <v>4.286665307432914E-07</v>
+        <v>1.840424368165372E-07</v>
       </c>
       <c r="I28">
-        <v>47156.95292273725</v>
+        <v>24448.8354126511</v>
       </c>
       <c r="J28">
-        <v>46902.49717471094</v>
+        <v>24259.25779157913</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29">
-        <v>5.155894205246726E-06</v>
+        <v>1.112164799357215E-05</v>
       </c>
       <c r="B29">
-        <v>4358660083.504517</v>
+        <v>3174354219.682825</v>
       </c>
       <c r="C29">
-        <v>6.916778483205973E+23</v>
+        <v>2.708831933261094E+27</v>
       </c>
       <c r="D29">
-        <v>3.717226786226913</v>
+        <v>4.647402463992828</v>
       </c>
       <c r="E29">
-        <v>41985.5678566891</v>
+        <v>67944.10807022532</v>
       </c>
       <c r="F29">
-        <v>0.0003868698718171921</v>
+        <v>0.0002445519150348527</v>
       </c>
       <c r="G29">
-        <v>4225.200891689518</v>
+        <v>6916.185817857103</v>
       </c>
       <c r="H29">
-        <v>2.727869071597922E-07</v>
+        <v>4.870066972662589E-07</v>
       </c>
       <c r="I29">
-        <v>41955.96329444398</v>
+        <v>67808.80250263136</v>
       </c>
       <c r="J29">
-        <v>41809.35483196878</v>
+        <v>67278.58115120162</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30">
-        <v>2.846359567850719E-06</v>
+        <v>1.079867318115197E-06</v>
       </c>
       <c r="B30">
-        <v>4691773844.174121</v>
+        <v>6329454802.557953</v>
       </c>
       <c r="C30">
-        <v>330599769182899.6</v>
+        <v>7259755031.77724</v>
       </c>
       <c r="D30">
-        <v>1.918766297605485</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E30">
-        <v>23282.5659792716</v>
+        <v>11435.45926399586</v>
       </c>
       <c r="F30">
-        <v>0.0001176409695746432</v>
+        <v>0.0001252487141836088</v>
       </c>
       <c r="G30">
-        <v>2370.547301224675</v>
+        <v>1153.211541220438</v>
       </c>
       <c r="H30">
-        <v>2.374270251227021E-07</v>
+        <v>1.176268968067751E-07</v>
       </c>
       <c r="I30">
-        <v>23235.57630894102</v>
+        <v>11424.71969197269</v>
       </c>
       <c r="J30">
-        <v>23052.06061558635</v>
+        <v>11374.56255503677</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31">
-        <v>4.401862214214046E-06</v>
+        <v>1.457021844473067E-05</v>
       </c>
       <c r="B31">
-        <v>5243145417.800243</v>
+        <v>814011400.1225661</v>
       </c>
       <c r="C31">
-        <v>7.403379786733478E+20</v>
+        <v>1.00929658133223E+69</v>
       </c>
       <c r="D31">
-        <v>3.117162415468774</v>
+        <v>13.43158264489157</v>
       </c>
       <c r="E31">
-        <v>42319.61885793022</v>
+        <v>25658.33362943157</v>
       </c>
       <c r="F31">
-        <v>8.332324325735155E-05</v>
+        <v>2.389134918881087E-05</v>
       </c>
       <c r="G31">
-        <v>4354.122967946574</v>
+        <v>2789.880653770735</v>
       </c>
       <c r="H31">
-        <v>2.672481946660027E-07</v>
+        <v>2.317978563688338E-07</v>
       </c>
       <c r="I31">
-        <v>42183.88432220405</v>
+        <v>25409.3921951787</v>
       </c>
       <c r="J31">
-        <v>41715.74875927257</v>
+        <v>24814.86642149592</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32">
-        <v>4.38417539900936E-06</v>
+        <v>3.595975379880317E-06</v>
       </c>
       <c r="B32">
-        <v>2965926231.051027</v>
+        <v>7834518070.962525</v>
       </c>
       <c r="C32">
-        <v>2.569949638679621E+29</v>
+        <v>34860234846.12953</v>
       </c>
       <c r="D32">
-        <v>4.746183115043161</v>
+        <v>1.172400631717902</v>
       </c>
       <c r="E32">
-        <v>25098.57928699406</v>
+        <v>47493.06067371411</v>
       </c>
       <c r="F32">
-        <v>8.500306663361379E-05</v>
+        <v>0.0001231287995282132</v>
       </c>
       <c r="G32">
-        <v>2559.937076287697</v>
+        <v>4880.353625719172</v>
       </c>
       <c r="H32">
-        <v>1.884516193670647E-07</v>
+        <v>3.77499091716874E-07</v>
       </c>
       <c r="I32">
-        <v>25042.93578967374</v>
+        <v>47347.45227554992</v>
       </c>
       <c r="J32">
-        <v>24830.79309064559</v>
+        <v>46838.81951490916</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33">
-        <v>5.565009025350623E-06</v>
+        <v>1.066455475502229E-05</v>
       </c>
       <c r="B33">
-        <v>7492146437.476669</v>
+        <v>1697188333.492436</v>
       </c>
       <c r="C33">
-        <v>73708406111552.23</v>
+        <v>1.402474827151607E+39</v>
       </c>
       <c r="D33">
-        <v>1.808094616979342</v>
+        <v>7.03438298228171</v>
       </c>
       <c r="E33">
-        <v>72373.76589178828</v>
+        <v>36716.96510087697</v>
       </c>
       <c r="F33">
-        <v>0.0001825025225913223</v>
+        <v>0.0001033426693361046</v>
       </c>
       <c r="G33">
-        <v>7408.52268229367</v>
+        <v>3773.580739906075</v>
       </c>
       <c r="H33">
-        <v>4.795260231573296E-07</v>
+        <v>3.186231712342348E-07</v>
       </c>
       <c r="I33">
-        <v>72183.60356610513</v>
+        <v>36603.76040107877</v>
       </c>
       <c r="J33">
-        <v>71490.48167856362</v>
+        <v>36208.94307241785</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34">
-        <v>2.163130784293166E-06</v>
+        <v>9.514400648185241E-06</v>
       </c>
       <c r="B34">
-        <v>9766749581.531368</v>
+        <v>1489776711.982428</v>
       </c>
       <c r="C34">
-        <v>7910411678578907</v>
+        <v>1.370866707336935E+37</v>
       </c>
       <c r="D34">
-        <v>2.085085359951184</v>
+        <v>6.587336563576383</v>
       </c>
       <c r="E34">
-        <v>37050.70271071739</v>
+        <v>28553.20444185337</v>
       </c>
       <c r="F34">
-        <v>0.0003053805567594082</v>
+        <v>7.991210012573975E-05</v>
       </c>
       <c r="G34">
-        <v>3723.853600634279</v>
+        <v>2952.623798793722</v>
       </c>
       <c r="H34">
-        <v>1.720184389960465E-07</v>
+        <v>3.025819330782764E-07</v>
       </c>
       <c r="I34">
-        <v>37029.83234453679</v>
+        <v>28445.0896033996</v>
       </c>
       <c r="J34">
-        <v>36921.79443726264</v>
+        <v>28089.76383570423</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35">
-        <v>8.733911285146709E-06</v>
+        <v>5.005210331038592E-06</v>
       </c>
       <c r="B35">
-        <v>2024163223.871302</v>
+        <v>8677297028.639235</v>
       </c>
       <c r="C35">
-        <v>2.184656380132445E+41</v>
+        <v>135625580525344</v>
       </c>
       <c r="D35">
-        <v>7.348253640122212</v>
+        <v>1.83868865126091</v>
       </c>
       <c r="E35">
-        <v>36033.65985578678</v>
+        <v>75451.95486657722</v>
       </c>
       <c r="F35">
-        <v>8.773382635594443E-05</v>
+        <v>0.0002070775466902857</v>
       </c>
       <c r="G35">
-        <v>3695.873166652553</v>
+        <v>7685.355808959755</v>
       </c>
       <c r="H35">
-        <v>2.502601115332136E-07</v>
+        <v>4.274104073092795E-07</v>
       </c>
       <c r="I35">
-        <v>35930.87409903804</v>
+        <v>75296.22117513051</v>
       </c>
       <c r="J35">
-        <v>35564.5411245229</v>
+        <v>74691.46874899733</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36">
-        <v>4.433409673621705E-06</v>
+        <v>1.340306122261276E-06</v>
       </c>
       <c r="B36">
-        <v>7040042022.13155</v>
+        <v>7576929581.159606</v>
       </c>
       <c r="C36">
-        <v>140340957251.5141</v>
+        <v>3.405330252856403E+17</v>
       </c>
       <c r="D36">
-        <v>1.29558910124998</v>
+        <v>2.341470412877318</v>
       </c>
       <c r="E36">
-        <v>52807.81410515244</v>
+        <v>18042.00085192996</v>
       </c>
       <c r="F36">
-        <v>0.0005406832572912663</v>
+        <v>3.990373665411905E-05</v>
       </c>
       <c r="G36">
-        <v>5320.098605189854</v>
+        <v>1844.589568293328</v>
       </c>
       <c r="H36">
-        <v>4.472854221892535E-07</v>
+        <v>9.925551621086516E-08</v>
       </c>
       <c r="I36">
-        <v>52764.12833329177</v>
+        <v>17997.12364848515</v>
       </c>
       <c r="J36">
-        <v>52554.75592517686</v>
+        <v>17831.12655453113</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37">
-        <v>5.832493180346111E-06</v>
+        <v>6.281194944218136E-06</v>
       </c>
       <c r="B37">
-        <v>4483133621.122993</v>
+        <v>2879315365.73531</v>
       </c>
       <c r="C37">
-        <v>2.572008124290487E+22</v>
+        <v>2.305842773436286E+23</v>
       </c>
       <c r="D37">
-        <v>3.471290316042875</v>
+        <v>3.705000423382406</v>
       </c>
       <c r="E37">
-        <v>48487.3379395517</v>
+        <v>33783.88748011192</v>
       </c>
       <c r="F37">
-        <v>0.0001993058299766102</v>
+        <v>0.0003454484643764831</v>
       </c>
       <c r="G37">
-        <v>4920.105564293171</v>
+        <v>3407.717399632996</v>
       </c>
       <c r="H37">
-        <v>3.259684905744322E-07</v>
+        <v>3.332139937664935E-07</v>
       </c>
       <c r="I37">
-        <v>48408.03597250947</v>
+        <v>33751.30008942101</v>
       </c>
       <c r="J37">
-        <v>48081.79527999079</v>
+        <v>33600.11246515236</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38">
-        <v>2.92409199288758E-06</v>
+        <v>4.039361170875552E-06</v>
       </c>
       <c r="B38">
-        <v>2792013145.514606</v>
+        <v>6378029583.016113</v>
       </c>
       <c r="C38">
-        <v>2876468332776976</v>
+        <v>6760504547.952612</v>
       </c>
       <c r="D38">
-        <v>2.129223363204195</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E38">
-        <v>14451.49680880574</v>
+        <v>43219.79547995302</v>
       </c>
       <c r="F38">
-        <v>2.90279126014856E-05</v>
+        <v>0.0001215736169578968</v>
       </c>
       <c r="G38">
-        <v>1548.04759686002</v>
+        <v>4462.757553450922</v>
       </c>
       <c r="H38">
-        <v>2.296503147692659E-07</v>
+        <v>4.399962029049819E-07</v>
       </c>
       <c r="I38">
-        <v>14337.1657910508</v>
+        <v>43063.37547389122</v>
       </c>
       <c r="J38">
-        <v>14042.33221705748</v>
+        <v>42542.39248680077</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39">
-        <v>2.811772910276823E-06</v>
+        <v>3.251851039539453E-06</v>
       </c>
       <c r="B39">
-        <v>4223790372.482856</v>
+        <v>4264309629.9893</v>
       </c>
       <c r="C39">
-        <v>4.384153126283228E+30</v>
+        <v>7.032699831943823E+28</v>
       </c>
       <c r="D39">
-        <v>4.809953505663969</v>
+        <v>4.527459075142948</v>
       </c>
       <c r="E39">
-        <v>22944.01657754848</v>
+        <v>26608.56585692962</v>
       </c>
       <c r="F39">
-        <v>8.594037198839851E-05</v>
+        <v>6.084990246691341E-05</v>
       </c>
       <c r="G39">
-        <v>2323.100927320091</v>
+        <v>2718.194674267294</v>
       </c>
       <c r="H39">
-        <v>1.194417383477728E-07</v>
+        <v>1.456931457564475E-07</v>
       </c>
       <c r="I39">
-        <v>22912.12850025377</v>
+        <v>26544.8568696248</v>
       </c>
       <c r="J39">
-        <v>22775.78606344944</v>
+        <v>26306.80468839733</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40">
-        <v>4.169157232642731E-06</v>
+        <v>2.587242339057462E-06</v>
       </c>
       <c r="B40">
-        <v>3340603594.679696</v>
+        <v>6580839104.561071</v>
       </c>
       <c r="C40">
-        <v>4.513300984948122E+24</v>
+        <v>154370700381759.8</v>
       </c>
       <c r="D40">
-        <v>3.842693998798184</v>
+        <v>1.827339430479564</v>
       </c>
       <c r="E40">
-        <v>26179.0641675337</v>
+        <v>29588.65739321859</v>
       </c>
       <c r="F40">
-        <v>8.155085020046163E-05</v>
+        <v>7.634701567044287E-05</v>
       </c>
       <c r="G40">
-        <v>2679.928478990289</v>
+        <v>3036.185215856094</v>
       </c>
       <c r="H40">
-        <v>2.146733178440313E-07</v>
+        <v>2.216732058332069E-07</v>
       </c>
       <c r="I40">
-        <v>26110.15076504824</v>
+        <v>29502.74686373611</v>
       </c>
       <c r="J40">
-        <v>25859.09434587941</v>
+        <v>29198.0555939713</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41">
-        <v>2.844829866489576E-06</v>
+        <v>2.163503825855844E-05</v>
       </c>
       <c r="B41">
-        <v>5126938273.30998</v>
+        <v>1834131556.701378</v>
       </c>
       <c r="C41">
-        <v>3.937522199575457E+18</v>
+        <v>1.994154050607122E+39</v>
       </c>
       <c r="D41">
-        <v>2.640235604368326</v>
+        <v>7.455978263250617</v>
       </c>
       <c r="E41">
-        <v>26184.53658499197</v>
+        <v>80900.45908402608</v>
       </c>
       <c r="F41">
-        <v>0.0003212601518455499</v>
+        <v>0.0004140822395076191</v>
       </c>
       <c r="G41">
-        <v>2632.727287788409</v>
+        <v>8197.538192601272</v>
       </c>
       <c r="H41">
-        <v>1.945825416613586E-07</v>
+        <v>6.113225269496849E-07</v>
       </c>
       <c r="I41">
-        <v>26168.67699689284</v>
+        <v>80781.02321269424</v>
       </c>
       <c r="J41">
-        <v>26087.72819111552</v>
+        <v>80277.52525211504</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42">
-        <v>1.094142945047139E-05</v>
+        <v>2.879327573809873E-06</v>
       </c>
       <c r="B42">
-        <v>2044971427.717645</v>
+        <v>5573316534.523101</v>
       </c>
       <c r="C42">
-        <v>3.913102586613643E+40</v>
+        <v>7.512395160283909E+17</v>
       </c>
       <c r="D42">
-        <v>7.322120314959123</v>
+        <v>2.506523285113672</v>
       </c>
       <c r="E42">
-        <v>45587.3704256264</v>
+        <v>28684.61335520455</v>
       </c>
       <c r="F42">
-        <v>0.0001099842418578653</v>
+        <v>0.0001187198767047446</v>
       </c>
       <c r="G42">
-        <v>4676.091109048817</v>
+        <v>2912.816629711484</v>
       </c>
       <c r="H42">
-        <v>3.145875689037078E-07</v>
+        <v>2.039752110828361E-07</v>
       </c>
       <c r="I42">
-        <v>45456.97701841954</v>
+        <v>28635.32969499229</v>
       </c>
       <c r="J42">
-        <v>44992.6004286119</v>
+        <v>28434.99177086788</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43">
-        <v>4.75559154387283E-06</v>
+        <v>1.132193416834811E-05</v>
       </c>
       <c r="B43">
-        <v>2469096422.222856</v>
+        <v>1246816174.444117</v>
       </c>
       <c r="C43">
-        <v>8.060702885325717E+26</v>
+        <v>3.175289487192117E+46</v>
       </c>
       <c r="D43">
-        <v>4.318014796830012</v>
+        <v>8.576039784826879</v>
       </c>
       <c r="E43">
-        <v>22377.34950785355</v>
+        <v>29399.97597385011</v>
       </c>
       <c r="F43">
-        <v>0.0001369266172445517</v>
+        <v>3.530162321043115E-05</v>
       </c>
       <c r="G43">
-        <v>2270.384788965071</v>
+        <v>3149.442188746661</v>
       </c>
       <c r="H43">
-        <v>2.219819988541751E-07</v>
+        <v>2.794308424034118E-07</v>
       </c>
       <c r="I43">
-        <v>22341.07190987608</v>
+        <v>29167.25976122605</v>
       </c>
       <c r="J43">
-        <v>22191.51223711533</v>
+        <v>28567.2472617468</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44">
-        <v>8.650304319807689E-06</v>
+        <v>2.30337405454675E-06</v>
       </c>
       <c r="B44">
-        <v>1453332774.245512</v>
+        <v>4240843992.712803</v>
       </c>
       <c r="C44">
-        <v>8.422746778729168E+33</v>
+        <v>3.757692130599512E+23</v>
       </c>
       <c r="D44">
-        <v>5.912065738932056</v>
+        <v>3.505056008095895</v>
       </c>
       <c r="E44">
-        <v>24991.25645886753</v>
+        <v>18143.6944262822</v>
       </c>
       <c r="F44">
-        <v>8.189366918664686E-05</v>
+        <v>6.066639753646911E-05</v>
       </c>
       <c r="G44">
-        <v>2582.762137513154</v>
+        <v>1848.755514942666</v>
       </c>
       <c r="H44">
-        <v>3.045198000196298E-07</v>
+        <v>1.277504817152049E-07</v>
       </c>
       <c r="I44">
-        <v>24898.32702372708</v>
+        <v>18105.48767926615</v>
       </c>
       <c r="J44">
-        <v>24591.2667483704</v>
+        <v>17957.87885763014</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45">
-        <v>5.546640770824751E-06</v>
+        <v>3.969490723617418E-06</v>
       </c>
       <c r="B45">
-        <v>3271434576.934899</v>
+        <v>9289491965.096697</v>
       </c>
       <c r="C45">
-        <v>9.417843095454557E+23</v>
+        <v>9856840217.376663</v>
       </c>
       <c r="D45">
-        <v>3.782400406931226</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E45">
-        <v>34125.37838313309</v>
+        <v>61714.08795176133</v>
       </c>
       <c r="F45">
-        <v>5.64343290818098E-05</v>
+        <v>0.0003424433665662793</v>
       </c>
       <c r="G45">
-        <v>3569.998783981444</v>
+        <v>6241.539644769992</v>
       </c>
       <c r="H45">
-        <v>2.893318451740296E-07</v>
+        <v>4.323854124387786E-07</v>
       </c>
       <c r="I45">
-        <v>33950.42177683517</v>
+        <v>61636.16478554592</v>
       </c>
       <c r="J45">
-        <v>33426.86906770691</v>
+        <v>61295.55199014665</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46">
-        <v>6.936282447923599E-06</v>
+        <v>3.494914429127888E-06</v>
       </c>
       <c r="B46">
-        <v>1757347286.741205</v>
+        <v>5460421458.527568</v>
       </c>
       <c r="C46">
-        <v>1.571326937295259E+48</v>
+        <v>1.409514600805649E+21</v>
       </c>
       <c r="D46">
-        <v>8.563136899790852</v>
+        <v>3.126232449759494</v>
       </c>
       <c r="E46">
-        <v>25234.4972235001</v>
+        <v>34975.44493020629</v>
       </c>
       <c r="F46">
-        <v>8.249513847589471E-05</v>
+        <v>8.891271564055534E-05</v>
       </c>
       <c r="G46">
-        <v>2570.647825329892</v>
+        <v>3572.501136689074</v>
       </c>
       <c r="H46">
-        <v>1.714414115389346E-07</v>
+        <v>2.117231025989824E-07</v>
       </c>
       <c r="I46">
-        <v>25182.05488685579</v>
+        <v>34892.15977057468</v>
       </c>
       <c r="J46">
-        <v>24978.76348386537</v>
+        <v>34580.51102977888</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47">
-        <v>4.544830034505184E-06</v>
+        <v>1.131161181204194E-05</v>
       </c>
       <c r="B47">
-        <v>3820245580.708888</v>
+        <v>1826469989.063514</v>
       </c>
       <c r="C47">
-        <v>7.073823647801901E+21</v>
+        <v>1.370083150785648E+41</v>
       </c>
       <c r="D47">
-        <v>3.330269015267727</v>
+        <v>7.460128534345239</v>
       </c>
       <c r="E47">
-        <v>32042.93725550908</v>
+        <v>42310.48865857054</v>
       </c>
       <c r="F47">
-        <v>0.0001399892409652691</v>
+        <v>5.429282025907351E-05</v>
       </c>
       <c r="G47">
-        <v>3258.343544032394</v>
+        <v>4455.103069964958</v>
       </c>
       <c r="H47">
-        <v>2.623699362167885E-07</v>
+        <v>3.194515123683071E-07</v>
       </c>
       <c r="I47">
-        <v>31982.88190164076</v>
+        <v>42061.53954289509</v>
       </c>
       <c r="J47">
-        <v>31743.93544529723</v>
+        <v>41349.52649482833</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48">
-        <v>2.621106087853433E-06</v>
+        <v>1.276562382875194E-06</v>
       </c>
       <c r="B48">
-        <v>8714136593.094669</v>
+        <v>12358284220.7196</v>
       </c>
       <c r="C48">
-        <v>9478714331.143049</v>
+        <v>14033562533.6419</v>
       </c>
       <c r="D48">
-        <v>1.05980198019802</v>
+        <v>1.059801980198019</v>
       </c>
       <c r="E48">
-        <v>38225.33225073895</v>
+        <v>26447.27578636571</v>
       </c>
       <c r="F48">
-        <v>0.0002325814122293982</v>
+        <v>4.755058386998837E-05</v>
       </c>
       <c r="G48">
-        <v>3864.765027428432</v>
+        <v>2714.333451564452</v>
       </c>
       <c r="H48">
-        <v>2.855096826651588E-07</v>
+        <v>1.390523346330711E-07</v>
       </c>
       <c r="I48">
-        <v>38178.40802590058</v>
+        <v>26369.93592755695</v>
       </c>
       <c r="J48">
-        <v>37971.97962043752</v>
+        <v>26096.18428037945</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49">
-        <v>2.119972445072427E-06</v>
+        <v>3.035906624048699E-06</v>
       </c>
       <c r="B49">
-        <v>6545163248.78296</v>
+        <v>7708523427.773377</v>
       </c>
       <c r="C49">
-        <v>82094209907179.28</v>
+        <v>6.930351373281155E+17</v>
       </c>
       <c r="D49">
-        <v>1.767384013705509</v>
+        <v>2.481145542572339</v>
       </c>
       <c r="E49">
-        <v>24082.81667999687</v>
+        <v>41816.39676235845</v>
       </c>
       <c r="F49">
-        <v>4.253960906120287E-05</v>
+        <v>9.010612712730949E-05</v>
       </c>
       <c r="G49">
-        <v>2502.488510171758</v>
+        <v>4272.075117866923</v>
       </c>
       <c r="H49">
-        <v>1.848954191945574E-07</v>
+        <v>2.165229174131971E-07</v>
       </c>
       <c r="I49">
-        <v>23978.14241091679</v>
+        <v>41715.91293832391</v>
       </c>
       <c r="J49">
-        <v>23648.17784673054</v>
+        <v>41340.80938935433</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50">
-        <v>1.425850285864802E-05</v>
+        <v>1.680483249084049E-06</v>
       </c>
       <c r="B50">
-        <v>1685268925.297</v>
+        <v>10865681029.33669</v>
       </c>
       <c r="C50">
-        <v>1.489653535953117E+51</v>
+        <v>12137432292.6745</v>
       </c>
       <c r="D50">
-        <v>9.667376744126649</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E50">
-        <v>50409.35221842371</v>
+        <v>30594.86938103308</v>
       </c>
       <c r="F50">
-        <v>8.337163778482892E-05</v>
+        <v>7.590397986932618E-05</v>
       </c>
       <c r="G50">
-        <v>5211.334889298795</v>
+        <v>3125.891359211119</v>
       </c>
       <c r="H50">
-        <v>3.131363246573665E-07</v>
+        <v>1.830502936884296E-07</v>
       </c>
       <c r="I50">
-        <v>50220.01925458324</v>
+        <v>30521.0866909133</v>
       </c>
       <c r="J50">
-        <v>49596.26214704942</v>
+        <v>30245.91876900966</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51">
-        <v>3.329933241758487E-06</v>
+        <v>3.259727504468164E-06</v>
       </c>
       <c r="B51">
-        <v>9306159090.607271</v>
+        <v>2617828295.90276</v>
       </c>
       <c r="C51">
-        <v>9978817335.581141</v>
+        <v>4.177817862076157E+34</v>
       </c>
       <c r="D51">
-        <v>1.05980198019802</v>
+        <v>5.613966017327944</v>
       </c>
       <c r="E51">
-        <v>51877.37121234697</v>
+        <v>16811.22343723322</v>
       </c>
       <c r="F51">
-        <v>0.0002377403606930671</v>
+        <v>0.0001008580814419354</v>
       </c>
       <c r="G51">
-        <v>5258.971447675839</v>
+        <v>1699.182011816814</v>
       </c>
       <c r="H51">
-        <v>3.627202224116126E-07</v>
+        <v>1.203867352987509E-07</v>
       </c>
       <c r="I51">
-        <v>51798.22196074569</v>
+        <v>16791.15713935157</v>
       </c>
       <c r="J51">
-        <v>51467.14602171726</v>
+        <v>16702.32117261412</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52">
-        <v>6.178307958394582E-06</v>
+        <v>3.063442588860743E-06</v>
       </c>
       <c r="B52">
-        <v>1364575606.146235</v>
+        <v>6354860755.391926</v>
       </c>
       <c r="C52">
-        <v>2.382641344379037E+44</v>
+        <v>4.966192947789874E+25</v>
       </c>
       <c r="D52">
-        <v>7.779902517659625</v>
+        <v>3.911505590989967</v>
       </c>
       <c r="E52">
-        <v>17368.15894099373</v>
+        <v>36618.89718090618</v>
       </c>
       <c r="F52">
-        <v>2.329422636903005E-05</v>
+        <v>0.0001392795803632373</v>
       </c>
       <c r="G52">
-        <v>1849.262052317736</v>
+        <v>3698.67146229306</v>
       </c>
       <c r="H52">
-        <v>1.675701349531019E-07</v>
+        <v>1.554432969475228E-07</v>
       </c>
       <c r="I52">
-        <v>17243.21876519555</v>
+        <v>36578.0285762368</v>
       </c>
       <c r="J52">
-        <v>16909.80604389096</v>
+        <v>36394.36303437478</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53">
-        <v>4.516818952893543E-06</v>
+        <v>9.063193053838757E-06</v>
       </c>
       <c r="B53">
-        <v>6579255350.756497</v>
+        <v>2933487494.549249</v>
       </c>
       <c r="C53">
-        <v>1436436076029.649</v>
+        <v>2.889878828224124E+29</v>
       </c>
       <c r="D53">
-        <v>1.48837376814982</v>
+        <v>4.990230451243914</v>
       </c>
       <c r="E53">
-        <v>50897.97444437642</v>
+        <v>51744.01231441411</v>
       </c>
       <c r="F53">
-        <v>0.0001088143057836128</v>
+        <v>9.225902582559348E-05</v>
       </c>
       <c r="G53">
-        <v>5270.328353042029</v>
+        <v>5362.459918579277</v>
       </c>
       <c r="H53">
-        <v>4.288392767146685E-07</v>
+        <v>3.7256294115205E-07</v>
       </c>
       <c r="I53">
-        <v>50697.3845459271</v>
+        <v>51535.05821759426</v>
       </c>
       <c r="J53">
-        <v>50045.9606491074</v>
+        <v>50861.42998844285</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54">
-        <v>6.979795290601219E-06</v>
+        <v>6.03992993975508E-06</v>
       </c>
       <c r="B54">
-        <v>2001626302.126647</v>
+        <v>2632439907.309736</v>
       </c>
       <c r="C54">
-        <v>1.671567015014136E+33</v>
+        <v>4.05414868749059E+25</v>
       </c>
       <c r="D54">
-        <v>5.661160293879608</v>
+        <v>4.131029680114125</v>
       </c>
       <c r="E54">
-        <v>27750.57507726903</v>
+        <v>30197.50822984728</v>
       </c>
       <c r="F54">
-        <v>3.073136455201414E-05</v>
+        <v>7.610830267489704E-05</v>
       </c>
       <c r="G54">
-        <v>2982.94068847683</v>
+        <v>3124.298767541067</v>
       </c>
       <c r="H54">
-        <v>2.557918487202489E-07</v>
+        <v>2.927749515610515E-07</v>
       </c>
       <c r="I54">
-        <v>27519.59376532467</v>
+        <v>30081.3438470069</v>
       </c>
       <c r="J54">
-        <v>26934.96200580734</v>
+        <v>29701.35539877116</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55">
-        <v>2.726436548558768E-06</v>
+        <v>9.583426022814721E-06</v>
       </c>
       <c r="B55">
-        <v>3144923301.438823</v>
+        <v>1619221496.394978</v>
       </c>
       <c r="C55">
-        <v>8.697306407676436E+19</v>
+        <v>3.227381606333094E+37</v>
       </c>
       <c r="D55">
-        <v>2.912316237226558</v>
+        <v>6.65747433113841</v>
       </c>
       <c r="E55">
-        <v>15574.29376104834</v>
+        <v>31349.299948931</v>
       </c>
       <c r="F55">
-        <v>0.0001137918140910179</v>
+        <v>5.594647717781486E-05</v>
       </c>
       <c r="G55">
-        <v>1578.8664009914</v>
+        <v>3287.096848757232</v>
       </c>
       <c r="H55">
-        <v>1.740302169989535E-07</v>
+        <v>3.017327493329735E-07</v>
       </c>
       <c r="I55">
-        <v>15550.47484450771</v>
+        <v>31180.22566685974</v>
       </c>
       <c r="J55">
-        <v>15450.89887133651</v>
+        <v>30682.52552728025</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56">
-        <v>4.73487494928239E-06</v>
+        <v>9.963015457629938E-07</v>
       </c>
       <c r="B56">
-        <v>5029222891.921732</v>
+        <v>10833623939.02378</v>
       </c>
       <c r="C56">
-        <v>2.675293137878704E+20</v>
+        <v>12485940714.20446</v>
       </c>
       <c r="D56">
-        <v>3.050653112618343</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E56">
-        <v>43528.70707050305</v>
+        <v>18066.32032409028</v>
       </c>
       <c r="F56">
-        <v>0.0001121613141596912</v>
+        <v>7.909511027166891E-05</v>
       </c>
       <c r="G56">
-        <v>4454.904923347654</v>
+        <v>1828.941521575153</v>
       </c>
       <c r="H56">
-        <v>2.921262913953077E-07</v>
+        <v>1.085243132614118E-07</v>
       </c>
       <c r="I56">
-        <v>43415.33571906154</v>
+        <v>18041.53200279458</v>
       </c>
       <c r="J56">
-        <v>43001.12685261272</v>
+        <v>17935.22883962667</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57">
-        <v>6.758531984698909E-06</v>
+        <v>3.917210437614189E-06</v>
       </c>
       <c r="B57">
-        <v>4269680499.430791</v>
+        <v>3540818804.138232</v>
       </c>
       <c r="C57">
-        <v>4.171986750502071E+23</v>
+        <v>4.544187802649071E+16</v>
       </c>
       <c r="D57">
-        <v>3.73812652983647</v>
+        <v>2.356225802820752</v>
       </c>
       <c r="E57">
-        <v>53978.05195889904</v>
+        <v>24695.05691340386</v>
       </c>
       <c r="F57">
-        <v>0.000291872305673544</v>
+        <v>7.171513219828838E-05</v>
       </c>
       <c r="G57">
-        <v>5457.051132653826</v>
+        <v>2559.047619287877</v>
       </c>
       <c r="H57">
-        <v>3.559522504986963E-07</v>
+        <v>2.88924721636114E-07</v>
       </c>
       <c r="I57">
-        <v>53912.22314027245</v>
+        <v>24595.56588235109</v>
       </c>
       <c r="J57">
-        <v>53622.20021819068</v>
+        <v>24274.59904627009</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58">
-        <v>5.7726259144709E-06</v>
+        <v>6.626281031458723E-06</v>
       </c>
       <c r="B58">
-        <v>9005431609.587654</v>
+        <v>2124994264.602201</v>
       </c>
       <c r="C58">
-        <v>2.169808464055413E+16</v>
+        <v>2.903016142561788E+37</v>
       </c>
       <c r="D58">
-        <v>2.262042945641724</v>
+        <v>6.451437997128112</v>
       </c>
       <c r="E58">
-        <v>91968.41648388565</v>
+        <v>28243.55258958958</v>
       </c>
       <c r="F58">
-        <v>0.0002637500216915089</v>
+        <v>0.0001070981323138208</v>
       </c>
       <c r="G58">
-        <v>9333.950288921329</v>
+        <v>2875.367431956377</v>
       </c>
       <c r="H58">
-        <v>4.368940301846388E-07</v>
+        <v>2.149284409822682E-07</v>
       </c>
       <c r="I58">
-        <v>91816.07354996035</v>
+        <v>28186.87239737022</v>
       </c>
       <c r="J58">
-        <v>91191.27532821514</v>
+        <v>27965.19295514007</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59">
-        <v>2.897754090748216E-06</v>
+        <v>4.132944978872232E-06</v>
       </c>
       <c r="B59">
-        <v>4591501567.65675</v>
+        <v>4559239689.519527</v>
       </c>
       <c r="C59">
-        <v>6.774586165589788E+16</v>
+        <v>229762757835529.1</v>
       </c>
       <c r="D59">
-        <v>2.335288991267224</v>
+        <v>1.919361101833067</v>
       </c>
       <c r="E59">
-        <v>23601.18648207227</v>
+        <v>32858.16726475994</v>
       </c>
       <c r="F59">
-        <v>0.0001778698129163369</v>
+        <v>0.0001572281704337838</v>
       </c>
       <c r="G59">
-        <v>2385.788160432044</v>
+        <v>3350.647370438513</v>
       </c>
       <c r="H59">
-        <v>2.149530039069977E-07</v>
+        <v>3.446869576726726E-07</v>
       </c>
       <c r="I59">
-        <v>23572.66480182248</v>
+        <v>32786.13321591269</v>
       </c>
       <c r="J59">
-        <v>23446.74751081617</v>
+        <v>32510.70246558731</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60">
-        <v>4.115836773313896E-06</v>
+        <v>8.91888102243909E-06</v>
       </c>
       <c r="B60">
-        <v>11013409078.10945</v>
+        <v>799319132.8989192</v>
       </c>
       <c r="C60">
-        <v>11660770189.6501</v>
+        <v>4.442446572507322E+72</v>
       </c>
       <c r="D60">
-        <v>1.05980198019802</v>
+        <v>13.6297835816456</v>
       </c>
       <c r="E60">
-        <v>75909.37589842694</v>
+        <v>15395.35461896805</v>
       </c>
       <c r="F60">
-        <v>0.0002415987045320358</v>
+        <v>1.980981955232348E-05</v>
       </c>
       <c r="G60">
-        <v>7717.713785243778</v>
+        <v>1637.362216637342</v>
       </c>
       <c r="H60">
-        <v>4.48326474268275E-07</v>
+        <v>1.398640049231899E-07</v>
       </c>
       <c r="I60">
-        <v>75768.5134590924</v>
+        <v>15286.6582248119</v>
       </c>
       <c r="J60">
-        <v>75206.66560969713</v>
+        <v>14994.66173124932</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61">
-        <v>7.0995107805064E-06</v>
+        <v>4.773691647634124E-06</v>
       </c>
       <c r="B61">
-        <v>4045647279.193727</v>
+        <v>7500018949.375866</v>
       </c>
       <c r="C61">
-        <v>4.752174181707361E+19</v>
+        <v>7958947329013696</v>
       </c>
       <c r="D61">
-        <v>2.993782875666521</v>
+        <v>2.176357917178469</v>
       </c>
       <c r="E61">
-        <v>52342.24180399289</v>
+        <v>63150.65792818904</v>
       </c>
       <c r="F61">
-        <v>0.0002611284383098288</v>
+        <v>0.0001578671671237138</v>
       </c>
       <c r="G61">
-        <v>5314.348119619081</v>
+        <v>6448.269512185451</v>
       </c>
       <c r="H61">
-        <v>4.441417867946318E-07</v>
+        <v>3.699881190056692E-07</v>
       </c>
       <c r="I61">
-        <v>52253.21520485978</v>
+        <v>63002.65379555955</v>
       </c>
       <c r="J61">
-        <v>51890.42999390327</v>
+        <v>62446.50642869055</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62">
-        <v>1.290009426043073E-06</v>
+        <v>1.248986039843773E-05</v>
       </c>
       <c r="B62">
-        <v>12452365081.71204</v>
+        <v>2379958879.839941</v>
       </c>
       <c r="C62">
-        <v>14131538654.25207</v>
+        <v>4.892686934962446E+25</v>
       </c>
       <c r="D62">
-        <v>1.05980198019802</v>
+        <v>4.356635198739006</v>
       </c>
       <c r="E62">
-        <v>26927.45510893351</v>
+        <v>56812.43180425037</v>
       </c>
       <c r="F62">
-        <v>4.921611066476909E-05</v>
+        <v>0.0001724393261949266</v>
       </c>
       <c r="G62">
-        <v>2761.938111763385</v>
+        <v>5852.794494592173</v>
       </c>
       <c r="H62">
-        <v>1.405170830632997E-07</v>
+        <v>5.785547689977004E-07</v>
       </c>
       <c r="I62">
-        <v>26850.57444130014</v>
+        <v>56621.81923295355</v>
       </c>
       <c r="J62">
-        <v>26576.63822992209</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63">
-        <v>3.925905143998859E-06</v>
-      </c>
-      <c r="B63">
-        <v>4865883774.106353</v>
-      </c>
-      <c r="C63">
-        <v>1.968753060204922E+24</v>
-      </c>
-      <c r="D63">
-        <v>3.732820066311383</v>
-      </c>
-      <c r="E63">
-        <v>35757.84394714692</v>
-      </c>
-      <c r="F63">
-        <v>9.921573274114907E-05</v>
-      </c>
-      <c r="G63">
-        <v>3642.929537896593</v>
-      </c>
-      <c r="H63">
-        <v>2.070052281752801E-07</v>
-      </c>
-      <c r="I63">
-        <v>35683.23823250036</v>
-      </c>
-      <c r="J63">
-        <v>35394.32281474775</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64">
-        <v>4.281174460324837E-06</v>
-      </c>
-      <c r="B64">
-        <v>3665379034.354751</v>
-      </c>
-      <c r="C64">
-        <v>2.932676931224388E+22</v>
-      </c>
-      <c r="D64">
-        <v>3.436625829111878</v>
-      </c>
-      <c r="E64">
-        <v>29060.98918782372</v>
-      </c>
-      <c r="F64">
-        <v>0.0001550716328960892</v>
-      </c>
-      <c r="G64">
-        <v>2946.77464328993</v>
-      </c>
-      <c r="H64">
-        <v>2.411652640762388E-07</v>
-      </c>
-      <c r="I64">
-        <v>29015.79393837088</v>
-      </c>
-      <c r="J64">
-        <v>28827.60460395981</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65">
-        <v>5.587181712687931E-06</v>
-      </c>
-      <c r="B65">
-        <v>3585245338.238588</v>
-      </c>
-      <c r="C65">
-        <v>976629106785.5354</v>
-      </c>
-      <c r="D65">
-        <v>1.51496191118768</v>
-      </c>
-      <c r="E65">
-        <v>34332.90865192036</v>
-      </c>
-      <c r="F65">
-        <v>0.0001542918777050769</v>
-      </c>
-      <c r="G65">
-        <v>3538.652977192488</v>
-      </c>
-      <c r="H65">
-        <v>5.26107416982505E-07</v>
-      </c>
-      <c r="I65">
-        <v>34215.83963858653</v>
-      </c>
-      <c r="J65">
-        <v>33819.10010314203</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66">
-        <v>2.271293026985056E-06</v>
-      </c>
-      <c r="B66">
-        <v>3542526090.478796</v>
-      </c>
-      <c r="C66">
-        <v>3.614566221309445E+19</v>
-      </c>
-      <c r="D66">
-        <v>2.809509635874326</v>
-      </c>
-      <c r="E66">
-        <v>14549.32681898673</v>
-      </c>
-      <c r="F66">
-        <v>0.0001407658825218667</v>
-      </c>
-      <c r="G66">
-        <v>1468.770869961694</v>
-      </c>
-      <c r="H66">
-        <v>1.48761732295613E-07</v>
-      </c>
-      <c r="I66">
-        <v>14533.95105447226</v>
-      </c>
-      <c r="J66">
-        <v>14464.01576633197</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67">
-        <v>7.410451666856672E-06</v>
-      </c>
-      <c r="B67">
-        <v>3436136626.625036</v>
-      </c>
-      <c r="C67">
-        <v>3.11185902538433E+17</v>
-      </c>
-      <c r="D67">
-        <v>2.592630922966478</v>
-      </c>
-      <c r="E67">
-        <v>45856.09222352558</v>
-      </c>
-      <c r="F67">
-        <v>9.11243555251421E-05</v>
-      </c>
-      <c r="G67">
-        <v>4818.035577521029</v>
-      </c>
-      <c r="H67">
-        <v>5.131924872597872E-07</v>
-      </c>
-      <c r="I67">
-        <v>45597.84071778283</v>
-      </c>
-      <c r="J67">
-        <v>44848.37482452484</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68">
-        <v>2.518534488721082E-06</v>
-      </c>
-      <c r="B68">
-        <v>4668221953.831958</v>
-      </c>
-      <c r="C68">
-        <v>1.313722191291522E+16</v>
-      </c>
-      <c r="D68">
-        <v>2.193505201632055</v>
-      </c>
-      <c r="E68">
-        <v>20778.87060442954</v>
-      </c>
-      <c r="F68">
-        <v>5.421484213330937E-05</v>
-      </c>
-      <c r="G68">
-        <v>2144.898506837287</v>
-      </c>
-      <c r="H68">
-        <v>1.942686585894397E-07</v>
-      </c>
-      <c r="I68">
-        <v>20704.41344176917</v>
-      </c>
-      <c r="J68">
-        <v>20455.69675242953</v>
+        <v>55972.82626806186</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -438,1954 +438,2274 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>2.256657051398123E-06</v>
+        <v>3.125905876819727E-06</v>
       </c>
       <c r="B2">
-        <v>12739914668.90881</v>
+        <v>3585738269.767113</v>
       </c>
       <c r="C2">
-        <v>13982339979.97377</v>
+        <v>4.684367762103285E+19</v>
       </c>
       <c r="D2">
-        <v>1.05980198019802</v>
+        <v>2.874081422229258</v>
       </c>
       <c r="E2">
-        <v>48122.00230910497</v>
+        <v>20417.55265851556</v>
       </c>
       <c r="F2">
-        <v>0.0001772340790388241</v>
+        <v>3.434188455235128E-05</v>
       </c>
       <c r="G2">
-        <v>4872.26789893256</v>
+        <v>2149.542395269187</v>
       </c>
       <c r="H2">
-        <v>2.45811278534102E-07</v>
+        <v>2.014395933733673E-07</v>
       </c>
       <c r="I2">
-        <v>48055.26045574713</v>
+        <v>20297.78918138486</v>
       </c>
       <c r="J2">
-        <v>47769.7571801262</v>
+        <v>19954.90195084461</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>4.557807256545888E-06</v>
+        <v>9.025810318358854E-06</v>
       </c>
       <c r="B3">
-        <v>6691813252.141661</v>
+        <v>1736387804.198377</v>
       </c>
       <c r="C3">
-        <v>96176312600.10886</v>
+        <v>1.738047979469205E+36</v>
       </c>
       <c r="D3">
-        <v>1.269942852270748</v>
+        <v>6.371759692908888</v>
       </c>
       <c r="E3">
-        <v>51634.41385152386</v>
+        <v>31559.39003718144</v>
       </c>
       <c r="F3">
-        <v>0.0001761879667623749</v>
+        <v>3.999843332588542E-05</v>
       </c>
       <c r="G3">
-        <v>5285.726845295714</v>
+        <v>3366.283172693485</v>
       </c>
       <c r="H3">
-        <v>4.636276248112839E-07</v>
+        <v>2.962117951208361E-07</v>
       </c>
       <c r="I3">
-        <v>51498.54111803127</v>
+        <v>31325.67429387551</v>
       </c>
       <c r="J3">
-        <v>51003.49932070971</v>
+        <v>30708.40872144009</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>5.476643209396849E-06</v>
+        <v>4.880526229568082E-06</v>
       </c>
       <c r="B4">
-        <v>6205211723.911633</v>
+        <v>3620837982.829711</v>
       </c>
       <c r="C4">
-        <v>2.445121126183082E+19</v>
+        <v>3.325977914268479E+31</v>
       </c>
       <c r="D4">
-        <v>2.861995782598798</v>
+        <v>5.158293446357678</v>
       </c>
       <c r="E4">
-        <v>61641.9057643331</v>
+        <v>34432.3110080461</v>
       </c>
       <c r="F4">
-        <v>0.0001681700204314984</v>
+        <v>0.0002072597976931175</v>
       </c>
       <c r="G4">
-        <v>6280.970229519343</v>
+        <v>3472.346703179666</v>
       </c>
       <c r="H4">
-        <v>3.539950515075426E-07</v>
+        <v>1.947296878781305E-07</v>
       </c>
       <c r="I4">
-        <v>61512.15059423751</v>
+        <v>34399.96033874047</v>
       </c>
       <c r="J4">
-        <v>61010.80212482233</v>
+        <v>34249.02170069712</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>1.687761179469438E-06</v>
+        <v>1.932983814653488E-06</v>
       </c>
       <c r="B5">
-        <v>4327936135.222946</v>
+        <v>9440599464.512983</v>
       </c>
       <c r="C5">
-        <v>2.837912287272015E+30</v>
+        <v>10457643611.39281</v>
       </c>
       <c r="D5">
-        <v>4.629972889203504</v>
+        <v>1.059801980198021</v>
       </c>
       <c r="E5">
-        <v>14031.12475423902</v>
+        <v>30622.03029617295</v>
       </c>
       <c r="F5">
-        <v>0.0001293322632996166</v>
+        <v>5.397945856868609E-05</v>
       </c>
       <c r="G5">
-        <v>1410.35247433375</v>
+        <v>3169.704010492514</v>
       </c>
       <c r="H5">
-        <v>7.414986813628295E-08</v>
+        <v>2.105544670916292E-07</v>
       </c>
       <c r="I5">
-        <v>14023.08031100585</v>
+        <v>30502.58476186715</v>
       </c>
       <c r="J5">
-        <v>13981.57928549693</v>
+        <v>30113.48171952345</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>1.720289257116658E-06</v>
+        <v>1.67732031907685E-06</v>
       </c>
       <c r="B6">
-        <v>12384974987.73924</v>
+        <v>3999518302.70004</v>
       </c>
       <c r="C6">
-        <v>13815193692.93708</v>
+        <v>7.354047380397434E+22</v>
       </c>
       <c r="D6">
-        <v>1.05980198019802</v>
+        <v>3.328235989767439</v>
       </c>
       <c r="E6">
-        <v>35663.52416295992</v>
+        <v>12393.43231886502</v>
       </c>
       <c r="F6">
-        <v>0.0001316091767157524</v>
+        <v>3.263848408337557E-05</v>
       </c>
       <c r="G6">
-        <v>3612.05263865097</v>
+        <v>1272.45038236353</v>
       </c>
       <c r="H6">
-        <v>1.873862497087615E-07</v>
+        <v>9.687632898251387E-08</v>
       </c>
       <c r="I6">
-        <v>35612.74613812105</v>
+        <v>12356.64659611277</v>
       </c>
       <c r="J6">
-        <v>35396.8567633597</v>
+        <v>12226.97820109314</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>7.047755418967829E-07</v>
+        <v>7.163423652715365E-06</v>
       </c>
       <c r="B7">
-        <v>12053807276.42321</v>
+        <v>2123230652.513561</v>
       </c>
       <c r="C7">
-        <v>14182813245.70691</v>
+        <v>2.71279610686719E+42</v>
       </c>
       <c r="D7">
-        <v>1.05980198019802</v>
+        <v>7.450353945863144</v>
       </c>
       <c r="E7">
-        <v>14241.68645228369</v>
+        <v>31228.11830008889</v>
       </c>
       <c r="F7">
-        <v>2.613660566984872E-05</v>
+        <v>2.360171257548903E-05</v>
       </c>
       <c r="G7">
-        <v>1461.816636594616</v>
+        <v>3364.020623753713</v>
       </c>
       <c r="H7">
-        <v>7.676920909443464E-08</v>
+        <v>2.025575001897338E-07</v>
       </c>
       <c r="I7">
-        <v>14199.85535076564</v>
+        <v>30960.1085292613</v>
       </c>
       <c r="J7">
-        <v>14051.97157109735</v>
+        <v>30289.44561528326</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>4.548326438588888E-06</v>
+        <v>2.611398815335429E-06</v>
       </c>
       <c r="B8">
-        <v>9336109608.606815</v>
+        <v>4696458270.103481</v>
       </c>
       <c r="C8">
-        <v>100475686408656.9</v>
+        <v>1.425609249716958E+19</v>
       </c>
       <c r="D8">
-        <v>1.802199452694152</v>
+        <v>2.735439491973959</v>
       </c>
       <c r="E8">
-        <v>73644.18404643344</v>
+        <v>22125.52231480951</v>
       </c>
       <c r="F8">
-        <v>0.0001961120645742109</v>
+        <v>0.0001045202846125255</v>
       </c>
       <c r="G8">
-        <v>7497.106737807756</v>
+        <v>2245.757210383206</v>
       </c>
       <c r="H8">
-        <v>3.926052349433208E-07</v>
+        <v>1.742881062389721E-07</v>
       </c>
       <c r="I8">
-        <v>73496.75256513966</v>
+        <v>22088.62789380701</v>
       </c>
       <c r="J8">
-        <v>72919.78419803274</v>
+        <v>21937.55723725141</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>1.149561290935854E-05</v>
+        <v>7.113609063764915E-06</v>
       </c>
       <c r="B9">
-        <v>1916434868.575949</v>
+        <v>927921179.2764771</v>
       </c>
       <c r="C9">
-        <v>1.511640347282036E+37</v>
+        <v>1.398433747424273E+56</v>
       </c>
       <c r="D9">
-        <v>6.666434784839965</v>
+        <v>10.17440868964644</v>
       </c>
       <c r="E9">
-        <v>44359.88433027342</v>
+        <v>13903.95159770834</v>
       </c>
       <c r="F9">
-        <v>0.000186476746570785</v>
+        <v>4.445689393600531E-05</v>
       </c>
       <c r="G9">
-        <v>4513.378973227116</v>
+        <v>1432.224747513411</v>
       </c>
       <c r="H9">
-        <v>3.614761492453601E-07</v>
+        <v>1.48607916133321E-07</v>
       </c>
       <c r="I9">
-        <v>44273.89484116257</v>
+        <v>13857.47427799436</v>
       </c>
       <c r="J9">
-        <v>43934.63137096525</v>
+        <v>13699.06039846917</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>8.276977835471247E-06</v>
+        <v>5.738221843573332E-06</v>
       </c>
       <c r="B10">
-        <v>3547079104.344962</v>
+        <v>1839009404.49493</v>
       </c>
       <c r="C10">
-        <v>1.128550760992706E+29</v>
+        <v>4.453075625802577E+43</v>
       </c>
       <c r="D10">
-        <v>4.86336976166053</v>
+        <v>7.57521923738531</v>
       </c>
       <c r="E10">
-        <v>56942.36679052481</v>
+        <v>21596.27754431618</v>
       </c>
       <c r="F10">
-        <v>8.948664049956977E-05</v>
+        <v>4.533773166713847E-05</v>
       </c>
       <c r="G10">
-        <v>5893.626488149792</v>
+        <v>2228.085770189134</v>
       </c>
       <c r="H10">
-        <v>3.481634183951338E-07</v>
+        <v>1.596844714717384E-07</v>
       </c>
       <c r="I10">
-        <v>56720.82255819446</v>
+        <v>21520.21308236338</v>
       </c>
       <c r="J10">
-        <v>55998.57253203546</v>
+        <v>21264.84649760725</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>2.966155101074069E-06</v>
+        <v>1.723300529607677E-05</v>
       </c>
       <c r="B11">
-        <v>5436668973.402788</v>
+        <v>1128869000.694602</v>
       </c>
       <c r="C11">
-        <v>3.468667284591158E+20</v>
+        <v>4.45431119552479E+61</v>
       </c>
       <c r="D11">
-        <v>2.990051126605531</v>
+        <v>12.04932051587419</v>
       </c>
       <c r="E11">
-        <v>29376.6478209759</v>
+        <v>41494.51513083652</v>
       </c>
       <c r="F11">
-        <v>0.0001259845112949367</v>
+        <v>0.000112115095284058</v>
       </c>
       <c r="G11">
-        <v>2976.642134895998</v>
+        <v>4251.048297344812</v>
       </c>
       <c r="H11">
-        <v>1.857311507275788E-07</v>
+        <v>3.050077318004378E-07</v>
       </c>
       <c r="I11">
-        <v>29333.33965119989</v>
+        <v>41381.62981499078</v>
       </c>
       <c r="J11">
-        <v>29150.70785023123</v>
+        <v>40974.03864842245</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>5.347609570394546E-06</v>
+        <v>1.291927699537181E-06</v>
       </c>
       <c r="B12">
-        <v>3363979902.58015</v>
+        <v>7148629885.84951</v>
       </c>
       <c r="C12">
-        <v>6.749741810889933E+19</v>
+        <v>3.454136241247261E+17</v>
       </c>
       <c r="D12">
-        <v>2.99136625103958</v>
+        <v>2.343160065056259</v>
       </c>
       <c r="E12">
-        <v>32867.34588325315</v>
+        <v>16414.96625343918</v>
       </c>
       <c r="F12">
-        <v>7.688350037801967E-05</v>
+        <v>3.348307941831501E-05</v>
       </c>
       <c r="G12">
-        <v>3415.525259281741</v>
+        <v>1683.690187243583</v>
       </c>
       <c r="H12">
-        <v>3.34742155949346E-07</v>
+        <v>9.562888201572964E-08</v>
       </c>
       <c r="I12">
-        <v>32724.24513774602</v>
+        <v>16368.0845179951</v>
       </c>
       <c r="J12">
-        <v>32273.38726966222</v>
+        <v>16201.05360369657</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
-        <v>3.231342566156886E-06</v>
+        <v>5.562264952358299E-06</v>
       </c>
       <c r="B13">
-        <v>8044486466.056783</v>
+        <v>6491851089.186145</v>
       </c>
       <c r="C13">
-        <v>41377268433325.18</v>
+        <v>2.523633934140503E+17</v>
       </c>
       <c r="D13">
-        <v>1.722910350945136</v>
+        <v>2.485928363362039</v>
       </c>
       <c r="E13">
-        <v>44879.72430810134</v>
+        <v>64602.96611353839</v>
       </c>
       <c r="F13">
-        <v>0.0002564720534762446</v>
+        <v>0.0001145926268263991</v>
       </c>
       <c r="G13">
-        <v>4532.950827984954</v>
+        <v>6661.322724728523</v>
       </c>
       <c r="H13">
-        <v>2.855954829723994E-07</v>
+        <v>3.961997374654607E-07</v>
       </c>
       <c r="I13">
-        <v>44829.74831124043</v>
+        <v>64379.6037653443</v>
       </c>
       <c r="J13">
-        <v>44605.04219568798</v>
+        <v>63625.67502522712</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
-        <v>2.055585025922593E-06</v>
+        <v>2.657504203154304E-06</v>
       </c>
       <c r="B14">
-        <v>12523014831.6289</v>
+        <v>11683517935.59754</v>
       </c>
       <c r="C14">
-        <v>13821208382.98229</v>
+        <v>12698152120.4957</v>
       </c>
       <c r="D14">
-        <v>1.059801980198019</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E14">
-        <v>43107.39933378094</v>
+        <v>51992.95520260166</v>
       </c>
       <c r="F14">
-        <v>0.0001218736609739122</v>
+        <v>0.0001596720943246829</v>
       </c>
       <c r="G14">
-        <v>4382.018041254272</v>
+        <v>5284.129178015415</v>
       </c>
       <c r="H14">
-        <v>2.239090707400734E-07</v>
+        <v>2.894744265560373E-07</v>
       </c>
       <c r="I14">
-        <v>43028.20143614073</v>
+        <v>51898.6955828736</v>
       </c>
       <c r="J14">
-        <v>42711.52639778993</v>
+        <v>51520.55199657666</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>1.223760293126235E-05</v>
+        <v>5.030889464025536E-06</v>
       </c>
       <c r="B15">
-        <v>3729801552.50725</v>
+        <v>3130940372.405571</v>
       </c>
       <c r="C15">
-        <v>1.312835601441439E+25</v>
+        <v>1.001640517690644E+24</v>
       </c>
       <c r="D15">
-        <v>4.195578444558869</v>
+        <v>3.768880940072552</v>
       </c>
       <c r="E15">
-        <v>86790.53669175172</v>
+        <v>29520.96964572794</v>
       </c>
       <c r="F15">
-        <v>0.0001921099929961272</v>
+        <v>0.0001232776486869791</v>
       </c>
       <c r="G15">
-        <v>8917.09476858892</v>
+        <v>3008.821504080608</v>
       </c>
       <c r="H15">
-        <v>5.854462387808991E-07</v>
+        <v>2.631977629346289E-07</v>
       </c>
       <c r="I15">
-        <v>86526.04658129202</v>
+        <v>29457.94237960814</v>
       </c>
       <c r="J15">
-        <v>85600.57401483582</v>
+        <v>29215.30007212284</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
-        <v>5.013124947875444E-06</v>
+        <v>3.401384014744212E-06</v>
       </c>
       <c r="B16">
-        <v>3040944677.919991</v>
+        <v>2397679373.38238</v>
       </c>
       <c r="C16">
-        <v>2.813520262394221E+27</v>
+        <v>1.69605840118633E+35</v>
       </c>
       <c r="D16">
-        <v>4.417143481600988</v>
+        <v>5.747268212042216</v>
       </c>
       <c r="E16">
-        <v>29158.74177812421</v>
+        <v>16152.67420840217</v>
       </c>
       <c r="F16">
-        <v>9.717783465276577E-05</v>
+        <v>3.43366488338997E-05</v>
       </c>
       <c r="G16">
-        <v>2977.842195327531</v>
+        <v>1667.311049793521</v>
       </c>
       <c r="H16">
-        <v>2.294687399090306E-07</v>
+        <v>1.229245241276676E-07</v>
       </c>
       <c r="I16">
-        <v>29089.88842532964</v>
+        <v>16094.84795400961</v>
       </c>
       <c r="J16">
-        <v>28831.67196306168</v>
+        <v>15901.63256245734</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17">
-        <v>8.422106766323365E-06</v>
+        <v>9.392059833728612E-06</v>
       </c>
       <c r="B17">
-        <v>3839252208.245855</v>
+        <v>2209544380.622752</v>
       </c>
       <c r="C17">
-        <v>3.517872019592862E+27</v>
+        <v>2.920809379581833E+29</v>
       </c>
       <c r="D17">
-        <v>4.56715949517684</v>
+        <v>5.027725173159621</v>
       </c>
       <c r="E17">
-        <v>62029.96354575368</v>
+        <v>40410.609503396</v>
       </c>
       <c r="F17">
-        <v>0.0003651349280358248</v>
+        <v>0.0001057965474550605</v>
       </c>
       <c r="G17">
-        <v>6260.250748530278</v>
+        <v>4172.895134030478</v>
       </c>
       <c r="H17">
-        <v>3.744709782437233E-07</v>
+        <v>3.834966895644663E-07</v>
       </c>
       <c r="I17">
-        <v>61966.34755247044</v>
+        <v>40264.12707707279</v>
       </c>
       <c r="J17">
-        <v>61675.0931987181</v>
+        <v>39776.4648509796</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18">
-        <v>2.867106044473968E-06</v>
+        <v>1.190905625664123E-05</v>
       </c>
       <c r="B18">
-        <v>7287278531.664982</v>
+        <v>1865308500.105677</v>
       </c>
       <c r="C18">
-        <v>500068137515.005</v>
+        <v>3.083789417955132E+44</v>
       </c>
       <c r="D18">
-        <v>1.381427665720483</v>
+        <v>8.166510259562871</v>
       </c>
       <c r="E18">
-        <v>35556.55932942725</v>
+        <v>45806.43776613366</v>
       </c>
       <c r="F18">
-        <v>0.0001095185161279965</v>
+        <v>0.0001027129903190374</v>
       </c>
       <c r="G18">
-        <v>3637.903825075897</v>
+        <v>4704.348976934458</v>
       </c>
       <c r="H18">
-        <v>2.814816503608489E-07</v>
+        <v>3.082082796567797E-07</v>
       </c>
       <c r="I18">
-        <v>35465.17278261262</v>
+        <v>45668.98754355468</v>
       </c>
       <c r="J18">
-        <v>35130.09176210016</v>
+        <v>45185.9467649938</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19">
-        <v>4.813585975518217E-06</v>
+        <v>3.258346482657611E-06</v>
       </c>
       <c r="B19">
-        <v>3994948588.039815</v>
+        <v>5629825870.184869</v>
       </c>
       <c r="C19">
-        <v>1.274148169331852E+20</v>
+        <v>2941682378452.053</v>
       </c>
       <c r="D19">
-        <v>3.011942299401699</v>
+        <v>1.544230366678171</v>
       </c>
       <c r="E19">
-        <v>35108.29722630692</v>
+        <v>31489.8818512203</v>
       </c>
       <c r="F19">
-        <v>0.0001057458625763856</v>
+        <v>8.420118503182126E-05</v>
       </c>
       <c r="G19">
-        <v>3600.411369907396</v>
+        <v>3251.329141578664</v>
       </c>
       <c r="H19">
-        <v>2.997989810793051E-07</v>
+        <v>3.040563897689138E-07</v>
       </c>
       <c r="I19">
-        <v>35008.76206266614</v>
+        <v>31376.1696773796</v>
       </c>
       <c r="J19">
-        <v>34653.41631549998</v>
+        <v>30997.18329079703</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20">
-        <v>2.545121055739353E-06</v>
+        <v>4.930487709592349E-06</v>
       </c>
       <c r="B20">
-        <v>5034318572.381765</v>
+        <v>3658365295.642342</v>
       </c>
       <c r="C20">
-        <v>77438393316615.92</v>
+        <v>4.092508719983794E+21</v>
       </c>
       <c r="D20">
-        <v>1.793853458576999</v>
+        <v>3.304751009079162</v>
       </c>
       <c r="E20">
-        <v>22253.21033463352</v>
+        <v>33241.62951883718</v>
       </c>
       <c r="F20">
-        <v>5.782991572568478E-05</v>
+        <v>0.0002088250851206324</v>
       </c>
       <c r="G20">
-        <v>2301.593895410465</v>
+        <v>3365.184254093086</v>
       </c>
       <c r="H20">
-        <v>2.202355481513791E-07</v>
+        <v>2.863302915860143E-07</v>
       </c>
       <c r="I20">
-        <v>22168.46271024783</v>
+        <v>33196.05029416009</v>
       </c>
       <c r="J20">
-        <v>21890.4114522885</v>
+        <v>33000.55595743053</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21">
-        <v>1.529292552451663E-05</v>
+        <v>1.874859518858083E-06</v>
       </c>
       <c r="B21">
-        <v>2174334705.572186</v>
+        <v>20677498112.28812</v>
       </c>
       <c r="C21">
-        <v>1.299468304307375E+38</v>
+        <v>22946962103.18439</v>
       </c>
       <c r="D21">
-        <v>6.993803421100753</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E21">
-        <v>67401.61037596426</v>
+        <v>64856.83484941199</v>
       </c>
       <c r="F21">
-        <v>0.0001548093083130597</v>
+        <v>0.0002333968932519055</v>
       </c>
       <c r="G21">
-        <v>6920.189012536044</v>
+        <v>6536.75845999963</v>
       </c>
       <c r="H21">
-        <v>4.594352192600095E-07</v>
+        <v>2.042231517264919E-07</v>
       </c>
       <c r="I21">
-        <v>67201.57929269802</v>
+        <v>64800.08487712484</v>
       </c>
       <c r="J21">
-        <v>66496.4441432231</v>
+        <v>64530.51026884199</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22">
-        <v>4.083108115074745E-06</v>
+        <v>2.528612014777631E-06</v>
       </c>
       <c r="B22">
-        <v>6596352812.456501</v>
+        <v>4983679792.910171</v>
       </c>
       <c r="C22">
-        <v>6987417464.798065</v>
+        <v>5921733245608.685</v>
       </c>
       <c r="D22">
-        <v>1.05980198019802</v>
+        <v>1.596731923860861</v>
       </c>
       <c r="E22">
-        <v>45160.49229492153</v>
+        <v>21655.67758105847</v>
       </c>
       <c r="F22">
-        <v>0.0001427679164939651</v>
+        <v>0.0001036679221650369</v>
       </c>
       <c r="G22">
-        <v>4642.667879008392</v>
+        <v>2209.22052472181</v>
       </c>
       <c r="H22">
-        <v>4.447614339705094E-07</v>
+        <v>2.321891283805348E-07</v>
       </c>
       <c r="I22">
-        <v>45019.80490657015</v>
+        <v>21607.17450704073</v>
       </c>
       <c r="J22">
-        <v>44530.56857068635</v>
+        <v>21422.74414674548</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23">
-        <v>1.118994713034372E-05</v>
+        <v>7.677196455236789E-06</v>
       </c>
       <c r="B23">
-        <v>2393243786.059372</v>
+        <v>1950776622.693986</v>
       </c>
       <c r="C23">
-        <v>5.004529163250754E+34</v>
+        <v>1.531365834706269E+34</v>
       </c>
       <c r="D23">
-        <v>6.134625701618906</v>
+        <v>5.888153906338607</v>
       </c>
       <c r="E23">
-        <v>53321.46476379972</v>
+        <v>29764.69581476254</v>
       </c>
       <c r="F23">
-        <v>0.0005025871254236334</v>
+        <v>6.797875609379335E-05</v>
       </c>
       <c r="G23">
-        <v>5368.48414459152</v>
+        <v>3083.373923316396</v>
       </c>
       <c r="H23">
-        <v>3.805606093768337E-07</v>
+        <v>2.712842618257568E-07</v>
       </c>
       <c r="I23">
-        <v>53281.089576898</v>
+        <v>29645.91321271794</v>
       </c>
       <c r="J23">
-        <v>53084.01674768933</v>
+        <v>29261.6096842647</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24">
-        <v>1.261227564387091E-06</v>
+        <v>2.838459967007613E-06</v>
       </c>
       <c r="B24">
-        <v>7879665829.836873</v>
+        <v>6639059663.571969</v>
       </c>
       <c r="C24">
-        <v>8954295676.219631</v>
+        <v>110539764734.896</v>
       </c>
       <c r="D24">
-        <v>1.05980198019802</v>
+        <v>1.271435086193121</v>
       </c>
       <c r="E24">
-        <v>16626.39548250992</v>
+        <v>31999.94480479433</v>
       </c>
       <c r="F24">
-        <v>0.0001538423887521537</v>
+        <v>5.164150182254318E-05</v>
       </c>
       <c r="G24">
-        <v>1676.002250680173</v>
+        <v>3360.940825348054</v>
       </c>
       <c r="H24">
-        <v>1.373819561693548E-07</v>
+        <v>2.88594628402794E-07</v>
       </c>
       <c r="I24">
-        <v>16611.54803536639</v>
+        <v>31821.11553271807</v>
       </c>
       <c r="J24">
-        <v>16541.36946149052</v>
+        <v>31300.8125125794</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25">
-        <v>2.535256192775147E-06</v>
+        <v>1.930045769663619E-06</v>
       </c>
       <c r="B25">
-        <v>8938681292.631721</v>
+        <v>13168986382.60005</v>
       </c>
       <c r="C25">
-        <v>165387205558.6402</v>
+        <v>14589019991.50941</v>
       </c>
       <c r="D25">
-        <v>1.277180636531821</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E25">
-        <v>38452.23533620412</v>
+        <v>42652.09127008013</v>
       </c>
       <c r="F25">
-        <v>5.652638487024421E-05</v>
+        <v>5.345170544489423E-05</v>
       </c>
       <c r="G25">
-        <v>4002.745176361067</v>
+        <v>4416.191109321664</v>
       </c>
       <c r="H25">
-        <v>2.572926276832331E-07</v>
+        <v>2.102344341495823E-07</v>
       </c>
       <c r="I25">
-        <v>38277.2112887145</v>
+        <v>42484.33351195386</v>
       </c>
       <c r="J25">
-        <v>37733.31995799686</v>
+        <v>41939.20713905706</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26">
-        <v>3.089738199157271E-06</v>
+        <v>1.482157899227998E-06</v>
       </c>
       <c r="B26">
-        <v>8226675752.56635</v>
+        <v>9988939475.226763</v>
       </c>
       <c r="C26">
-        <v>10858497954.87824</v>
+        <v>11242187726.78588</v>
       </c>
       <c r="D26">
-        <v>1.075645645462612</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E26">
-        <v>42619.2724403217</v>
+        <v>24786.54165812975</v>
       </c>
       <c r="F26">
-        <v>0.0001429846928248074</v>
+        <v>0.0001012243718780559</v>
       </c>
       <c r="G26">
-        <v>4351.741423985009</v>
+        <v>2514.23401231253</v>
       </c>
       <c r="H26">
-        <v>3.348003587357461E-07</v>
+        <v>1.614472735114668E-07</v>
       </c>
       <c r="I26">
-        <v>42519.47890704076</v>
+        <v>24747.00849535246</v>
       </c>
       <c r="J26">
-        <v>42144.39968365587</v>
+        <v>24583.38703278324</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27">
-        <v>6.621299872177863E-06</v>
+        <v>3.348514127357652E-06</v>
       </c>
       <c r="B27">
-        <v>4793285330.054667</v>
+        <v>3985811775.356389</v>
       </c>
       <c r="C27">
-        <v>5.824277880127428E+20</v>
+        <v>4.330694760945495E+22</v>
       </c>
       <c r="D27">
-        <v>3.176578312171774</v>
+        <v>3.413570354963249</v>
       </c>
       <c r="E27">
-        <v>58198.94281094823</v>
+        <v>24691.18871465695</v>
       </c>
       <c r="F27">
-        <v>0.0003726535151885322</v>
+        <v>0.0001435446878391306</v>
       </c>
       <c r="G27">
-        <v>5875.599739975746</v>
+        <v>2498.474642273441</v>
       </c>
       <c r="H27">
-        <v>3.963194378251115E-07</v>
+        <v>1.896252233302256E-07</v>
       </c>
       <c r="I27">
-        <v>58137.04785663611</v>
+        <v>24658.57119153723</v>
       </c>
       <c r="J27">
-        <v>57855.91430677369</v>
+        <v>24517.46244983396</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28">
-        <v>1.689591565022163E-06</v>
+        <v>5.239056992427492E-06</v>
       </c>
       <c r="B28">
-        <v>8657003466.133289</v>
+        <v>2928469917.595381</v>
       </c>
       <c r="C28">
-        <v>9667119162.717632</v>
+        <v>3.26929138301649E+27</v>
       </c>
       <c r="D28">
-        <v>1.05980198019802</v>
+        <v>4.444821013272588</v>
       </c>
       <c r="E28">
-        <v>24497.07697918463</v>
+        <v>29348.19536014658</v>
       </c>
       <c r="F28">
-        <v>9.345678563315304E-05</v>
+        <v>0.0001451373455419562</v>
       </c>
       <c r="G28">
-        <v>2493.125107798638</v>
+        <v>2978.226870527252</v>
       </c>
       <c r="H28">
-        <v>1.840424368165372E-07</v>
+        <v>2.38516475521985E-07</v>
       </c>
       <c r="I28">
-        <v>24448.8354126511</v>
+        <v>29299.96498846592</v>
       </c>
       <c r="J28">
-        <v>24259.25779157913</v>
+        <v>29101.77990636559</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29">
-        <v>1.112164799357215E-05</v>
+        <v>3.358710908877152E-06</v>
       </c>
       <c r="B29">
-        <v>3174354219.682825</v>
+        <v>2370749409.444085</v>
       </c>
       <c r="C29">
-        <v>2.708831933261094E+27</v>
+        <v>3.665353644836144E+39</v>
       </c>
       <c r="D29">
-        <v>4.647402463992828</v>
+        <v>6.532473108159005</v>
       </c>
       <c r="E29">
-        <v>67944.10807022532</v>
+        <v>16000.96182640079</v>
       </c>
       <c r="F29">
-        <v>0.0002445519150348527</v>
+        <v>4.601326365841182E-05</v>
       </c>
       <c r="G29">
-        <v>6916.185817857103</v>
+        <v>1633.792163756596</v>
       </c>
       <c r="H29">
-        <v>4.870066972662589E-07</v>
+        <v>1.076645044608752E-07</v>
       </c>
       <c r="I29">
-        <v>67808.80250263136</v>
+        <v>15963.52184738244</v>
       </c>
       <c r="J29">
-        <v>67278.58115120162</v>
+        <v>15822.77561289264</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30">
-        <v>1.079867318115197E-06</v>
+        <v>1.536063066707136E-06</v>
       </c>
       <c r="B30">
-        <v>6329454802.557953</v>
+        <v>8013584961.89557</v>
       </c>
       <c r="C30">
-        <v>7259755031.77724</v>
+        <v>8999751023.10899</v>
       </c>
       <c r="D30">
         <v>1.05980198019802</v>
       </c>
       <c r="E30">
-        <v>11435.45926399586</v>
+        <v>20608.17879815602</v>
       </c>
       <c r="F30">
-        <v>0.0001252487141836088</v>
+        <v>0.0001046585343218686</v>
       </c>
       <c r="G30">
-        <v>1153.211541220438</v>
+        <v>2090.469796005127</v>
       </c>
       <c r="H30">
-        <v>1.176268968067751E-07</v>
+        <v>1.673190111463158E-07</v>
       </c>
       <c r="I30">
-        <v>11424.71969197269</v>
+        <v>20575.2322246121</v>
       </c>
       <c r="J30">
-        <v>11374.56255503677</v>
+        <v>20438.94877787422</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31">
-        <v>1.457021844473067E-05</v>
+        <v>3.399323259311847E-06</v>
       </c>
       <c r="B31">
-        <v>814011400.1225661</v>
+        <v>4277511681.072515</v>
       </c>
       <c r="C31">
-        <v>1.00929658133223E+69</v>
+        <v>4.540312640206407E+16</v>
       </c>
       <c r="D31">
-        <v>13.43158264489157</v>
+        <v>2.326144804571572</v>
       </c>
       <c r="E31">
-        <v>25658.33362943157</v>
+        <v>25810.44276066786</v>
       </c>
       <c r="F31">
-        <v>2.389134918881087E-05</v>
+        <v>0.0001113176219882092</v>
       </c>
       <c r="G31">
-        <v>2789.880653770735</v>
+        <v>2633.795396609</v>
       </c>
       <c r="H31">
-        <v>2.317978563688338E-07</v>
+        <v>2.52788693597268E-07</v>
       </c>
       <c r="I31">
-        <v>25409.3921951787</v>
+        <v>25751.83040450984</v>
       </c>
       <c r="J31">
-        <v>24814.86642149592</v>
+        <v>25529.75936056797</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32">
-        <v>3.595975379880317E-06</v>
+        <v>5.236870791036558E-06</v>
       </c>
       <c r="B32">
-        <v>7834518070.962525</v>
+        <v>3533248195.844752</v>
       </c>
       <c r="C32">
-        <v>34860234846.12953</v>
+        <v>3.33772344453066E+33</v>
       </c>
       <c r="D32">
-        <v>1.172400631717902</v>
+        <v>5.561592956245582</v>
       </c>
       <c r="E32">
-        <v>47493.06067371411</v>
+        <v>36458.29467671689</v>
       </c>
       <c r="F32">
-        <v>0.0001231287995282132</v>
+        <v>7.668621013167233E-05</v>
       </c>
       <c r="G32">
-        <v>4880.353625719172</v>
+        <v>3729.301000897457</v>
       </c>
       <c r="H32">
-        <v>3.77499091716874E-07</v>
+        <v>1.950818232090533E-07</v>
       </c>
       <c r="I32">
-        <v>47347.45227554992</v>
+        <v>36365.54852868825</v>
       </c>
       <c r="J32">
-        <v>46838.81951490916</v>
+        <v>36024.54291389888</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33">
-        <v>1.066455475502229E-05</v>
+        <v>6.755077996601752E-06</v>
       </c>
       <c r="B33">
-        <v>1697188333.492436</v>
+        <v>1321172215.54009</v>
       </c>
       <c r="C33">
-        <v>1.402474827151607E+39</v>
+        <v>8.584097893477478E+40</v>
       </c>
       <c r="D33">
-        <v>7.03438298228171</v>
+        <v>7.169147170896989</v>
       </c>
       <c r="E33">
-        <v>36716.96510087697</v>
+        <v>18118.55585736552</v>
       </c>
       <c r="F33">
-        <v>0.0001033426693361046</v>
+        <v>0.0001172350425068447</v>
       </c>
       <c r="G33">
-        <v>3773.580739906075</v>
+        <v>1839.42282649374</v>
       </c>
       <c r="H33">
-        <v>3.186231712342348E-07</v>
+        <v>1.981913316692374E-07</v>
       </c>
       <c r="I33">
-        <v>36603.76040107877</v>
+        <v>18087.92558985754</v>
       </c>
       <c r="J33">
-        <v>36208.94307241785</v>
+        <v>17962.92186028983</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34">
-        <v>9.514400648185241E-06</v>
+        <v>8.007295167537754E-06</v>
       </c>
       <c r="B34">
-        <v>1489776711.982428</v>
+        <v>1690106308.164036</v>
       </c>
       <c r="C34">
-        <v>1.370866707336935E+37</v>
+        <v>1.518661211251211E+45</v>
       </c>
       <c r="D34">
-        <v>6.587336563576383</v>
+        <v>8.06859342864421</v>
       </c>
       <c r="E34">
-        <v>28553.20444185337</v>
+        <v>27839.86855258906</v>
       </c>
       <c r="F34">
-        <v>7.991210012573975E-05</v>
+        <v>0.0001105898838553321</v>
       </c>
       <c r="G34">
-        <v>2952.623798793722</v>
+        <v>2831.489540831835</v>
       </c>
       <c r="H34">
-        <v>3.025819330782764E-07</v>
+        <v>2.096640039965694E-07</v>
       </c>
       <c r="I34">
-        <v>28445.0896033996</v>
+        <v>27787.08779084136</v>
       </c>
       <c r="J34">
-        <v>28089.76383570423</v>
+        <v>27577.68495868921</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35">
-        <v>5.005210331038592E-06</v>
+        <v>1.19277021204424E-05</v>
       </c>
       <c r="B35">
-        <v>8677297028.639235</v>
+        <v>1567569974.132424</v>
       </c>
       <c r="C35">
-        <v>135625580525344</v>
+        <v>1.395302942004507E+69</v>
       </c>
       <c r="D35">
-        <v>1.83868865126091</v>
+        <v>13.18311321414294</v>
       </c>
       <c r="E35">
-        <v>75451.95486657722</v>
+        <v>40057.3533578916</v>
       </c>
       <c r="F35">
-        <v>0.0002070775466902857</v>
+        <v>0.0001673565261908377</v>
       </c>
       <c r="G35">
-        <v>7685.355808959755</v>
+        <v>4047.369104884672</v>
       </c>
       <c r="H35">
-        <v>4.274104073092795E-07</v>
+        <v>1.932696325525397E-07</v>
       </c>
       <c r="I35">
-        <v>75296.22117513051</v>
+        <v>40011.09361445215</v>
       </c>
       <c r="J35">
-        <v>74691.46874899733</v>
+        <v>39804.77450225805</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36">
-        <v>1.340306122261276E-06</v>
+        <v>3.460541236293204E-06</v>
       </c>
       <c r="B36">
-        <v>7576929581.159606</v>
+        <v>9127523094.255844</v>
       </c>
       <c r="C36">
-        <v>3.405330252856403E+17</v>
+        <v>9764777214.2619</v>
       </c>
       <c r="D36">
-        <v>2.341470412877318</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E36">
-        <v>18042.00085192996</v>
+        <v>52963.08821952067</v>
       </c>
       <c r="F36">
-        <v>3.990373665411905E-05</v>
+        <v>0.0001199023401650377</v>
       </c>
       <c r="G36">
-        <v>1844.589568293328</v>
+        <v>5446.162850049521</v>
       </c>
       <c r="H36">
-        <v>9.925551621086516E-08</v>
+        <v>3.769469823454992E-07</v>
       </c>
       <c r="I36">
-        <v>17997.12364848515</v>
+        <v>52796.58374385683</v>
       </c>
       <c r="J36">
-        <v>17831.12655453113</v>
+        <v>52219.0572010306</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37">
-        <v>6.281194944218136E-06</v>
+        <v>7.537725686731271E-06</v>
       </c>
       <c r="B37">
-        <v>2879315365.73531</v>
+        <v>2814568213.045622</v>
       </c>
       <c r="C37">
-        <v>2.305842773436286E+23</v>
+        <v>5.033204891103693E+33</v>
       </c>
       <c r="D37">
-        <v>3.705000423382406</v>
+        <v>5.755697966541194</v>
       </c>
       <c r="E37">
-        <v>33783.88748011192</v>
+        <v>41983.72515429464</v>
       </c>
       <c r="F37">
-        <v>0.0003454484643764831</v>
+        <v>0.0001066744584712131</v>
       </c>
       <c r="G37">
-        <v>3407.717399632996</v>
+        <v>4294.732514095485</v>
       </c>
       <c r="H37">
-        <v>3.332139937664935E-07</v>
+        <v>2.720406178083908E-07</v>
       </c>
       <c r="I37">
-        <v>33751.30008942101</v>
+        <v>41876.65848911016</v>
       </c>
       <c r="J37">
-        <v>33600.11246515236</v>
+        <v>41483.26049399843</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38">
-        <v>4.039361170875552E-06</v>
+        <v>1.670691605493371E-05</v>
       </c>
       <c r="B38">
-        <v>6378029583.016113</v>
+        <v>2208954570.101778</v>
       </c>
       <c r="C38">
-        <v>6760504547.952612</v>
+        <v>6.467045502784181E+30</v>
       </c>
       <c r="D38">
-        <v>1.05980198019802</v>
+        <v>5.517735089012294</v>
       </c>
       <c r="E38">
-        <v>43219.79547995302</v>
+        <v>72652.50279114158</v>
       </c>
       <c r="F38">
-        <v>0.0001215736169578968</v>
+        <v>0.0002353463953871518</v>
       </c>
       <c r="G38">
-        <v>4462.757553450922</v>
+        <v>7439.425587333164</v>
       </c>
       <c r="H38">
-        <v>4.399962029049819E-07</v>
+        <v>6.269040123263959E-07</v>
       </c>
       <c r="I38">
-        <v>43063.37547389122</v>
+        <v>72458.97467089824</v>
       </c>
       <c r="J38">
-        <v>42542.39248680077</v>
+        <v>71756.19643137106</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39">
-        <v>3.251851039539453E-06</v>
+        <v>6.159082885367908E-06</v>
       </c>
       <c r="B39">
-        <v>4264309629.9893</v>
+        <v>2590250836.711864</v>
       </c>
       <c r="C39">
-        <v>7.032699831943823E+28</v>
+        <v>1.052628626255437E+33</v>
       </c>
       <c r="D39">
-        <v>4.527459075142948</v>
+        <v>5.552993062422088</v>
       </c>
       <c r="E39">
-        <v>26608.56585692962</v>
+        <v>31401.37337064375</v>
       </c>
       <c r="F39">
-        <v>6.084990246691341E-05</v>
+        <v>0.000136505937048144</v>
       </c>
       <c r="G39">
-        <v>2718.194674267294</v>
+        <v>3187.7057484724</v>
       </c>
       <c r="H39">
-        <v>1.456931457564475E-07</v>
+        <v>2.297624408723256E-07</v>
       </c>
       <c r="I39">
-        <v>26544.8568696248</v>
+        <v>31348.51958019039</v>
       </c>
       <c r="J39">
-        <v>26306.80468839733</v>
+        <v>31132.59075792115</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40">
-        <v>2.587242339057462E-06</v>
+        <v>5.080670815910529E-06</v>
       </c>
       <c r="B40">
-        <v>6580839104.561071</v>
+        <v>4118753640.868618</v>
       </c>
       <c r="C40">
-        <v>154370700381759.8</v>
+        <v>3.504571729343002E+28</v>
       </c>
       <c r="D40">
-        <v>1.827339430479564</v>
+        <v>4.601884925509854</v>
       </c>
       <c r="E40">
-        <v>29588.65739321859</v>
+        <v>40168.71891279676</v>
       </c>
       <c r="F40">
-        <v>7.634701567044287E-05</v>
+        <v>0.000336760973759995</v>
       </c>
       <c r="G40">
-        <v>3036.185215856094</v>
+        <v>4040.96248107454</v>
       </c>
       <c r="H40">
-        <v>2.216732058332069E-07</v>
+        <v>2.244081878567064E-07</v>
       </c>
       <c r="I40">
-        <v>29502.74686373611</v>
+        <v>40141.95159080246</v>
       </c>
       <c r="J40">
-        <v>29198.0555939713</v>
+        <v>40007.88239847241</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41">
-        <v>2.163503825855844E-05</v>
+        <v>4.657815757539411E-06</v>
       </c>
       <c r="B41">
-        <v>1834131556.701378</v>
+        <v>8664449001.25732</v>
       </c>
       <c r="C41">
-        <v>1.994154050607122E+39</v>
+        <v>9106124926.23867</v>
       </c>
       <c r="D41">
-        <v>7.455978263250617</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E41">
-        <v>80900.45908402608</v>
+        <v>67615.15238531286</v>
       </c>
       <c r="F41">
-        <v>0.0004140822395076191</v>
+        <v>0.0002180024430635659</v>
       </c>
       <c r="G41">
-        <v>8197.538192601272</v>
+        <v>6903.141479392283</v>
       </c>
       <c r="H41">
-        <v>6.113225269496849E-07</v>
+        <v>5.073627141650497E-07</v>
       </c>
       <c r="I41">
-        <v>80781.02321269424</v>
+        <v>67457.78989546731</v>
       </c>
       <c r="J41">
-        <v>80277.52525211504</v>
+        <v>66865.39032466547</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42">
-        <v>2.879327573809873E-06</v>
+        <v>1.367571283178688E-05</v>
       </c>
       <c r="B42">
-        <v>5573316534.523101</v>
+        <v>1451895839.864731</v>
       </c>
       <c r="C42">
-        <v>7.512395160283909E+17</v>
+        <v>1.132854718025448E+43</v>
       </c>
       <c r="D42">
-        <v>2.506523285113672</v>
+        <v>7.982853791392714</v>
       </c>
       <c r="E42">
-        <v>28684.61335520455</v>
+        <v>40815.05367992478</v>
       </c>
       <c r="F42">
-        <v>0.0001187198767047446</v>
+        <v>0.0001599914854168276</v>
       </c>
       <c r="G42">
-        <v>2912.816629711484</v>
+        <v>4164.574840654676</v>
       </c>
       <c r="H42">
-        <v>2.039752110828361E-07</v>
+        <v>3.61805731674999E-07</v>
       </c>
       <c r="I42">
-        <v>28635.32969499229</v>
+        <v>40722.75426585567</v>
       </c>
       <c r="J42">
-        <v>28434.99177086788</v>
+        <v>40372.66584419538</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43">
-        <v>1.132193416834811E-05</v>
+        <v>9.319607306149234E-06</v>
       </c>
       <c r="B43">
-        <v>1246816174.444117</v>
+        <v>1774881506.72405</v>
       </c>
       <c r="C43">
-        <v>3.175289487192117E+46</v>
+        <v>7.829779167254874E+41</v>
       </c>
       <c r="D43">
-        <v>8.576039784826879</v>
+        <v>7.504922188112621</v>
       </c>
       <c r="E43">
-        <v>29399.97597385011</v>
+        <v>33769.98387266738</v>
       </c>
       <c r="F43">
-        <v>3.530162321043115E-05</v>
+        <v>0.0001227783018980768</v>
       </c>
       <c r="G43">
-        <v>3149.442188746661</v>
+        <v>3441.776794850503</v>
       </c>
       <c r="H43">
-        <v>2.794308424034118E-07</v>
+        <v>2.61684818249149E-07</v>
       </c>
       <c r="I43">
-        <v>29167.25976122605</v>
+        <v>33698.00786424097</v>
       </c>
       <c r="J43">
-        <v>28567.2472617468</v>
+        <v>33420.79225887959</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44">
-        <v>2.30337405454675E-06</v>
+        <v>3.59556818536054E-06</v>
       </c>
       <c r="B44">
-        <v>4240843992.712803</v>
+        <v>4839381622.238189</v>
       </c>
       <c r="C44">
-        <v>3.757692130599512E+23</v>
+        <v>5.68771477773354E+18</v>
       </c>
       <c r="D44">
-        <v>3.505056008095895</v>
+        <v>2.704281942788766</v>
       </c>
       <c r="E44">
-        <v>18143.6944262822</v>
+        <v>31345.49913844977</v>
       </c>
       <c r="F44">
-        <v>6.066639753646911E-05</v>
+        <v>0.0001662174383565121</v>
       </c>
       <c r="G44">
-        <v>1848.755514942666</v>
+        <v>3175.605452255892</v>
       </c>
       <c r="H44">
-        <v>1.277504817152049E-07</v>
+        <v>2.418970865063219E-07</v>
       </c>
       <c r="I44">
-        <v>18105.48767926615</v>
+        <v>31299.88187354876</v>
       </c>
       <c r="J44">
-        <v>17957.87885763014</v>
+        <v>31106.92652055038</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45">
-        <v>3.969490723617418E-06</v>
+        <v>5.573348093228181E-06</v>
       </c>
       <c r="B45">
-        <v>9289491965.096697</v>
+        <v>3757703315.061712</v>
       </c>
       <c r="C45">
-        <v>9856840217.376663</v>
+        <v>1.741973382576292E+27</v>
       </c>
       <c r="D45">
-        <v>1.05980198019802</v>
+        <v>4.390099069867869</v>
       </c>
       <c r="E45">
-        <v>61714.08795176133</v>
+        <v>40036.91928659791</v>
       </c>
       <c r="F45">
-        <v>0.0003424433665662793</v>
+        <v>9.790496086290838E-05</v>
       </c>
       <c r="G45">
-        <v>6241.539644769992</v>
+        <v>4098.083950051844</v>
       </c>
       <c r="H45">
-        <v>4.323854124387786E-07</v>
+        <v>2.564701481873757E-07</v>
       </c>
       <c r="I45">
-        <v>61636.16478554592</v>
+        <v>39932.03926282896</v>
       </c>
       <c r="J45">
-        <v>61295.55199014665</v>
+        <v>39549.44939498423</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46">
-        <v>3.494914429127888E-06</v>
+        <v>1.115475797158113E-05</v>
       </c>
       <c r="B46">
-        <v>5460421458.527568</v>
+        <v>950101539.0909799</v>
       </c>
       <c r="C46">
-        <v>1.409514600805649E+21</v>
+        <v>3.174486884708316E+36</v>
       </c>
       <c r="D46">
-        <v>3.126232449759494</v>
+        <v>6.576470882277751</v>
       </c>
       <c r="E46">
-        <v>34975.44493020629</v>
+        <v>21719.01334483857</v>
       </c>
       <c r="F46">
-        <v>8.891271564055534E-05</v>
+        <v>1.696751966900452E-05</v>
       </c>
       <c r="G46">
-        <v>3572.501136689074</v>
+        <v>2581.223211155017</v>
       </c>
       <c r="H46">
-        <v>2.117231025989824E-07</v>
+        <v>3.553045068597695E-07</v>
       </c>
       <c r="I46">
-        <v>34892.15977057468</v>
+        <v>21264.21125964839</v>
       </c>
       <c r="J46">
-        <v>34580.51102977888</v>
+        <v>20489.0842059492</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47">
-        <v>1.131161181204194E-05</v>
+        <v>1.460464215324009E-06</v>
       </c>
       <c r="B47">
-        <v>1826469989.063514</v>
+        <v>9125310182.416277</v>
       </c>
       <c r="C47">
-        <v>1.370083150785648E+41</v>
+        <v>10279264286.32908</v>
       </c>
       <c r="D47">
-        <v>7.460128534345239</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E47">
-        <v>42310.48865857054</v>
+        <v>22300.08296559034</v>
       </c>
       <c r="F47">
-        <v>5.429282025907351E-05</v>
+        <v>0.0001505781594026385</v>
       </c>
       <c r="G47">
-        <v>4455.103069964958</v>
+        <v>2251.212119372642</v>
       </c>
       <c r="H47">
-        <v>3.194515123683071E-07</v>
+        <v>1.590842417990272E-07</v>
       </c>
       <c r="I47">
-        <v>42061.53954289509</v>
+        <v>22276.52316246411</v>
       </c>
       <c r="J47">
-        <v>41349.52649482833</v>
+        <v>22169.35651686813</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48">
-        <v>1.276562382875194E-06</v>
+        <v>2.122006834392825E-06</v>
       </c>
       <c r="B48">
-        <v>12358284220.7196</v>
+        <v>10170923978.42132</v>
       </c>
       <c r="C48">
-        <v>14033562533.6419</v>
+        <v>11203960863.81577</v>
       </c>
       <c r="D48">
-        <v>1.059801980198019</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E48">
-        <v>26447.27578636571</v>
+        <v>36165.71585941695</v>
       </c>
       <c r="F48">
-        <v>4.755058386998837E-05</v>
+        <v>9.297611014666856E-05</v>
       </c>
       <c r="G48">
-        <v>2714.333451564452</v>
+        <v>3697.490719372491</v>
       </c>
       <c r="H48">
-        <v>1.390523346330711E-07</v>
+        <v>2.311442107240154E-07</v>
       </c>
       <c r="I48">
-        <v>26369.93592755695</v>
+        <v>36075.80571116052</v>
       </c>
       <c r="J48">
-        <v>26096.18428037945</v>
+        <v>35743.18851629481</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49">
-        <v>3.035906624048699E-06</v>
+        <v>3.085262618537489E-06</v>
       </c>
       <c r="B49">
-        <v>7708523427.773377</v>
+        <v>4480221342.800673</v>
       </c>
       <c r="C49">
-        <v>6.930351373281155E+17</v>
+        <v>1.099507028813147E+19</v>
       </c>
       <c r="D49">
-        <v>2.481145542572339</v>
+        <v>2.741441732952179</v>
       </c>
       <c r="E49">
-        <v>41816.39676235845</v>
+        <v>24990.7302604295</v>
       </c>
       <c r="F49">
-        <v>9.010612712730949E-05</v>
+        <v>5.739184872688701E-05</v>
       </c>
       <c r="G49">
-        <v>4272.075117866923</v>
+        <v>2579.646432727905</v>
       </c>
       <c r="H49">
-        <v>2.165229174131971E-07</v>
+        <v>2.055987568938707E-07</v>
       </c>
       <c r="I49">
-        <v>41715.91293832391</v>
+        <v>24901.20425300177</v>
       </c>
       <c r="J49">
-        <v>41340.80938935433</v>
+        <v>24602.12823431802</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50">
-        <v>1.680483249084049E-06</v>
+        <v>2.29262390699503E-06</v>
       </c>
       <c r="B50">
-        <v>10865681029.33669</v>
+        <v>3317104054.585199</v>
       </c>
       <c r="C50">
-        <v>12137432292.6745</v>
+        <v>4.128536059647409E+27</v>
       </c>
       <c r="D50">
-        <v>1.05980198019802</v>
+        <v>4.235103866494857</v>
       </c>
       <c r="E50">
-        <v>30594.86938103308</v>
+        <v>14445.4670943234</v>
       </c>
       <c r="F50">
-        <v>7.590397986932618E-05</v>
+        <v>0.0001331281948055185</v>
       </c>
       <c r="G50">
-        <v>3125.891359211119</v>
+        <v>1455.172431263591</v>
       </c>
       <c r="H50">
-        <v>1.830502936884296E-07</v>
+        <v>1.088063863189261E-07</v>
       </c>
       <c r="I50">
-        <v>30521.0866909133</v>
+        <v>14433.66073673312</v>
       </c>
       <c r="J50">
-        <v>30245.91876900966</v>
+        <v>14376.93377294036</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51">
-        <v>3.259727504468164E-06</v>
+        <v>2.781155463702577E-06</v>
       </c>
       <c r="B51">
-        <v>2617828295.90276</v>
+        <v>7205234859.859289</v>
       </c>
       <c r="C51">
-        <v>4.177817862076157E+34</v>
+        <v>514396263888071.8</v>
       </c>
       <c r="D51">
-        <v>5.613966017327944</v>
+        <v>1.918131165643087</v>
       </c>
       <c r="E51">
-        <v>16811.22343723322</v>
+        <v>35008.29767947801</v>
       </c>
       <c r="F51">
-        <v>0.0001008580814419354</v>
+        <v>5.662403818078617E-05</v>
       </c>
       <c r="G51">
-        <v>1699.182011816814</v>
+        <v>3629.939382840871</v>
       </c>
       <c r="H51">
-        <v>1.203867352987509E-07</v>
+        <v>2.32030951637861E-07</v>
       </c>
       <c r="I51">
-        <v>16791.15713935157</v>
+        <v>34864.84255181905</v>
       </c>
       <c r="J51">
-        <v>16702.32117261412</v>
+        <v>34404.4133508077</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52">
-        <v>3.063442588860743E-06</v>
+        <v>6.112717839530481E-06</v>
       </c>
       <c r="B52">
-        <v>6354860755.391926</v>
+        <v>4580788002.957466</v>
       </c>
       <c r="C52">
-        <v>4.966192947789874E+25</v>
+        <v>1.548928356568794E+22</v>
       </c>
       <c r="D52">
-        <v>3.911505590989967</v>
+        <v>3.437163172702742</v>
       </c>
       <c r="E52">
-        <v>36618.89718090618</v>
+        <v>51872.51838489764</v>
       </c>
       <c r="F52">
-        <v>0.0001392795803632373</v>
+        <v>0.0001866312102759807</v>
       </c>
       <c r="G52">
-        <v>3698.67146229306</v>
+        <v>5273.376678353913</v>
       </c>
       <c r="H52">
-        <v>1.554432969475228E-07</v>
+        <v>3.442966976035783E-07</v>
       </c>
       <c r="I52">
-        <v>36578.0285762368</v>
+        <v>51776.82411838191</v>
       </c>
       <c r="J52">
-        <v>36394.36303437478</v>
+        <v>51394.5779059487</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53">
-        <v>9.063193053838757E-06</v>
+        <v>3.823507336382444E-06</v>
       </c>
       <c r="B53">
-        <v>2933487494.549249</v>
+        <v>5131975633.949746</v>
       </c>
       <c r="C53">
-        <v>2.889878828224124E+29</v>
+        <v>10635538896169.75</v>
       </c>
       <c r="D53">
-        <v>4.990230451243914</v>
+        <v>1.660436375380759</v>
       </c>
       <c r="E53">
-        <v>51744.01231441411</v>
+        <v>33780.79089287356</v>
       </c>
       <c r="F53">
-        <v>9.225902582559348E-05</v>
+        <v>0.000310756218994979</v>
       </c>
       <c r="G53">
-        <v>5362.459918579277</v>
+        <v>3411.768844908003</v>
       </c>
       <c r="H53">
-        <v>3.7256294115205E-07</v>
+        <v>3.443541860072679E-07</v>
       </c>
       <c r="I53">
-        <v>51535.05821759426</v>
+        <v>33743.35783107283</v>
       </c>
       <c r="J53">
-        <v>50861.42998844285</v>
+        <v>33574.86571514206</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54">
-        <v>6.03992993975508E-06</v>
+        <v>4.865100854469071E-06</v>
       </c>
       <c r="B54">
-        <v>2632439907.309736</v>
+        <v>5786685993.900639</v>
       </c>
       <c r="C54">
-        <v>4.05414868749059E+25</v>
+        <v>2.039471734107798E+20</v>
       </c>
       <c r="D54">
-        <v>4.131029680114125</v>
+        <v>3.021779510312499</v>
       </c>
       <c r="E54">
-        <v>30197.50822984728</v>
+        <v>51373.30712030411</v>
       </c>
       <c r="F54">
-        <v>7.610830267489704E-05</v>
+        <v>0.0001533933048047179</v>
       </c>
       <c r="G54">
-        <v>3124.298767541067</v>
+        <v>5228.444219872576</v>
       </c>
       <c r="H54">
-        <v>2.927749515610515E-07</v>
+        <v>3.022798081919417E-07</v>
       </c>
       <c r="I54">
-        <v>30081.3438470069</v>
+        <v>51272.06988936837</v>
       </c>
       <c r="J54">
-        <v>29701.35539877116</v>
+        <v>50874.30003466793</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55">
-        <v>9.583426022814721E-06</v>
+        <v>4.076288756477878E-06</v>
       </c>
       <c r="B55">
-        <v>1619221496.394978</v>
+        <v>2872962917.449002</v>
       </c>
       <c r="C55">
-        <v>3.227381606333094E+37</v>
+        <v>4.020726148753338E+23</v>
       </c>
       <c r="D55">
-        <v>6.65747433113841</v>
+        <v>3.656067861702589</v>
       </c>
       <c r="E55">
-        <v>31349.299948931</v>
+        <v>21858.48200128725</v>
       </c>
       <c r="F55">
-        <v>5.594647717781486E-05</v>
+        <v>0.0001215930867087059</v>
       </c>
       <c r="G55">
-        <v>3287.096848757232</v>
+        <v>2221.212938177858</v>
       </c>
       <c r="H55">
-        <v>3.017327493329735E-07</v>
+        <v>2.185832209099376E-07</v>
       </c>
       <c r="I55">
-        <v>31180.22566685974</v>
+        <v>21819.18784789932</v>
       </c>
       <c r="J55">
-        <v>30682.52552728025</v>
+        <v>21661.22062690066</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56">
-        <v>9.963015457629938E-07</v>
+        <v>6.417885566491359E-06</v>
       </c>
       <c r="B56">
-        <v>10833623939.02378</v>
+        <v>6783930491.723097</v>
       </c>
       <c r="C56">
-        <v>12485940714.20446</v>
+        <v>5.890814884352142E+17</v>
       </c>
       <c r="D56">
-        <v>1.05980198019802</v>
+        <v>2.570162296645403</v>
       </c>
       <c r="E56">
-        <v>18066.32032409028</v>
+        <v>78051.40971545958</v>
       </c>
       <c r="F56">
-        <v>7.909511027166891E-05</v>
+        <v>0.0002218774327853875</v>
       </c>
       <c r="G56">
-        <v>1828.941521575153</v>
+        <v>7946.686143997797</v>
       </c>
       <c r="H56">
-        <v>1.085243132614118E-07</v>
+        <v>4.470796819297233E-07</v>
       </c>
       <c r="I56">
-        <v>18041.53200279458</v>
+        <v>77894.13730162421</v>
       </c>
       <c r="J56">
-        <v>17935.22883962667</v>
+        <v>77279.66773567486</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57">
-        <v>3.917210437614189E-06</v>
+        <v>4.511431921606499E-06</v>
       </c>
       <c r="B57">
-        <v>3540818804.138232</v>
+        <v>4390946847.52358</v>
       </c>
       <c r="C57">
-        <v>4.544187802649071E+16</v>
+        <v>2.79629932863222E+21</v>
       </c>
       <c r="D57">
-        <v>2.356225802820752</v>
+        <v>3.242810405537142</v>
       </c>
       <c r="E57">
-        <v>24695.05691340386</v>
+        <v>36463.2371832403</v>
       </c>
       <c r="F57">
-        <v>7.171513219828838E-05</v>
+        <v>0.0001101001438555402</v>
       </c>
       <c r="G57">
-        <v>2559.047619287877</v>
+        <v>3725.557546051296</v>
       </c>
       <c r="H57">
-        <v>2.88924721636114E-07</v>
+        <v>2.658280413946709E-07</v>
       </c>
       <c r="I57">
-        <v>24595.56588235109</v>
+        <v>36375.19959687666</v>
       </c>
       <c r="J57">
-        <v>24274.59904627009</v>
+        <v>36046.97010430585</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58">
-        <v>6.626281031458723E-06</v>
+        <v>1.206215202573971E-05</v>
       </c>
       <c r="B58">
-        <v>2124994264.602201</v>
+        <v>1781173751.903831</v>
       </c>
       <c r="C58">
-        <v>2.903016142561788E+37</v>
+        <v>1.323965756899785E+32</v>
       </c>
       <c r="D58">
-        <v>6.451437997128112</v>
+        <v>5.67266433188987</v>
       </c>
       <c r="E58">
-        <v>28243.55258958958</v>
+        <v>42415.15024318299</v>
       </c>
       <c r="F58">
-        <v>0.0001070981323138208</v>
+        <v>0.000222354651612595</v>
       </c>
       <c r="G58">
-        <v>2875.367431956377</v>
+        <v>4317.263184488126</v>
       </c>
       <c r="H58">
-        <v>2.149284409822682E-07</v>
+        <v>4.412195922209026E-07</v>
       </c>
       <c r="I58">
-        <v>28186.87239737022</v>
+        <v>42330.98562077207</v>
       </c>
       <c r="J58">
-        <v>27965.19295514007</v>
+        <v>42000.87271427526</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59">
-        <v>4.132944978872232E-06</v>
+        <v>2.502370472933053E-06</v>
       </c>
       <c r="B59">
-        <v>4559239689.519527</v>
+        <v>7787290454.143358</v>
       </c>
       <c r="C59">
-        <v>229762757835529.1</v>
+        <v>500379910538687.9</v>
       </c>
       <c r="D59">
-        <v>1.919361101833067</v>
+        <v>1.902596581787244</v>
       </c>
       <c r="E59">
-        <v>32858.16726475994</v>
+        <v>33978.40699428821</v>
       </c>
       <c r="F59">
-        <v>0.0001572281704337838</v>
+        <v>7.283642382881473E-05</v>
       </c>
       <c r="G59">
-        <v>3350.647370438513</v>
+        <v>3485.891810204838</v>
       </c>
       <c r="H59">
-        <v>3.446869576726726E-07</v>
+        <v>2.097190732585596E-07</v>
       </c>
       <c r="I59">
-        <v>32786.13321591269</v>
+        <v>33880.5724267593</v>
       </c>
       <c r="J59">
-        <v>32510.70246558731</v>
+        <v>33532.78695185664</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60">
-        <v>8.91888102243909E-06</v>
+        <v>7.608102480869781E-06</v>
       </c>
       <c r="B60">
-        <v>799319132.8989192</v>
+        <v>2180638710.896625</v>
       </c>
       <c r="C60">
-        <v>4.442446572507322E+72</v>
+        <v>4.947121117947757E+24</v>
       </c>
       <c r="D60">
-        <v>13.6297835816456</v>
+        <v>4.030495887321324</v>
       </c>
       <c r="E60">
-        <v>15395.35461896805</v>
+        <v>31427.13860416858</v>
       </c>
       <c r="F60">
-        <v>1.980981955232348E-05</v>
+        <v>8.640912259989358E-05</v>
       </c>
       <c r="G60">
-        <v>1637.362216637342</v>
+        <v>3265.960959925849</v>
       </c>
       <c r="H60">
-        <v>1.398640049231899E-07</v>
+        <v>3.765207823046227E-07</v>
       </c>
       <c r="I60">
-        <v>15286.6582248119</v>
+        <v>31290.19738249193</v>
       </c>
       <c r="J60">
-        <v>14994.66173124932</v>
+        <v>30858.85290960803</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61">
-        <v>4.773691647634124E-06</v>
+        <v>3.267981356184607E-06</v>
       </c>
       <c r="B61">
-        <v>7500018949.375866</v>
+        <v>5910422508.396195</v>
       </c>
       <c r="C61">
-        <v>7958947329013696</v>
+        <v>142475340186.4799</v>
       </c>
       <c r="D61">
-        <v>2.176357917178469</v>
+        <v>1.303407172722104</v>
       </c>
       <c r="E61">
-        <v>63150.65792818904</v>
+        <v>32724.66900889602</v>
       </c>
       <c r="F61">
-        <v>0.0001578671671237138</v>
+        <v>0.0001809607255950918</v>
       </c>
       <c r="G61">
-        <v>6448.269512185451</v>
+        <v>3325.994198690203</v>
       </c>
       <c r="H61">
-        <v>3.699881190056692E-07</v>
+        <v>3.288833416808629E-07</v>
       </c>
       <c r="I61">
-        <v>63002.65379555955</v>
+        <v>32665.19423356201</v>
       </c>
       <c r="J61">
-        <v>62446.50642869055</v>
+        <v>32426.74388697701</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62">
-        <v>1.248986039843773E-05</v>
+        <v>7.009475933951465E-06</v>
       </c>
       <c r="B62">
-        <v>2379958879.839941</v>
+        <v>3250565846.618239</v>
       </c>
       <c r="C62">
-        <v>4.892686934962446E+25</v>
+        <v>5.702428094586084E+24</v>
       </c>
       <c r="D62">
-        <v>4.356635198739006</v>
+        <v>3.988179393057766</v>
       </c>
       <c r="E62">
-        <v>56812.43180425037</v>
+        <v>43179.59237320254</v>
       </c>
       <c r="F62">
-        <v>0.0001724393261949266</v>
+        <v>5.718822137509037E-05</v>
       </c>
       <c r="G62">
-        <v>5852.794494592173</v>
+        <v>4555.778968319989</v>
       </c>
       <c r="H62">
-        <v>5.785547689977004E-07</v>
+        <v>3.499721016927484E-07</v>
       </c>
       <c r="I62">
-        <v>56621.81923295355</v>
+        <v>42915.34822764728</v>
       </c>
       <c r="J62">
-        <v>55972.82626806186</v>
+        <v>42169.52835722938</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63">
+        <v>4.341834635558163E-06</v>
+      </c>
+      <c r="B63">
+        <v>1974239092.84479</v>
+      </c>
+      <c r="C63">
+        <v>8.712763896876548E+36</v>
+      </c>
+      <c r="D63">
+        <v>6.174249794390916</v>
+      </c>
+      <c r="E63">
+        <v>17131.55878867341</v>
+      </c>
+      <c r="F63">
+        <v>3.935844539342785E-05</v>
+      </c>
+      <c r="G63">
+        <v>1770.653440143049</v>
+      </c>
+      <c r="H63">
+        <v>1.467736080684434E-07</v>
+      </c>
+      <c r="I63">
+        <v>17067.67260947818</v>
+      </c>
+      <c r="J63">
+        <v>16856.75539081234</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64">
+        <v>2.976118823481458E-06</v>
+      </c>
+      <c r="B64">
+        <v>8017310816.03373</v>
+      </c>
+      <c r="C64">
+        <v>8654754955.813782</v>
+      </c>
+      <c r="D64">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E64">
+        <v>40008.37926121343</v>
+      </c>
+      <c r="F64">
+        <v>0.0001034471817413376</v>
+      </c>
+      <c r="G64">
+        <v>4113.677467753854</v>
+      </c>
+      <c r="H64">
+        <v>3.241802172005449E-07</v>
+      </c>
+      <c r="I64">
+        <v>39883.00199273285</v>
+      </c>
+      <c r="J64">
+        <v>39447.73447183551</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65">
+        <v>8.859094345967784E-07</v>
+      </c>
+      <c r="B65">
+        <v>15519156206.40494</v>
+      </c>
+      <c r="C65">
+        <v>18012152124.16476</v>
+      </c>
+      <c r="D65">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E65">
+        <v>23003.37503971799</v>
+      </c>
+      <c r="F65">
+        <v>9.859425468498081E-05</v>
+      </c>
+      <c r="G65">
+        <v>2320.60070393332</v>
+      </c>
+      <c r="H65">
+        <v>9.649961240177776E-08</v>
+      </c>
+      <c r="I65">
+        <v>22980.86037309407</v>
+      </c>
+      <c r="J65">
+        <v>22876.70402923562</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66">
+        <v>2.645670582596059E-06</v>
+      </c>
+      <c r="B66">
+        <v>4104895592.606637</v>
+      </c>
+      <c r="C66">
+        <v>4.253368990830292E+27</v>
+      </c>
+      <c r="D66">
+        <v>4.2567882171419</v>
+      </c>
+      <c r="E66">
+        <v>20648.38860841596</v>
+      </c>
+      <c r="F66">
+        <v>0.0001131028011995705</v>
+      </c>
+      <c r="G66">
+        <v>2085.379712952571</v>
+      </c>
+      <c r="H66">
+        <v>1.250152927903636E-07</v>
+      </c>
+      <c r="I66">
+        <v>20625.56543940377</v>
+      </c>
+      <c r="J66">
+        <v>20522.7771541489</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67">
+        <v>1.963514863295178E-05</v>
+      </c>
+      <c r="B67">
+        <v>836565989.4069779</v>
+      </c>
+      <c r="C67">
+        <v>1.148883644981741E+55</v>
+      </c>
+      <c r="D67">
+        <v>10.81185139375873</v>
+      </c>
+      <c r="E67">
+        <v>34747.37365496664</v>
+      </c>
+      <c r="F67">
+        <v>0.000149969064827851</v>
+      </c>
+      <c r="G67">
+        <v>3555.331755322266</v>
+      </c>
+      <c r="H67">
+        <v>3.864933279253623E-07</v>
+      </c>
+      <c r="I67">
+        <v>34657.82433293819</v>
+      </c>
+      <c r="J67">
+        <v>34329.71707195408</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68">
+        <v>3.116599447357656E-06</v>
+      </c>
+      <c r="B68">
+        <v>6850259328.626147</v>
+      </c>
+      <c r="C68">
+        <v>40265362740299.38</v>
+      </c>
+      <c r="D68">
+        <v>1.731290383981964</v>
+      </c>
+      <c r="E68">
+        <v>36898.46770335839</v>
+      </c>
+      <c r="F68">
+        <v>0.000155262946860494</v>
+      </c>
+      <c r="G68">
+        <v>3748.614872044337</v>
+      </c>
+      <c r="H68">
+        <v>2.747632511166796E-07</v>
+      </c>
+      <c r="I68">
+        <v>36833.16981257116</v>
+      </c>
+      <c r="J68">
+        <v>36569.64845504517</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69">
+        <v>2.563714768978536E-06</v>
+      </c>
+      <c r="B69">
+        <v>8010442930.387486</v>
+      </c>
+      <c r="C69">
+        <v>8724822331.350859</v>
+      </c>
+      <c r="D69">
+        <v>1.05980198019802</v>
+      </c>
+      <c r="E69">
+        <v>34416.21091384623</v>
+      </c>
+      <c r="F69">
+        <v>0.0001076609439023949</v>
+      </c>
+      <c r="G69">
+        <v>3521.965068934754</v>
+      </c>
+      <c r="H69">
+        <v>2.79258208405631E-07</v>
+      </c>
+      <c r="I69">
+        <v>34326.93982767942</v>
+      </c>
+      <c r="J69">
+        <v>34000.42275009239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70">
+        <v>4.239442705615301E-06</v>
+      </c>
+      <c r="B70">
+        <v>2830709387.953676</v>
+      </c>
+      <c r="C70">
+        <v>9.819781545966848E+23</v>
+      </c>
+      <c r="D70">
+        <v>3.737325731500037</v>
+      </c>
+      <c r="E70">
+        <v>22504.36242973758</v>
+      </c>
+      <c r="F70">
+        <v>5.943942194675944E-05</v>
+      </c>
+      <c r="G70">
+        <v>2326.531666220965</v>
+      </c>
+      <c r="H70">
+        <v>2.233180830669668E-07</v>
+      </c>
+      <c r="I70">
+        <v>22419.81195946291</v>
+      </c>
+      <c r="J70">
+        <v>22141.28974612356</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71">
+        <v>6.16604833435539E-06</v>
+      </c>
+      <c r="B71">
+        <v>1128800390.700567</v>
+      </c>
+      <c r="C71">
+        <v>1.857778667940053E+42</v>
+      </c>
+      <c r="D71">
+        <v>7.391007572203891</v>
+      </c>
+      <c r="E71">
+        <v>14196.15608059557</v>
+      </c>
+      <c r="F71">
+        <v>6.111654302971549E-05</v>
+      </c>
+      <c r="G71">
+        <v>1456.346005181634</v>
+      </c>
+      <c r="H71">
+        <v>1.756997444680251E-07</v>
+      </c>
+      <c r="I71">
+        <v>14155.34452823771</v>
+      </c>
+      <c r="J71">
+        <v>14010.20325742304</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72">
+        <v>9.420931392404494E-06</v>
+      </c>
+      <c r="B72">
+        <v>4122978580.901768</v>
+      </c>
+      <c r="C72">
+        <v>3.514865627136587E+24</v>
+      </c>
+      <c r="D72">
+        <v>4.002075021083737</v>
+      </c>
+      <c r="E72">
+        <v>73414.09243487478</v>
+      </c>
+      <c r="F72">
+        <v>0.0001550876402320215</v>
+      </c>
+      <c r="G72">
+        <v>7541.222484356183</v>
+      </c>
+      <c r="H72">
+        <v>4.690071980833294E-07</v>
+      </c>
+      <c r="I72">
+        <v>73192.07772279844</v>
+      </c>
+      <c r="J72">
+        <v>72413.55619526183</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -438,2274 +438,1602 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>3.125905876819727E-06</v>
+        <v>2.043358282330331E-06</v>
       </c>
       <c r="B2">
-        <v>3585738269.767113</v>
+        <v>5127236195.060856</v>
       </c>
       <c r="C2">
-        <v>4.684367762103285E+19</v>
+        <v>2.352276985986371E+19</v>
       </c>
       <c r="D2">
-        <v>2.874081422229258</v>
+        <v>2.734480607992634</v>
       </c>
       <c r="E2">
-        <v>20417.55265851556</v>
+        <v>18915.70217219382</v>
       </c>
       <c r="F2">
-        <v>3.434188455235128E-05</v>
+        <v>5.461268944045677E-05</v>
       </c>
       <c r="G2">
-        <v>2149.542395269187</v>
+        <v>1934.092539166727</v>
       </c>
       <c r="H2">
-        <v>2.014395933733673E-07</v>
+        <v>1.364097957499011E-07</v>
       </c>
       <c r="I2">
-        <v>20297.78918138486</v>
+        <v>18868.45514780789</v>
       </c>
       <c r="J2">
-        <v>19954.90195084461</v>
+        <v>18693.88654113083</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>9.025810318358854E-06</v>
+        <v>6.049362565616766E-06</v>
       </c>
       <c r="B3">
-        <v>1736387804.198377</v>
+        <v>4622025538.021038</v>
       </c>
       <c r="C3">
-        <v>1.738047979469205E+36</v>
+        <v>7126725869823.13</v>
       </c>
       <c r="D3">
-        <v>6.371759692908888</v>
+        <v>1.661037966821092</v>
       </c>
       <c r="E3">
-        <v>31559.39003718144</v>
+        <v>48405.82016558199</v>
       </c>
       <c r="F3">
-        <v>3.999843332588542E-05</v>
+        <v>8.179673287190483E-05</v>
       </c>
       <c r="G3">
-        <v>3366.283172693485</v>
+        <v>5130.702301844288</v>
       </c>
       <c r="H3">
-        <v>2.962117951208361E-07</v>
+        <v>5.447208022848533E-07</v>
       </c>
       <c r="I3">
-        <v>31325.67429387551</v>
+        <v>48083.46429304189</v>
       </c>
       <c r="J3">
-        <v>30708.40872144009</v>
+        <v>47199.6191764929</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>4.880526229568082E-06</v>
+        <v>8.661130081977954E-06</v>
       </c>
       <c r="B4">
-        <v>3620837982.829711</v>
+        <v>2757096644.118438</v>
       </c>
       <c r="C4">
-        <v>3.325977914268479E+31</v>
+        <v>1.500401075251696E+29</v>
       </c>
       <c r="D4">
-        <v>5.158293446357678</v>
+        <v>4.924129993298621</v>
       </c>
       <c r="E4">
-        <v>34432.3110080461</v>
+        <v>46405.16465915993</v>
       </c>
       <c r="F4">
-        <v>0.0002072597976931175</v>
+        <v>8.492154329385757E-05</v>
       </c>
       <c r="G4">
-        <v>3472.346703179666</v>
+        <v>4817.71788322706</v>
       </c>
       <c r="H4">
-        <v>1.947296878781305E-07</v>
+        <v>3.603099387378258E-07</v>
       </c>
       <c r="I4">
-        <v>34399.96033874047</v>
+        <v>46208.27419548098</v>
       </c>
       <c r="J4">
-        <v>34249.02170069712</v>
+        <v>45583.00366147791</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>1.932983814653488E-06</v>
+        <v>2.182714522862528E-06</v>
       </c>
       <c r="B5">
-        <v>9440599464.512983</v>
+        <v>9662164446.907743</v>
       </c>
       <c r="C5">
-        <v>10457643611.39281</v>
+        <v>10625589062.58301</v>
       </c>
       <c r="D5">
-        <v>1.059801980198021</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E5">
-        <v>30622.03029617295</v>
+        <v>35311.61406178008</v>
       </c>
       <c r="F5">
-        <v>5.397945856868609E-05</v>
+        <v>0.0001401555542107188</v>
       </c>
       <c r="G5">
-        <v>3169.704010492514</v>
+        <v>3585.073096147407</v>
       </c>
       <c r="H5">
-        <v>2.105544670916292E-07</v>
+        <v>2.377569277562034E-07</v>
       </c>
       <c r="I5">
-        <v>30502.58476186715</v>
+        <v>35251.71218403631</v>
       </c>
       <c r="J5">
-        <v>30113.48171952345</v>
+        <v>35007.45426267909</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>1.67732031907685E-06</v>
+        <v>6.174055462529555E-06</v>
       </c>
       <c r="B6">
-        <v>3999518302.70004</v>
+        <v>4833855117.086716</v>
       </c>
       <c r="C6">
-        <v>7.354047380397434E+22</v>
+        <v>5.253906479416595E+19</v>
       </c>
       <c r="D6">
-        <v>3.328235989767439</v>
+        <v>2.964336778034586</v>
       </c>
       <c r="E6">
-        <v>12393.43231886502</v>
+        <v>54270.09903429714</v>
       </c>
       <c r="F6">
-        <v>3.263848408337557E-05</v>
+        <v>0.0005854259194709228</v>
       </c>
       <c r="G6">
-        <v>1272.45038236353</v>
+        <v>5459.469220591127</v>
       </c>
       <c r="H6">
-        <v>9.687632898251387E-08</v>
+        <v>3.890524930498245E-07</v>
       </c>
       <c r="I6">
-        <v>12356.64659611277</v>
+        <v>54234.03312634001</v>
       </c>
       <c r="J6">
-        <v>12226.97820109314</v>
+        <v>54053.29274278641</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>7.163423652715365E-06</v>
+        <v>4.367205030723479E-06</v>
       </c>
       <c r="B7">
-        <v>2123230652.513561</v>
+        <v>2856465666.119994</v>
       </c>
       <c r="C7">
-        <v>2.71279610686719E+42</v>
+        <v>2.969255878912619E+24</v>
       </c>
       <c r="D7">
-        <v>7.450353945863144</v>
+        <v>3.832210345270585</v>
       </c>
       <c r="E7">
-        <v>31228.11830008889</v>
+        <v>23511.40647743947</v>
       </c>
       <c r="F7">
-        <v>2.360171257548903E-05</v>
+        <v>3.992503235589201E-05</v>
       </c>
       <c r="G7">
-        <v>3364.020623753713</v>
+        <v>2470.590442737808</v>
       </c>
       <c r="H7">
-        <v>2.025575001897338E-07</v>
+        <v>2.253769857343598E-07</v>
       </c>
       <c r="I7">
-        <v>30960.1085292613</v>
+        <v>23378.68448300185</v>
       </c>
       <c r="J7">
-        <v>30289.44561528326</v>
+        <v>22993.81290118055</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>2.611398815335429E-06</v>
+        <v>1.666562507067209E-06</v>
       </c>
       <c r="B8">
-        <v>4696458270.103481</v>
+        <v>5658796267.101504</v>
       </c>
       <c r="C8">
-        <v>1.425609249716958E+19</v>
+        <v>39540235282408.82</v>
       </c>
       <c r="D8">
-        <v>2.735439491973959</v>
+        <v>1.710083916189186</v>
       </c>
       <c r="E8">
-        <v>22125.52231480951</v>
+        <v>16303.24117036523</v>
       </c>
       <c r="F8">
-        <v>0.0001045202846125255</v>
+        <v>4.955232819907918E-05</v>
       </c>
       <c r="G8">
-        <v>2245.757210383206</v>
+        <v>1674.108014895638</v>
       </c>
       <c r="H8">
-        <v>1.742881062389721E-07</v>
+        <v>1.478638547920945E-07</v>
       </c>
       <c r="I8">
-        <v>22088.62789380701</v>
+        <v>16254.59239496621</v>
       </c>
       <c r="J8">
-        <v>21937.55723725141</v>
+        <v>16083.36136528774</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>7.113609063764915E-06</v>
+        <v>1.170769350922742E-05</v>
       </c>
       <c r="B9">
-        <v>927921179.2764771</v>
+        <v>4291456709.250612</v>
       </c>
       <c r="C9">
-        <v>1.398433747424273E+56</v>
+        <v>8.398126459924264E+25</v>
       </c>
       <c r="D9">
-        <v>10.17440868964644</v>
+        <v>4.333324216259731</v>
       </c>
       <c r="E9">
-        <v>13903.95159770834</v>
+        <v>95717.25914640771</v>
       </c>
       <c r="F9">
-        <v>4.445689393600531E-05</v>
+        <v>0.0006650731564701839</v>
       </c>
       <c r="G9">
-        <v>1432.224747513411</v>
+        <v>9642.29702543106</v>
       </c>
       <c r="H9">
-        <v>1.48607916133321E-07</v>
+        <v>5.448332565616591E-07</v>
       </c>
       <c r="I9">
-        <v>13857.47427799436</v>
+        <v>95638.84680108518</v>
       </c>
       <c r="J9">
-        <v>13699.06039846917</v>
+        <v>95262.27403020079</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>5.738221843573332E-06</v>
+        <v>3.758037236363823E-06</v>
       </c>
       <c r="B10">
-        <v>1839009404.49493</v>
+        <v>1970502123.476547</v>
       </c>
       <c r="C10">
-        <v>4.453075625802577E+43</v>
+        <v>4.869719605757695E+28</v>
       </c>
       <c r="D10">
-        <v>7.57521923738531</v>
+        <v>4.600299845463315</v>
       </c>
       <c r="E10">
-        <v>21596.27754431618</v>
+        <v>14266.27962249726</v>
       </c>
       <c r="F10">
-        <v>4.533773166713847E-05</v>
+        <v>3.843155803613785E-05</v>
       </c>
       <c r="G10">
-        <v>2228.085770189134</v>
+        <v>1482.100123995225</v>
       </c>
       <c r="H10">
-        <v>1.596844714717384E-07</v>
+        <v>1.660388973100136E-07</v>
       </c>
       <c r="I10">
-        <v>21520.21308236338</v>
+        <v>14204.64388722448</v>
       </c>
       <c r="J10">
-        <v>21264.84649760725</v>
+        <v>14009.98973346848</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>1.723300529607677E-05</v>
+        <v>5.858077687177371E-06</v>
       </c>
       <c r="B11">
-        <v>1128869000.694602</v>
+        <v>3469954879.280107</v>
       </c>
       <c r="C11">
-        <v>4.45431119552479E+61</v>
+        <v>8.452782261316507E+34</v>
       </c>
       <c r="D11">
-        <v>12.04932051587419</v>
+        <v>5.872487884195206</v>
       </c>
       <c r="E11">
-        <v>41494.51513083652</v>
+        <v>40287.07590327971</v>
       </c>
       <c r="F11">
-        <v>0.000112115095284058</v>
+        <v>0.0001333602561224985</v>
       </c>
       <c r="G11">
-        <v>4251.048297344812</v>
+        <v>4085.127822020782</v>
       </c>
       <c r="H11">
-        <v>3.050077318004378E-07</v>
+        <v>2.075166892260914E-07</v>
       </c>
       <c r="I11">
-        <v>41381.62981499078</v>
+        <v>40224.38675695437</v>
       </c>
       <c r="J11">
-        <v>40974.03864842245</v>
+        <v>39963.38921440972</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>1.291927699537181E-06</v>
+        <v>2.550920439751627E-06</v>
       </c>
       <c r="B12">
-        <v>7148629885.84951</v>
+        <v>5990385544.499911</v>
       </c>
       <c r="C12">
-        <v>3.454136241247261E+17</v>
+        <v>370945367810.4188</v>
       </c>
       <c r="D12">
-        <v>2.343160065056259</v>
+        <v>1.370111949773192</v>
       </c>
       <c r="E12">
-        <v>16414.96625343918</v>
+        <v>26048.59597849682</v>
       </c>
       <c r="F12">
-        <v>3.348307941831501E-05</v>
+        <v>5.280867459609441E-05</v>
       </c>
       <c r="G12">
-        <v>1683.690187243583</v>
+        <v>2716.437243666883</v>
       </c>
       <c r="H12">
-        <v>9.562888201572964E-08</v>
+        <v>2.513365401524873E-07</v>
       </c>
       <c r="I12">
-        <v>16368.0845179951</v>
+        <v>25924.62081647771</v>
       </c>
       <c r="J12">
-        <v>16201.05360369657</v>
+        <v>25544.72103164676</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
-        <v>5.562264952358299E-06</v>
+        <v>3.696422512669191E-06</v>
       </c>
       <c r="B13">
-        <v>6491851089.186145</v>
+        <v>2512021592.575085</v>
       </c>
       <c r="C13">
-        <v>2.523633934140503E+17</v>
+        <v>4.163573064086583E+23</v>
       </c>
       <c r="D13">
-        <v>2.485928363362039</v>
+        <v>3.648868581803006</v>
       </c>
       <c r="E13">
-        <v>64602.96611353839</v>
+        <v>17396.20144871652</v>
       </c>
       <c r="F13">
-        <v>0.0001145926268263991</v>
+        <v>3.442738055485639E-05</v>
       </c>
       <c r="G13">
-        <v>6661.322724728523</v>
+        <v>1829.905378568315</v>
       </c>
       <c r="H13">
-        <v>3.961997374654607E-07</v>
+        <v>1.985289150062312E-07</v>
       </c>
       <c r="I13">
-        <v>64379.6037653443</v>
+        <v>17295.8845223869</v>
       </c>
       <c r="J13">
-        <v>63625.67502522712</v>
+        <v>17007.03456838597</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
-        <v>2.657504203154304E-06</v>
+        <v>5.329632439916942E-06</v>
       </c>
       <c r="B14">
-        <v>11683517935.59754</v>
+        <v>8666670562.075039</v>
       </c>
       <c r="C14">
-        <v>12698152120.4957</v>
+        <v>42266951122011.14</v>
       </c>
       <c r="D14">
-        <v>1.05980198019802</v>
+        <v>1.748053129833145</v>
       </c>
       <c r="E14">
-        <v>51992.95520260166</v>
+        <v>80011.41707986225</v>
       </c>
       <c r="F14">
-        <v>0.0001596720943246829</v>
+        <v>0.0001432714035481565</v>
       </c>
       <c r="G14">
-        <v>5284.129178015415</v>
+        <v>8236.122495753016</v>
       </c>
       <c r="H14">
-        <v>2.894744265560373E-07</v>
+        <v>4.675169911008031E-07</v>
       </c>
       <c r="I14">
-        <v>51898.6955828736</v>
+        <v>79750.32731567691</v>
       </c>
       <c r="J14">
-        <v>51520.55199657666</v>
+        <v>78854.26832044432</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>5.030889464025536E-06</v>
+        <v>3.883859988316869E-06</v>
       </c>
       <c r="B15">
-        <v>3130940372.405571</v>
+        <v>9981708551.358763</v>
       </c>
       <c r="C15">
-        <v>1.001640517690644E+24</v>
+        <v>10605155388.82389</v>
       </c>
       <c r="D15">
-        <v>3.768880940072552</v>
+        <v>1.059801980198021</v>
       </c>
       <c r="E15">
-        <v>29520.96964572794</v>
+        <v>65210.07438353699</v>
       </c>
       <c r="F15">
-        <v>0.0001232776486869791</v>
+        <v>6.733099676824972E-05</v>
       </c>
       <c r="G15">
-        <v>3008.821504080608</v>
+        <v>6889.765878113409</v>
       </c>
       <c r="H15">
-        <v>2.631977629346289E-07</v>
+        <v>4.230578983120739E-07</v>
       </c>
       <c r="I15">
-        <v>29457.94237960814</v>
+        <v>64800.34278380397</v>
       </c>
       <c r="J15">
-        <v>29215.30007212284</v>
+        <v>63654.21821708216</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
-        <v>3.401384014744212E-06</v>
+        <v>3.380392709823458E-06</v>
       </c>
       <c r="B16">
-        <v>2397679373.38238</v>
+        <v>4077288393.160055</v>
       </c>
       <c r="C16">
-        <v>1.69605840118633E+35</v>
+        <v>1.068558335639919E+17</v>
       </c>
       <c r="D16">
-        <v>5.747268212042216</v>
+        <v>2.39667310073531</v>
       </c>
       <c r="E16">
-        <v>16152.67420840217</v>
+        <v>24609.85390520707</v>
       </c>
       <c r="F16">
-        <v>3.43366488338997E-05</v>
+        <v>4.759740459907991E-05</v>
       </c>
       <c r="G16">
-        <v>1667.311049793521</v>
+        <v>2575.744360601655</v>
       </c>
       <c r="H16">
-        <v>1.229245241276676E-07</v>
+        <v>2.46614364372369E-07</v>
       </c>
       <c r="I16">
-        <v>16094.84795400961</v>
+        <v>24482.34393845046</v>
       </c>
       <c r="J16">
-        <v>15901.63256245734</v>
+        <v>24102.07148128112</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17">
-        <v>9.392059833728612E-06</v>
+        <v>2.187663380277322E-06</v>
       </c>
       <c r="B17">
-        <v>2209544380.622752</v>
+        <v>13412561915.95068</v>
       </c>
       <c r="C17">
-        <v>2.920809379581833E+29</v>
+        <v>14747945095.09706</v>
       </c>
       <c r="D17">
-        <v>5.027725173159621</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E17">
-        <v>40410.609503396</v>
+        <v>49121.33121463029</v>
       </c>
       <c r="F17">
-        <v>0.0001057965474550605</v>
+        <v>0.0001548048691827366</v>
       </c>
       <c r="G17">
-        <v>4172.895134030478</v>
+        <v>4980.185727345703</v>
       </c>
       <c r="H17">
-        <v>3.834966895644663E-07</v>
+        <v>2.38295992816027E-07</v>
       </c>
       <c r="I17">
-        <v>40264.12707707279</v>
+        <v>49045.71720809397</v>
       </c>
       <c r="J17">
-        <v>39776.4648509796</v>
+        <v>48730.09727939642</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18">
-        <v>1.190905625664123E-05</v>
+        <v>6.798778832670672E-06</v>
       </c>
       <c r="B18">
-        <v>1865308500.105677</v>
+        <v>1290635913.965243</v>
       </c>
       <c r="C18">
-        <v>3.083789417955132E+44</v>
+        <v>2.467113770656142E+46</v>
       </c>
       <c r="D18">
-        <v>8.166510259562871</v>
+        <v>8.227980478625751</v>
       </c>
       <c r="E18">
-        <v>45806.43776613366</v>
+        <v>18083.42707686223</v>
       </c>
       <c r="F18">
-        <v>0.0001027129903190374</v>
+        <v>0.0001064532887545924</v>
       </c>
       <c r="G18">
-        <v>4704.348976934458</v>
+        <v>1835.048611106737</v>
       </c>
       <c r="H18">
-        <v>3.082082796567797E-07</v>
+        <v>1.746799699337091E-07</v>
       </c>
       <c r="I18">
-        <v>45668.98754355468</v>
+        <v>18053.75385083944</v>
       </c>
       <c r="J18">
-        <v>45185.9467649938</v>
+        <v>17931.77765997374</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19">
-        <v>3.258346482657611E-06</v>
+        <v>5.372272654782217E-06</v>
       </c>
       <c r="B19">
-        <v>5629825870.184869</v>
+        <v>2783406549.309166</v>
       </c>
       <c r="C19">
-        <v>2941682378452.053</v>
+        <v>3.068614666303722E+23</v>
       </c>
       <c r="D19">
-        <v>1.544230366678171</v>
+        <v>3.696556597154334</v>
       </c>
       <c r="E19">
-        <v>31489.8818512203</v>
+        <v>28037.66392785895</v>
       </c>
       <c r="F19">
-        <v>8.420118503182126E-05</v>
+        <v>5.725736043020043E-05</v>
       </c>
       <c r="G19">
-        <v>3251.329141578664</v>
+        <v>2929.599652741756</v>
       </c>
       <c r="H19">
-        <v>3.040563897689138E-07</v>
+        <v>2.855238795111081E-07</v>
       </c>
       <c r="I19">
-        <v>31376.1696773796</v>
+        <v>27897.84919457466</v>
       </c>
       <c r="J19">
-        <v>30997.18329079703</v>
+        <v>27475.71674042101</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20">
-        <v>4.930487709592349E-06</v>
+        <v>5.913678103654003E-06</v>
       </c>
       <c r="B20">
-        <v>3658365295.642342</v>
+        <v>1628042091.099464</v>
       </c>
       <c r="C20">
-        <v>4.092508719983794E+21</v>
+        <v>2.853438937693118E+43</v>
       </c>
       <c r="D20">
-        <v>3.304751009079162</v>
+        <v>7.564847918293384</v>
       </c>
       <c r="E20">
-        <v>33241.62951883718</v>
+        <v>19679.79118004764</v>
       </c>
       <c r="F20">
-        <v>0.0002088250851206324</v>
+        <v>6.64962516948797E-05</v>
       </c>
       <c r="G20">
-        <v>3365.184254093086</v>
+        <v>2011.870729830216</v>
       </c>
       <c r="H20">
-        <v>2.863302915860143E-07</v>
+        <v>1.647842500256626E-07</v>
       </c>
       <c r="I20">
-        <v>33196.05029416009</v>
+        <v>19631.0227224638</v>
       </c>
       <c r="J20">
-        <v>33000.55595743053</v>
+        <v>19450.45223396456</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21">
-        <v>1.874859518858083E-06</v>
+        <v>2.042350735123807E-06</v>
       </c>
       <c r="B21">
-        <v>20677498112.28812</v>
+        <v>3213056419.658475</v>
       </c>
       <c r="C21">
-        <v>22946962103.18439</v>
+        <v>4.909878149370443E+21</v>
       </c>
       <c r="D21">
-        <v>1.05980198019802</v>
+        <v>3.1744353137788</v>
       </c>
       <c r="E21">
-        <v>64856.83484941199</v>
+        <v>12046.33833474075</v>
       </c>
       <c r="F21">
-        <v>0.0002333968932519055</v>
+        <v>5.514356032268296E-05</v>
       </c>
       <c r="G21">
-        <v>6536.75845999963</v>
+        <v>1228.680614350417</v>
       </c>
       <c r="H21">
-        <v>2.042231517264919E-07</v>
+        <v>1.223078079342613E-07</v>
       </c>
       <c r="I21">
-        <v>64800.08487712484</v>
+        <v>12019.61968932259</v>
       </c>
       <c r="J21">
-        <v>64530.51026884199</v>
+        <v>11917.76559257034</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22">
-        <v>2.528612014777631E-06</v>
+        <v>6.860831974872855E-06</v>
       </c>
       <c r="B22">
-        <v>4983679792.910171</v>
+        <v>1536007227.20179</v>
       </c>
       <c r="C22">
-        <v>5921733245608.685</v>
+        <v>2.923338727843276E+27</v>
       </c>
       <c r="D22">
-        <v>1.596731923860861</v>
+        <v>4.567124539179384</v>
       </c>
       <c r="E22">
-        <v>21655.67758105847</v>
+        <v>20308.15012775854</v>
       </c>
       <c r="F22">
-        <v>0.0001036679221650369</v>
+        <v>5.507404813698241E-05</v>
       </c>
       <c r="G22">
-        <v>2209.22052472181</v>
+        <v>2132.052880020509</v>
       </c>
       <c r="H22">
-        <v>2.321891283805348E-07</v>
+        <v>3.050542728927135E-07</v>
       </c>
       <c r="I22">
-        <v>21607.17450704073</v>
+        <v>20195.66360859782</v>
       </c>
       <c r="J22">
-        <v>21422.74414674548</v>
+        <v>19867.424107436</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23">
-        <v>7.677196455236789E-06</v>
+        <v>9.373828877828443E-06</v>
       </c>
       <c r="B23">
-        <v>1950776622.693986</v>
+        <v>2396802322.633597</v>
       </c>
       <c r="C23">
-        <v>1.531365834706269E+34</v>
+        <v>8.488704529147648E+30</v>
       </c>
       <c r="D23">
-        <v>5.888153906338607</v>
+        <v>5.309651015377753</v>
       </c>
       <c r="E23">
-        <v>29764.69581476254</v>
+        <v>43956.66353703271</v>
       </c>
       <c r="F23">
-        <v>6.797875609379335E-05</v>
+        <v>0.0002691521554933571</v>
       </c>
       <c r="G23">
-        <v>3083.373923316396</v>
+        <v>4449.215951272896</v>
       </c>
       <c r="H23">
-        <v>2.712842618257568E-07</v>
+        <v>3.643232132111173E-07</v>
       </c>
       <c r="I23">
-        <v>29645.91321271794</v>
+        <v>43897.16398417755</v>
       </c>
       <c r="J23">
-        <v>29261.6096842647</v>
+        <v>43641.20133472011</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24">
-        <v>2.838459967007613E-06</v>
+        <v>1.956396392419038E-06</v>
       </c>
       <c r="B24">
-        <v>6639059663.571969</v>
+        <v>12590432370.34372</v>
       </c>
       <c r="C24">
-        <v>110539764734.896</v>
+        <v>13936773015.07799</v>
       </c>
       <c r="D24">
-        <v>1.271435086193121</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E24">
-        <v>31999.94480479433</v>
+        <v>41248.28131904893</v>
       </c>
       <c r="F24">
-        <v>5.164150182254318E-05</v>
+        <v>0.0001158656874108605</v>
       </c>
       <c r="G24">
-        <v>3360.940825348054</v>
+        <v>4193.107048281212</v>
       </c>
       <c r="H24">
-        <v>2.88594628402794E-07</v>
+        <v>2.131047330572813E-07</v>
       </c>
       <c r="I24">
-        <v>31821.11553271807</v>
+        <v>41172.41585640858</v>
       </c>
       <c r="J24">
-        <v>31300.8125125794</v>
+        <v>40869.14808132736</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25">
-        <v>1.930045769663619E-06</v>
+        <v>1.745819385360364E-05</v>
       </c>
       <c r="B25">
-        <v>13168986382.60005</v>
+        <v>1241510422.214209</v>
       </c>
       <c r="C25">
-        <v>14589019991.50941</v>
+        <v>2.938349173064098E+37</v>
       </c>
       <c r="D25">
-        <v>1.05980198019802</v>
+        <v>6.981740103201528</v>
       </c>
       <c r="E25">
-        <v>42652.09127008013</v>
+        <v>44068.96593178452</v>
       </c>
       <c r="F25">
-        <v>5.345170544489423E-05</v>
+        <v>8.453089408690223E-05</v>
       </c>
       <c r="G25">
-        <v>4416.191109321664</v>
+        <v>4653.391804766101</v>
       </c>
       <c r="H25">
-        <v>2.102344341495823E-07</v>
+        <v>5.253498108169145E-07</v>
       </c>
       <c r="I25">
-        <v>42484.33351195386</v>
+        <v>43795.0823633538</v>
       </c>
       <c r="J25">
-        <v>41939.20713905706</v>
+        <v>43026.0901291285</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26">
-        <v>1.482157899227998E-06</v>
+        <v>7.923914750343495E-06</v>
       </c>
       <c r="B26">
-        <v>9988939475.226763</v>
+        <v>2586910157.060757</v>
       </c>
       <c r="C26">
-        <v>11242187726.78588</v>
+        <v>3.845065063668568E+28</v>
       </c>
       <c r="D26">
-        <v>1.05980198019802</v>
+        <v>4.784656635641022</v>
       </c>
       <c r="E26">
-        <v>24786.54165812975</v>
+        <v>39645.00666950154</v>
       </c>
       <c r="F26">
-        <v>0.0001012243718780559</v>
+        <v>0.0001066594480667857</v>
       </c>
       <c r="G26">
-        <v>2514.23401231253</v>
+        <v>4077.630949471608</v>
       </c>
       <c r="H26">
-        <v>1.614472735114668E-07</v>
+        <v>3.381794387253067E-07</v>
       </c>
       <c r="I26">
-        <v>24747.00849535246</v>
+        <v>39519.30635558881</v>
       </c>
       <c r="J26">
-        <v>24583.38703278324</v>
+        <v>39084.3595155642</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27">
-        <v>3.348514127357652E-06</v>
+        <v>2.48705745654972E-06</v>
       </c>
       <c r="B27">
-        <v>3985811775.356389</v>
+        <v>6139654276.614969</v>
       </c>
       <c r="C27">
-        <v>4.330694760945495E+22</v>
+        <v>11898102509.14609</v>
       </c>
       <c r="D27">
-        <v>3.413570354963249</v>
+        <v>1.103820578331863</v>
       </c>
       <c r="E27">
-        <v>24691.18871465695</v>
+        <v>25640.27679347952</v>
       </c>
       <c r="F27">
-        <v>0.0001435446878391306</v>
+        <v>0.000109552122749567</v>
       </c>
       <c r="G27">
-        <v>2498.474642273441</v>
+        <v>2620.270440335908</v>
       </c>
       <c r="H27">
-        <v>1.896252233302256E-07</v>
+        <v>2.670067316856072E-07</v>
       </c>
       <c r="I27">
-        <v>24658.57119153723</v>
+        <v>25577.78483682623</v>
       </c>
       <c r="J27">
-        <v>24517.46244983396</v>
+        <v>25345.37748922331</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28">
-        <v>5.239056992427492E-06</v>
+        <v>7.476791290724473E-06</v>
       </c>
       <c r="B28">
-        <v>2928469917.595381</v>
+        <v>1341227148.27086</v>
       </c>
       <c r="C28">
-        <v>3.26929138301649E+27</v>
+        <v>1.024561972444765E+60</v>
       </c>
       <c r="D28">
-        <v>4.444821013272588</v>
+        <v>10.93477490455503</v>
       </c>
       <c r="E28">
-        <v>29348.19536014658</v>
+        <v>21224.99758401718</v>
       </c>
       <c r="F28">
-        <v>0.0001451373455419562</v>
+        <v>6.504737895401539E-05</v>
       </c>
       <c r="G28">
-        <v>2978.226870527252</v>
+        <v>2165.243408583586</v>
       </c>
       <c r="H28">
-        <v>2.38516475521985E-07</v>
+        <v>1.455496781959858E-07</v>
       </c>
       <c r="I28">
-        <v>29299.96498846592</v>
+        <v>21177.50463937065</v>
       </c>
       <c r="J28">
-        <v>29101.77990636559</v>
+        <v>20996.8702467118</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29">
-        <v>3.358710908877152E-06</v>
+        <v>9.513314402650834E-06</v>
       </c>
       <c r="B29">
-        <v>2370749409.444085</v>
+        <v>1951363780.727175</v>
       </c>
       <c r="C29">
-        <v>3.665353644836144E+39</v>
+        <v>6.579887522920801E+36</v>
       </c>
       <c r="D29">
-        <v>6.532473108159005</v>
+        <v>6.500765991659309</v>
       </c>
       <c r="E29">
-        <v>16000.96182640079</v>
+        <v>37354.14528720242</v>
       </c>
       <c r="F29">
-        <v>4.601326365841182E-05</v>
+        <v>7.200735591045848E-05</v>
       </c>
       <c r="G29">
-        <v>1633.792163756596</v>
+        <v>3878.44700468872</v>
       </c>
       <c r="H29">
-        <v>1.076645044608752E-07</v>
+        <v>3.063586926528365E-07</v>
       </c>
       <c r="I29">
-        <v>15963.52184738244</v>
+        <v>37195.22031390412</v>
       </c>
       <c r="J29">
-        <v>15822.77561289264</v>
+        <v>36690.94069731067</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30">
-        <v>1.536063066707136E-06</v>
+        <v>8.038883297885796E-06</v>
       </c>
       <c r="B30">
-        <v>8013584961.89557</v>
+        <v>1535239539.765562</v>
       </c>
       <c r="C30">
-        <v>8999751023.10899</v>
+        <v>7.417601075565434E+41</v>
       </c>
       <c r="D30">
-        <v>1.05980198019802</v>
+        <v>7.430912236892116</v>
       </c>
       <c r="E30">
-        <v>20608.17879815602</v>
+        <v>25148.35374043235</v>
       </c>
       <c r="F30">
-        <v>0.0001046585343218686</v>
+        <v>0.0001708459369768284</v>
       </c>
       <c r="G30">
-        <v>2090.469796005127</v>
+        <v>2545.025242175164</v>
       </c>
       <c r="H30">
-        <v>1.673190111463158E-07</v>
+        <v>2.278839827159067E-07</v>
       </c>
       <c r="I30">
-        <v>20575.2322246121</v>
+        <v>25114.80944250798</v>
       </c>
       <c r="J30">
-        <v>20438.94877787422</v>
+        <v>24970.01392487806</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31">
-        <v>3.399323259311847E-06</v>
+        <v>3.039428217829988E-06</v>
       </c>
       <c r="B31">
-        <v>4277511681.072515</v>
+        <v>8995554400.335499</v>
       </c>
       <c r="C31">
-        <v>4.540312640206407E+16</v>
+        <v>9698561017.046843</v>
       </c>
       <c r="D31">
-        <v>2.326144804571572</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E31">
-        <v>25810.44276066786</v>
+        <v>45785.50338988728</v>
       </c>
       <c r="F31">
-        <v>0.0001113176219882092</v>
+        <v>0.0001800503444706987</v>
       </c>
       <c r="G31">
-        <v>2633.795396609</v>
+        <v>4654.321628711877</v>
       </c>
       <c r="H31">
-        <v>2.52788693597268E-07</v>
+        <v>3.31076330705426E-07</v>
       </c>
       <c r="I31">
-        <v>25751.83040450984</v>
+        <v>45701.31306797265</v>
       </c>
       <c r="J31">
-        <v>25529.75936056797</v>
+        <v>45364.74717789261</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32">
-        <v>5.236870791036558E-06</v>
+        <v>1.77079113421659E-06</v>
       </c>
       <c r="B32">
-        <v>3533248195.844752</v>
+        <v>10398139448.07952</v>
       </c>
       <c r="C32">
-        <v>3.33772344453066E+33</v>
+        <v>11578865744.82121</v>
       </c>
       <c r="D32">
-        <v>5.561592956245582</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E32">
-        <v>36458.29467671689</v>
+        <v>30811.81879554968</v>
       </c>
       <c r="F32">
-        <v>7.668621013167233E-05</v>
+        <v>0.0001726378607155522</v>
       </c>
       <c r="G32">
-        <v>3729.301000897457</v>
+        <v>3112.165158710239</v>
       </c>
       <c r="H32">
-        <v>1.950818232090533E-07</v>
+        <v>1.928872765354189E-07</v>
       </c>
       <c r="I32">
-        <v>36365.54852868825</v>
+        <v>30777.3929298216</v>
       </c>
       <c r="J32">
-        <v>36024.54291389888</v>
+        <v>30622.71959781262</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33">
-        <v>6.755077996601752E-06</v>
+        <v>3.185368730524395E-06</v>
       </c>
       <c r="B33">
-        <v>1321172215.54009</v>
+        <v>7218493827.32128</v>
       </c>
       <c r="C33">
-        <v>8.584097893477478E+40</v>
+        <v>7760825553.404645</v>
       </c>
       <c r="D33">
-        <v>7.169147170896989</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E33">
-        <v>18118.55585736552</v>
+        <v>38708.37603093049</v>
       </c>
       <c r="F33">
-        <v>0.0001172350425068447</v>
+        <v>4.894342418032951E-05</v>
       </c>
       <c r="G33">
-        <v>1839.42282649374</v>
+        <v>4117.810368823505</v>
       </c>
       <c r="H33">
-        <v>1.981913316692374E-07</v>
+        <v>3.469732185347524E-07</v>
       </c>
       <c r="I33">
-        <v>18087.92558985754</v>
+        <v>38433.96184678553</v>
       </c>
       <c r="J33">
-        <v>17962.92186028983</v>
+        <v>37697.86799488736</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34">
-        <v>8.007295167537754E-06</v>
+        <v>1.013452597086768E-05</v>
       </c>
       <c r="B34">
-        <v>1690106308.164036</v>
+        <v>4439607923.776803</v>
       </c>
       <c r="C34">
-        <v>1.518661211251211E+45</v>
+        <v>7.762512957865836E+20</v>
       </c>
       <c r="D34">
-        <v>8.06859342864421</v>
+        <v>3.287893719853837</v>
       </c>
       <c r="E34">
-        <v>27839.86855258906</v>
+        <v>83195.94749366507</v>
       </c>
       <c r="F34">
-        <v>0.0001105898838553321</v>
+        <v>0.0001114129336845818</v>
       </c>
       <c r="G34">
-        <v>2831.489540831835</v>
+        <v>8716.695522348889</v>
       </c>
       <c r="H34">
-        <v>2.096640039965694E-07</v>
+        <v>5.908696199114885E-07</v>
       </c>
       <c r="I34">
-        <v>27787.08779084136</v>
+        <v>82754.72441257353</v>
       </c>
       <c r="J34">
-        <v>27577.68495868921</v>
+        <v>81448.77389546891</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35">
-        <v>1.19277021204424E-05</v>
+        <v>5.211010676332686E-06</v>
       </c>
       <c r="B35">
-        <v>1567569974.132424</v>
+        <v>2055015756.145427</v>
       </c>
       <c r="C35">
-        <v>1.395302942004507E+69</v>
+        <v>6.184104596336484E+25</v>
       </c>
       <c r="D35">
-        <v>13.18311321414294</v>
+        <v>4.147997343633836</v>
       </c>
       <c r="E35">
-        <v>40057.3533578916</v>
+        <v>20336.44286101302</v>
       </c>
       <c r="F35">
-        <v>0.0001673565261908377</v>
+        <v>7.796722503674092E-05</v>
       </c>
       <c r="G35">
-        <v>4047.369104884672</v>
+        <v>2092.735446992468</v>
       </c>
       <c r="H35">
-        <v>1.932696325525397E-07</v>
+        <v>2.517196383944855E-07</v>
       </c>
       <c r="I35">
-        <v>40011.09361445215</v>
+        <v>20270.78601557839</v>
       </c>
       <c r="J35">
-        <v>39804.77450225805</v>
+        <v>20044.76485030172</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36">
-        <v>3.460541236293204E-06</v>
+        <v>7.503077368107439E-06</v>
       </c>
       <c r="B36">
-        <v>9127523094.255844</v>
+        <v>1295287796.310878</v>
       </c>
       <c r="C36">
-        <v>9764777214.2619</v>
+        <v>2.230479857906178E+63</v>
       </c>
       <c r="D36">
-        <v>1.05980198019802</v>
+        <v>11.59120916909253</v>
       </c>
       <c r="E36">
-        <v>52963.08821952067</v>
+        <v>20630.13048895242</v>
       </c>
       <c r="F36">
-        <v>0.0001199023401650377</v>
+        <v>0.0001960182932564723</v>
       </c>
       <c r="G36">
-        <v>5446.162850049521</v>
+        <v>2076.079425690833</v>
       </c>
       <c r="H36">
-        <v>3.769469823454992E-07</v>
+        <v>1.379454235040294E-07</v>
       </c>
       <c r="I36">
-        <v>52796.58374385683</v>
+        <v>20615.61229251287</v>
       </c>
       <c r="J36">
-        <v>52219.0572010306</v>
+        <v>20543.68665804758</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37">
-        <v>7.537725686731271E-06</v>
+        <v>2.867577865527873E-06</v>
       </c>
       <c r="B37">
-        <v>2814568213.045622</v>
+        <v>4260382958.369288</v>
       </c>
       <c r="C37">
-        <v>5.033204891103693E+33</v>
+        <v>1.751297723981989E+22</v>
       </c>
       <c r="D37">
-        <v>5.755697966541194</v>
+        <v>3.308822787418684</v>
       </c>
       <c r="E37">
-        <v>41983.72515429464</v>
+        <v>22503.14507827817</v>
       </c>
       <c r="F37">
-        <v>0.0001066744584712131</v>
+        <v>0.0002361510538504044</v>
       </c>
       <c r="G37">
-        <v>4294.732514095485</v>
+        <v>2264.582929416343</v>
       </c>
       <c r="H37">
-        <v>2.720406178083908E-07</v>
+        <v>1.663719440693085E-07</v>
       </c>
       <c r="I37">
-        <v>41876.65848911016</v>
+        <v>22487.29127651314</v>
       </c>
       <c r="J37">
-        <v>41483.26049399843</v>
+        <v>22408.76623580908</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38">
-        <v>1.670691605493371E-05</v>
+        <v>4.719227239896547E-06</v>
       </c>
       <c r="B38">
-        <v>2208954570.101778</v>
+        <v>2666205485.684206</v>
       </c>
       <c r="C38">
-        <v>6.467045502784181E+30</v>
+        <v>1.525795156262905E+25</v>
       </c>
       <c r="D38">
-        <v>5.517735089012294</v>
+        <v>3.98819595013225</v>
       </c>
       <c r="E38">
-        <v>72652.50279114158</v>
+        <v>23741.19620627987</v>
       </c>
       <c r="F38">
-        <v>0.0002353463953871518</v>
+        <v>0.0001330587990173612</v>
       </c>
       <c r="G38">
-        <v>7439.425587333164</v>
+        <v>2411.956801271381</v>
       </c>
       <c r="H38">
-        <v>6.269040123263959E-07</v>
+        <v>2.356227719983843E-07</v>
       </c>
       <c r="I38">
-        <v>72458.97467089824</v>
+        <v>23699.15489445387</v>
       </c>
       <c r="J38">
-        <v>71756.19643137106</v>
+        <v>23529.51691080923</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39">
-        <v>6.159082885367908E-06</v>
+        <v>8.673376717372689E-06</v>
       </c>
       <c r="B39">
-        <v>2590250836.711864</v>
+        <v>3830505087.896635</v>
       </c>
       <c r="C39">
-        <v>1.052628626255437E+33</v>
+        <v>9.935607268201795E+25</v>
       </c>
       <c r="D39">
-        <v>5.552993062422088</v>
+        <v>4.272078909024446</v>
       </c>
       <c r="E39">
-        <v>31401.37337064375</v>
+        <v>63215.79877059019</v>
       </c>
       <c r="F39">
-        <v>0.000136505937048144</v>
+        <v>0.0002890584955818636</v>
       </c>
       <c r="G39">
-        <v>3187.7057484724</v>
+        <v>6402.000255609593</v>
       </c>
       <c r="H39">
-        <v>2.297624408723256E-07</v>
+        <v>4.085862164915996E-07</v>
       </c>
       <c r="I39">
-        <v>31348.51958019039</v>
+        <v>63126.44279442289</v>
       </c>
       <c r="J39">
-        <v>31132.59075792115</v>
+        <v>62745.88864821415</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40">
-        <v>5.080670815910529E-06</v>
+        <v>2.851038198241045E-06</v>
       </c>
       <c r="B40">
-        <v>4118753640.868618</v>
+        <v>2397315255.065523</v>
       </c>
       <c r="C40">
-        <v>3.504571729343002E+28</v>
+        <v>1.999614077162603E+38</v>
       </c>
       <c r="D40">
-        <v>4.601884925509854</v>
+        <v>6.233786414990225</v>
       </c>
       <c r="E40">
-        <v>40168.71891279676</v>
+        <v>13685.99044274406</v>
       </c>
       <c r="F40">
-        <v>0.000336760973759995</v>
+        <v>2.146509226402189E-05</v>
       </c>
       <c r="G40">
-        <v>4040.96248107454</v>
+        <v>1423.408022394583</v>
       </c>
       <c r="H40">
-        <v>2.244081878567064E-07</v>
+        <v>9.551371180691069E-08</v>
       </c>
       <c r="I40">
-        <v>40141.95159080246</v>
+        <v>13625.09157816609</v>
       </c>
       <c r="J40">
-        <v>40007.88239847241</v>
+        <v>13434.50686207297</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41">
-        <v>4.657815757539411E-06</v>
+        <v>2.084264077735422E-06</v>
       </c>
       <c r="B41">
-        <v>8664449001.25732</v>
+        <v>10613768920.33337</v>
       </c>
       <c r="C41">
-        <v>9106124926.23867</v>
+        <v>11704339260.03662</v>
       </c>
       <c r="D41">
         <v>1.05980198019802</v>
       </c>
       <c r="E41">
-        <v>67615.15238531286</v>
+        <v>37319.52684811447</v>
       </c>
       <c r="F41">
-        <v>0.0002180024430635659</v>
+        <v>2.473329858582907E-05</v>
       </c>
       <c r="G41">
-        <v>6903.141479392283</v>
+        <v>4040.261245429394</v>
       </c>
       <c r="H41">
-        <v>5.073627141650497E-07</v>
+        <v>2.270329988481966E-07</v>
       </c>
       <c r="I41">
-        <v>67457.78989546731</v>
+        <v>36976.96178076119</v>
       </c>
       <c r="J41">
-        <v>66865.39032466547</v>
+        <v>36141.23548579655</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42">
-        <v>1.367571283178688E-05</v>
+        <v>4.19357913976215E-06</v>
       </c>
       <c r="B42">
-        <v>1451895839.864731</v>
+        <v>4838652561.482054</v>
       </c>
       <c r="C42">
-        <v>1.132854718025448E+43</v>
+        <v>2.354042923913397E+17</v>
       </c>
       <c r="D42">
-        <v>7.982853791392714</v>
+        <v>2.470289754168974</v>
       </c>
       <c r="E42">
-        <v>40815.05367992478</v>
+        <v>36315.16418601249</v>
       </c>
       <c r="F42">
-        <v>0.0001599914854168276</v>
+        <v>6.758221082113951E-05</v>
       </c>
       <c r="G42">
-        <v>4164.574840654676</v>
+        <v>3776.578882696539</v>
       </c>
       <c r="H42">
-        <v>3.61805731674999E-07</v>
+        <v>2.999555649506474E-07</v>
       </c>
       <c r="I42">
-        <v>40722.75426585567</v>
+        <v>36153.98367035107</v>
       </c>
       <c r="J42">
-        <v>40372.66584419538</v>
+        <v>35649.16901155847</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43">
-        <v>9.319607306149234E-06</v>
+        <v>9.627151211577479E-06</v>
       </c>
       <c r="B43">
-        <v>1774881506.72405</v>
+        <v>1763253116.473062</v>
       </c>
       <c r="C43">
-        <v>7.829779167254874E+41</v>
+        <v>5.836665323592887E+37</v>
       </c>
       <c r="D43">
-        <v>7.504922188112621</v>
+        <v>6.703462252424722</v>
       </c>
       <c r="E43">
-        <v>33769.98387266738</v>
+        <v>34258.90261565877</v>
       </c>
       <c r="F43">
-        <v>0.0001227783018980768</v>
+        <v>8.428691321177897E-05</v>
       </c>
       <c r="G43">
-        <v>3441.776794850503</v>
+        <v>3536.048770489725</v>
       </c>
       <c r="H43">
-        <v>2.61684818249149E-07</v>
+        <v>3.011356974976471E-07</v>
       </c>
       <c r="I43">
-        <v>33698.00786424097</v>
+        <v>34136.50427241005</v>
       </c>
       <c r="J43">
-        <v>33420.79225887959</v>
+        <v>33727.29139834226</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44">
-        <v>3.59556818536054E-06</v>
+        <v>9.276735316622645E-06</v>
       </c>
       <c r="B44">
-        <v>4839381622.238189</v>
+        <v>1595130987.399682</v>
       </c>
       <c r="C44">
-        <v>5.68771477773354E+18</v>
+        <v>3.644921745735154E+28</v>
       </c>
       <c r="D44">
-        <v>2.704281942788766</v>
+        <v>4.872771431066306</v>
       </c>
       <c r="E44">
-        <v>31345.49913844977</v>
+        <v>28746.40827079779</v>
       </c>
       <c r="F44">
-        <v>0.0001662174383565121</v>
+        <v>7.425468939446545E-05</v>
       </c>
       <c r="G44">
-        <v>3175.605452255892</v>
+        <v>3010.366390376406</v>
       </c>
       <c r="H44">
-        <v>2.418970865063219E-07</v>
+        <v>3.895466193952311E-07</v>
       </c>
       <c r="I44">
-        <v>31299.88187354876</v>
+        <v>28595.60208935709</v>
       </c>
       <c r="J44">
-        <v>31106.92652055038</v>
+        <v>28147.66017421712</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45">
-        <v>5.573348093228181E-06</v>
+        <v>3.574749216675071E-06</v>
       </c>
       <c r="B45">
-        <v>3757703315.061712</v>
+        <v>9266882263.804161</v>
       </c>
       <c r="C45">
-        <v>1.741973382576292E+27</v>
+        <v>9894634204.928934</v>
       </c>
       <c r="D45">
-        <v>4.390099069867869</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E45">
-        <v>40036.91928659791</v>
+        <v>55585.56290461633</v>
       </c>
       <c r="F45">
-        <v>9.790496086290838E-05</v>
+        <v>0.0001012197989861364</v>
       </c>
       <c r="G45">
-        <v>4098.083950051844</v>
+        <v>5751.007599214123</v>
       </c>
       <c r="H45">
-        <v>2.564701481873757E-07</v>
+        <v>3.893873350606232E-07</v>
       </c>
       <c r="I45">
-        <v>39932.03926282896</v>
+        <v>55371.72811711358</v>
       </c>
       <c r="J45">
-        <v>39549.44939498423</v>
+        <v>54672.25521095924</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46">
-        <v>1.115475797158113E-05</v>
+        <v>3.521914597535473E-06</v>
       </c>
       <c r="B46">
-        <v>950101539.0909799</v>
+        <v>4518774950.802546</v>
       </c>
       <c r="C46">
-        <v>3.174486884708316E+36</v>
+        <v>10175968846521.33</v>
       </c>
       <c r="D46">
-        <v>6.576470882277751</v>
+        <v>1.662707620773915</v>
       </c>
       <c r="E46">
-        <v>21719.01334483857</v>
+        <v>27443.62655201216</v>
       </c>
       <c r="F46">
-        <v>1.696751966900452E-05</v>
+        <v>0.0001193610545257885</v>
       </c>
       <c r="G46">
-        <v>2581.223211155017</v>
+        <v>2809.953776433768</v>
       </c>
       <c r="H46">
-        <v>3.553045068597695E-07</v>
+        <v>3.169740373864752E-07</v>
       </c>
       <c r="I46">
-        <v>21264.21125964839</v>
+        <v>27370.74752842044</v>
       </c>
       <c r="J46">
-        <v>20489.0842059492</v>
+        <v>27105.87433801279</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47">
-        <v>1.460464215324009E-06</v>
+        <v>5.817031862700905E-06</v>
       </c>
       <c r="B47">
-        <v>9125310182.416277</v>
+        <v>2722154845.010031</v>
       </c>
       <c r="C47">
-        <v>10279264286.32908</v>
+        <v>5.283849892737631E+30</v>
       </c>
       <c r="D47">
-        <v>1.05980198019802</v>
+        <v>5.090228182565505</v>
       </c>
       <c r="E47">
-        <v>22300.08296559034</v>
+        <v>30918.26415206577</v>
       </c>
       <c r="F47">
-        <v>0.0001505781594026385</v>
+        <v>4.969257632735637E-05</v>
       </c>
       <c r="G47">
-        <v>2251.212119372642</v>
+        <v>3223.361131487504</v>
       </c>
       <c r="H47">
-        <v>1.590842417990272E-07</v>
+        <v>2.348952816130335E-07</v>
       </c>
       <c r="I47">
-        <v>22276.52316246411</v>
+        <v>30772.11446730919</v>
       </c>
       <c r="J47">
-        <v>22169.35651686813</v>
+        <v>30323.29851073797</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48">
-        <v>2.122006834392825E-06</v>
+        <v>6.097418622329566E-06</v>
       </c>
       <c r="B48">
-        <v>10170923978.42132</v>
+        <v>3597067545.875651</v>
       </c>
       <c r="C48">
-        <v>11203960863.81577</v>
+        <v>1.206846603780981E+25</v>
       </c>
       <c r="D48">
-        <v>1.05980198019802</v>
+        <v>4.00736632225754</v>
       </c>
       <c r="E48">
-        <v>36165.71585941695</v>
+        <v>41456.52180279859</v>
       </c>
       <c r="F48">
-        <v>9.297611014666856E-05</v>
+        <v>0.000104127473861159</v>
       </c>
       <c r="G48">
-        <v>3697.490719372491</v>
+        <v>4254.300197618683</v>
       </c>
       <c r="H48">
-        <v>2.311442107240154E-07</v>
+        <v>3.032157572303558E-07</v>
       </c>
       <c r="I48">
-        <v>36075.80571116052</v>
+        <v>41335.80178353324</v>
       </c>
       <c r="J48">
-        <v>35743.18851629481</v>
+        <v>40907.99990787836</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49">
-        <v>3.085262618537489E-06</v>
+        <v>4.166123776299457E-06</v>
       </c>
       <c r="B49">
-        <v>4480221342.800673</v>
+        <v>4448181414.034302</v>
       </c>
       <c r="C49">
-        <v>1.099507028813147E+19</v>
+        <v>906628504142842.2</v>
       </c>
       <c r="D49">
-        <v>2.741441732952179</v>
+        <v>2.031640950392333</v>
       </c>
       <c r="E49">
-        <v>24990.7302604295</v>
+        <v>32588.19105705373</v>
       </c>
       <c r="F49">
-        <v>5.739184872688701E-05</v>
+        <v>5.991282250609077E-05</v>
       </c>
       <c r="G49">
-        <v>2579.646432727905</v>
+        <v>3423.489648804954</v>
       </c>
       <c r="H49">
-        <v>2.055987568938707E-07</v>
+        <v>3.363821440524629E-07</v>
       </c>
       <c r="I49">
-        <v>24901.20425300177</v>
+        <v>32405.22378694309</v>
       </c>
       <c r="J49">
-        <v>24602.12823431802</v>
+        <v>31873.70020113766</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50">
-        <v>2.29262390699503E-06</v>
+        <v>3.062985948373662E-06</v>
       </c>
       <c r="B50">
-        <v>3317104054.585199</v>
+        <v>6454124360.954324</v>
       </c>
       <c r="C50">
-        <v>4.128536059647409E+27</v>
+        <v>1154221433867010</v>
       </c>
       <c r="D50">
-        <v>4.235103866494857</v>
+        <v>1.996680148397073</v>
       </c>
       <c r="E50">
-        <v>14445.4670943234</v>
+        <v>34590.27376206456</v>
       </c>
       <c r="F50">
-        <v>0.0001331281948055185</v>
+        <v>0.0001153746627226242</v>
       </c>
       <c r="G50">
-        <v>1455.172431263591</v>
+        <v>3526.431238729392</v>
       </c>
       <c r="H50">
-        <v>1.088063863189261E-07</v>
+        <v>2.498036155827859E-07</v>
       </c>
       <c r="I50">
-        <v>14433.66073673312</v>
+        <v>34515.38058148351</v>
       </c>
       <c r="J50">
-        <v>14376.93377294036</v>
+        <v>34228.09574510952</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51">
-        <v>2.781155463702577E-06</v>
+        <v>4.155953557410702E-06</v>
       </c>
       <c r="B51">
-        <v>7205234859.859289</v>
+        <v>3998931213.415319</v>
       </c>
       <c r="C51">
-        <v>514396263888071.8</v>
+        <v>2.343562962296764E+24</v>
       </c>
       <c r="D51">
-        <v>1.918131165643087</v>
+        <v>3.775000928174281</v>
       </c>
       <c r="E51">
-        <v>35008.29767947801</v>
+        <v>31124.19769468504</v>
       </c>
       <c r="F51">
-        <v>5.662403818078617E-05</v>
+        <v>0.0001840030266726534</v>
       </c>
       <c r="G51">
-        <v>3629.939382840871</v>
+        <v>3145.475595876032</v>
       </c>
       <c r="H51">
-        <v>2.32030951637861E-07</v>
+        <v>2.171362390630465E-07</v>
       </c>
       <c r="I51">
-        <v>34864.84255181905</v>
+        <v>31087.46899867668</v>
       </c>
       <c r="J51">
-        <v>34404.4133508077</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52">
-        <v>6.112717839530481E-06</v>
-      </c>
-      <c r="B52">
-        <v>4580788002.957466</v>
-      </c>
-      <c r="C52">
-        <v>1.548928356568794E+22</v>
-      </c>
-      <c r="D52">
-        <v>3.437163172702742</v>
-      </c>
-      <c r="E52">
-        <v>51872.51838489764</v>
-      </c>
-      <c r="F52">
-        <v>0.0001866312102759807</v>
-      </c>
-      <c r="G52">
-        <v>5273.376678353913</v>
-      </c>
-      <c r="H52">
-        <v>3.442966976035783E-07</v>
-      </c>
-      <c r="I52">
-        <v>51776.82411838191</v>
-      </c>
-      <c r="J52">
-        <v>51394.5779059487</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53">
-        <v>3.823507336382444E-06</v>
-      </c>
-      <c r="B53">
-        <v>5131975633.949746</v>
-      </c>
-      <c r="C53">
-        <v>10635538896169.75</v>
-      </c>
-      <c r="D53">
-        <v>1.660436375380759</v>
-      </c>
-      <c r="E53">
-        <v>33780.79089287356</v>
-      </c>
-      <c r="F53">
-        <v>0.000310756218994979</v>
-      </c>
-      <c r="G53">
-        <v>3411.768844908003</v>
-      </c>
-      <c r="H53">
-        <v>3.443541860072679E-07</v>
-      </c>
-      <c r="I53">
-        <v>33743.35783107283</v>
-      </c>
-      <c r="J53">
-        <v>33574.86571514206</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54">
-        <v>4.865100854469071E-06</v>
-      </c>
-      <c r="B54">
-        <v>5786685993.900639</v>
-      </c>
-      <c r="C54">
-        <v>2.039471734107798E+20</v>
-      </c>
-      <c r="D54">
-        <v>3.021779510312499</v>
-      </c>
-      <c r="E54">
-        <v>51373.30712030411</v>
-      </c>
-      <c r="F54">
-        <v>0.0001533933048047179</v>
-      </c>
-      <c r="G54">
-        <v>5228.444219872576</v>
-      </c>
-      <c r="H54">
-        <v>3.022798081919417E-07</v>
-      </c>
-      <c r="I54">
-        <v>51272.06988936837</v>
-      </c>
-      <c r="J54">
-        <v>50874.30003466793</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55">
-        <v>4.076288756477878E-06</v>
-      </c>
-      <c r="B55">
-        <v>2872962917.449002</v>
-      </c>
-      <c r="C55">
-        <v>4.020726148753338E+23</v>
-      </c>
-      <c r="D55">
-        <v>3.656067861702589</v>
-      </c>
-      <c r="E55">
-        <v>21858.48200128725</v>
-      </c>
-      <c r="F55">
-        <v>0.0001215930867087059</v>
-      </c>
-      <c r="G55">
-        <v>2221.212938177858</v>
-      </c>
-      <c r="H55">
-        <v>2.185832209099376E-07</v>
-      </c>
-      <c r="I55">
-        <v>21819.18784789932</v>
-      </c>
-      <c r="J55">
-        <v>21661.22062690066</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56">
-        <v>6.417885566491359E-06</v>
-      </c>
-      <c r="B56">
-        <v>6783930491.723097</v>
-      </c>
-      <c r="C56">
-        <v>5.890814884352142E+17</v>
-      </c>
-      <c r="D56">
-        <v>2.570162296645403</v>
-      </c>
-      <c r="E56">
-        <v>78051.40971545958</v>
-      </c>
-      <c r="F56">
-        <v>0.0002218774327853875</v>
-      </c>
-      <c r="G56">
-        <v>7946.686143997797</v>
-      </c>
-      <c r="H56">
-        <v>4.470796819297233E-07</v>
-      </c>
-      <c r="I56">
-        <v>77894.13730162421</v>
-      </c>
-      <c r="J56">
-        <v>77279.66773567486</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57">
-        <v>4.511431921606499E-06</v>
-      </c>
-      <c r="B57">
-        <v>4390946847.52358</v>
-      </c>
-      <c r="C57">
-        <v>2.79629932863222E+21</v>
-      </c>
-      <c r="D57">
-        <v>3.242810405537142</v>
-      </c>
-      <c r="E57">
-        <v>36463.2371832403</v>
-      </c>
-      <c r="F57">
-        <v>0.0001101001438555402</v>
-      </c>
-      <c r="G57">
-        <v>3725.557546051296</v>
-      </c>
-      <c r="H57">
-        <v>2.658280413946709E-07</v>
-      </c>
-      <c r="I57">
-        <v>36375.19959687666</v>
-      </c>
-      <c r="J57">
-        <v>36046.97010430585</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58">
-        <v>1.206215202573971E-05</v>
-      </c>
-      <c r="B58">
-        <v>1781173751.903831</v>
-      </c>
-      <c r="C58">
-        <v>1.323965756899785E+32</v>
-      </c>
-      <c r="D58">
-        <v>5.67266433188987</v>
-      </c>
-      <c r="E58">
-        <v>42415.15024318299</v>
-      </c>
-      <c r="F58">
-        <v>0.000222354651612595</v>
-      </c>
-      <c r="G58">
-        <v>4317.263184488126</v>
-      </c>
-      <c r="H58">
-        <v>4.412195922209026E-07</v>
-      </c>
-      <c r="I58">
-        <v>42330.98562077207</v>
-      </c>
-      <c r="J58">
-        <v>42000.87271427526</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59">
-        <v>2.502370472933053E-06</v>
-      </c>
-      <c r="B59">
-        <v>7787290454.143358</v>
-      </c>
-      <c r="C59">
-        <v>500379910538687.9</v>
-      </c>
-      <c r="D59">
-        <v>1.902596581787244</v>
-      </c>
-      <c r="E59">
-        <v>33978.40699428821</v>
-      </c>
-      <c r="F59">
-        <v>7.283642382881473E-05</v>
-      </c>
-      <c r="G59">
-        <v>3485.891810204838</v>
-      </c>
-      <c r="H59">
-        <v>2.097190732585596E-07</v>
-      </c>
-      <c r="I59">
-        <v>33880.5724267593</v>
-      </c>
-      <c r="J59">
-        <v>33532.78695185664</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60">
-        <v>7.608102480869781E-06</v>
-      </c>
-      <c r="B60">
-        <v>2180638710.896625</v>
-      </c>
-      <c r="C60">
-        <v>4.947121117947757E+24</v>
-      </c>
-      <c r="D60">
-        <v>4.030495887321324</v>
-      </c>
-      <c r="E60">
-        <v>31427.13860416858</v>
-      </c>
-      <c r="F60">
-        <v>8.640912259989358E-05</v>
-      </c>
-      <c r="G60">
-        <v>3265.960959925849</v>
-      </c>
-      <c r="H60">
-        <v>3.765207823046227E-07</v>
-      </c>
-      <c r="I60">
-        <v>31290.19738249193</v>
-      </c>
-      <c r="J60">
-        <v>30858.85290960803</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61">
-        <v>3.267981356184607E-06</v>
-      </c>
-      <c r="B61">
-        <v>5910422508.396195</v>
-      </c>
-      <c r="C61">
-        <v>142475340186.4799</v>
-      </c>
-      <c r="D61">
-        <v>1.303407172722104</v>
-      </c>
-      <c r="E61">
-        <v>32724.66900889602</v>
-      </c>
-      <c r="F61">
-        <v>0.0001809607255950918</v>
-      </c>
-      <c r="G61">
-        <v>3325.994198690203</v>
-      </c>
-      <c r="H61">
-        <v>3.288833416808629E-07</v>
-      </c>
-      <c r="I61">
-        <v>32665.19423356201</v>
-      </c>
-      <c r="J61">
-        <v>32426.74388697701</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62">
-        <v>7.009475933951465E-06</v>
-      </c>
-      <c r="B62">
-        <v>3250565846.618239</v>
-      </c>
-      <c r="C62">
-        <v>5.702428094586084E+24</v>
-      </c>
-      <c r="D62">
-        <v>3.988179393057766</v>
-      </c>
-      <c r="E62">
-        <v>43179.59237320254</v>
-      </c>
-      <c r="F62">
-        <v>5.718822137509037E-05</v>
-      </c>
-      <c r="G62">
-        <v>4555.778968319989</v>
-      </c>
-      <c r="H62">
-        <v>3.499721016927484E-07</v>
-      </c>
-      <c r="I62">
-        <v>42915.34822764728</v>
-      </c>
-      <c r="J62">
-        <v>42169.52835722938</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63">
-        <v>4.341834635558163E-06</v>
-      </c>
-      <c r="B63">
-        <v>1974239092.84479</v>
-      </c>
-      <c r="C63">
-        <v>8.712763896876548E+36</v>
-      </c>
-      <c r="D63">
-        <v>6.174249794390916</v>
-      </c>
-      <c r="E63">
-        <v>17131.55878867341</v>
-      </c>
-      <c r="F63">
-        <v>3.935844539342785E-05</v>
-      </c>
-      <c r="G63">
-        <v>1770.653440143049</v>
-      </c>
-      <c r="H63">
-        <v>1.467736080684434E-07</v>
-      </c>
-      <c r="I63">
-        <v>17067.67260947818</v>
-      </c>
-      <c r="J63">
-        <v>16856.75539081234</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64">
-        <v>2.976118823481458E-06</v>
-      </c>
-      <c r="B64">
-        <v>8017310816.03373</v>
-      </c>
-      <c r="C64">
-        <v>8654754955.813782</v>
-      </c>
-      <c r="D64">
-        <v>1.05980198019802</v>
-      </c>
-      <c r="E64">
-        <v>40008.37926121343</v>
-      </c>
-      <c r="F64">
-        <v>0.0001034471817413376</v>
-      </c>
-      <c r="G64">
-        <v>4113.677467753854</v>
-      </c>
-      <c r="H64">
-        <v>3.241802172005449E-07</v>
-      </c>
-      <c r="I64">
-        <v>39883.00199273285</v>
-      </c>
-      <c r="J64">
-        <v>39447.73447183551</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65">
-        <v>8.859094345967784E-07</v>
-      </c>
-      <c r="B65">
-        <v>15519156206.40494</v>
-      </c>
-      <c r="C65">
-        <v>18012152124.16476</v>
-      </c>
-      <c r="D65">
-        <v>1.05980198019802</v>
-      </c>
-      <c r="E65">
-        <v>23003.37503971799</v>
-      </c>
-      <c r="F65">
-        <v>9.859425468498081E-05</v>
-      </c>
-      <c r="G65">
-        <v>2320.60070393332</v>
-      </c>
-      <c r="H65">
-        <v>9.649961240177776E-08</v>
-      </c>
-      <c r="I65">
-        <v>22980.86037309407</v>
-      </c>
-      <c r="J65">
-        <v>22876.70402923562</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66">
-        <v>2.645670582596059E-06</v>
-      </c>
-      <c r="B66">
-        <v>4104895592.606637</v>
-      </c>
-      <c r="C66">
-        <v>4.253368990830292E+27</v>
-      </c>
-      <c r="D66">
-        <v>4.2567882171419</v>
-      </c>
-      <c r="E66">
-        <v>20648.38860841596</v>
-      </c>
-      <c r="F66">
-        <v>0.0001131028011995705</v>
-      </c>
-      <c r="G66">
-        <v>2085.379712952571</v>
-      </c>
-      <c r="H66">
-        <v>1.250152927903636E-07</v>
-      </c>
-      <c r="I66">
-        <v>20625.56543940377</v>
-      </c>
-      <c r="J66">
-        <v>20522.7771541489</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67">
-        <v>1.963514863295178E-05</v>
-      </c>
-      <c r="B67">
-        <v>836565989.4069779</v>
-      </c>
-      <c r="C67">
-        <v>1.148883644981741E+55</v>
-      </c>
-      <c r="D67">
-        <v>10.81185139375873</v>
-      </c>
-      <c r="E67">
-        <v>34747.37365496664</v>
-      </c>
-      <c r="F67">
-        <v>0.000149969064827851</v>
-      </c>
-      <c r="G67">
-        <v>3555.331755322266</v>
-      </c>
-      <c r="H67">
-        <v>3.864933279253623E-07</v>
-      </c>
-      <c r="I67">
-        <v>34657.82433293819</v>
-      </c>
-      <c r="J67">
-        <v>34329.71707195408</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68">
-        <v>3.116599447357656E-06</v>
-      </c>
-      <c r="B68">
-        <v>6850259328.626147</v>
-      </c>
-      <c r="C68">
-        <v>40265362740299.38</v>
-      </c>
-      <c r="D68">
-        <v>1.731290383981964</v>
-      </c>
-      <c r="E68">
-        <v>36898.46770335839</v>
-      </c>
-      <c r="F68">
-        <v>0.000155262946860494</v>
-      </c>
-      <c r="G68">
-        <v>3748.614872044337</v>
-      </c>
-      <c r="H68">
-        <v>2.747632511166796E-07</v>
-      </c>
-      <c r="I68">
-        <v>36833.16981257116</v>
-      </c>
-      <c r="J68">
-        <v>36569.64845504517</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69">
-        <v>2.563714768978536E-06</v>
-      </c>
-      <c r="B69">
-        <v>8010442930.387486</v>
-      </c>
-      <c r="C69">
-        <v>8724822331.350859</v>
-      </c>
-      <c r="D69">
-        <v>1.05980198019802</v>
-      </c>
-      <c r="E69">
-        <v>34416.21091384623</v>
-      </c>
-      <c r="F69">
-        <v>0.0001076609439023949</v>
-      </c>
-      <c r="G69">
-        <v>3521.965068934754</v>
-      </c>
-      <c r="H69">
-        <v>2.79258208405631E-07</v>
-      </c>
-      <c r="I69">
-        <v>34326.93982767942</v>
-      </c>
-      <c r="J69">
-        <v>34000.42275009239</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70">
-        <v>4.239442705615301E-06</v>
-      </c>
-      <c r="B70">
-        <v>2830709387.953676</v>
-      </c>
-      <c r="C70">
-        <v>9.819781545966848E+23</v>
-      </c>
-      <c r="D70">
-        <v>3.737325731500037</v>
-      </c>
-      <c r="E70">
-        <v>22504.36242973758</v>
-      </c>
-      <c r="F70">
-        <v>5.943942194675944E-05</v>
-      </c>
-      <c r="G70">
-        <v>2326.531666220965</v>
-      </c>
-      <c r="H70">
-        <v>2.233180830669668E-07</v>
-      </c>
-      <c r="I70">
-        <v>22419.81195946291</v>
-      </c>
-      <c r="J70">
-        <v>22141.28974612356</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71">
-        <v>6.16604833435539E-06</v>
-      </c>
-      <c r="B71">
-        <v>1128800390.700567</v>
-      </c>
-      <c r="C71">
-        <v>1.857778667940053E+42</v>
-      </c>
-      <c r="D71">
-        <v>7.391007572203891</v>
-      </c>
-      <c r="E71">
-        <v>14196.15608059557</v>
-      </c>
-      <c r="F71">
-        <v>6.111654302971549E-05</v>
-      </c>
-      <c r="G71">
-        <v>1456.346005181634</v>
-      </c>
-      <c r="H71">
-        <v>1.756997444680251E-07</v>
-      </c>
-      <c r="I71">
-        <v>14155.34452823771</v>
-      </c>
-      <c r="J71">
-        <v>14010.20325742304</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72">
-        <v>9.420931392404494E-06</v>
-      </c>
-      <c r="B72">
-        <v>4122978580.901768</v>
-      </c>
-      <c r="C72">
-        <v>3.514865627136587E+24</v>
-      </c>
-      <c r="D72">
-        <v>4.002075021083737</v>
-      </c>
-      <c r="E72">
-        <v>73414.09243487478</v>
-      </c>
-      <c r="F72">
-        <v>0.0001550876402320215</v>
-      </c>
-      <c r="G72">
-        <v>7541.222484356183</v>
-      </c>
-      <c r="H72">
-        <v>4.690071980833294E-07</v>
-      </c>
-      <c r="I72">
-        <v>73192.07772279844</v>
-      </c>
-      <c r="J72">
-        <v>72413.55619526183</v>
+        <v>30924.44923350254</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Current Waveform CIGRE.xlsx
+++ b/Data/output/DIR Current Waveform CIGRE.xlsx
@@ -438,1602 +438,1602 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>2.043358282330331E-06</v>
+        <v>3.095093905887314E-06</v>
       </c>
       <c r="B2">
-        <v>5127236195.060856</v>
+        <v>9853801714.845154</v>
       </c>
       <c r="C2">
-        <v>2.352276985986371E+19</v>
+        <v>114763283953533.6</v>
       </c>
       <c r="D2">
-        <v>2.734480607992634</v>
+        <v>1.784262719727796</v>
       </c>
       <c r="E2">
-        <v>18915.70217219382</v>
+        <v>52879.57550962448</v>
       </c>
       <c r="F2">
-        <v>5.461268944045677E-05</v>
+        <v>0.0001049680591863113</v>
       </c>
       <c r="G2">
-        <v>1934.092539166727</v>
+        <v>5409.733796954204</v>
       </c>
       <c r="H2">
-        <v>1.364097957499011E-07</v>
+        <v>2.685896539145266E-07</v>
       </c>
       <c r="I2">
-        <v>18868.45514780789</v>
+        <v>52744.26856963365</v>
       </c>
       <c r="J2">
-        <v>18693.88654113083</v>
+        <v>52247.55476044018</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>6.049362565616766E-06</v>
+        <v>2.803551473117002E-06</v>
       </c>
       <c r="B3">
-        <v>4622025538.021038</v>
+        <v>5396143115.999586</v>
       </c>
       <c r="C3">
-        <v>7126725869823.13</v>
+        <v>2.689812118131795E+17</v>
       </c>
       <c r="D3">
-        <v>1.661037966821092</v>
+        <v>2.426262082680806</v>
       </c>
       <c r="E3">
-        <v>48405.82016558199</v>
+        <v>26940.10806943099</v>
       </c>
       <c r="F3">
-        <v>8.179673287190483E-05</v>
+        <v>0.0001586964091983253</v>
       </c>
       <c r="G3">
-        <v>5130.702301844288</v>
+        <v>2725.011696809801</v>
       </c>
       <c r="H3">
-        <v>5.447208022848533E-07</v>
+        <v>2.029081155015346E-07</v>
       </c>
       <c r="I3">
-        <v>48083.46429304189</v>
+        <v>26905.66263624576</v>
       </c>
       <c r="J3">
-        <v>47199.6191764929</v>
+        <v>26755.52712314299</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>8.661130081977954E-06</v>
+        <v>1.408128586654047E-06</v>
       </c>
       <c r="B4">
-        <v>2757096644.118438</v>
+        <v>10359636514.33138</v>
       </c>
       <c r="C4">
-        <v>1.500401075251696E+29</v>
+        <v>11695174123.46207</v>
       </c>
       <c r="D4">
-        <v>4.924129993298621</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E4">
-        <v>46405.16465915993</v>
+        <v>24412.28929135861</v>
       </c>
       <c r="F4">
-        <v>8.492154329385757E-05</v>
+        <v>0.0001299728289110696</v>
       </c>
       <c r="G4">
-        <v>4817.71788322706</v>
+        <v>2467.157405858557</v>
       </c>
       <c r="H4">
-        <v>3.603099387378258E-07</v>
+        <v>1.533834695933972E-07</v>
       </c>
       <c r="I4">
-        <v>46208.27419548098</v>
+        <v>24383.47987277783</v>
       </c>
       <c r="J4">
-        <v>45583.00366147791</v>
+        <v>24255.61092724638</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>2.182714522862528E-06</v>
+        <v>2.929518974950595E-06</v>
       </c>
       <c r="B5">
-        <v>9662164446.907743</v>
+        <v>2403805238.197168</v>
       </c>
       <c r="C5">
-        <v>10625589062.58301</v>
+        <v>4.230775032080347E+29</v>
       </c>
       <c r="D5">
-        <v>1.05980198019802</v>
+        <v>4.68357695233852</v>
       </c>
       <c r="E5">
-        <v>35311.61406178008</v>
+        <v>13550.98178449532</v>
       </c>
       <c r="F5">
-        <v>0.0001401555542107188</v>
+        <v>0.0001455537543404936</v>
       </c>
       <c r="G5">
-        <v>3585.073096147407</v>
+        <v>1365.773688045649</v>
       </c>
       <c r="H5">
-        <v>2.377569277562034E-07</v>
+        <v>1.274086037064629E-07</v>
       </c>
       <c r="I5">
-        <v>35251.71218403631</v>
+        <v>13539.1201071663</v>
       </c>
       <c r="J5">
-        <v>35007.45426267909</v>
+        <v>13482.93934392441</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>6.174055462529555E-06</v>
+        <v>1.940607173306379E-06</v>
       </c>
       <c r="B6">
-        <v>4833855117.086716</v>
+        <v>8463786771.864015</v>
       </c>
       <c r="C6">
-        <v>5.253906479416595E+19</v>
+        <v>9373391406.618982</v>
       </c>
       <c r="D6">
-        <v>2.964336778034586</v>
+        <v>1.059801980198019</v>
       </c>
       <c r="E6">
-        <v>54270.09903429714</v>
+        <v>27529.07443180045</v>
       </c>
       <c r="F6">
-        <v>0.0005854259194709228</v>
+        <v>7.787802709766725E-05</v>
       </c>
       <c r="G6">
-        <v>5459.469220591127</v>
+        <v>2820.157561554607</v>
       </c>
       <c r="H6">
-        <v>3.890524930498245E-07</v>
+        <v>2.113848580170162E-07</v>
       </c>
       <c r="I6">
-        <v>54234.03312634001</v>
+        <v>27454.35207805095</v>
       </c>
       <c r="J6">
-        <v>54053.29274278641</v>
+        <v>27184.38851417617</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>4.367205030723479E-06</v>
+        <v>1.318301668610805E-05</v>
       </c>
       <c r="B7">
-        <v>2856465666.119994</v>
+        <v>3075355422.149995</v>
       </c>
       <c r="C7">
-        <v>2.969255878912619E+24</v>
+        <v>3.559146120505468E+28</v>
       </c>
       <c r="D7">
-        <v>3.832210345270585</v>
+        <v>4.933018941378005</v>
       </c>
       <c r="E7">
-        <v>23511.40647743947</v>
+        <v>78721.38441053174</v>
       </c>
       <c r="F7">
-        <v>3.992503235589201E-05</v>
+        <v>0.000171505189497715</v>
       </c>
       <c r="G7">
-        <v>2470.590442737808</v>
+        <v>8098.328992240339</v>
       </c>
       <c r="H7">
-        <v>2.253769857343598E-07</v>
+        <v>5.475408074301736E-07</v>
       </c>
       <c r="I7">
-        <v>23378.68448300185</v>
+        <v>78470.06157587934</v>
       </c>
       <c r="J7">
-        <v>22993.81290118055</v>
+        <v>77602.13196868681</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>1.666562507067209E-06</v>
+        <v>2.469553069999228E-06</v>
       </c>
       <c r="B8">
-        <v>5658796267.101504</v>
+        <v>8606848233.861671</v>
       </c>
       <c r="C8">
-        <v>39540235282408.82</v>
+        <v>1881637230950350</v>
       </c>
       <c r="D8">
-        <v>1.710083916189186</v>
+        <v>1.995624322293021</v>
       </c>
       <c r="E8">
-        <v>16303.24117036523</v>
+        <v>37231.02451491402</v>
       </c>
       <c r="F8">
-        <v>4.955232819907918E-05</v>
+        <v>6.118314289217669E-05</v>
       </c>
       <c r="G8">
-        <v>1674.108014895638</v>
+        <v>3833.43905810044</v>
       </c>
       <c r="H8">
-        <v>1.478638547920945E-07</v>
+        <v>2.014669950473508E-07</v>
       </c>
       <c r="I8">
-        <v>16254.59239496621</v>
+        <v>37108.42828534843</v>
       </c>
       <c r="J8">
-        <v>16083.36136528774</v>
+        <v>36688.76647443824</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>1.170769350922742E-05</v>
+        <v>3.264251093212967E-06</v>
       </c>
       <c r="B9">
-        <v>4291456709.250612</v>
+        <v>1982746345.95714</v>
       </c>
       <c r="C9">
-        <v>8.398126459924264E+25</v>
+        <v>1.197140993040701E+33</v>
       </c>
       <c r="D9">
-        <v>4.333324216259731</v>
+        <v>5.356340940737125</v>
       </c>
       <c r="E9">
-        <v>95717.25914640771</v>
+        <v>12693.18086164122</v>
       </c>
       <c r="F9">
-        <v>0.0006650731564701839</v>
+        <v>4.76769592243367E-05</v>
       </c>
       <c r="G9">
-        <v>9642.29702543106</v>
+        <v>1299.475407096821</v>
       </c>
       <c r="H9">
-        <v>5.448332565616591E-07</v>
+        <v>1.258601743282481E-07</v>
       </c>
       <c r="I9">
-        <v>95638.84680108518</v>
+        <v>12659.67272727156</v>
       </c>
       <c r="J9">
-        <v>95262.27403020079</v>
+        <v>12537.69375883809</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>3.758037236363823E-06</v>
+        <v>1.152100710041511E-05</v>
       </c>
       <c r="B10">
-        <v>1970502123.476547</v>
+        <v>1430718753.612805</v>
       </c>
       <c r="C10">
-        <v>4.869719605757695E+28</v>
+        <v>1.010253595827242E+41</v>
       </c>
       <c r="D10">
-        <v>4.600299845463315</v>
+        <v>7.465217154868848</v>
       </c>
       <c r="E10">
-        <v>14266.27962249726</v>
+        <v>33652.5268569556</v>
       </c>
       <c r="F10">
-        <v>3.843155803613785E-05</v>
+        <v>0.0001186440909574217</v>
       </c>
       <c r="G10">
-        <v>1482.100123995225</v>
+        <v>3448.256938150904</v>
       </c>
       <c r="H10">
-        <v>1.660388973100136E-07</v>
+        <v>3.251518780620219E-07</v>
       </c>
       <c r="I10">
-        <v>14204.64388722448</v>
+        <v>33560.299909783</v>
       </c>
       <c r="J10">
-        <v>14009.98973346848</v>
+        <v>33227.96631137377</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>5.858077687177371E-06</v>
+        <v>4.518399018459578E-06</v>
       </c>
       <c r="B11">
-        <v>3469954879.280107</v>
+        <v>4432273694.945361</v>
       </c>
       <c r="C11">
-        <v>8.452782261316507E+34</v>
+        <v>4.850478680143997E+19</v>
       </c>
       <c r="D11">
-        <v>5.872487884195206</v>
+        <v>2.915457243781239</v>
       </c>
       <c r="E11">
-        <v>40287.07590327971</v>
+        <v>36443.46674827151</v>
       </c>
       <c r="F11">
-        <v>0.0001333602561224985</v>
+        <v>8.84322161046498E-05</v>
       </c>
       <c r="G11">
-        <v>4085.127822020782</v>
+        <v>3751.234092289719</v>
       </c>
       <c r="H11">
-        <v>2.075166892260914E-07</v>
+        <v>2.881873409637825E-07</v>
       </c>
       <c r="I11">
-        <v>40224.38675695437</v>
+        <v>36324.70295109088</v>
       </c>
       <c r="J11">
-        <v>39963.38921440972</v>
+        <v>35916.9524878908</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>2.550920439751627E-06</v>
+        <v>4.632117655060477E-06</v>
       </c>
       <c r="B12">
-        <v>5990385544.499911</v>
+        <v>2461058313.450615</v>
       </c>
       <c r="C12">
-        <v>370945367810.4188</v>
+        <v>1.788514141836639E+25</v>
       </c>
       <c r="D12">
-        <v>1.370111949773192</v>
+        <v>4.003023344534324</v>
       </c>
       <c r="E12">
-        <v>26048.59597849682</v>
+        <v>21585.13252383699</v>
       </c>
       <c r="F12">
-        <v>5.280867459609441E-05</v>
+        <v>4.823021269817529E-05</v>
       </c>
       <c r="G12">
-        <v>2716.437243666883</v>
+        <v>2251.379363587061</v>
       </c>
       <c r="H12">
-        <v>2.513365401524873E-07</v>
+        <v>2.305574754518495E-07</v>
       </c>
       <c r="I12">
-        <v>25924.62081647771</v>
+        <v>21481.94795583326</v>
       </c>
       <c r="J12">
-        <v>25544.72103164676</v>
+        <v>21166.19560712307</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
-        <v>3.696422512669191E-06</v>
+        <v>4.595046506284519E-06</v>
       </c>
       <c r="B13">
-        <v>2512021592.575085</v>
+        <v>3960046346.616693</v>
       </c>
       <c r="C13">
-        <v>4.163573064086583E+23</v>
+        <v>3.394086547154097E+23</v>
       </c>
       <c r="D13">
-        <v>3.648868581803006</v>
+        <v>3.642154997032612</v>
       </c>
       <c r="E13">
-        <v>17396.20144871652</v>
+        <v>33957.77778521121</v>
       </c>
       <c r="F13">
-        <v>3.442738055485639E-05</v>
+        <v>0.000118067849571406</v>
       </c>
       <c r="G13">
-        <v>1829.905378568315</v>
+        <v>3459.755182874702</v>
       </c>
       <c r="H13">
-        <v>1.985289150062312E-07</v>
+        <v>2.471590390528804E-07</v>
       </c>
       <c r="I13">
-        <v>17295.8845223869</v>
+        <v>33886.6917803739</v>
       </c>
       <c r="J13">
-        <v>17007.03456838597</v>
+        <v>33611.64044239766</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
-        <v>5.329632439916942E-06</v>
+        <v>2.625553859273501E-06</v>
       </c>
       <c r="B14">
-        <v>8666670562.075039</v>
+        <v>6360985898.668345</v>
       </c>
       <c r="C14">
-        <v>42266951122011.14</v>
+        <v>23520679626.50256</v>
       </c>
       <c r="D14">
-        <v>1.748053129833145</v>
+        <v>1.153979220195431</v>
       </c>
       <c r="E14">
-        <v>80011.41707986225</v>
+        <v>28117.2696955382</v>
       </c>
       <c r="F14">
-        <v>0.0001432714035481565</v>
+        <v>0.0001053332453925102</v>
       </c>
       <c r="G14">
-        <v>8236.122495753016</v>
+        <v>2878.342659334136</v>
       </c>
       <c r="H14">
-        <v>4.675169911008031E-07</v>
+        <v>2.772849756514536E-07</v>
       </c>
       <c r="I14">
-        <v>79750.32731567691</v>
+        <v>28043.25226244895</v>
       </c>
       <c r="J14">
-        <v>78854.26832044432</v>
+        <v>27773.60363479135</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>3.883859988316869E-06</v>
+        <v>4.356275421093592E-06</v>
       </c>
       <c r="B15">
-        <v>9981708551.358763</v>
+        <v>3362889276.838271</v>
       </c>
       <c r="C15">
-        <v>10605155388.82389</v>
+        <v>2.660743898869098E+22</v>
       </c>
       <c r="D15">
-        <v>1.059801980198021</v>
+        <v>3.439134995416449</v>
       </c>
       <c r="E15">
-        <v>65210.07438353699</v>
+        <v>27254.41120603176</v>
       </c>
       <c r="F15">
-        <v>6.733099676824972E-05</v>
+        <v>4.080968440154321E-05</v>
       </c>
       <c r="G15">
-        <v>6889.765878113409</v>
+        <v>2872.853612450638</v>
       </c>
       <c r="H15">
-        <v>4.230578983120739E-07</v>
+        <v>2.452551920520163E-07</v>
       </c>
       <c r="I15">
-        <v>64800.34278380397</v>
+        <v>27090.61954842347</v>
       </c>
       <c r="J15">
-        <v>63654.21821708216</v>
+        <v>26625.48315177709</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
-        <v>3.380392709823458E-06</v>
+        <v>2.116414048816717E-06</v>
       </c>
       <c r="B16">
-        <v>4077288393.160055</v>
+        <v>6900289541.918099</v>
       </c>
       <c r="C16">
-        <v>1.068558335639919E+17</v>
+        <v>571066258786418.1</v>
       </c>
       <c r="D16">
-        <v>2.39667310073531</v>
+        <v>1.910319952334531</v>
       </c>
       <c r="E16">
-        <v>24609.85390520707</v>
+        <v>25413.48360027937</v>
       </c>
       <c r="F16">
-        <v>4.759740459907991E-05</v>
+        <v>0.0003292434954348905</v>
       </c>
       <c r="G16">
-        <v>2575.744360601655</v>
+        <v>2553.642512577018</v>
       </c>
       <c r="H16">
-        <v>2.46614364372369E-07</v>
+        <v>1.769738468293822E-07</v>
       </c>
       <c r="I16">
-        <v>24482.34393845046</v>
+        <v>25399.82343078039</v>
       </c>
       <c r="J16">
-        <v>24102.07148128112</v>
+        <v>25328.47032173885</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17">
-        <v>2.187663380277322E-06</v>
+        <v>6.582573681366157E-06</v>
       </c>
       <c r="B17">
-        <v>13412561915.95068</v>
+        <v>1971801618.289985</v>
       </c>
       <c r="C17">
-        <v>14747945095.09706</v>
+        <v>4.98340355390149E+29</v>
       </c>
       <c r="D17">
-        <v>1.05980198019802</v>
+        <v>4.962384656307083</v>
       </c>
       <c r="E17">
-        <v>49121.33121463029</v>
+        <v>25298.74094172587</v>
       </c>
       <c r="F17">
-        <v>0.0001548048691827366</v>
+        <v>4.36403757988427E-05</v>
       </c>
       <c r="G17">
-        <v>4980.185727345703</v>
+        <v>2671.761684943871</v>
       </c>
       <c r="H17">
-        <v>2.38295992816027E-07</v>
+        <v>2.719515127348823E-07</v>
       </c>
       <c r="I17">
-        <v>49045.71720809397</v>
+        <v>25141.08806309111</v>
       </c>
       <c r="J17">
-        <v>48730.09727939642</v>
+        <v>24698.84967185992</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18">
-        <v>6.798778832670672E-06</v>
+        <v>3.764431405716347E-06</v>
       </c>
       <c r="B18">
-        <v>1290635913.965243</v>
+        <v>5097921178.924644</v>
       </c>
       <c r="C18">
-        <v>2.467113770656142E+46</v>
+        <v>41399211229233.75</v>
       </c>
       <c r="D18">
-        <v>8.227980478625751</v>
+        <v>1.767852813243277</v>
       </c>
       <c r="E18">
-        <v>18083.42707686223</v>
+        <v>33286.91989898885</v>
       </c>
       <c r="F18">
-        <v>0.0001064532887545924</v>
+        <v>8.887942621240977E-05</v>
       </c>
       <c r="G18">
-        <v>1835.048611106737</v>
+        <v>3439.341517289284</v>
       </c>
       <c r="H18">
-        <v>1.746799699337091E-07</v>
+        <v>3.282726379870081E-07</v>
       </c>
       <c r="I18">
-        <v>18053.75385083944</v>
+        <v>33163.97597966618</v>
       </c>
       <c r="J18">
-        <v>17931.77765997374</v>
+        <v>32756.93059985973</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19">
-        <v>5.372272654782217E-06</v>
+        <v>2.796937751436242E-06</v>
       </c>
       <c r="B19">
-        <v>2783406549.309166</v>
+        <v>5562299684.813634</v>
       </c>
       <c r="C19">
-        <v>3.068614666303722E+23</v>
+        <v>37963162696.08054</v>
       </c>
       <c r="D19">
-        <v>3.696556597154334</v>
+        <v>1.202139396245623</v>
       </c>
       <c r="E19">
-        <v>28037.66392785895</v>
+        <v>26278.40723378587</v>
       </c>
       <c r="F19">
-        <v>5.725736043020043E-05</v>
+        <v>8.035797345191538E-05</v>
       </c>
       <c r="G19">
-        <v>2929.599652741756</v>
+        <v>2713.426515268256</v>
       </c>
       <c r="H19">
-        <v>2.855238795111081E-07</v>
+        <v>2.907964504573194E-07</v>
       </c>
       <c r="I19">
-        <v>27897.84919457466</v>
+        <v>26183.31190946401</v>
       </c>
       <c r="J19">
-        <v>27475.71674042101</v>
+        <v>25866.57028331747</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20">
-        <v>5.913678103654003E-06</v>
+        <v>3.770973999911516E-06</v>
       </c>
       <c r="B20">
-        <v>1628042091.099464</v>
+        <v>4574169910.627184</v>
       </c>
       <c r="C20">
-        <v>2.853438937693118E+43</v>
+        <v>1.501438576729499E+23</v>
       </c>
       <c r="D20">
-        <v>7.564847918293384</v>
+        <v>3.52428834238128</v>
       </c>
       <c r="E20">
-        <v>19679.79118004764</v>
+        <v>32060.20189056123</v>
       </c>
       <c r="F20">
-        <v>6.64962516948797E-05</v>
+        <v>9.874731127620697E-05</v>
       </c>
       <c r="G20">
-        <v>2011.870729830216</v>
+        <v>3266.868732194952</v>
       </c>
       <c r="H20">
-        <v>1.647842500256626E-07</v>
+        <v>2.082412210539422E-07</v>
       </c>
       <c r="I20">
-        <v>19631.0227224638</v>
+        <v>31992.59239818475</v>
       </c>
       <c r="J20">
-        <v>19450.45223396456</v>
+        <v>31731.48440738768</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21">
-        <v>2.042350735123807E-06</v>
+        <v>6.60920578761979E-06</v>
       </c>
       <c r="B21">
-        <v>3213056419.658475</v>
+        <v>2181797397.521666</v>
       </c>
       <c r="C21">
-        <v>4.909878149370443E+21</v>
+        <v>1.122351274244988E+30</v>
       </c>
       <c r="D21">
-        <v>3.1744353137788</v>
+        <v>5.0230066802344</v>
       </c>
       <c r="E21">
-        <v>12046.33833474075</v>
+        <v>28033.16222065014</v>
       </c>
       <c r="F21">
-        <v>5.514356032268296E-05</v>
+        <v>0.0001296015676292791</v>
       </c>
       <c r="G21">
-        <v>1228.680614350417</v>
+        <v>2855.896232607561</v>
       </c>
       <c r="H21">
-        <v>1.223078079342613E-07</v>
+        <v>2.70094862753428E-07</v>
       </c>
       <c r="I21">
-        <v>12019.61968932259</v>
+        <v>27974.73998671398</v>
       </c>
       <c r="J21">
-        <v>11917.76559257034</v>
+        <v>27748.43027536091</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22">
-        <v>6.860831974872855E-06</v>
+        <v>3.387491489010209E-06</v>
       </c>
       <c r="B22">
-        <v>1536007227.20179</v>
+        <v>2832192057.4092</v>
       </c>
       <c r="C22">
-        <v>2.923338727843276E+27</v>
+        <v>1.015542799069869E+30</v>
       </c>
       <c r="D22">
-        <v>4.567124539179384</v>
+        <v>4.782052240123287</v>
       </c>
       <c r="E22">
-        <v>20308.15012775854</v>
+        <v>18564.51656464226</v>
       </c>
       <c r="F22">
-        <v>5.507404813698241E-05</v>
+        <v>3.872954017850544E-05</v>
       </c>
       <c r="G22">
-        <v>2132.052880020509</v>
+        <v>1918.85085637295</v>
       </c>
       <c r="H22">
-        <v>3.050542728927135E-07</v>
+        <v>1.446422630779132E-07</v>
       </c>
       <c r="I22">
-        <v>20195.66360859782</v>
+        <v>18495.18412029923</v>
       </c>
       <c r="J22">
-        <v>19867.424107436</v>
+        <v>18266.38728912941</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23">
-        <v>9.373828877828443E-06</v>
+        <v>9.335334379894937E-06</v>
       </c>
       <c r="B23">
-        <v>2396802322.633597</v>
+        <v>1687441998.231116</v>
       </c>
       <c r="C23">
-        <v>8.488704529147648E+30</v>
+        <v>1.030169091421331E+30</v>
       </c>
       <c r="D23">
-        <v>5.309651015377753</v>
+        <v>5.157068467241815</v>
       </c>
       <c r="E23">
-        <v>43956.66353703271</v>
+        <v>30766.26784067976</v>
       </c>
       <c r="F23">
-        <v>0.0002691521554933571</v>
+        <v>0.0001119953886596688</v>
       </c>
       <c r="G23">
-        <v>4449.215951272896</v>
+        <v>3168.736583868411</v>
       </c>
       <c r="H23">
-        <v>3.643232132111173E-07</v>
+        <v>3.725535050065495E-07</v>
       </c>
       <c r="I23">
-        <v>43897.16398417755</v>
+        <v>30663.92361867927</v>
       </c>
       <c r="J23">
-        <v>43641.20133472011</v>
+        <v>30314.60669738726</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24">
-        <v>1.956396392419038E-06</v>
+        <v>7.954902657675255E-06</v>
       </c>
       <c r="B24">
-        <v>12590432370.34372</v>
+        <v>1133161980.194879</v>
       </c>
       <c r="C24">
-        <v>13936773015.07799</v>
+        <v>2.370115968698804E+43</v>
       </c>
       <c r="D24">
-        <v>1.05980198019802</v>
+        <v>7.745207204202815</v>
       </c>
       <c r="E24">
-        <v>41248.28131904893</v>
+        <v>18602.22437671517</v>
       </c>
       <c r="F24">
-        <v>0.0001158656874108605</v>
+        <v>2.307561129473334E-05</v>
       </c>
       <c r="G24">
-        <v>4193.107048281212</v>
+        <v>2017.435460434367</v>
       </c>
       <c r="H24">
-        <v>2.131047330572813E-07</v>
+        <v>2.166877424189814E-07</v>
       </c>
       <c r="I24">
-        <v>41172.41585640858</v>
+        <v>18427.54324031201</v>
       </c>
       <c r="J24">
-        <v>40869.14808132736</v>
+        <v>18005.07703926368</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25">
-        <v>1.745819385360364E-05</v>
+        <v>2.063162641036341E-06</v>
       </c>
       <c r="B25">
-        <v>1241510422.214209</v>
+        <v>4941427570.000004</v>
       </c>
       <c r="C25">
-        <v>2.938349173064098E+37</v>
+        <v>1.037718390765059E+20</v>
       </c>
       <c r="D25">
-        <v>6.981740103201528</v>
+        <v>2.851040376476438</v>
       </c>
       <c r="E25">
-        <v>44068.96593178452</v>
+        <v>18484.78771742411</v>
       </c>
       <c r="F25">
-        <v>8.453089408690223E-05</v>
+        <v>6.28958879949147E-05</v>
       </c>
       <c r="G25">
-        <v>4653.391804766101</v>
+        <v>1883.849505905366</v>
       </c>
       <c r="H25">
-        <v>5.253498108169145E-07</v>
+        <v>1.337239974007933E-07</v>
       </c>
       <c r="I25">
-        <v>43795.0823633538</v>
+        <v>18445.48690168749</v>
       </c>
       <c r="J25">
-        <v>43026.0901291285</v>
+        <v>18294.02471654154</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26">
-        <v>7.923914750343495E-06</v>
+        <v>4.377116822127206E-06</v>
       </c>
       <c r="B26">
-        <v>2586910157.060757</v>
+        <v>3585566737.100033</v>
       </c>
       <c r="C26">
-        <v>3.845065063668568E+28</v>
+        <v>2.121158384707471E+22</v>
       </c>
       <c r="D26">
-        <v>4.784656635641022</v>
+        <v>3.416675506377147</v>
       </c>
       <c r="E26">
-        <v>39645.00666950154</v>
+        <v>29079.50445600225</v>
       </c>
       <c r="F26">
-        <v>0.0001066594480667857</v>
+        <v>9.019310838658093E-05</v>
       </c>
       <c r="G26">
-        <v>4077.630949471608</v>
+        <v>2979.825644928421</v>
       </c>
       <c r="H26">
-        <v>3.381794387253067E-07</v>
+        <v>2.476982314744671E-07</v>
       </c>
       <c r="I26">
-        <v>39519.30635558881</v>
+        <v>28999.64312341537</v>
       </c>
       <c r="J26">
-        <v>39084.3595155642</v>
+        <v>28712.03443828029</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27">
-        <v>2.48705745654972E-06</v>
+        <v>2.62779629215376E-06</v>
       </c>
       <c r="B27">
-        <v>6139654276.614969</v>
+        <v>5545079951.877789</v>
       </c>
       <c r="C27">
-        <v>11898102509.14609</v>
+        <v>2973909202064371</v>
       </c>
       <c r="D27">
-        <v>1.103820578331863</v>
+        <v>2.069580394597897</v>
       </c>
       <c r="E27">
-        <v>25640.27679347952</v>
+        <v>25698.4941231137</v>
       </c>
       <c r="F27">
-        <v>0.000109552122749567</v>
+        <v>3.065263153505067E-05</v>
       </c>
       <c r="G27">
-        <v>2620.270440335908</v>
+        <v>2728.221222665202</v>
       </c>
       <c r="H27">
-        <v>2.670067316856072E-07</v>
+        <v>2.098917947426291E-07</v>
       </c>
       <c r="I27">
-        <v>25577.78483682623</v>
+        <v>25522.52544494277</v>
       </c>
       <c r="J27">
-        <v>25345.37748922331</v>
+        <v>25044.70716918674</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28">
-        <v>7.476791290724473E-06</v>
+        <v>8.603111182347602E-06</v>
       </c>
       <c r="B28">
-        <v>1341227148.27086</v>
+        <v>3059652830.288584</v>
       </c>
       <c r="C28">
-        <v>1.024561972444765E+60</v>
+        <v>2.171748794353697E+36</v>
       </c>
       <c r="D28">
-        <v>10.93477490455503</v>
+        <v>6.320388207447473</v>
       </c>
       <c r="E28">
-        <v>21224.99758401718</v>
+        <v>52703.05025883801</v>
       </c>
       <c r="F28">
-        <v>6.504737895401539E-05</v>
+        <v>0.0001060234048456436</v>
       </c>
       <c r="G28">
-        <v>2165.243408583586</v>
+        <v>5397.58497008767</v>
       </c>
       <c r="H28">
-        <v>1.455496781959858E-07</v>
+        <v>2.845007807745887E-07</v>
       </c>
       <c r="I28">
-        <v>21177.50463937065</v>
+        <v>52561.62809861149</v>
       </c>
       <c r="J28">
-        <v>20996.8702467118</v>
+        <v>52049.08975130901</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29">
-        <v>9.513314402650834E-06</v>
+        <v>4.937217182874797E-06</v>
       </c>
       <c r="B29">
-        <v>1951363780.727175</v>
+        <v>11606963399.04157</v>
       </c>
       <c r="C29">
-        <v>6.579887522920801E+36</v>
+        <v>12156212507.06837</v>
       </c>
       <c r="D29">
-        <v>6.500765991659309</v>
+        <v>1.05980198019802</v>
       </c>
       <c r="E29">
-        <v>37354.14528720242</v>
+        <v>95948.50053304604</v>
       </c>
       <c r="F29">
-        <v>7.200735591045848E-05</v>
+        <v>0.0003208794401990491</v>
       </c>
       <c r="G29">
-        <v>3878.44700468872</v>
+        <v>9739.579627421468</v>
       </c>
       <c r="H29">
-        <v>3.063586926528365E-07</v>
+        <v>5.377971222393251E-07</v>
       </c>
       <c r="I29">
-        <v>37195.22031390412</v>
+        <v>95787.68989513844</v>
       </c>
       <c r="J29">
-        <v>36690.94069731067</v>
+        <v>95130.03486420243</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30">
-        <v>8.038883297885796E-06</v>
+        <v>1.933807761027709E-06</v>
       </c>
       <c r="B30">
-        <v>1535239539.765562</v>
+        <v>7459188870.450013</v>
       </c>
       <c r="C30">
-        <v>7.417601075565434E+41</v>
+        <v>299717886163665.8</v>
       </c>
       <c r="D30">
-        <v>7.430912236892116</v>
+        <v>1.849728434385399</v>
       </c>
       <c r="E30">
-        <v>25148.35374043235</v>
+        <v>25037.89242607955</v>
       </c>
       <c r="F30">
-        <v>0.0001708459369768284</v>
+        <v>0.000230298334570334</v>
       </c>
       <c r="G30">
-        <v>2545.025242175164</v>
+        <v>2519.894744750986</v>
       </c>
       <c r="H30">
-        <v>2.278839827159067E-07</v>
+        <v>1.645980889836116E-07</v>
       </c>
       <c r="I30">
-        <v>25114.80944250798</v>
+        <v>25019.99742369841</v>
       </c>
       <c r="J30">
-        <v>24970.01392487806</v>
+        <v>24931.61922497332</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31">
-        <v>3.039428217829988E-06</v>
+        <v>1.189292210124813E-05</v>
       </c>
       <c r="B31">
-        <v>8995554400.335499</v>
+        <v>1450989716.079865</v>
       </c>
       <c r="C31">
-        <v>9698561017.046843</v>
+        <v>6.423461147358951E+44</v>
       </c>
       <c r="D31">
-        <v>1.05980198019802</v>
+        <v>8.252306863280616</v>
       </c>
       <c r="E31">
-        <v>45785.50338988728</v>
+        <v>35675.47349030875</v>
       </c>
       <c r="F31">
-        <v>0.0001800503444706987</v>
+        <v>6.798129453059101E-05</v>
       </c>
       <c r="G31">
-        <v>4654.321628711877</v>
+        <v>3711.454101736612</v>
       </c>
       <c r="H31">
-        <v>3.31076330705426E-07</v>
+        <v>3.046901035458875E-07</v>
       </c>
       <c r="I31">
-        <v>45701.31306797265</v>
+        <v>35515.57709841349</v>
       </c>
       <c r="J31">
-        <v>45364.74717789261</v>
+        <v>35016.29883904393</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32">
-        <v>1.77079113421659E-06</v>
+        <v>3.841196458227124E-06</v>
       </c>
       <c r="B32">
-        <v>10398139448.07952</v>
+        <v>5911877311.162629</v>
       </c>
       <c r="C32">
-        <v>11578865744.82121</v>
+        <v>34850950501929.22</v>
       </c>
       <c r="D32">
-        <v>1.05980198019802</v>
+        <v>1.743656238718176</v>
       </c>
       <c r="E32">
-        <v>30811.81879554968</v>
+        <v>39284.42309464565</v>
       </c>
       <c r="F32">
-        <v>0.0001726378607155522</v>
+        <v>0.000157303420201025</v>
       </c>
       <c r="G32">
-        <v>3112.165158710239</v>
+        <v>4004.275968247023</v>
       </c>
       <c r="H32">
-        <v>1.928872765354189E-07</v>
+        <v>3.373939465946873E-07</v>
       </c>
       <c r="I32">
-        <v>30777.3929298216</v>
+        <v>39200.16347377624</v>
       </c>
       <c r="J32">
-        <v>30622.71959781262</v>
+        <v>38876.16531074073</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33">
-        <v>3.185368730524395E-06</v>
+        <v>2.215589977403273E-06</v>
       </c>
       <c r="B33">
-        <v>7218493827.32128</v>
+        <v>7973368589.847602</v>
       </c>
       <c r="C33">
-        <v>7760825553.404645</v>
+        <v>8760566093.048971</v>
       </c>
       <c r="D33">
         <v>1.05980198019802</v>
       </c>
       <c r="E33">
-        <v>38708.37603093049</v>
+        <v>29587.23502906059</v>
       </c>
       <c r="F33">
-        <v>4.894342418032951E-05</v>
+        <v>0.0001213890561269216</v>
       </c>
       <c r="G33">
-        <v>4117.810368823505</v>
+        <v>3011.664606541096</v>
       </c>
       <c r="H33">
-        <v>3.469732185347524E-07</v>
+        <v>2.41337958160466E-07</v>
       </c>
       <c r="I33">
-        <v>38433.96184678553</v>
+        <v>29528.41158057722</v>
       </c>
       <c r="J33">
-        <v>37697.86799488736</v>
+        <v>29297.80485636051</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34">
-        <v>1.013452597086768E-05</v>
+        <v>2.773152660028354E-06</v>
       </c>
       <c r="B34">
-        <v>4439607923.776803</v>
+        <v>10088928882.09521</v>
       </c>
       <c r="C34">
-        <v>7.762512957865836E+20</v>
+        <v>163195683482.0734</v>
       </c>
       <c r="D34">
-        <v>3.287893719853837</v>
+        <v>1.268712865477397</v>
       </c>
       <c r="E34">
-        <v>83195.94749366507</v>
+        <v>47329.46153320177</v>
       </c>
       <c r="F34">
-        <v>0.0001114129336845818</v>
+        <v>0.0001455182906797287</v>
       </c>
       <c r="G34">
-        <v>8716.695522348889</v>
+        <v>4815.552800619159</v>
       </c>
       <c r="H34">
-        <v>5.908696199114885E-07</v>
+        <v>2.82200973636651E-07</v>
       </c>
       <c r="I34">
-        <v>82754.72441257353</v>
+        <v>47237.67636953623</v>
       </c>
       <c r="J34">
-        <v>81448.77389546891</v>
+        <v>46875.5875145361</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35">
-        <v>5.211010676332686E-06</v>
+        <v>7.13261798703901E-06</v>
       </c>
       <c r="B35">
-        <v>2055015756.145427</v>
+        <v>3669797551.12166</v>
       </c>
       <c r="C35">
-        <v>6.184104596336484E+25</v>
+        <v>1.672276789479397E+19</v>
       </c>
       <c r="D35">
-        <v>4.147997343633836</v>
+        <v>2.915317549128999</v>
       </c>
       <c r="E35">
-        <v>20336.44286101302</v>
+        <v>47595.08679399544</v>
       </c>
       <c r="F35">
-        <v>7.796722503674092E-05</v>
+        <v>0.0001827517653605766</v>
       </c>
       <c r="G35">
-        <v>2092.735446992468</v>
+        <v>4866.143098202006</v>
       </c>
       <c r="H35">
-        <v>2.517196383944855E-07</v>
+        <v>4.549402422494413E-07</v>
       </c>
       <c r="I35">
-        <v>20270.78601557839</v>
+        <v>47476.60410643713</v>
       </c>
       <c r="J35">
-        <v>20044.76485030172</v>
+        <v>47038.4409318075</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36">
-        <v>7.503077368107439E-06</v>
+        <v>2.571942430314737E-06</v>
       </c>
       <c r="B36">
-        <v>1295287796.310878</v>
+        <v>6891428005.395751</v>
       </c>
       <c r="C36">
-        <v>2.230479857906178E+63</v>
+        <v>7556936478852816</v>
       </c>
       <c r="D36">
-        <v>11.59120916909253</v>
+        <v>2.122870626214565</v>
       </c>
       <c r="E36">
-        <v>20630.13048895242</v>
+        <v>31290.29772158941</v>
       </c>
       <c r="F36">
-        <v>0.0001960182932564723</v>
+        <v>3.665128552543642E-05</v>
       </c>
       <c r="G36">
-        <v>2076.079425690833</v>
+        <v>3284.51083096375</v>
       </c>
       <c r="H36">
-        <v>1.379454235040294E-07</v>
+        <v>2.023552593684804E-07</v>
       </c>
       <c r="I36">
-        <v>20615.61229251287</v>
+        <v>31117.54098958406</v>
       </c>
       <c r="J36">
-        <v>20543.68665804758</v>
+        <v>30612.89369743222</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37">
-        <v>2.867577865527873E-06</v>
+        <v>6.294971463220252E-06</v>
       </c>
       <c r="B37">
-        <v>4260382958.369288</v>
+        <v>3855022824.781809</v>
       </c>
       <c r="C37">
-        <v>1.751297723981989E+22</v>
+        <v>6.153991712363734E+23</v>
       </c>
       <c r="D37">
-        <v>3.308822787418684</v>
+        <v>3.762701294510052</v>
       </c>
       <c r="E37">
-        <v>22503.14507827817</v>
+        <v>45554.88669346945</v>
       </c>
       <c r="F37">
-        <v>0.0002361510538504044</v>
+        <v>8.341734044413636E-05</v>
       </c>
       <c r="G37">
-        <v>2264.582929416343</v>
+        <v>4717.570486151032</v>
       </c>
       <c r="H37">
-        <v>1.663719440693085E-07</v>
+        <v>3.29771526991586E-07</v>
       </c>
       <c r="I37">
-        <v>22487.29127651314</v>
+        <v>45374.79578590935</v>
       </c>
       <c r="J37">
-        <v>22408.76623580908</v>
+        <v>44790.48597737757</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38">
-        <v>4.719227239896547E-06</v>
+        <v>3.144589288996248E-06</v>
       </c>
       <c r="B38">
-        <v>2666205485.684206</v>
+        <v>4382774969.378913</v>
       </c>
       <c r="C38">
-        <v>1.525795156262905E+25</v>
+        <v>1.430147701346279E+18</v>
       </c>
       <c r="D38">
-        <v>3.98819595013225</v>
+        <v>2.586103012667902</v>
       </c>
       <c r="E38">
-        <v>23741.19620627987</v>
+        <v>24765.71228705485</v>
       </c>
       <c r="F38">
-        <v>0.0001330587990173612</v>
+        <v>5.844674110613336E-05</v>
       </c>
       <c r="G38">
-        <v>2411.956801271381</v>
+        <v>2559.761899542495</v>
       </c>
       <c r="H38">
-        <v>2.356227719983843E-07</v>
+        <v>2.181431571601503E-07</v>
       </c>
       <c r="I38">
-        <v>23699.15489445387</v>
+        <v>24673.27820834707</v>
       </c>
       <c r="J38">
-        <v>23529.51691080923</v>
+        <v>24368.19037048593</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39">
-        <v>8.673376717372689E-06</v>
+        <v>4.278896888645577E-06</v>
       </c>
       <c r="B39">
-        <v>3830505087.896635</v>
+        <v>3477599172.218296</v>
       </c>
       <c r="C39">
-        <v>9.935607268201795E+25</v>
+        <v>1.649565947950016E+23</v>
       </c>
       <c r="D39">
-        <v>4.272078909024446</v>
+        <v>3.579490811950767</v>
       </c>
       <c r="E39">
-        <v>63215.79877059019</v>
+        <v>27714.86818442688</v>
       </c>
       <c r="F39">
-        <v>0.0002890584955818636</v>
+        <v>0.0001024069406163122</v>
       </c>
       <c r="G39">
-        <v>6402.000255609593</v>
+        <v>2828.331866062244</v>
       </c>
       <c r="H39">
-        <v>4.085862164915996E-07</v>
+        <v>2.333816466377697E-07</v>
       </c>
       <c r="I39">
-        <v>63126.44279442289</v>
+        <v>27651.70702040516</v>
       </c>
       <c r="J39">
-        <v>62745.88864821415</v>
+        <v>27412.62347023459</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40">
-        <v>2.851038198241045E-06</v>
+        <v>4.237878438147073E-06</v>
       </c>
       <c r="B40">
-        <v>2397315255.065523</v>
+        <v>3235742001.967429</v>
       </c>
       <c r="C40">
-        <v>1.999614077162603E+38</v>
+        <v>4.730095450740523E+28</v>
       </c>
       <c r="D40">
-        <v>6.233786414990225</v>
+        <v>4.592868780167711</v>
       </c>
       <c r="E40">
-        <v>13685.99044274406</v>
+        <v>26353.39566161862</v>
       </c>
       <c r="F40">
-        <v>2.146509226402189E-05</v>
+        <v>8.936906889988169E-05</v>
       </c>
       <c r="G40">
-        <v>1423.408022394583</v>
+        <v>2685.102301482012</v>
       </c>
       <c r="H40">
-        <v>9.551371180691069E-08</v>
+        <v>1.875047981830567E-07</v>
       </c>
       <c r="I40">
-        <v>13625.09157816609</v>
+        <v>26298.10373348512</v>
       </c>
       <c r="J40">
-        <v>13434.50686207297</v>
+        <v>26084.2871358109</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41">
-        <v>2.084264077735422E-06</v>
+        <v>2.566269698954758E-06</v>
       </c>
       <c r="B41">
-        <v>10613768920.33337</v>
+        <v>6308502648.160143</v>
       </c>
       <c r="C41">
-        <v>11704339260.03662</v>
+        <v>1.746004470032921E+17</v>
       </c>
       <c r="D41">
-        <v>1.05980198019802</v>
+        <v>2.371237807166404</v>
       </c>
       <c r="E41">
-        <v>37319.52684811447</v>
+        <v>28780.03149924931</v>
       </c>
       <c r="F41">
-        <v>2.473329858582907E-05</v>
+        <v>0.0001009215426212195</v>
       </c>
       <c r="G41">
-        <v>4040.261245429394</v>
+        <v>2926.385951873273</v>
       </c>
       <c r="H41">
-        <v>2.270329988481966E-07</v>
+        <v>1.885129204211928E-07</v>
       </c>
       <c r="I41">
-        <v>36976.96178076119</v>
+        <v>28726.27283041782</v>
       </c>
       <c r="J41">
-        <v>36141.23548579655</v>
+        <v>28512.19979945095</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42">
-        <v>4.19357913976215E-06</v>
+        <v>7.38677559920946E-06</v>
       </c>
       <c r="B42">
-        <v>4838652561.482054</v>
+        <v>2591740779.220472</v>
       </c>
       <c r="C42">
-        <v>2.354042923913397E+17</v>
+        <v>7.725584985534356E+34</v>
       </c>
       <c r="D42">
-        <v>2.470289754168974</v>
+        <v>5.984733878896616</v>
       </c>
       <c r="E42">
-        <v>36315.16418601249</v>
+        <v>38092.41652869932</v>
       </c>
       <c r="F42">
-        <v>6.758221082113951E-05</v>
+        <v>8.225017820187466E-05</v>
       </c>
       <c r="G42">
-        <v>3776.578882696539</v>
+        <v>3916.403210618405</v>
       </c>
       <c r="H42">
-        <v>2.999555649506474E-07</v>
+        <v>2.570957110339431E-07</v>
       </c>
       <c r="I42">
-        <v>36153.98367035107</v>
+        <v>37973.34813120102</v>
       </c>
       <c r="J42">
-        <v>35649.16901155847</v>
+        <v>37559.68428934132</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43">
-        <v>9.627151211577479E-06</v>
+        <v>1.616933832648377E-06</v>
       </c>
       <c r="B43">
-        <v>1763253116.473062</v>
+        <v>6109484386.67274</v>
       </c>
       <c r="C43">
-        <v>5.836665323592887E+37</v>
+        <v>348491030702.8367</v>
       </c>
       <c r="D43">
-        <v>6.703462252424722</v>
+        <v>1.351490568780379</v>
       </c>
       <c r="E43">
-        <v>34258.90261565877</v>
+        <v>16824.98602276188</v>
       </c>
       <c r="F43">
-        <v>8.428691321177897E-05</v>
+        <v>3.354322363290609E-05</v>
       </c>
       <c r="G43">
-        <v>3536.048770489725</v>
+        <v>1754.842790568335</v>
       </c>
       <c r="H43">
-        <v>3.011356974976471E-07</v>
+        <v>1.602548656003238E-07</v>
       </c>
       <c r="I43">
-        <v>34136.50427241005</v>
+        <v>16744.60359132617</v>
       </c>
       <c r="J43">
-        <v>33727.29139834226</v>
+        <v>16498.58253832807</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44">
-        <v>9.276735316622645E-06</v>
+        <v>3.560972831230261E-06</v>
       </c>
       <c r="B44">
-        <v>1595130987.399682</v>
+        <v>6129907791.191779</v>
       </c>
       <c r="C44">
-        <v>3.644921745735154E+28</v>
+        <v>3.411496133041848E+16</v>
       </c>
       <c r="D44">
-        <v>4.872771431066306</v>
+        <v>2.280010439307729</v>
       </c>
       <c r="E44">
-        <v>28746.40827079779</v>
+        <v>38610.03455070234</v>
       </c>
       <c r="F44">
-        <v>7.425468939446545E-05</v>
+        <v>0.0003832876715212879</v>
       </c>
       <c r="G44">
-        <v>3010.366390376406</v>
+        <v>3885.316570637353</v>
       </c>
       <c r="H44">
-        <v>3.895466193952311E-07</v>
+        <v>2.681777637915293E-07</v>
       </c>
       <c r="I44">
-        <v>28595.60208935709</v>
+        <v>38583.01997784999</v>
       </c>
       <c r="J44">
-        <v>28147.66017421712</v>
+        <v>38449.02901769679</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45">
-        <v>3.574749216675071E-06</v>
+        <v>2.507456682340977E-06</v>
       </c>
       <c r="B45">
-        <v>9266882263.804161</v>
+        <v>7471276580.411211</v>
       </c>
       <c r="C45">
-        <v>9894634204.928934</v>
+        <v>8148377539.041365</v>
       </c>
       <c r="D45">
         <v>1.05980198019802</v>
       </c>
       <c r="E45">
-        <v>55585.56290461633</v>
+        <v>31428.90878433212</v>
       </c>
       <c r="F45">
-        <v>0.0001012197989861364</v>
+        <v>7.46368194983222E-05</v>
       </c>
       <c r="G45">
-        <v>5751.007599214123</v>
+        <v>3246.402322817293</v>
       </c>
       <c r="H45">
-        <v>3.893873350606232E-07</v>
+        <v>2.731301739328285E-07</v>
       </c>
       <c r="I45">
-        <v>55371.72811711358</v>
+        <v>31313.8960683498</v>
       </c>
       <c r="J45">
-        <v>54672.25521095924</v>
+        <v>30932.0705262067</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46">
-        <v>3.521914597535473E-06</v>
+        <v>6.725766004650741E-06</v>
       </c>
       <c r="B46">
-        <v>4518774950.802546</v>
+        <v>1514484213.903819</v>
       </c>
       <c r="C46">
-        <v>10175968846521.33</v>
+        <v>1.285066478953795E+49</v>
       </c>
       <c r="D46">
-        <v>1.662707620773915</v>
+        <v>8.732151610798152</v>
       </c>
       <c r="E46">
-        <v>27443.62655201216</v>
+        <v>21146.36273008272</v>
       </c>
       <c r="F46">
-        <v>0.0001193610545257885</v>
+        <v>5.564121050625004E-05</v>
       </c>
       <c r="G46">
-        <v>2809.953776433768</v>
+        <v>2170.426963904576</v>
       </c>
       <c r="H46">
-        <v>3.169740373864752E-07</v>
+        <v>1.631098252411297E-07</v>
       </c>
       <c r="I46">
-        <v>27370.74752842044</v>
+        <v>21084.37307353127</v>
       </c>
       <c r="J46">
-        <v>27105.87433801279</v>
+        <v>20865.10193846012</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47">
-        <v>5.817031862700905E-06</v>
+        <v>5.414407489414845E-06</v>
       </c>
       <c r="B47">
-        <v>2722154845.010031</v>
+        <v>3556850219.468632</v>
       </c>
       <c r="C47">
-        <v>5.283849892737631E+30</v>
+        <v>1.872619137235786E+17</v>
       </c>
       <c r="D47">
-        <v>5.090228182565505</v>
+        <v>2.50744502537311</v>
       </c>
       <c r="E47">
-        <v>30918.26415206577</v>
+        <v>34513.34159988273</v>
       </c>
       <c r="F47">
-        <v>4.969257632735637E-05</v>
+        <v>8.989330365220963E-05</v>
       </c>
       <c r="G47">
-        <v>3223.361131487504</v>
+        <v>3583.839464595522</v>
       </c>
       <c r="H47">
-        <v>2.348952816130335E-07</v>
+        <v>3.834697292387395E-07</v>
       </c>
       <c r="I47">
-        <v>30772.11446730919</v>
+        <v>34366.11348365244</v>
       </c>
       <c r="J47">
-        <v>30323.29851073797</v>
+        <v>33899.32993483675</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48">
-        <v>6.097418622329566E-06</v>
+        <v>3.761953253345543E-06</v>
       </c>
       <c r="B48">
-        <v>3597067545.875651</v>
+        <v>5283863988.919968</v>
       </c>
       <c r="C48">
-        <v>1.206846603780981E+25</v>
+        <v>2129162159483.334</v>
       </c>
       <c r="D48">
-        <v>4.00736632225754</v>
+        <v>1.529843224553018</v>
       </c>
       <c r="E48">
-        <v>41456.52180279859</v>
+        <v>34098.12938579977</v>
       </c>
       <c r="F48">
-        <v>0.000104127473861159</v>
+        <v>9.905728900836677E-05</v>
       </c>
       <c r="G48">
-        <v>4254.300197618683</v>
+        <v>3519.053516620475</v>
       </c>
       <c r="H48">
-        <v>3.032157572303558E-07</v>
+        <v>3.52612223906438E-07</v>
       </c>
       <c r="I48">
-        <v>41335.80178353324</v>
+        <v>33976.75096575477</v>
       </c>
       <c r="J48">
-        <v>40907.99990787836</v>
+        <v>33570.51341531456</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49">
-        <v>4.166123776299457E-06</v>
+        <v>8.040992999816291E-06</v>
       </c>
       <c r="B49">
-        <v>4448181414.034302</v>
+        <v>2078149299.920317</v>
       </c>
       <c r="C49">
-        <v>906628504142842.2</v>
+        <v>6.913367113146361E+24</v>
       </c>
       <c r="D49">
-        <v>2.031640950392333</v>
+        <v>4.077120254503626</v>
       </c>
       <c r="E49">
-        <v>32588.19105705373</v>
+        <v>31725.3420118337</v>
       </c>
       <c r="F49">
-        <v>5.991282250609077E-05</v>
+        <v>7.667261319154969E-05</v>
       </c>
       <c r="G49">
-        <v>3423.489648804954</v>
+        <v>3319.303232387132</v>
       </c>
       <c r="H49">
-        <v>3.363821440524629E-07</v>
+        <v>3.941176374880717E-07</v>
       </c>
       <c r="I49">
-        <v>32405.22378694309</v>
+        <v>31562.26531049619</v>
       </c>
       <c r="J49">
-        <v>31873.70020113766</v>
+        <v>31074.67296618555</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50">
-        <v>3.062985948373662E-06</v>
+        <v>9.576099881953184E-06</v>
       </c>
       <c r="B50">
-        <v>6454124360.954324</v>
+        <v>1754292890.275734</v>
       </c>
       <c r="C50">
-        <v>1154221433867010</v>
+        <v>1.450450934063703E+36</v>
       </c>
       <c r="D50">
-        <v>1.996680148397073</v>
+        <v>6.382688685862719</v>
       </c>
       <c r="E50">
-        <v>34590.27376206456</v>
+        <v>33708.87868096661</v>
       </c>
       <c r="F50">
-        <v>0.0001153746627226242</v>
+        <v>8.553919774267817E-05</v>
       </c>
       <c r="G50">
-        <v>3526.431238729392</v>
+        <v>3482.169839706383</v>
       </c>
       <c r="H50">
-        <v>2.498036155827859E-07</v>
+        <v>3.137640403886282E-07</v>
       </c>
       <c r="I50">
-        <v>34515.38058148351</v>
+        <v>33585.23204584469</v>
       </c>
       <c r="J50">
-        <v>34228.09574510952</v>
+        <v>33175.02442001812</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51">
-        <v>4.155953557410702E-06</v>
+        <v>2.15048395347494E-06</v>
       </c>
       <c r="B51">
-        <v>3998931213.415319</v>
+        <v>7267411313.974556</v>
       </c>
       <c r="C51">
-        <v>2.343562962296764E+24</v>
+        <v>7999165758.430323</v>
       </c>
       <c r="D51">
-        <v>3.775000928174281</v>
+        <v>1.059801980198021</v>
       </c>
       <c r="E51">
-        <v>31124.19769468504</v>
+        <v>26168.02410531105</v>
       </c>
       <c r="F51">
-        <v>0.0001840030266726534</v>
+        <v>0.0001364628486863349</v>
       </c>
       <c r="G51">
-        <v>3145.475595876032</v>
+        <v>2657.229405094018</v>
       </c>
       <c r="H51">
-        <v>2.171362390630465E-07</v>
+        <v>2.342461428701539E-07</v>
       </c>
       <c r="I51">
-        <v>31087.46899867668</v>
+        <v>26123.10522246337</v>
       </c>
       <c r="J51">
-        <v>30924.44923350254</v>
+        <v>25940.46939531886</v>
       </c>
     </row>
   </sheetData>
